--- a/docassemble/PowerOfAttorneyProperty/data/sources/poa_property_es.xlsx
+++ b/docassemble/PowerOfAttorneyProperty/data/sources/poa_property_es.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mnewsted\local-DA-easyforms-dev\sources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3FE542E-0FFD-455C-B4ED-1265ABD026B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1B12DC0-F368-4826-A16B-EA88C483B0D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-35805" yWindow="-3510" windowWidth="31260" windowHeight="18555" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -8551,11 +8551,6 @@
 </t>
   </si>
   <si>
-    <t>“Incompetente” significa no poder manejar sus propios asuntos debido a una enfermedad, discapacidad o edad.
-Una persona puede ser declarada incompetente o legalmente discapacitada por un tribunal.
-Una persona puede ser certificada por un médico como incapaz de tomar decisiones o manejar asuntos comerciales.</t>
-  </si>
-  <si>
     <t>72a27500d356a32cf3a67fb5e3b5d7e7</t>
   </si>
   <si>
@@ -8888,151 +8883,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% if for_yourself == True:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">La persona nombrada como un **{successor agent}** tendrá poder notarial para la propiedad por usted si </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${agent.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> muere, se vuelve **{incompetent}**, renuncia o se niega a actuar como su apoderado.
-If you list more than one successor agent, you should list them in order of preference
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% else:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">La persona nombrada como un sucesor agente tendrá poder notarial para la propiedad de </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${principal.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> si </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${agent.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> muere, se vuelve **{incompetent}**, renuncia o se niega a aceptar el cargo de agente.
-If </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${principal.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> lists more than one successor agent, they should list them in order of preference.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>% endif</t>
-    </r>
-  </si>
-  <si>
     <t>any other successors</t>
   </si>
   <si>
@@ -10082,129 +9932,11 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% if user_path == "Shirley":
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[YOUTUBE TB5zr804MT4]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% elif user_path == "Federico" or user_path == "Frederico":
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[YOUTUBE 91-jZQBqIFs]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% elif user_path == "Lisa":
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[YOUTUBE dYfra7eRTx0]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>% endif</t>
-    </r>
-  </si>
-  <si>
     <t>cf8cf4353bde42d565dc4827a0bdd44c</t>
   </si>
   <si>
     <t xml:space="preserve">**Video: When does a POA for Property go into effect?**
 </t>
-  </si>
-  <si>
-    <t>Video: ¿Cuándo entra en vigor un poder notarial para la propiedad?</t>
   </si>
   <si>
     <t>effective date option</t>
@@ -10895,263 +10627,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${collapse_template(video_when_effect)}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% if for_yourself == True:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Este Poder Notarial entrará en vigor cuando usted firme el formulario a menos que indique que debe entrar en vigencia en un momento posterior.
-Aún tendrá la autoridad para tomar decisiones. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${agent.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> podrá tomar decisiones por usted cuando no pueda hacerlo.
-Aún puede cambiar de opinión y **{revoke}** el Poder Notarial después de firmarlo, siempre que tenga la **{legal capacity}** requerida.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% else:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Este Poder Notarial entrará en vigor cuando </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${principal.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> firme el formulario a menos que indique que debe entrar en vigencia en un momento posterior.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${principal.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> seguirá teniendo la autoridad para tomar decisiones. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${agent.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> podrá tomar decisiones por ellos cuando no puedan hacerlo.
-Este Poder Notarial entrará en vigor cuando </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${principal.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> firme el formulario a menos que indique que debe entrar en vigencia en un momento posterior.
-Ellos seguirán teniendo la autoridad para tomar decisiones. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${agent.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> podrá tomar decisiones por ellos cuando no puedan hacerlo.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${principal.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> aún puede cambiar de opinión y **{revoke}** el Poder Notarial después de firmarlo, siempre que tenga la **{legal capacity}** requerida.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% endif
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${collapse_template(prove_capacity)}</t>
-    </r>
-  </si>
-  <si>
     <t>fc758e86b06fc64902c58e0436d9fe73</t>
   </si>
   <si>
@@ -12159,9 +11634,6 @@
 </t>
   </si>
   <si>
-    <t>Demostrando la capacidad legal</t>
-  </si>
-  <si>
     <t>Question_439</t>
   </si>
   <si>
@@ -12284,106 +11756,168 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% if user_path == "Shirley":
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[YOUTUBE 1F6ogUQHaTA]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% elif user_path == "Federico" or user_path == "Frederico":
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[YOUTUBE dq2xc4tMg_g]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% elif user_path == "Lisa":
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[YOUTUBE 8SLjaI_mfuE]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
+    <t>9b57945bd3a50aa1e6326a3dd89b05cb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">**Video: When does my Power of Attorney end?**
+</t>
+  </si>
+  <si>
+    <t>**Video: ¿Cuándo termina mi poder notarial?**</t>
+  </si>
+  <si>
+    <t>revocation option</t>
+  </si>
+  <si>
+    <t>60eaec322f9c1133ada229cc9e6fa51a</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% if for_yourself == True:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Do you want this Power of Attorney to last until your death?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% else:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Does </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${principal.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> want this Power of Attorney to last until their death?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% endif
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% if for_yourself == True:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">¿Quieres que este poder notarial dure hasta tu muerte?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% else:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">¿Quiere </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${principal.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> que este poder notarial dure hasta su muerte?
 </t>
     </r>
     <r>
@@ -12399,557 +11933,7 @@
     </r>
   </si>
   <si>
-    <t>9b57945bd3a50aa1e6326a3dd89b05cb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">**Video: When does my Power of Attorney end?**
-</t>
-  </si>
-  <si>
-    <t>**Video: ¿Cuándo termina mi poder notarial?**</t>
-  </si>
-  <si>
-    <t>revocation option</t>
-  </si>
-  <si>
-    <t>60eaec322f9c1133ada229cc9e6fa51a</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% if for_yourself == True:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Do you want this Power of Attorney to last until your death?
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% else:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Does </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${principal.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> want this Power of Attorney to last until their death?
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% endif
-</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% if for_yourself == True:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">¿Quieres que este poder notarial dure hasta tu muerte?
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% else:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">¿Quiere </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${principal.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> que este poder notarial dure hasta su muerte?
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>% endif</t>
-    </r>
-  </si>
-  <si>
     <t>2fb7ec9ffa1932d3e1afb129dc308501</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${collapse_template(video_when_end)}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% if for_yourself == True:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">This Power of Attorney for Property will last until your death. However, you may choose to end it earlier. If you only want the Power of Attorney to last for a specific time, click **No**.
-You can end a Power of Attorney by making a formal Revocation. To make a Power of Attorney Revocation, use ILAO's </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[**Power of Attorney Revocation Easy Form**]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>https://www.illinoislegalaid.org/legal-information/power-attorney-revocation</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">).
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% else:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">This Power of Attorney for Property will last until </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${principal.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">'s death. However, they may choose to end it earlier. If they only want the Power of Attorney to last for a specific time, click **No**.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${principal.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> can end a Power of Attorney by making a formal Revocation. To make a Power of Attorney Revocation, use ILAO's </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[**Power of Attorney Revocation Easy Form**]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>https://www.illinoislegalaid.org/legal-information/power-attorney-revocation</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">).
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% endif
-</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${collapse_template(video_when_end)}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% if for_yourself == True:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Este poder notarial para bienes durará hasta su muerte. Sin embargo, puede elegir terminarlo antes. Si solo desea que el poder notarial dure por un tiempo específico, haga clic en **No**.
-Puede terminar un poder notarial realizando una Revocación formal. Para realizar una Revocación de Poder Notarial, use el </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[**Formulario Fácil de Revocación de Poder Notarial**]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> de ILAO.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% else:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Este poder notarial para bienes durará hasta la muerte de </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${principal.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">. Sin embargo, la persona puede elegir terminarlo antes. Si la persona solo quiere que el poder notarial dure por un tiempo específico, haga clic en **No**.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${principal.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> puede terminar un poder notarial realizando una Revocación formal. Para realizar una Revocación de Poder Notarial, use el </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[**Formulario Fácil de Revocación de Poder Notarial**]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> de ILAO.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>% endif</t>
-    </r>
   </si>
   <si>
     <t>Question_441</t>
@@ -25002,9 +23986,6 @@
   </si>
   <si>
     <t>Transacciones con instituciones financieras</t>
-  </si>
-  <si>
-    <t>Algunos ejemplos de transacciones con instituciones financieras son depositar o retirar dinero de una cuenta o emitir cheques.</t>
   </si>
   <si>
     <t>Algunos ejemplos de **transacciones de acciones y bonos** son comprar acciones y conservar los  intereses o las participaciones de esas acciones.</t>
@@ -26417,40 +25398,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>No. Puede listar a alguien fuera de los Estados Unidos como el agente sucesor. El agente sucesor no necesita ser ciudadano de los Estados Unidos. Sin embargo, puede haber problemas si un banco o una organización financiera no puede contactarlo. Quizá quiera consultar a un abogado para obtener asesoría. Use [**Get Legal Help**](</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>https://es.illinoislegalaid.org/get-legal-help</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>) para encontrar servicios legales gratuitos o de bajo costo en su zona.
-Para direcciones internacionales, habrá espacio para dos líneas para ingresar la dirección. Debe ingresar la dirección internacional usando el alfabeto inglés.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>Sus formularios están adjuntos.
 ¡Gracias por usar ILAO Easy Forms!
 [Illinois Legal Aid Online](</t>
@@ -26502,6 +25449,755 @@
   </si>
   <si>
     <t>[YOUTUBE hLR1cooGYxg]</t>
+  </si>
+  <si>
+    <t>Algunos ejemplos de **transacciones con instituciones financieras** son depositar o retirar dinero de una cuenta o emitir cheques.</t>
+  </si>
+  <si>
+    <t>**Incompetente** significa no poder manejar sus propios asuntos debido a una enfermedad, discapacidad o edad.
+Una persona puede ser declarada incompetente o legalmente discapacitada por un tribunal.
+Una persona puede ser certificada por un médico como incapaz de tomar decisiones o manejar asuntos comerciales.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% if for_yourself == True:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">La persona nombrada como un **{agente sucesor}** tendrá poder notarial para la propiedad por usted si </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${agent.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> muere, se vuelve **{incompetente}**, renuncia o se niega a actuar como su apoderado.
+If you list more than one successor agent, you should list them in order of preference
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% else:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">La persona nombrada como un sucesor agente tendrá poder notarial para la propiedad de </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${principal.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> si </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${agent.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> muere, se vuelve **{incompetent}**, renuncia o se niega a aceptar el cargo de agente.
+If </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${principal.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> lists more than one successor agent, they should list them in order of preference.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>% endif</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>No. Puede listar a alguien fuera de los Estados Unidos como el agente sucesor. El agente sucesor no necesita ser ciudadano de los Estados Unidos. Sin embargo, puede haber problemas si un banco o una organización financiera no puede contactarlo. Quizá quiera consultar a un abogado para obtener asesoría. Usa [**Obtener ayuda legal**](</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>https://es.illinoislegalaid.org/get-legal-help</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>) para encontrar servicios legales gratuitos o de bajo costo en su zona.
+Para direcciones internacionales, habrá espacio para dos líneas para ingresar la dirección. Debe ingresar la dirección internacional usando el alfabeto inglés.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${collapse_template(video_when_effect)}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% if for_yourself == True:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Este Poder Notarial entrará en vigor cuando usted firme el formulario a menos que indique que debe entrar en vigencia en un momento posterior.
+Aún tendrá la autoridad para tomar decisiones. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${agent.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> podrá tomar decisiones por usted cuando no pueda hacerlo.
+Aún puede cambiar de opinión y **{revocar}** el Poder Notarial después de firmarlo, siempre que tenga la **{capacidad legal}** requerida.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% else:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Este Poder Notarial entrará en vigor cuando </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${principal.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> firme el formulario a menos que indique que debe entrar en vigencia en un momento posterior.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${principal.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> seguirá teniendo la autoridad para tomar decisiones. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${agent.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> podrá tomar decisiones por ellos cuando no puedan hacerlo.
+Este Poder Notarial entrará en vigor cuando </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${principal.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> firme el formulario a menos que indique que debe entrar en vigencia en un momento posterior.
+Ellos seguirán teniendo la autoridad para tomar decisiones. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${agent.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> podrá tomar decisiones por ellos cuando no puedan hacerlo.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${principal.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> aún puede cambiar de opinión y **{revoke}** el Poder Notarial después de firmarlo, siempre que tenga la **{legal capacity}** requerida.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% endif
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${collapse_template(prove_capacity)}</t>
+    </r>
+  </si>
+  <si>
+    <t>**Video: ¿Cuándo entra en vigor un poder notarial para la propiedad?**</t>
+  </si>
+  <si>
+    <t>[YOUTUBE Dg7Lc7efTJI]</t>
+  </si>
+  <si>
+    <t>**Demostrando la capacidad legal**</t>
+  </si>
+  <si>
+    <t>[YOUTUBE Xx99zYlIwgE]</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${collapse_template(video_when_end)}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% if for_yourself == True:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>This Power of Attorney for Property will last until your death. However, you may choose to end it earlier. If you only want the Power of Attorney to last for a specific time, click **No**.
+You can end a Power of Attorney by making a formal Revocation. To make a Power of Attorney Revocation, use ILAO's [**Power of Attorney Revocation Easy Form**](</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>https://www.illinoislegalaid.org/legal-information/power-attorney-revocation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">).
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% else:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">This Power of Attorney for Property will last until </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${principal.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">'s death. However, they may choose to end it earlier. If they only want the Power of Attorney to last for a specific time, click **No**.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${principal.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> can end a Power of Attorney by making a formal Revocation. To make a Power of Attorney Revocation, use ILAO's [**Power of Attorney Revocation Easy Form**](</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>https://www.illinoislegalaid.org/legal-information/power-attorney-revocation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">).
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% endif
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${collapse_template(video_when_end)}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% if for_yourself == True:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Este poder notarial para bienes durará hasta su muerte. Sin embargo, puede elegir terminarlo antes. Si solo desea que el poder notarial dure por un tiempo específico, haga clic en **No**.
+Puede terminar un poder notarial realizando una Revocación formal. Para realizar una Revocación de Poder Notarial, use el [**Formulario Fácil de Revocación de Poder Notarial**](https://es.illinoislegalaid.org/legal-information/power-attorney-revocation) de ILAO.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% else:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Este poder notarial para bienes durará hasta la muerte de </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${principal.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Sin embargo, la persona puede elegir terminarlo antes. Si la persona solo quiere que el poder notarial dure por un tiempo específico, haga clic en **No**.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${principal.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> puede terminar un poder notarial realizando una Revocación formal. Para realizar una Revocación de Poder Notarial, use el [**Formulario Fácil de Revocación de Poder Notarial**](https://es.illinoislegalaid.org/legal-information/power-attorney-revocation) de ILAO.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>% endif</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -26590,7 +26286,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -26600,15 +26296,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -26986,7 +26673,7 @@
         <v>13</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>791</v>
+        <v>782</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="403.2">
@@ -26999,20 +26686,20 @@
       <c r="C3" s="2">
         <v>1</v>
       </c>
-      <c r="D3" s="6" t="s">
-        <v>855</v>
-      </c>
-      <c r="E3" s="6" t="s">
+      <c r="D3" s="2" t="s">
+        <v>845</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="7" t="s">
-        <v>856</v>
+      <c r="G3" s="3" t="s">
+        <v>846</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>857</v>
+        <v>847</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="187.2">
@@ -27038,7 +26725,7 @@
         <v>16</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>792</v>
+        <v>783</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="28.8">
@@ -27064,7 +26751,7 @@
         <v>19</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>793</v>
+        <v>784</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="302.39999999999998">
@@ -27090,7 +26777,7 @@
         <v>21</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>858</v>
+        <v>848</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -27116,7 +26803,7 @@
         <v>24</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>754</v>
+        <v>745</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="72">
@@ -27142,7 +26829,7 @@
         <v>26</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>794</v>
+        <v>785</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -27168,7 +26855,7 @@
         <v>28</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>775</v>
+        <v>766</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="43.2">
@@ -27194,7 +26881,7 @@
         <v>30</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>795</v>
+        <v>786</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="28.8">
@@ -27246,7 +26933,7 @@
         <v>35</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>796</v>
+        <v>787</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="43.2">
@@ -27272,7 +26959,7 @@
         <v>38</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>797</v>
+        <v>788</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="43.2">
@@ -27298,7 +26985,7 @@
         <v>40</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>798</v>
+        <v>789</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="86.4">
@@ -27324,7 +27011,7 @@
         <v>43</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>861</v>
+        <v>851</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="115.2">
@@ -27350,7 +27037,7 @@
         <v>46</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>859</v>
+        <v>849</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="28.8">
@@ -27402,7 +27089,7 @@
         <v>52</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>799</v>
+        <v>790</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="273.60000000000002">
@@ -27428,7 +27115,7 @@
         <v>54</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>860</v>
+        <v>850</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="28.8">
@@ -27454,7 +27141,7 @@
         <v>57</v>
       </c>
       <c r="H20" t="s">
-        <v>800</v>
+        <v>791</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="129.6">
@@ -27480,7 +27167,7 @@
         <v>59</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>801</v>
+        <v>792</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -27506,7 +27193,7 @@
         <v>62</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>802</v>
+        <v>793</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="43.2">
@@ -27532,7 +27219,7 @@
         <v>64</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>803</v>
+        <v>794</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="72">
@@ -27558,7 +27245,7 @@
         <v>66</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>804</v>
+        <v>795</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="28.8">
@@ -27584,7 +27271,7 @@
         <v>68</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>805</v>
+        <v>796</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="57.6">
@@ -27610,7 +27297,7 @@
         <v>70</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>867</v>
+        <v>856</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -27636,7 +27323,7 @@
         <v>72</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>806</v>
+        <v>797</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -27662,7 +27349,7 @@
         <v>74</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>807</v>
+        <v>798</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="28.8">
@@ -27688,7 +27375,7 @@
         <v>77</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>808</v>
+        <v>799</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="259.2">
@@ -27714,7 +27401,7 @@
         <v>79</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>809</v>
+        <v>800</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="86.4">
@@ -27740,7 +27427,7 @@
         <v>82</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>810</v>
+        <v>801</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="403.2">
@@ -27766,7 +27453,7 @@
         <v>84</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>811</v>
+        <v>802</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -27792,7 +27479,7 @@
         <v>86</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>812</v>
+        <v>803</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -27818,7 +27505,7 @@
         <v>88</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -27844,7 +27531,7 @@
         <v>90</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>814</v>
+        <v>805</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -27870,7 +27557,7 @@
         <v>92</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>815</v>
+        <v>806</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -27922,7 +27609,7 @@
         <v>97</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>816</v>
+        <v>807</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="115.2">
@@ -27948,7 +27635,7 @@
         <v>100</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>817</v>
+        <v>808</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="28.8">
@@ -27974,7 +27661,7 @@
         <v>102</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>818</v>
+        <v>809</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="28.8">
@@ -28000,7 +27687,7 @@
         <v>105</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>819</v>
+        <v>810</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="86.4">
@@ -28025,8 +27712,8 @@
       <c r="G42" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="H42" s="9" t="s">
-        <v>868</v>
+      <c r="H42" s="6" t="s">
+        <v>857</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="28.8">
@@ -28052,7 +27739,7 @@
         <v>111</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>869</v>
+        <v>858</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="144">
@@ -28104,7 +27791,7 @@
         <v>117</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>820</v>
+        <v>811</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="86.4">
@@ -28130,7 +27817,7 @@
         <v>120</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>821</v>
+        <v>812</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="86.4">
@@ -28156,7 +27843,7 @@
         <v>123</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>822</v>
+        <v>813</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="345.6">
@@ -28182,7 +27869,7 @@
         <v>125</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>823</v>
+        <v>814</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="28.8">
@@ -28208,7 +27895,7 @@
         <v>128</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>824</v>
+        <v>815</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="28.8">
@@ -28260,7 +27947,7 @@
         <v>133</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>825</v>
+        <v>816</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="43.2">
@@ -28286,7 +27973,7 @@
         <v>135</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>826</v>
+        <v>817</v>
       </c>
     </row>
     <row r="53" spans="1:8">
@@ -28312,7 +27999,7 @@
         <v>137</v>
       </c>
       <c r="H53" t="s">
-        <v>871</v>
+        <v>860</v>
       </c>
     </row>
     <row r="54" spans="1:8">
@@ -28338,7 +28025,7 @@
         <v>139</v>
       </c>
       <c r="H54" t="s">
-        <v>872</v>
+        <v>861</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="129.6">
@@ -28364,7 +28051,7 @@
         <v>142</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>862</v>
+        <v>852</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="28.8">
@@ -28390,7 +28077,7 @@
         <v>144</v>
       </c>
       <c r="H56" s="4" t="s">
-        <v>870</v>
+        <v>859</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="28.8">
@@ -28442,7 +28129,7 @@
         <v>150</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>827</v>
+        <v>818</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="115.2">
@@ -28467,8 +28154,8 @@
       <c r="G59" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="H59" s="8" t="s">
-        <v>873</v>
+      <c r="H59" s="5" t="s">
+        <v>862</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="28.8">
@@ -28520,7 +28207,7 @@
         <v>159</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>828</v>
+        <v>819</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="244.8">
@@ -28546,7 +28233,7 @@
         <v>161</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>829</v>
+        <v>820</v>
       </c>
     </row>
     <row r="63" spans="1:8">
@@ -28572,7 +28259,7 @@
         <v>163</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>830</v>
+        <v>821</v>
       </c>
     </row>
     <row r="64" spans="1:8">
@@ -28598,7 +28285,7 @@
         <v>165</v>
       </c>
       <c r="H64" s="4" t="s">
-        <v>831</v>
+        <v>822</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="43.2">
@@ -28650,7 +28337,7 @@
         <v>170</v>
       </c>
       <c r="H66" s="4" t="s">
-        <v>832</v>
+        <v>823</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="43.2">
@@ -28676,7 +28363,7 @@
         <v>172</v>
       </c>
       <c r="H67" s="4" t="s">
-        <v>833</v>
+        <v>863</v>
       </c>
     </row>
     <row r="68" spans="1:8">
@@ -28728,7 +28415,7 @@
         <v>177</v>
       </c>
       <c r="H69" s="4" t="s">
-        <v>834</v>
+        <v>824</v>
       </c>
     </row>
     <row r="70" spans="1:8">
@@ -28754,7 +28441,7 @@
         <v>179</v>
       </c>
       <c r="H70" s="4" t="s">
-        <v>835</v>
+        <v>825</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="72">
@@ -28780,7 +28467,7 @@
         <v>181</v>
       </c>
       <c r="H71" s="4" t="s">
-        <v>836</v>
+        <v>826</v>
       </c>
     </row>
     <row r="72" spans="1:8">
@@ -28806,7 +28493,7 @@
         <v>183</v>
       </c>
       <c r="H72" s="4" t="s">
-        <v>837</v>
+        <v>827</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="43.2">
@@ -28832,7 +28519,7 @@
         <v>185</v>
       </c>
       <c r="H73" s="4" t="s">
-        <v>838</v>
+        <v>828</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -28884,7 +28571,7 @@
         <v>190</v>
       </c>
       <c r="H75" s="4" t="s">
-        <v>840</v>
+        <v>830</v>
       </c>
     </row>
     <row r="76" spans="1:8">
@@ -28910,7 +28597,7 @@
         <v>192</v>
       </c>
       <c r="H76" s="4" t="s">
-        <v>839</v>
+        <v>829</v>
       </c>
     </row>
     <row r="77" spans="1:8" ht="43.2">
@@ -28936,7 +28623,7 @@
         <v>194</v>
       </c>
       <c r="H77" s="4" t="s">
-        <v>841</v>
+        <v>831</v>
       </c>
     </row>
     <row r="78" spans="1:8">
@@ -28962,7 +28649,7 @@
         <v>196</v>
       </c>
       <c r="H78" s="4" t="s">
-        <v>842</v>
+        <v>832</v>
       </c>
     </row>
     <row r="79" spans="1:8" ht="57.6">
@@ -28988,7 +28675,7 @@
         <v>198</v>
       </c>
       <c r="H79" s="4" t="s">
-        <v>843</v>
+        <v>833</v>
       </c>
     </row>
     <row r="80" spans="1:8">
@@ -29040,7 +28727,7 @@
         <v>203</v>
       </c>
       <c r="H81" s="4" t="s">
-        <v>844</v>
+        <v>834</v>
       </c>
     </row>
     <row r="82" spans="1:8">
@@ -29092,7 +28779,7 @@
         <v>208</v>
       </c>
       <c r="H83" s="4" t="s">
-        <v>845</v>
+        <v>835</v>
       </c>
     </row>
     <row r="84" spans="1:8">
@@ -29144,7 +28831,7 @@
         <v>213</v>
       </c>
       <c r="H85" s="4" t="s">
-        <v>846</v>
+        <v>836</v>
       </c>
     </row>
     <row r="86" spans="1:8">
@@ -29196,7 +28883,7 @@
         <v>218</v>
       </c>
       <c r="H87" s="4" t="s">
-        <v>847</v>
+        <v>837</v>
       </c>
     </row>
     <row r="88" spans="1:8">
@@ -29248,7 +28935,7 @@
         <v>223</v>
       </c>
       <c r="H89" s="4" t="s">
-        <v>849</v>
+        <v>839</v>
       </c>
     </row>
     <row r="90" spans="1:8">
@@ -29274,7 +28961,7 @@
         <v>225</v>
       </c>
       <c r="H90" s="4" t="s">
-        <v>848</v>
+        <v>838</v>
       </c>
     </row>
     <row r="91" spans="1:8" ht="43.2">
@@ -29300,7 +28987,7 @@
         <v>227</v>
       </c>
       <c r="H91" s="4" t="s">
-        <v>850</v>
+        <v>840</v>
       </c>
     </row>
     <row r="92" spans="1:8">
@@ -29352,7 +29039,7 @@
         <v>232</v>
       </c>
       <c r="H93" s="4" t="s">
-        <v>851</v>
+        <v>841</v>
       </c>
     </row>
     <row r="94" spans="1:8">
@@ -29404,7 +29091,7 @@
         <v>238</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>852</v>
+        <v>842</v>
       </c>
     </row>
     <row r="96" spans="1:8" ht="100.8">
@@ -29430,7 +29117,7 @@
         <v>241</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>853</v>
+        <v>843</v>
       </c>
     </row>
     <row r="97" spans="1:8" ht="115.2">
@@ -29456,7 +29143,7 @@
         <v>244</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>854</v>
+        <v>844</v>
       </c>
     </row>
     <row r="98" spans="1:8" ht="259.2">
@@ -29482,7 +29169,7 @@
         <v>246</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>863</v>
+        <v>853</v>
       </c>
     </row>
     <row r="99" spans="1:8" ht="28.8">
@@ -29534,7 +29221,7 @@
         <v>252</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>864</v>
+        <v>854</v>
       </c>
     </row>
     <row r="101" spans="1:8" ht="86.4">
@@ -31016,7 +30703,7 @@
         <v>433</v>
       </c>
       <c r="H157" s="4" t="s">
-        <v>434</v>
+        <v>864</v>
       </c>
     </row>
     <row r="158" spans="1:8">
@@ -31030,7 +30717,7 @@
         <v>2</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E158" s="2" t="s">
         <v>11</v>
@@ -31039,10 +30726,10 @@
         <v>12</v>
       </c>
       <c r="G158" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="H158" s="4" t="s">
         <v>436</v>
-      </c>
-      <c r="H158" s="4" t="s">
-        <v>437</v>
       </c>
     </row>
     <row r="159" spans="1:8" ht="43.2">
@@ -31056,7 +30743,7 @@
         <v>3</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E159" s="2" t="s">
         <v>11</v>
@@ -31065,10 +30752,10 @@
         <v>12</v>
       </c>
       <c r="G159" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="H159" s="4" t="s">
         <v>439</v>
-      </c>
-      <c r="H159" s="4" t="s">
-        <v>440</v>
       </c>
     </row>
     <row r="160" spans="1:8" ht="86.4">
@@ -31082,7 +30769,7 @@
         <v>4</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E160" s="2" t="s">
         <v>11</v>
@@ -31091,10 +30778,10 @@
         <v>12</v>
       </c>
       <c r="G160" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="H160" s="3" t="s">
         <v>442</v>
-      </c>
-      <c r="H160" s="3" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="161" spans="1:8" ht="216">
@@ -31108,7 +30795,7 @@
         <v>5</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E161" s="2" t="s">
         <v>11</v>
@@ -31117,10 +30804,10 @@
         <v>12</v>
       </c>
       <c r="G161" s="3" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H161" s="3" t="s">
-        <v>446</v>
+        <v>865</v>
       </c>
     </row>
     <row r="162" spans="1:8" ht="86.4">
@@ -31128,13 +30815,13 @@
         <v>8</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C162" s="2">
         <v>0</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E162" s="2" t="s">
         <v>11</v>
@@ -31143,10 +30830,10 @@
         <v>12</v>
       </c>
       <c r="G162" s="3" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="H162" s="3" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="163" spans="1:8" ht="72">
@@ -31154,13 +30841,13 @@
         <v>8</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C163" s="2">
         <v>1</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="E163" s="2" t="s">
         <v>11</v>
@@ -31169,10 +30856,10 @@
         <v>12</v>
       </c>
       <c r="G163" s="3" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="H163" s="3" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="164" spans="1:8">
@@ -31180,13 +30867,13 @@
         <v>8</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C164" s="2">
         <v>2</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="E164" s="2" t="s">
         <v>11</v>
@@ -31195,10 +30882,10 @@
         <v>12</v>
       </c>
       <c r="G164" s="3" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="H164" s="4" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="165" spans="1:8" ht="86.4">
@@ -31206,13 +30893,13 @@
         <v>8</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C165" s="2">
         <v>0</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="E165" s="2" t="s">
         <v>11</v>
@@ -31221,10 +30908,10 @@
         <v>12</v>
       </c>
       <c r="G165" s="3" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="H165" s="3" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="166" spans="1:8" ht="28.8">
@@ -31232,13 +30919,13 @@
         <v>8</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C166" s="2">
         <v>0</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="E166" s="2" t="s">
         <v>11</v>
@@ -31247,10 +30934,10 @@
         <v>12</v>
       </c>
       <c r="G166" s="3" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="H166" s="3" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="167" spans="1:8" ht="28.8">
@@ -31258,13 +30945,13 @@
         <v>8</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C167" s="2">
         <v>1</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="E167" s="2" t="s">
         <v>11</v>
@@ -31273,10 +30960,10 @@
         <v>12</v>
       </c>
       <c r="G167" s="3" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="H167" s="5" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="168" spans="1:8">
@@ -31284,13 +30971,13 @@
         <v>8</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C168" s="2">
         <v>2</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="E168" s="2" t="s">
         <v>11</v>
@@ -31299,10 +30986,10 @@
         <v>12</v>
       </c>
       <c r="G168" s="3" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="H168" s="3" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="169" spans="1:8" ht="129.6">
@@ -31310,13 +30997,13 @@
         <v>8</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C169" s="2">
         <v>0</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="E169" s="2" t="s">
         <v>11</v>
@@ -31325,10 +31012,10 @@
         <v>12</v>
       </c>
       <c r="G169" s="3" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="H169" s="3" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
     </row>
     <row r="170" spans="1:8" ht="28.8">
@@ -31336,13 +31023,13 @@
         <v>8</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C170" s="2">
         <v>1</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="E170" s="2" t="s">
         <v>11</v>
@@ -31351,10 +31038,10 @@
         <v>12</v>
       </c>
       <c r="G170" s="3" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="H170" s="4" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="171" spans="1:8" ht="28.8">
@@ -31362,13 +31049,13 @@
         <v>8</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C171" s="2">
         <v>0</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="E171" s="2" t="s">
         <v>11</v>
@@ -31377,10 +31064,10 @@
         <v>12</v>
       </c>
       <c r="G171" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="H171" s="3" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="172" spans="1:8" ht="100.8">
@@ -31388,13 +31075,13 @@
         <v>8</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C172" s="2">
         <v>1</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="E172" s="2" t="s">
         <v>11</v>
@@ -31403,10 +31090,10 @@
         <v>12</v>
       </c>
       <c r="G172" s="3" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="H172" s="3" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
     </row>
     <row r="173" spans="1:8" ht="115.2">
@@ -31414,13 +31101,13 @@
         <v>8</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C173" s="2">
         <v>0</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="E173" s="2" t="s">
         <v>11</v>
@@ -31429,10 +31116,10 @@
         <v>12</v>
       </c>
       <c r="G173" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="H173" s="3" t="s">
-        <v>487</v>
+        <v>484</v>
+      </c>
+      <c r="H173" s="5" t="s">
+        <v>869</v>
       </c>
     </row>
     <row r="174" spans="1:8" ht="28.8">
@@ -31440,13 +31127,13 @@
         <v>8</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C174" s="2">
         <v>1</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="E174" s="2" t="s">
         <v>11</v>
@@ -31455,10 +31142,10 @@
         <v>12</v>
       </c>
       <c r="G174" s="3" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="H174" s="4" t="s">
-        <v>490</v>
+        <v>868</v>
       </c>
     </row>
     <row r="175" spans="1:8">
@@ -31466,13 +31153,13 @@
         <v>8</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="C175" s="2">
         <v>0</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="E175" s="2" t="s">
         <v>11</v>
@@ -31481,10 +31168,10 @@
         <v>12</v>
       </c>
       <c r="G175" s="3" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="H175" s="4" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
     </row>
     <row r="176" spans="1:8" ht="28.8">
@@ -31492,13 +31179,13 @@
         <v>8</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="C176" s="2">
         <v>1</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="E176" s="2" t="s">
         <v>11</v>
@@ -31507,10 +31194,10 @@
         <v>12</v>
       </c>
       <c r="G176" s="3" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="H176" s="4" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
     </row>
     <row r="177" spans="1:8">
@@ -31518,13 +31205,13 @@
         <v>8</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="C177" s="2">
         <v>2</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="E177" s="2" t="s">
         <v>11</v>
@@ -31533,10 +31220,10 @@
         <v>12</v>
       </c>
       <c r="G177" s="3" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="H177" s="4" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
     </row>
     <row r="178" spans="1:8" ht="86.4">
@@ -31544,13 +31231,13 @@
         <v>8</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="C178" s="2">
         <v>3</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="E178" s="2" t="s">
         <v>11</v>
@@ -31559,10 +31246,10 @@
         <v>12</v>
       </c>
       <c r="G178" s="3" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="H178" s="3" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
     </row>
     <row r="179" spans="1:8" ht="86.4">
@@ -31570,13 +31257,13 @@
         <v>8</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="C179" s="2">
         <v>4</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="E179" s="2" t="s">
         <v>11</v>
@@ -31585,10 +31272,10 @@
         <v>12</v>
       </c>
       <c r="G179" s="3" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="H179" s="3" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
     </row>
     <row r="180" spans="1:8" ht="409.6">
@@ -31596,13 +31283,13 @@
         <v>8</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="C180" s="2">
         <v>5</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="E180" s="2" t="s">
         <v>11</v>
@@ -31611,10 +31298,10 @@
         <v>12</v>
       </c>
       <c r="G180" s="3" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="H180" s="3" t="s">
-        <v>509</v>
+        <v>867</v>
       </c>
     </row>
     <row r="181" spans="1:8">
@@ -31622,13 +31309,13 @@
         <v>8</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="C181" s="2">
         <v>6</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="E181" s="2" t="s">
         <v>11</v>
@@ -31637,10 +31324,10 @@
         <v>12</v>
       </c>
       <c r="G181" s="3" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="H181" s="4" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
     </row>
     <row r="182" spans="1:8" ht="144">
@@ -31648,13 +31335,13 @@
         <v>8</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="C182" s="2">
         <v>7</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="E182" s="2" t="s">
         <v>11</v>
@@ -31663,10 +31350,10 @@
         <v>12</v>
       </c>
       <c r="G182" s="3" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="H182" s="3" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
     </row>
     <row r="183" spans="1:8" ht="28.8">
@@ -31674,13 +31361,13 @@
         <v>8</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="C183" s="2">
         <v>8</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="E183" s="2" t="s">
         <v>11</v>
@@ -31689,10 +31376,10 @@
         <v>12</v>
       </c>
       <c r="G183" s="3" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="H183" s="3" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
     </row>
     <row r="184" spans="1:8" ht="57.6">
@@ -31700,13 +31387,13 @@
         <v>8</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="C184" s="2">
         <v>9</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="E184" s="2" t="s">
         <v>11</v>
@@ -31715,10 +31402,10 @@
         <v>12</v>
       </c>
       <c r="G184" s="3" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="H184" s="3" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
     </row>
     <row r="185" spans="1:8" ht="28.8">
@@ -31726,13 +31413,13 @@
         <v>8</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="C185" s="2">
         <v>10</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="E185" s="2" t="s">
         <v>11</v>
@@ -31741,10 +31428,10 @@
         <v>12</v>
       </c>
       <c r="G185" s="3" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="H185" s="3" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
     </row>
     <row r="186" spans="1:8">
@@ -31752,13 +31439,13 @@
         <v>8</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="C186" s="2">
         <v>11</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="E186" s="2" t="s">
         <v>11</v>
@@ -31767,10 +31454,10 @@
         <v>12</v>
       </c>
       <c r="G186" s="3" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="H186" s="4" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
     </row>
     <row r="187" spans="1:8">
@@ -31778,13 +31465,13 @@
         <v>8</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="C187" s="2">
         <v>12</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="E187" s="2" t="s">
         <v>11</v>
@@ -31793,10 +31480,10 @@
         <v>12</v>
       </c>
       <c r="G187" s="3" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="H187" s="4" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
     </row>
     <row r="188" spans="1:8" ht="115.2">
@@ -31804,13 +31491,13 @@
         <v>8</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="C188" s="2">
         <v>0</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="E188" s="2" t="s">
         <v>11</v>
@@ -31819,10 +31506,10 @@
         <v>12</v>
       </c>
       <c r="G188" s="3" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="H188" s="3" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
     </row>
     <row r="189" spans="1:8" ht="28.8">
@@ -31830,13 +31517,13 @@
         <v>8</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="C189" s="2">
         <v>1</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="E189" s="2" t="s">
         <v>11</v>
@@ -31845,10 +31532,10 @@
         <v>12</v>
       </c>
       <c r="G189" s="3" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="H189" s="4" t="s">
-        <v>537</v>
+        <v>870</v>
       </c>
     </row>
     <row r="190" spans="1:8" ht="115.2">
@@ -31856,13 +31543,13 @@
         <v>8</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="C190" s="2">
         <v>0</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="E190" s="2" t="s">
         <v>11</v>
@@ -31871,10 +31558,10 @@
         <v>12</v>
       </c>
       <c r="G190" s="3" t="s">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="H190" s="3" t="s">
-        <v>541</v>
+        <v>871</v>
       </c>
     </row>
     <row r="191" spans="1:8" ht="28.8">
@@ -31882,13 +31569,13 @@
         <v>8</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="C191" s="2">
         <v>1</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="E191" s="2" t="s">
         <v>11</v>
@@ -31897,10 +31584,10 @@
         <v>12</v>
       </c>
       <c r="G191" s="3" t="s">
-        <v>543</v>
+        <v>536</v>
       </c>
       <c r="H191" s="4" t="s">
-        <v>544</v>
+        <v>537</v>
       </c>
     </row>
     <row r="192" spans="1:8" ht="86.4">
@@ -31908,13 +31595,13 @@
         <v>8</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>545</v>
+        <v>538</v>
       </c>
       <c r="C192" s="2">
         <v>0</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>546</v>
+        <v>539</v>
       </c>
       <c r="E192" s="2" t="s">
         <v>11</v>
@@ -31923,10 +31610,10 @@
         <v>12</v>
       </c>
       <c r="G192" s="3" t="s">
-        <v>547</v>
+        <v>540</v>
       </c>
       <c r="H192" s="3" t="s">
-        <v>548</v>
+        <v>541</v>
       </c>
     </row>
     <row r="193" spans="1:8" ht="316.8">
@@ -31934,13 +31621,13 @@
         <v>8</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>545</v>
+        <v>538</v>
       </c>
       <c r="C193" s="2">
         <v>1</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>549</v>
+        <v>542</v>
       </c>
       <c r="E193" s="2" t="s">
         <v>11</v>
@@ -31949,10 +31636,10 @@
         <v>12</v>
       </c>
       <c r="G193" s="3" t="s">
-        <v>550</v>
+        <v>872</v>
       </c>
       <c r="H193" s="3" t="s">
-        <v>551</v>
+        <v>873</v>
       </c>
     </row>
     <row r="194" spans="1:8" ht="86.4">
@@ -31960,13 +31647,13 @@
         <v>8</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>552</v>
+        <v>543</v>
       </c>
       <c r="C194" s="2">
         <v>0</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>553</v>
+        <v>544</v>
       </c>
       <c r="E194" s="2" t="s">
         <v>11</v>
@@ -31975,10 +31662,10 @@
         <v>12</v>
       </c>
       <c r="G194" s="3" t="s">
-        <v>554</v>
+        <v>545</v>
       </c>
       <c r="H194" s="3" t="s">
-        <v>555</v>
+        <v>546</v>
       </c>
     </row>
     <row r="195" spans="1:8" ht="28.8">
@@ -31986,13 +31673,13 @@
         <v>8</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>552</v>
+        <v>543</v>
       </c>
       <c r="C195" s="2">
         <v>1</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>556</v>
+        <v>547</v>
       </c>
       <c r="E195" s="2" t="s">
         <v>11</v>
@@ -32001,10 +31688,10 @@
         <v>12</v>
       </c>
       <c r="G195" s="3" t="s">
-        <v>557</v>
+        <v>548</v>
       </c>
       <c r="H195" s="4" t="s">
-        <v>558</v>
+        <v>549</v>
       </c>
     </row>
     <row r="196" spans="1:8" ht="86.4">
@@ -32012,13 +31699,13 @@
         <v>8</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>559</v>
+        <v>550</v>
       </c>
       <c r="C196" s="2">
         <v>0</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>560</v>
+        <v>551</v>
       </c>
       <c r="E196" s="2" t="s">
         <v>11</v>
@@ -32027,10 +31714,10 @@
         <v>12</v>
       </c>
       <c r="G196" s="3" t="s">
-        <v>561</v>
+        <v>552</v>
       </c>
       <c r="H196" s="3" t="s">
-        <v>562</v>
+        <v>553</v>
       </c>
     </row>
     <row r="197" spans="1:8" ht="201.6">
@@ -32038,13 +31725,13 @@
         <v>8</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>559</v>
+        <v>550</v>
       </c>
       <c r="C197" s="2">
         <v>1</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>563</v>
+        <v>554</v>
       </c>
       <c r="E197" s="2" t="s">
         <v>11</v>
@@ -32053,10 +31740,10 @@
         <v>12</v>
       </c>
       <c r="G197" s="3" t="s">
-        <v>564</v>
+        <v>555</v>
       </c>
       <c r="H197" s="3" t="s">
-        <v>565</v>
+        <v>556</v>
       </c>
     </row>
     <row r="198" spans="1:8" ht="28.8">
@@ -32064,13 +31751,13 @@
         <v>8</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>559</v>
+        <v>550</v>
       </c>
       <c r="C198" s="2">
         <v>2</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>566</v>
+        <v>557</v>
       </c>
       <c r="E198" s="2" t="s">
         <v>11</v>
@@ -32079,10 +31766,10 @@
         <v>12</v>
       </c>
       <c r="G198" s="3" t="s">
-        <v>567</v>
+        <v>558</v>
       </c>
       <c r="H198" s="3" t="s">
-        <v>568</v>
+        <v>559</v>
       </c>
     </row>
     <row r="199" spans="1:8">
@@ -32090,13 +31777,13 @@
         <v>8</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>559</v>
+        <v>550</v>
       </c>
       <c r="C199" s="2">
         <v>3</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>569</v>
+        <v>560</v>
       </c>
       <c r="E199" s="2" t="s">
         <v>11</v>
@@ -32105,10 +31792,10 @@
         <v>12</v>
       </c>
       <c r="G199" s="3" t="s">
-        <v>570</v>
+        <v>561</v>
       </c>
       <c r="H199" s="3" t="s">
-        <v>571</v>
+        <v>562</v>
       </c>
     </row>
     <row r="200" spans="1:8" ht="100.8">
@@ -32116,13 +31803,13 @@
         <v>8</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>559</v>
+        <v>550</v>
       </c>
       <c r="C200" s="2">
         <v>4</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>572</v>
+        <v>563</v>
       </c>
       <c r="E200" s="2" t="s">
         <v>11</v>
@@ -32131,10 +31818,10 @@
         <v>12</v>
       </c>
       <c r="G200" s="3" t="s">
-        <v>573</v>
+        <v>564</v>
       </c>
       <c r="H200" s="4" t="s">
-        <v>574</v>
+        <v>565</v>
       </c>
     </row>
     <row r="201" spans="1:8" ht="28.8">
@@ -32142,13 +31829,13 @@
         <v>8</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>559</v>
+        <v>550</v>
       </c>
       <c r="C201" s="2">
         <v>5</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>575</v>
+        <v>566</v>
       </c>
       <c r="E201" s="2" t="s">
         <v>11</v>
@@ -32157,10 +31844,10 @@
         <v>12</v>
       </c>
       <c r="G201" s="3" t="s">
-        <v>576</v>
+        <v>567</v>
       </c>
       <c r="H201" s="3" t="s">
-        <v>577</v>
+        <v>568</v>
       </c>
     </row>
     <row r="202" spans="1:8">
@@ -32168,13 +31855,13 @@
         <v>8</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>559</v>
+        <v>550</v>
       </c>
       <c r="C202" s="2">
         <v>6</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>578</v>
+        <v>569</v>
       </c>
       <c r="E202" s="2" t="s">
         <v>11</v>
@@ -32183,10 +31870,10 @@
         <v>12</v>
       </c>
       <c r="G202" s="3" t="s">
-        <v>579</v>
+        <v>570</v>
       </c>
       <c r="H202" s="4" t="s">
-        <v>580</v>
+        <v>571</v>
       </c>
     </row>
     <row r="203" spans="1:8">
@@ -32194,13 +31881,13 @@
         <v>8</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>559</v>
+        <v>550</v>
       </c>
       <c r="C203" s="2">
         <v>7</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>581</v>
+        <v>572</v>
       </c>
       <c r="E203" s="2" t="s">
         <v>11</v>
@@ -32209,10 +31896,10 @@
         <v>12</v>
       </c>
       <c r="G203" s="3" t="s">
-        <v>582</v>
+        <v>573</v>
       </c>
       <c r="H203" s="4" t="s">
-        <v>583</v>
+        <v>574</v>
       </c>
     </row>
     <row r="204" spans="1:8" ht="100.8">
@@ -32220,13 +31907,13 @@
         <v>8</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>584</v>
+        <v>575</v>
       </c>
       <c r="C204" s="2">
         <v>0</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="E204" s="2" t="s">
         <v>11</v>
@@ -32235,10 +31922,10 @@
         <v>12</v>
       </c>
       <c r="G204" s="3" t="s">
-        <v>586</v>
+        <v>577</v>
       </c>
       <c r="H204" s="3" t="s">
-        <v>587</v>
+        <v>578</v>
       </c>
     </row>
     <row r="205" spans="1:8" ht="244.8">
@@ -32246,13 +31933,13 @@
         <v>8</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>584</v>
+        <v>575</v>
       </c>
       <c r="C205" s="2">
         <v>1</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>588</v>
+        <v>579</v>
       </c>
       <c r="E205" s="2" t="s">
         <v>11</v>
@@ -32261,10 +31948,10 @@
         <v>12</v>
       </c>
       <c r="G205" s="3" t="s">
-        <v>589</v>
+        <v>580</v>
       </c>
       <c r="H205" s="3" t="s">
-        <v>590</v>
+        <v>581</v>
       </c>
     </row>
     <row r="206" spans="1:8" ht="28.8">
@@ -32272,13 +31959,13 @@
         <v>8</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>591</v>
+        <v>582</v>
       </c>
       <c r="C206" s="2">
         <v>0</v>
       </c>
       <c r="D206" s="2" t="s">
-        <v>592</v>
+        <v>583</v>
       </c>
       <c r="E206" s="2" t="s">
         <v>11</v>
@@ -32287,10 +31974,10 @@
         <v>12</v>
       </c>
       <c r="G206" s="3" t="s">
-        <v>593</v>
+        <v>584</v>
       </c>
       <c r="H206" s="4" t="s">
-        <v>594</v>
+        <v>585</v>
       </c>
     </row>
     <row r="207" spans="1:8" ht="43.2">
@@ -32298,13 +31985,13 @@
         <v>8</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>591</v>
+        <v>582</v>
       </c>
       <c r="C207" s="2">
         <v>1</v>
       </c>
       <c r="D207" s="2" t="s">
-        <v>595</v>
+        <v>586</v>
       </c>
       <c r="E207" s="2" t="s">
         <v>11</v>
@@ -32313,10 +32000,10 @@
         <v>12</v>
       </c>
       <c r="G207" s="3" t="s">
-        <v>596</v>
+        <v>587</v>
       </c>
       <c r="H207" s="3" t="s">
-        <v>597</v>
+        <v>588</v>
       </c>
     </row>
     <row r="208" spans="1:8" ht="28.8">
@@ -32324,13 +32011,13 @@
         <v>8</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>598</v>
+        <v>589</v>
       </c>
       <c r="C208" s="2">
         <v>0</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>599</v>
+        <v>590</v>
       </c>
       <c r="E208" s="2" t="s">
         <v>11</v>
@@ -32339,10 +32026,10 @@
         <v>12</v>
       </c>
       <c r="G208" s="3" t="s">
-        <v>600</v>
+        <v>591</v>
       </c>
       <c r="H208" s="4" t="s">
-        <v>601</v>
+        <v>592</v>
       </c>
     </row>
     <row r="209" spans="1:8" ht="28.8">
@@ -32350,13 +32037,13 @@
         <v>8</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>602</v>
+        <v>593</v>
       </c>
       <c r="C209" s="2">
         <v>0</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>603</v>
+        <v>594</v>
       </c>
       <c r="E209" s="2" t="s">
         <v>11</v>
@@ -32365,10 +32052,10 @@
         <v>12</v>
       </c>
       <c r="G209" s="3" t="s">
-        <v>604</v>
+        <v>595</v>
       </c>
       <c r="H209" s="4" t="s">
-        <v>605</v>
+        <v>596</v>
       </c>
     </row>
     <row r="210" spans="1:8" ht="28.8">
@@ -32376,13 +32063,13 @@
         <v>8</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>602</v>
+        <v>593</v>
       </c>
       <c r="C210" s="2">
         <v>1</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>606</v>
+        <v>597</v>
       </c>
       <c r="E210" s="2" t="s">
         <v>11</v>
@@ -32391,10 +32078,10 @@
         <v>12</v>
       </c>
       <c r="G210" s="3" t="s">
-        <v>607</v>
+        <v>598</v>
       </c>
       <c r="H210" s="4" t="s">
-        <v>608</v>
+        <v>599</v>
       </c>
     </row>
     <row r="211" spans="1:8" ht="28.8">
@@ -32402,13 +32089,13 @@
         <v>8</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>609</v>
+        <v>600</v>
       </c>
       <c r="C211" s="2">
         <v>0</v>
       </c>
       <c r="D211" s="2" t="s">
-        <v>610</v>
+        <v>601</v>
       </c>
       <c r="E211" s="2" t="s">
         <v>11</v>
@@ -32417,10 +32104,10 @@
         <v>12</v>
       </c>
       <c r="G211" s="3" t="s">
-        <v>611</v>
+        <v>602</v>
       </c>
       <c r="H211" s="4" t="s">
-        <v>612</v>
+        <v>603</v>
       </c>
     </row>
     <row r="212" spans="1:8" ht="409.6">
@@ -32428,13 +32115,13 @@
         <v>8</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>609</v>
+        <v>600</v>
       </c>
       <c r="C212" s="2">
         <v>1</v>
       </c>
       <c r="D212" s="2" t="s">
-        <v>613</v>
+        <v>604</v>
       </c>
       <c r="E212" s="2" t="s">
         <v>11</v>
@@ -32443,10 +32130,10 @@
         <v>12</v>
       </c>
       <c r="G212" s="3" t="s">
-        <v>614</v>
+        <v>605</v>
       </c>
       <c r="H212" s="3" t="s">
-        <v>615</v>
+        <v>606</v>
       </c>
     </row>
     <row r="213" spans="1:8" ht="86.4">
@@ -32454,13 +32141,13 @@
         <v>8</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>616</v>
+        <v>607</v>
       </c>
       <c r="C213" s="2">
         <v>0</v>
       </c>
       <c r="D213" s="2" t="s">
-        <v>617</v>
+        <v>608</v>
       </c>
       <c r="E213" s="2" t="s">
         <v>11</v>
@@ -32469,10 +32156,10 @@
         <v>12</v>
       </c>
       <c r="G213" s="3" t="s">
-        <v>618</v>
+        <v>609</v>
       </c>
       <c r="H213" s="4" t="s">
-        <v>619</v>
+        <v>610</v>
       </c>
     </row>
     <row r="214" spans="1:8" ht="86.4">
@@ -32480,13 +32167,13 @@
         <v>8</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>616</v>
+        <v>607</v>
       </c>
       <c r="C214" s="2">
         <v>1</v>
       </c>
       <c r="D214" s="2" t="s">
-        <v>620</v>
+        <v>611</v>
       </c>
       <c r="E214" s="2" t="s">
         <v>11</v>
@@ -32495,10 +32182,10 @@
         <v>12</v>
       </c>
       <c r="G214" s="3" t="s">
-        <v>621</v>
+        <v>612</v>
       </c>
       <c r="H214" s="3" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
     </row>
     <row r="215" spans="1:8" ht="28.8">
@@ -32506,13 +32193,13 @@
         <v>8</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>623</v>
+        <v>614</v>
       </c>
       <c r="C215" s="2">
         <v>0</v>
       </c>
       <c r="D215" s="2" t="s">
-        <v>624</v>
+        <v>615</v>
       </c>
       <c r="E215" s="2" t="s">
         <v>11</v>
@@ -32521,10 +32208,10 @@
         <v>12</v>
       </c>
       <c r="G215" s="3" t="s">
-        <v>625</v>
+        <v>616</v>
       </c>
       <c r="H215" s="4" t="s">
-        <v>626</v>
+        <v>617</v>
       </c>
     </row>
     <row r="216" spans="1:8" ht="403.2">
@@ -32532,13 +32219,13 @@
         <v>8</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>623</v>
+        <v>614</v>
       </c>
       <c r="C216" s="2">
         <v>1</v>
       </c>
       <c r="D216" s="2" t="s">
-        <v>627</v>
+        <v>618</v>
       </c>
       <c r="E216" s="2" t="s">
         <v>11</v>
@@ -32547,10 +32234,10 @@
         <v>12</v>
       </c>
       <c r="G216" s="3" t="s">
-        <v>628</v>
+        <v>619</v>
       </c>
       <c r="H216" s="3" t="s">
-        <v>629</v>
+        <v>620</v>
       </c>
     </row>
     <row r="217" spans="1:8" ht="187.2">
@@ -32558,13 +32245,13 @@
         <v>8</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>623</v>
+        <v>614</v>
       </c>
       <c r="C217" s="2">
         <v>2</v>
       </c>
       <c r="D217" s="2" t="s">
-        <v>630</v>
+        <v>621</v>
       </c>
       <c r="E217" s="2" t="s">
         <v>11</v>
@@ -32573,10 +32260,10 @@
         <v>12</v>
       </c>
       <c r="G217" s="3" t="s">
-        <v>631</v>
+        <v>622</v>
       </c>
       <c r="H217" s="3" t="s">
-        <v>632</v>
+        <v>623</v>
       </c>
     </row>
     <row r="218" spans="1:8" ht="86.4">
@@ -32584,13 +32271,13 @@
         <v>8</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>633</v>
+        <v>624</v>
       </c>
       <c r="C218" s="2">
         <v>0</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>634</v>
+        <v>625</v>
       </c>
       <c r="E218" s="2" t="s">
         <v>11</v>
@@ -32599,10 +32286,10 @@
         <v>12</v>
       </c>
       <c r="G218" s="3" t="s">
-        <v>635</v>
+        <v>626</v>
       </c>
       <c r="H218" s="3" t="s">
-        <v>866</v>
+        <v>855</v>
       </c>
     </row>
     <row r="219" spans="1:8">
@@ -32610,13 +32297,13 @@
         <v>8</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>636</v>
+        <v>627</v>
       </c>
       <c r="C219" s="2">
         <v>1</v>
       </c>
       <c r="D219" s="2" t="s">
-        <v>637</v>
+        <v>628</v>
       </c>
       <c r="E219" s="2" t="s">
         <v>11</v>
@@ -32628,7 +32315,7 @@
         <v>22</v>
       </c>
       <c r="H219" s="4" t="s">
-        <v>638</v>
+        <v>629</v>
       </c>
     </row>
     <row r="220" spans="1:8">
@@ -32636,13 +32323,13 @@
         <v>8</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>639</v>
+        <v>630</v>
       </c>
       <c r="C220" s="2">
         <v>0</v>
       </c>
       <c r="D220" s="2" t="s">
-        <v>640</v>
+        <v>631</v>
       </c>
       <c r="E220" s="2" t="s">
         <v>11</v>
@@ -32651,10 +32338,10 @@
         <v>12</v>
       </c>
       <c r="G220" s="3" t="s">
-        <v>641</v>
+        <v>632</v>
       </c>
       <c r="H220" s="4" t="s">
-        <v>642</v>
+        <v>633</v>
       </c>
     </row>
     <row r="221" spans="1:8">
@@ -32662,13 +32349,13 @@
         <v>8</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>643</v>
+        <v>634</v>
       </c>
       <c r="C221" s="2">
         <v>0</v>
       </c>
       <c r="D221" s="2" t="s">
-        <v>644</v>
+        <v>635</v>
       </c>
       <c r="E221" s="2" t="s">
         <v>11</v>
@@ -32677,10 +32364,10 @@
         <v>12</v>
       </c>
       <c r="G221" s="3" t="s">
-        <v>645</v>
+        <v>636</v>
       </c>
       <c r="H221" s="4" t="s">
-        <v>646</v>
+        <v>637</v>
       </c>
     </row>
     <row r="222" spans="1:8">
@@ -32688,13 +32375,13 @@
         <v>8</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>647</v>
+        <v>638</v>
       </c>
       <c r="C222" s="2">
         <v>0</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>648</v>
+        <v>639</v>
       </c>
       <c r="E222" s="2" t="s">
         <v>11</v>
@@ -32703,10 +32390,10 @@
         <v>12</v>
       </c>
       <c r="G222" s="3" t="s">
-        <v>649</v>
+        <v>640</v>
       </c>
       <c r="H222" s="4" t="s">
-        <v>650</v>
+        <v>641</v>
       </c>
     </row>
     <row r="223" spans="1:8">
@@ -32714,13 +32401,13 @@
         <v>8</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>651</v>
+        <v>642</v>
       </c>
       <c r="C223" s="2">
         <v>0</v>
       </c>
       <c r="D223" s="2" t="s">
-        <v>652</v>
+        <v>643</v>
       </c>
       <c r="E223" s="2" t="s">
         <v>11</v>
@@ -32729,10 +32416,10 @@
         <v>12</v>
       </c>
       <c r="G223" s="3" t="s">
-        <v>653</v>
+        <v>644</v>
       </c>
       <c r="H223" s="4" t="s">
-        <v>654</v>
+        <v>645</v>
       </c>
     </row>
     <row r="224" spans="1:8">
@@ -32740,13 +32427,13 @@
         <v>8</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>655</v>
+        <v>646</v>
       </c>
       <c r="C224" s="2">
         <v>0</v>
       </c>
       <c r="D224" s="2" t="s">
-        <v>656</v>
+        <v>647</v>
       </c>
       <c r="E224" s="2" t="s">
         <v>11</v>
@@ -32755,10 +32442,10 @@
         <v>12</v>
       </c>
       <c r="G224" s="3" t="s">
-        <v>657</v>
+        <v>648</v>
       </c>
       <c r="H224" s="4" t="s">
-        <v>658</v>
+        <v>649</v>
       </c>
     </row>
     <row r="225" spans="1:8" ht="28.8">
@@ -32766,13 +32453,13 @@
         <v>8</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>659</v>
+        <v>650</v>
       </c>
       <c r="C225" s="2">
         <v>0</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>660</v>
+        <v>651</v>
       </c>
       <c r="E225" s="2" t="s">
         <v>11</v>
@@ -32781,10 +32468,10 @@
         <v>12</v>
       </c>
       <c r="G225" s="3" t="s">
-        <v>661</v>
+        <v>652</v>
       </c>
       <c r="H225" s="4" t="s">
-        <v>662</v>
+        <v>653</v>
       </c>
     </row>
     <row r="226" spans="1:8" ht="28.8">
@@ -32792,13 +32479,13 @@
         <v>8</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>659</v>
+        <v>650</v>
       </c>
       <c r="C226" s="2">
         <v>1</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>663</v>
+        <v>654</v>
       </c>
       <c r="E226" s="2" t="s">
         <v>11</v>
@@ -32807,10 +32494,10 @@
         <v>12</v>
       </c>
       <c r="G226" s="3" t="s">
-        <v>664</v>
+        <v>655</v>
       </c>
       <c r="H226" s="4" t="s">
-        <v>665</v>
+        <v>656</v>
       </c>
     </row>
     <row r="227" spans="1:8">
@@ -32818,13 +32505,13 @@
         <v>8</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>659</v>
+        <v>650</v>
       </c>
       <c r="C227" s="2">
         <v>2</v>
       </c>
       <c r="D227" s="2" t="s">
-        <v>666</v>
+        <v>657</v>
       </c>
       <c r="E227" s="2" t="s">
         <v>11</v>
@@ -32833,10 +32520,10 @@
         <v>12</v>
       </c>
       <c r="G227" s="3" t="s">
-        <v>667</v>
+        <v>658</v>
       </c>
       <c r="H227" s="4" t="s">
-        <v>668</v>
+        <v>659</v>
       </c>
     </row>
     <row r="228" spans="1:8" ht="100.8">
@@ -32844,13 +32531,13 @@
         <v>8</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>659</v>
+        <v>650</v>
       </c>
       <c r="C228" s="2">
         <v>3</v>
       </c>
       <c r="D228" s="2" t="s">
-        <v>669</v>
+        <v>660</v>
       </c>
       <c r="E228" s="2" t="s">
         <v>11</v>
@@ -32859,10 +32546,10 @@
         <v>12</v>
       </c>
       <c r="G228" s="3" t="s">
-        <v>670</v>
+        <v>661</v>
       </c>
       <c r="H228" s="3" t="s">
-        <v>671</v>
+        <v>662</v>
       </c>
     </row>
     <row r="229" spans="1:8" ht="187.2">
@@ -32870,13 +32557,13 @@
         <v>8</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>659</v>
+        <v>650</v>
       </c>
       <c r="C229" s="2">
         <v>4</v>
       </c>
       <c r="D229" s="2" t="s">
-        <v>672</v>
+        <v>663</v>
       </c>
       <c r="E229" s="2" t="s">
         <v>11</v>
@@ -32885,10 +32572,10 @@
         <v>12</v>
       </c>
       <c r="G229" s="3" t="s">
-        <v>673</v>
+        <v>664</v>
       </c>
       <c r="H229" s="3" t="s">
-        <v>674</v>
+        <v>665</v>
       </c>
     </row>
     <row r="230" spans="1:8" ht="100.8">
@@ -32896,13 +32583,13 @@
         <v>8</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>659</v>
+        <v>650</v>
       </c>
       <c r="C230" s="2">
         <v>5</v>
       </c>
       <c r="D230" s="2" t="s">
-        <v>675</v>
+        <v>666</v>
       </c>
       <c r="E230" s="2" t="s">
         <v>11</v>
@@ -32911,10 +32598,10 @@
         <v>12</v>
       </c>
       <c r="G230" s="3" t="s">
-        <v>676</v>
+        <v>667</v>
       </c>
       <c r="H230" s="3" t="s">
-        <v>677</v>
+        <v>668</v>
       </c>
     </row>
     <row r="231" spans="1:8" ht="100.8">
@@ -32922,13 +32609,13 @@
         <v>8</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>659</v>
+        <v>650</v>
       </c>
       <c r="C231" s="2">
         <v>6</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>678</v>
+        <v>669</v>
       </c>
       <c r="E231" s="2" t="s">
         <v>11</v>
@@ -32937,10 +32624,10 @@
         <v>12</v>
       </c>
       <c r="G231" s="3" t="s">
-        <v>679</v>
+        <v>670</v>
       </c>
       <c r="H231" s="3" t="s">
-        <v>680</v>
+        <v>671</v>
       </c>
     </row>
     <row r="232" spans="1:8" ht="43.2">
@@ -32948,13 +32635,13 @@
         <v>8</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>659</v>
+        <v>650</v>
       </c>
       <c r="C232" s="2">
         <v>7</v>
       </c>
       <c r="D232" s="2" t="s">
-        <v>681</v>
+        <v>672</v>
       </c>
       <c r="E232" s="2" t="s">
         <v>11</v>
@@ -32963,10 +32650,10 @@
         <v>12</v>
       </c>
       <c r="G232" s="3" t="s">
-        <v>682</v>
+        <v>673</v>
       </c>
       <c r="H232" s="3" t="s">
-        <v>683</v>
+        <v>674</v>
       </c>
     </row>
     <row r="233" spans="1:8" ht="100.8">
@@ -32974,13 +32661,13 @@
         <v>8</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>659</v>
+        <v>650</v>
       </c>
       <c r="C233" s="2">
         <v>8</v>
       </c>
       <c r="D233" s="2" t="s">
-        <v>684</v>
+        <v>675</v>
       </c>
       <c r="E233" s="2" t="s">
         <v>11</v>
@@ -32989,10 +32676,10 @@
         <v>12</v>
       </c>
       <c r="G233" s="3" t="s">
-        <v>685</v>
+        <v>676</v>
       </c>
       <c r="H233" s="3" t="s">
-        <v>686</v>
+        <v>677</v>
       </c>
     </row>
     <row r="234" spans="1:8" ht="43.2">
@@ -33000,13 +32687,13 @@
         <v>8</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>659</v>
+        <v>650</v>
       </c>
       <c r="C234" s="2">
         <v>9</v>
       </c>
       <c r="D234" s="2" t="s">
-        <v>687</v>
+        <v>678</v>
       </c>
       <c r="E234" s="2" t="s">
         <v>11</v>
@@ -33015,10 +32702,10 @@
         <v>12</v>
       </c>
       <c r="G234" s="3" t="s">
-        <v>688</v>
+        <v>679</v>
       </c>
       <c r="H234" s="3" t="s">
-        <v>689</v>
+        <v>680</v>
       </c>
     </row>
     <row r="235" spans="1:8" ht="409.6">
@@ -33026,13 +32713,13 @@
         <v>8</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>659</v>
+        <v>650</v>
       </c>
       <c r="C235" s="2">
         <v>10</v>
       </c>
       <c r="D235" s="2" t="s">
-        <v>690</v>
+        <v>681</v>
       </c>
       <c r="E235" s="2" t="s">
         <v>11</v>
@@ -33041,10 +32728,10 @@
         <v>12</v>
       </c>
       <c r="G235" s="3" t="s">
-        <v>691</v>
+        <v>682</v>
       </c>
       <c r="H235" s="3" t="s">
-        <v>692</v>
+        <v>683</v>
       </c>
     </row>
     <row r="236" spans="1:8" ht="43.2">
@@ -33052,13 +32739,13 @@
         <v>8</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>659</v>
+        <v>650</v>
       </c>
       <c r="C236" s="2">
         <v>11</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>693</v>
+        <v>684</v>
       </c>
       <c r="E236" s="2" t="s">
         <v>11</v>
@@ -33067,10 +32754,10 @@
         <v>12</v>
       </c>
       <c r="G236" s="3" t="s">
-        <v>694</v>
+        <v>685</v>
       </c>
       <c r="H236" s="3" t="s">
-        <v>695</v>
+        <v>686</v>
       </c>
     </row>
     <row r="237" spans="1:8" ht="43.2">
@@ -33078,13 +32765,13 @@
         <v>8</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>659</v>
+        <v>650</v>
       </c>
       <c r="C237" s="2">
         <v>12</v>
       </c>
       <c r="D237" s="2" t="s">
-        <v>696</v>
+        <v>687</v>
       </c>
       <c r="E237" s="2" t="s">
         <v>11</v>
@@ -33093,10 +32780,10 @@
         <v>12</v>
       </c>
       <c r="G237" s="3" t="s">
-        <v>697</v>
+        <v>688</v>
       </c>
       <c r="H237" s="3" t="s">
-        <v>698</v>
+        <v>689</v>
       </c>
     </row>
     <row r="238" spans="1:8" ht="115.2">
@@ -33104,13 +32791,13 @@
         <v>8</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>659</v>
+        <v>650</v>
       </c>
       <c r="C238" s="2">
         <v>13</v>
       </c>
       <c r="D238" s="2" t="s">
-        <v>699</v>
+        <v>690</v>
       </c>
       <c r="E238" s="2" t="s">
         <v>11</v>
@@ -33119,10 +32806,10 @@
         <v>12</v>
       </c>
       <c r="G238" s="3" t="s">
-        <v>700</v>
+        <v>691</v>
       </c>
       <c r="H238" s="3" t="s">
-        <v>701</v>
+        <v>692</v>
       </c>
     </row>
     <row r="239" spans="1:8" ht="43.2">
@@ -33130,13 +32817,13 @@
         <v>8</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>659</v>
+        <v>650</v>
       </c>
       <c r="C239" s="2">
         <v>14</v>
       </c>
       <c r="D239" s="2" t="s">
-        <v>702</v>
+        <v>693</v>
       </c>
       <c r="E239" s="2" t="s">
         <v>11</v>
@@ -33145,10 +32832,10 @@
         <v>12</v>
       </c>
       <c r="G239" s="3" t="s">
-        <v>703</v>
+        <v>694</v>
       </c>
       <c r="H239" s="3" t="s">
-        <v>704</v>
+        <v>695</v>
       </c>
     </row>
     <row r="240" spans="1:8" ht="43.2">
@@ -33156,13 +32843,13 @@
         <v>8</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>659</v>
+        <v>650</v>
       </c>
       <c r="C240" s="2">
         <v>15</v>
       </c>
       <c r="D240" s="2" t="s">
-        <v>705</v>
+        <v>696</v>
       </c>
       <c r="E240" s="2" t="s">
         <v>11</v>
@@ -33171,10 +32858,10 @@
         <v>12</v>
       </c>
       <c r="G240" s="3" t="s">
-        <v>706</v>
+        <v>697</v>
       </c>
       <c r="H240" s="3" t="s">
-        <v>707</v>
+        <v>698</v>
       </c>
     </row>
     <row r="241" spans="1:8" ht="115.2">
@@ -33182,13 +32869,13 @@
         <v>8</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>659</v>
+        <v>650</v>
       </c>
       <c r="C241" s="2">
         <v>16</v>
       </c>
       <c r="D241" s="2" t="s">
-        <v>708</v>
+        <v>699</v>
       </c>
       <c r="E241" s="2" t="s">
         <v>11</v>
@@ -33197,10 +32884,10 @@
         <v>12</v>
       </c>
       <c r="G241" s="3" t="s">
-        <v>709</v>
+        <v>700</v>
       </c>
       <c r="H241" s="3" t="s">
-        <v>710</v>
+        <v>701</v>
       </c>
     </row>
     <row r="242" spans="1:8" ht="129.6">
@@ -33208,13 +32895,13 @@
         <v>8</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>659</v>
+        <v>650</v>
       </c>
       <c r="C242" s="2">
         <v>17</v>
       </c>
       <c r="D242" s="2" t="s">
-        <v>711</v>
+        <v>702</v>
       </c>
       <c r="E242" s="2" t="s">
         <v>11</v>
@@ -33223,10 +32910,10 @@
         <v>12</v>
       </c>
       <c r="G242" s="3" t="s">
-        <v>712</v>
+        <v>703</v>
       </c>
       <c r="H242" s="3" t="s">
-        <v>713</v>
+        <v>704</v>
       </c>
     </row>
     <row r="243" spans="1:8" ht="129.6">
@@ -33234,13 +32921,13 @@
         <v>8</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>659</v>
+        <v>650</v>
       </c>
       <c r="C243" s="2">
         <v>18</v>
       </c>
       <c r="D243" s="2" t="s">
-        <v>714</v>
+        <v>705</v>
       </c>
       <c r="E243" s="2" t="s">
         <v>11</v>
@@ -33249,10 +32936,10 @@
         <v>12</v>
       </c>
       <c r="G243" s="3" t="s">
-        <v>715</v>
+        <v>706</v>
       </c>
       <c r="H243" s="3" t="s">
-        <v>716</v>
+        <v>707</v>
       </c>
     </row>
     <row r="244" spans="1:8" ht="100.8">
@@ -33260,13 +32947,13 @@
         <v>8</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>659</v>
+        <v>650</v>
       </c>
       <c r="C244" s="2">
         <v>19</v>
       </c>
       <c r="D244" s="2" t="s">
-        <v>717</v>
+        <v>708</v>
       </c>
       <c r="E244" s="2" t="s">
         <v>11</v>
@@ -33275,10 +32962,10 @@
         <v>12</v>
       </c>
       <c r="G244" s="3" t="s">
-        <v>718</v>
+        <v>709</v>
       </c>
       <c r="H244" s="3" t="s">
-        <v>719</v>
+        <v>710</v>
       </c>
     </row>
     <row r="245" spans="1:8" ht="86.4">
@@ -33286,13 +32973,13 @@
         <v>8</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>659</v>
+        <v>650</v>
       </c>
       <c r="C245" s="2">
         <v>20</v>
       </c>
       <c r="D245" s="2" t="s">
-        <v>720</v>
+        <v>711</v>
       </c>
       <c r="E245" s="2" t="s">
         <v>11</v>
@@ -33301,10 +32988,10 @@
         <v>12</v>
       </c>
       <c r="G245" s="3" t="s">
-        <v>721</v>
+        <v>712</v>
       </c>
       <c r="H245" s="3" t="s">
-        <v>722</v>
+        <v>713</v>
       </c>
     </row>
     <row r="246" spans="1:8" ht="216">
@@ -33312,13 +32999,13 @@
         <v>8</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>659</v>
+        <v>650</v>
       </c>
       <c r="C246" s="2">
         <v>21</v>
       </c>
       <c r="D246" s="2" t="s">
-        <v>723</v>
+        <v>714</v>
       </c>
       <c r="E246" s="2" t="s">
         <v>11</v>
@@ -33327,10 +33014,10 @@
         <v>12</v>
       </c>
       <c r="G246" s="3" t="s">
-        <v>724</v>
+        <v>715</v>
       </c>
       <c r="H246" s="3" t="s">
-        <v>725</v>
+        <v>716</v>
       </c>
     </row>
     <row r="247" spans="1:8" ht="100.8">
@@ -33338,13 +33025,13 @@
         <v>8</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>659</v>
+        <v>650</v>
       </c>
       <c r="C247" s="2">
         <v>22</v>
       </c>
       <c r="D247" s="2" t="s">
-        <v>726</v>
+        <v>717</v>
       </c>
       <c r="E247" s="2" t="s">
         <v>11</v>
@@ -33353,10 +33040,10 @@
         <v>12</v>
       </c>
       <c r="G247" s="3" t="s">
-        <v>727</v>
+        <v>718</v>
       </c>
       <c r="H247" s="3" t="s">
-        <v>728</v>
+        <v>719</v>
       </c>
     </row>
     <row r="248" spans="1:8" ht="187.2">
@@ -33364,13 +33051,13 @@
         <v>8</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>659</v>
+        <v>650</v>
       </c>
       <c r="C248" s="2">
         <v>23</v>
       </c>
       <c r="D248" s="2" t="s">
-        <v>729</v>
+        <v>720</v>
       </c>
       <c r="E248" s="2" t="s">
         <v>11</v>
@@ -33379,10 +33066,10 @@
         <v>12</v>
       </c>
       <c r="G248" s="3" t="s">
-        <v>730</v>
+        <v>721</v>
       </c>
       <c r="H248" s="3" t="s">
-        <v>731</v>
+        <v>722</v>
       </c>
     </row>
     <row r="249" spans="1:8" ht="28.8">
@@ -33390,13 +33077,13 @@
         <v>8</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>659</v>
+        <v>650</v>
       </c>
       <c r="C249" s="2">
         <v>24</v>
       </c>
       <c r="D249" s="2" t="s">
-        <v>732</v>
+        <v>723</v>
       </c>
       <c r="E249" s="2" t="s">
         <v>11</v>
@@ -33405,10 +33092,10 @@
         <v>12</v>
       </c>
       <c r="G249" s="3" t="s">
-        <v>733</v>
+        <v>724</v>
       </c>
       <c r="H249" s="4" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
     </row>
     <row r="250" spans="1:8" ht="43.2">
@@ -33416,13 +33103,13 @@
         <v>8</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>659</v>
+        <v>650</v>
       </c>
       <c r="C250" s="2">
         <v>25</v>
       </c>
       <c r="D250" s="2" t="s">
-        <v>735</v>
+        <v>726</v>
       </c>
       <c r="E250" s="2" t="s">
         <v>11</v>
@@ -33431,10 +33118,10 @@
         <v>12</v>
       </c>
       <c r="G250" s="3" t="s">
-        <v>736</v>
+        <v>727</v>
       </c>
       <c r="H250" s="3" t="s">
-        <v>737</v>
+        <v>728</v>
       </c>
     </row>
     <row r="251" spans="1:8" ht="43.2">
@@ -33442,13 +33129,13 @@
         <v>8</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>659</v>
+        <v>650</v>
       </c>
       <c r="C251" s="2">
         <v>26</v>
       </c>
       <c r="D251" s="2" t="s">
-        <v>738</v>
+        <v>729</v>
       </c>
       <c r="E251" s="2" t="s">
         <v>11</v>
@@ -33457,10 +33144,10 @@
         <v>12</v>
       </c>
       <c r="G251" s="3" t="s">
-        <v>739</v>
+        <v>730</v>
       </c>
       <c r="H251" s="3" t="s">
-        <v>740</v>
+        <v>731</v>
       </c>
     </row>
     <row r="252" spans="1:8" ht="43.2">
@@ -33468,13 +33155,13 @@
         <v>8</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>659</v>
+        <v>650</v>
       </c>
       <c r="C252" s="2">
         <v>27</v>
       </c>
       <c r="D252" s="2" t="s">
-        <v>741</v>
+        <v>732</v>
       </c>
       <c r="E252" s="2" t="s">
         <v>11</v>
@@ -33483,10 +33170,10 @@
         <v>12</v>
       </c>
       <c r="G252" s="3" t="s">
-        <v>742</v>
+        <v>733</v>
       </c>
       <c r="H252" s="3" t="s">
-        <v>743</v>
+        <v>734</v>
       </c>
     </row>
     <row r="253" spans="1:8">
@@ -33494,13 +33181,13 @@
         <v>8</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>744</v>
+        <v>735</v>
       </c>
       <c r="C253" s="2">
         <v>0</v>
       </c>
       <c r="D253" s="2" t="s">
-        <v>745</v>
+        <v>736</v>
       </c>
       <c r="E253" s="2" t="s">
         <v>11</v>
@@ -33509,10 +33196,10 @@
         <v>12</v>
       </c>
       <c r="G253" s="3" t="s">
-        <v>746</v>
+        <v>737</v>
       </c>
       <c r="H253" s="4" t="s">
-        <v>747</v>
+        <v>738</v>
       </c>
     </row>
     <row r="254" spans="1:8" ht="100.8">
@@ -33520,13 +33207,13 @@
         <v>8</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>744</v>
+        <v>735</v>
       </c>
       <c r="C254" s="2">
         <v>2</v>
       </c>
       <c r="D254" s="2" t="s">
-        <v>748</v>
+        <v>739</v>
       </c>
       <c r="E254" s="2" t="s">
         <v>11</v>
@@ -33535,10 +33222,10 @@
         <v>12</v>
       </c>
       <c r="G254" s="3" t="s">
-        <v>749</v>
+        <v>740</v>
       </c>
       <c r="H254" s="3" t="s">
-        <v>750</v>
+        <v>741</v>
       </c>
     </row>
     <row r="255" spans="1:8">
@@ -33546,13 +33233,13 @@
         <v>8</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>751</v>
+        <v>742</v>
       </c>
       <c r="C255" s="2">
         <v>0</v>
       </c>
       <c r="D255" s="2" t="s">
-        <v>752</v>
+        <v>743</v>
       </c>
       <c r="E255" s="2" t="s">
         <v>11</v>
@@ -33561,10 +33248,10 @@
         <v>12</v>
       </c>
       <c r="G255" s="3" t="s">
-        <v>753</v>
+        <v>744</v>
       </c>
       <c r="H255" s="4" t="s">
-        <v>754</v>
+        <v>745</v>
       </c>
     </row>
     <row r="256" spans="1:8">
@@ -33572,13 +33259,13 @@
         <v>8</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>755</v>
+        <v>746</v>
       </c>
       <c r="C256" s="2">
         <v>0</v>
       </c>
       <c r="D256" s="2" t="s">
-        <v>756</v>
+        <v>747</v>
       </c>
       <c r="E256" s="2" t="s">
         <v>11</v>
@@ -33587,10 +33274,10 @@
         <v>12</v>
       </c>
       <c r="G256" s="3" t="s">
-        <v>757</v>
+        <v>748</v>
       </c>
       <c r="H256" s="4" t="s">
-        <v>758</v>
+        <v>749</v>
       </c>
     </row>
     <row r="257" spans="1:8" ht="28.8">
@@ -33598,13 +33285,13 @@
         <v>8</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>759</v>
+        <v>750</v>
       </c>
       <c r="C257" s="2">
         <v>0</v>
       </c>
       <c r="D257" s="2" t="s">
-        <v>760</v>
+        <v>751</v>
       </c>
       <c r="E257" s="2" t="s">
         <v>11</v>
@@ -33613,10 +33300,10 @@
         <v>12</v>
       </c>
       <c r="G257" s="3" t="s">
-        <v>761</v>
+        <v>752</v>
       </c>
       <c r="H257" s="3" t="s">
-        <v>762</v>
+        <v>753</v>
       </c>
     </row>
     <row r="258" spans="1:8" ht="43.2">
@@ -33624,13 +33311,13 @@
         <v>8</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>759</v>
+        <v>750</v>
       </c>
       <c r="C258" s="2">
         <v>1</v>
       </c>
       <c r="D258" s="2" t="s">
-        <v>763</v>
+        <v>754</v>
       </c>
       <c r="E258" s="2" t="s">
         <v>11</v>
@@ -33639,10 +33326,10 @@
         <v>12</v>
       </c>
       <c r="G258" s="3" t="s">
-        <v>764</v>
+        <v>755</v>
       </c>
       <c r="H258" s="3" t="s">
-        <v>765</v>
+        <v>756</v>
       </c>
     </row>
     <row r="259" spans="1:8" ht="100.8">
@@ -33650,13 +33337,13 @@
         <v>8</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>759</v>
+        <v>750</v>
       </c>
       <c r="C259" s="2">
         <v>2</v>
       </c>
       <c r="D259" s="2" t="s">
-        <v>766</v>
+        <v>757</v>
       </c>
       <c r="E259" s="2" t="s">
         <v>11</v>
@@ -33665,10 +33352,10 @@
         <v>12</v>
       </c>
       <c r="G259" s="3" t="s">
-        <v>767</v>
+        <v>758</v>
       </c>
       <c r="H259" s="3" t="s">
-        <v>768</v>
+        <v>759</v>
       </c>
     </row>
     <row r="260" spans="1:8" ht="43.2">
@@ -33676,13 +33363,13 @@
         <v>8</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>759</v>
+        <v>750</v>
       </c>
       <c r="C260" s="2">
         <v>3</v>
       </c>
       <c r="D260" s="2" t="s">
-        <v>769</v>
+        <v>760</v>
       </c>
       <c r="E260" s="2" t="s">
         <v>11</v>
@@ -33691,10 +33378,10 @@
         <v>12</v>
       </c>
       <c r="G260" s="3" t="s">
-        <v>770</v>
+        <v>761</v>
       </c>
       <c r="H260" s="3" t="s">
-        <v>771</v>
+        <v>762</v>
       </c>
     </row>
     <row r="261" spans="1:8">
@@ -33702,13 +33389,13 @@
         <v>8</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>772</v>
+        <v>763</v>
       </c>
       <c r="C261" s="2">
         <v>0</v>
       </c>
       <c r="D261" s="2" t="s">
-        <v>773</v>
+        <v>764</v>
       </c>
       <c r="E261" s="2" t="s">
         <v>11</v>
@@ -33717,10 +33404,10 @@
         <v>12</v>
       </c>
       <c r="G261" s="3" t="s">
-        <v>774</v>
+        <v>765</v>
       </c>
       <c r="H261" s="4" t="s">
-        <v>775</v>
+        <v>766</v>
       </c>
     </row>
     <row r="262" spans="1:8">
@@ -33728,13 +33415,13 @@
         <v>8</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>776</v>
+        <v>767</v>
       </c>
       <c r="C262" s="2">
         <v>0</v>
       </c>
       <c r="D262" s="2" t="s">
-        <v>777</v>
+        <v>768</v>
       </c>
       <c r="E262" s="2" t="s">
         <v>11</v>
@@ -33743,10 +33430,10 @@
         <v>12</v>
       </c>
       <c r="G262" s="3" t="s">
-        <v>778</v>
+        <v>769</v>
       </c>
       <c r="H262" s="4" t="s">
-        <v>779</v>
+        <v>770</v>
       </c>
     </row>
     <row r="263" spans="1:8">
@@ -33754,13 +33441,13 @@
         <v>8</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>780</v>
+        <v>771</v>
       </c>
       <c r="C263" s="2">
         <v>0</v>
       </c>
       <c r="D263" s="2" t="s">
-        <v>781</v>
+        <v>772</v>
       </c>
       <c r="E263" s="2" t="s">
         <v>11</v>
@@ -33769,10 +33456,10 @@
         <v>12</v>
       </c>
       <c r="G263" s="3" t="s">
-        <v>782</v>
+        <v>773</v>
       </c>
       <c r="H263" s="4" t="s">
-        <v>783</v>
+        <v>774</v>
       </c>
     </row>
     <row r="264" spans="1:8">
@@ -33780,13 +33467,13 @@
         <v>8</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>780</v>
+        <v>771</v>
       </c>
       <c r="C264" s="2">
         <v>1</v>
       </c>
       <c r="D264" s="2" t="s">
-        <v>784</v>
+        <v>775</v>
       </c>
       <c r="E264" s="2" t="s">
         <v>11</v>
@@ -33795,10 +33482,10 @@
         <v>12</v>
       </c>
       <c r="G264" s="3" t="s">
-        <v>785</v>
+        <v>776</v>
       </c>
       <c r="H264" s="4" t="s">
-        <v>786</v>
+        <v>777</v>
       </c>
     </row>
     <row r="265" spans="1:8" ht="28.8">
@@ -33806,13 +33493,13 @@
         <v>8</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>787</v>
+        <v>778</v>
       </c>
       <c r="C265" s="2">
         <v>0</v>
       </c>
       <c r="D265" s="2" t="s">
-        <v>788</v>
+        <v>779</v>
       </c>
       <c r="E265" s="2" t="s">
         <v>11</v>
@@ -33821,14 +33508,14 @@
         <v>12</v>
       </c>
       <c r="G265" s="3" t="s">
-        <v>789</v>
+        <v>780</v>
       </c>
       <c r="H265" s="4" t="s">
-        <v>790</v>
+        <v>781</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/docassemble/PowerOfAttorneyProperty/data/sources/poa_property_es.xlsx
+++ b/docassemble/PowerOfAttorneyProperty/data/sources/poa_property_es.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mnewsted\local-DA-easyforms-dev\sources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1B12DC0-F368-4826-A16B-EA88C483B0D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9495667D-5045-4CC4-97C3-7A3E412DCFAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11942,94 +11942,6 @@
     <t>59f97fe5b9ca4961f0d468f1bb28401e</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">They can create a Power of Attorney Revocation to end a Power of Attorney.
-To make a Power of Attorney Revocation, use ILAO's </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[**Power of Attorney Revocation Easy Form**]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>https://www.illinoislegalaid.org/legal-information/power-attorney-revocation</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">).
-</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Pueden crear una Revocación de Poder para terminar un poder.
-Para hacer una Revocación de Poder, use el </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[Power of Attorney Revocation Easy Form]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> de ILAO.</t>
-    </r>
-  </si>
-  <si>
     <t>10b1c7c68ea5ce648fe1552ca8cafebc</t>
   </si>
   <si>
@@ -26198,6 +26110,38 @@
       </rPr>
       <t>% endif</t>
     </r>
+  </si>
+  <si>
+    <r>
+      <t>They can create a Power of Attorney Revocation to end a Power of Attorney.
+To make a Power of Attorney Revocation, use ILAO's [**Power of Attorney Revocation Easy Form**](</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>https://www.illinoislegalaid.org/legal-information/power-attorney-revocation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">).
+</t>
+    </r>
+  </si>
+  <si>
+    <t>Pueden crear una Revocación de Poder para terminar un poder.
+Para hacer una Revocación de Poder, use el [**Formulario Fácil de Revocación de Poder Notarial**](https://es.illinoislegalaid.org/legal-information/power-attorney-revocation) de ILAO].</t>
   </si>
 </sst>
 </file>
@@ -26673,7 +26617,7 @@
         <v>13</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="403.2">
@@ -26687,7 +26631,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>11</v>
@@ -26696,10 +26640,10 @@
         <v>12</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="187.2">
@@ -26725,7 +26669,7 @@
         <v>16</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="28.8">
@@ -26751,7 +26695,7 @@
         <v>19</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="302.39999999999998">
@@ -26777,7 +26721,7 @@
         <v>21</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -26803,7 +26747,7 @@
         <v>24</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="72">
@@ -26829,7 +26773,7 @@
         <v>26</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -26855,7 +26799,7 @@
         <v>28</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="43.2">
@@ -26881,7 +26825,7 @@
         <v>30</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="28.8">
@@ -26933,7 +26877,7 @@
         <v>35</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="43.2">
@@ -26959,7 +26903,7 @@
         <v>38</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="43.2">
@@ -26985,7 +26929,7 @@
         <v>40</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="86.4">
@@ -27011,7 +26955,7 @@
         <v>43</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="115.2">
@@ -27037,7 +26981,7 @@
         <v>46</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="28.8">
@@ -27089,7 +27033,7 @@
         <v>52</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="273.60000000000002">
@@ -27115,7 +27059,7 @@
         <v>54</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="28.8">
@@ -27141,7 +27085,7 @@
         <v>57</v>
       </c>
       <c r="H20" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="129.6">
@@ -27167,7 +27111,7 @@
         <v>59</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -27193,7 +27137,7 @@
         <v>62</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="43.2">
@@ -27219,7 +27163,7 @@
         <v>64</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="72">
@@ -27245,7 +27189,7 @@
         <v>66</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="28.8">
@@ -27271,7 +27215,7 @@
         <v>68</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="57.6">
@@ -27297,7 +27241,7 @@
         <v>70</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -27323,7 +27267,7 @@
         <v>72</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -27349,7 +27293,7 @@
         <v>74</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="28.8">
@@ -27375,7 +27319,7 @@
         <v>77</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="259.2">
@@ -27401,7 +27345,7 @@
         <v>79</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="86.4">
@@ -27427,7 +27371,7 @@
         <v>82</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="403.2">
@@ -27453,7 +27397,7 @@
         <v>84</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -27479,7 +27423,7 @@
         <v>86</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -27505,7 +27449,7 @@
         <v>88</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -27531,7 +27475,7 @@
         <v>90</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -27557,7 +27501,7 @@
         <v>92</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -27609,7 +27553,7 @@
         <v>97</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="115.2">
@@ -27635,7 +27579,7 @@
         <v>100</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="28.8">
@@ -27661,7 +27605,7 @@
         <v>102</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="28.8">
@@ -27687,7 +27631,7 @@
         <v>105</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="86.4">
@@ -27713,7 +27657,7 @@
         <v>108</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="28.8">
@@ -27739,7 +27683,7 @@
         <v>111</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="144">
@@ -27791,7 +27735,7 @@
         <v>117</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="86.4">
@@ -27817,7 +27761,7 @@
         <v>120</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="86.4">
@@ -27843,7 +27787,7 @@
         <v>123</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="345.6">
@@ -27869,7 +27813,7 @@
         <v>125</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="28.8">
@@ -27895,7 +27839,7 @@
         <v>128</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="28.8">
@@ -27947,7 +27891,7 @@
         <v>133</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="43.2">
@@ -27973,7 +27917,7 @@
         <v>135</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
     </row>
     <row r="53" spans="1:8">
@@ -27999,7 +27943,7 @@
         <v>137</v>
       </c>
       <c r="H53" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
     </row>
     <row r="54" spans="1:8">
@@ -28025,7 +27969,7 @@
         <v>139</v>
       </c>
       <c r="H54" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="129.6">
@@ -28051,7 +27995,7 @@
         <v>142</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="28.8">
@@ -28077,7 +28021,7 @@
         <v>144</v>
       </c>
       <c r="H56" s="4" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="28.8">
@@ -28129,7 +28073,7 @@
         <v>150</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="115.2">
@@ -28155,7 +28099,7 @@
         <v>153</v>
       </c>
       <c r="H59" s="5" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="28.8">
@@ -28207,7 +28151,7 @@
         <v>159</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="244.8">
@@ -28233,7 +28177,7 @@
         <v>161</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
     </row>
     <row r="63" spans="1:8">
@@ -28259,7 +28203,7 @@
         <v>163</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
     </row>
     <row r="64" spans="1:8">
@@ -28285,7 +28229,7 @@
         <v>165</v>
       </c>
       <c r="H64" s="4" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="43.2">
@@ -28337,7 +28281,7 @@
         <v>170</v>
       </c>
       <c r="H66" s="4" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="43.2">
@@ -28363,7 +28307,7 @@
         <v>172</v>
       </c>
       <c r="H67" s="4" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
     </row>
     <row r="68" spans="1:8">
@@ -28415,7 +28359,7 @@
         <v>177</v>
       </c>
       <c r="H69" s="4" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
     </row>
     <row r="70" spans="1:8">
@@ -28441,7 +28385,7 @@
         <v>179</v>
       </c>
       <c r="H70" s="4" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="72">
@@ -28467,7 +28411,7 @@
         <v>181</v>
       </c>
       <c r="H71" s="4" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
     </row>
     <row r="72" spans="1:8">
@@ -28493,7 +28437,7 @@
         <v>183</v>
       </c>
       <c r="H72" s="4" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="43.2">
@@ -28519,7 +28463,7 @@
         <v>185</v>
       </c>
       <c r="H73" s="4" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -28571,7 +28515,7 @@
         <v>190</v>
       </c>
       <c r="H75" s="4" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
     </row>
     <row r="76" spans="1:8">
@@ -28597,7 +28541,7 @@
         <v>192</v>
       </c>
       <c r="H76" s="4" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
     </row>
     <row r="77" spans="1:8" ht="43.2">
@@ -28623,7 +28567,7 @@
         <v>194</v>
       </c>
       <c r="H77" s="4" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="78" spans="1:8">
@@ -28649,7 +28593,7 @@
         <v>196</v>
       </c>
       <c r="H78" s="4" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
     </row>
     <row r="79" spans="1:8" ht="57.6">
@@ -28675,7 +28619,7 @@
         <v>198</v>
       </c>
       <c r="H79" s="4" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
     </row>
     <row r="80" spans="1:8">
@@ -28727,7 +28671,7 @@
         <v>203</v>
       </c>
       <c r="H81" s="4" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
     </row>
     <row r="82" spans="1:8">
@@ -28779,7 +28723,7 @@
         <v>208</v>
       </c>
       <c r="H83" s="4" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
     </row>
     <row r="84" spans="1:8">
@@ -28831,7 +28775,7 @@
         <v>213</v>
       </c>
       <c r="H85" s="4" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
     <row r="86" spans="1:8">
@@ -28883,7 +28827,7 @@
         <v>218</v>
       </c>
       <c r="H87" s="4" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
     </row>
     <row r="88" spans="1:8">
@@ -28935,7 +28879,7 @@
         <v>223</v>
       </c>
       <c r="H89" s="4" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
     </row>
     <row r="90" spans="1:8">
@@ -28961,7 +28905,7 @@
         <v>225</v>
       </c>
       <c r="H90" s="4" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
     </row>
     <row r="91" spans="1:8" ht="43.2">
@@ -28987,7 +28931,7 @@
         <v>227</v>
       </c>
       <c r="H91" s="4" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
     </row>
     <row r="92" spans="1:8">
@@ -29039,7 +28983,7 @@
         <v>232</v>
       </c>
       <c r="H93" s="4" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
     </row>
     <row r="94" spans="1:8">
@@ -29091,7 +29035,7 @@
         <v>238</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
     </row>
     <row r="96" spans="1:8" ht="100.8">
@@ -29117,7 +29061,7 @@
         <v>241</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
     </row>
     <row r="97" spans="1:8" ht="115.2">
@@ -29143,7 +29087,7 @@
         <v>244</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
     </row>
     <row r="98" spans="1:8" ht="259.2">
@@ -29169,7 +29113,7 @@
         <v>246</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
     </row>
     <row r="99" spans="1:8" ht="28.8">
@@ -29221,7 +29165,7 @@
         <v>252</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
     </row>
     <row r="101" spans="1:8" ht="86.4">
@@ -30703,7 +30647,7 @@
         <v>433</v>
       </c>
       <c r="H157" s="4" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
     </row>
     <row r="158" spans="1:8">
@@ -30807,7 +30751,7 @@
         <v>444</v>
       </c>
       <c r="H161" s="3" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
     </row>
     <row r="162" spans="1:8" ht="86.4">
@@ -31015,7 +30959,7 @@
         <v>471</v>
       </c>
       <c r="H169" s="3" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
     </row>
     <row r="170" spans="1:8" ht="28.8">
@@ -31119,7 +31063,7 @@
         <v>484</v>
       </c>
       <c r="H173" s="5" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
     </row>
     <row r="174" spans="1:8" ht="28.8">
@@ -31145,7 +31089,7 @@
         <v>486</v>
       </c>
       <c r="H174" s="4" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
     </row>
     <row r="175" spans="1:8">
@@ -31301,7 +31245,7 @@
         <v>504</v>
       </c>
       <c r="H180" s="3" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
     </row>
     <row r="181" spans="1:8">
@@ -31535,7 +31479,7 @@
         <v>531</v>
       </c>
       <c r="H189" s="4" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
     </row>
     <row r="190" spans="1:8" ht="115.2">
@@ -31561,7 +31505,7 @@
         <v>534</v>
       </c>
       <c r="H190" s="3" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
     </row>
     <row r="191" spans="1:8" ht="28.8">
@@ -31636,10 +31580,10 @@
         <v>12</v>
       </c>
       <c r="G193" s="3" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="H193" s="3" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
     </row>
     <row r="194" spans="1:8" ht="86.4">
@@ -31662,10 +31606,10 @@
         <v>12</v>
       </c>
       <c r="G194" s="3" t="s">
-        <v>545</v>
-      </c>
-      <c r="H194" s="3" t="s">
-        <v>546</v>
+        <v>872</v>
+      </c>
+      <c r="H194" s="4" t="s">
+        <v>873</v>
       </c>
     </row>
     <row r="195" spans="1:8" ht="28.8">
@@ -31679,7 +31623,7 @@
         <v>1</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="E195" s="2" t="s">
         <v>11</v>
@@ -31688,10 +31632,10 @@
         <v>12</v>
       </c>
       <c r="G195" s="3" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="H195" s="4" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
     </row>
     <row r="196" spans="1:8" ht="86.4">
@@ -31699,13 +31643,13 @@
         <v>8</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="C196" s="2">
         <v>0</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="E196" s="2" t="s">
         <v>11</v>
@@ -31714,10 +31658,10 @@
         <v>12</v>
       </c>
       <c r="G196" s="3" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="H196" s="3" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
     </row>
     <row r="197" spans="1:8" ht="201.6">
@@ -31725,13 +31669,13 @@
         <v>8</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="C197" s="2">
         <v>1</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="E197" s="2" t="s">
         <v>11</v>
@@ -31740,10 +31684,10 @@
         <v>12</v>
       </c>
       <c r="G197" s="3" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="H197" s="3" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="198" spans="1:8" ht="28.8">
@@ -31751,13 +31695,13 @@
         <v>8</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="C198" s="2">
         <v>2</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="E198" s="2" t="s">
         <v>11</v>
@@ -31766,10 +31710,10 @@
         <v>12</v>
       </c>
       <c r="G198" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="H198" s="3" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
     </row>
     <row r="199" spans="1:8">
@@ -31777,13 +31721,13 @@
         <v>8</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="C199" s="2">
         <v>3</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="E199" s="2" t="s">
         <v>11</v>
@@ -31792,10 +31736,10 @@
         <v>12</v>
       </c>
       <c r="G199" s="3" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="H199" s="3" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
     </row>
     <row r="200" spans="1:8" ht="100.8">
@@ -31803,13 +31747,13 @@
         <v>8</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="C200" s="2">
         <v>4</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="E200" s="2" t="s">
         <v>11</v>
@@ -31818,10 +31762,10 @@
         <v>12</v>
       </c>
       <c r="G200" s="3" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="H200" s="4" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
     </row>
     <row r="201" spans="1:8" ht="28.8">
@@ -31829,13 +31773,13 @@
         <v>8</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="C201" s="2">
         <v>5</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="E201" s="2" t="s">
         <v>11</v>
@@ -31844,10 +31788,10 @@
         <v>12</v>
       </c>
       <c r="G201" s="3" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="H201" s="3" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
     </row>
     <row r="202" spans="1:8">
@@ -31855,13 +31799,13 @@
         <v>8</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="C202" s="2">
         <v>6</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="E202" s="2" t="s">
         <v>11</v>
@@ -31870,10 +31814,10 @@
         <v>12</v>
       </c>
       <c r="G202" s="3" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="H202" s="4" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
     </row>
     <row r="203" spans="1:8">
@@ -31881,13 +31825,13 @@
         <v>8</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="C203" s="2">
         <v>7</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="E203" s="2" t="s">
         <v>11</v>
@@ -31896,10 +31840,10 @@
         <v>12</v>
       </c>
       <c r="G203" s="3" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="H203" s="4" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
     </row>
     <row r="204" spans="1:8" ht="100.8">
@@ -31907,13 +31851,13 @@
         <v>8</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="C204" s="2">
         <v>0</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="E204" s="2" t="s">
         <v>11</v>
@@ -31922,10 +31866,10 @@
         <v>12</v>
       </c>
       <c r="G204" s="3" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="H204" s="3" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
     </row>
     <row r="205" spans="1:8" ht="244.8">
@@ -31933,13 +31877,13 @@
         <v>8</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="C205" s="2">
         <v>1</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="E205" s="2" t="s">
         <v>11</v>
@@ -31948,10 +31892,10 @@
         <v>12</v>
       </c>
       <c r="G205" s="3" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="H205" s="3" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
     </row>
     <row r="206" spans="1:8" ht="28.8">
@@ -31959,13 +31903,13 @@
         <v>8</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="C206" s="2">
         <v>0</v>
       </c>
       <c r="D206" s="2" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="E206" s="2" t="s">
         <v>11</v>
@@ -31974,10 +31918,10 @@
         <v>12</v>
       </c>
       <c r="G206" s="3" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="H206" s="4" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
     </row>
     <row r="207" spans="1:8" ht="43.2">
@@ -31985,13 +31929,13 @@
         <v>8</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="C207" s="2">
         <v>1</v>
       </c>
       <c r="D207" s="2" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="E207" s="2" t="s">
         <v>11</v>
@@ -32000,10 +31944,10 @@
         <v>12</v>
       </c>
       <c r="G207" s="3" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="H207" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="208" spans="1:8" ht="28.8">
@@ -32011,13 +31955,13 @@
         <v>8</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="C208" s="2">
         <v>0</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="E208" s="2" t="s">
         <v>11</v>
@@ -32026,10 +31970,10 @@
         <v>12</v>
       </c>
       <c r="G208" s="3" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="H208" s="4" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
     </row>
     <row r="209" spans="1:8" ht="28.8">
@@ -32037,13 +31981,13 @@
         <v>8</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="C209" s="2">
         <v>0</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="E209" s="2" t="s">
         <v>11</v>
@@ -32052,10 +31996,10 @@
         <v>12</v>
       </c>
       <c r="G209" s="3" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="H209" s="4" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
     </row>
     <row r="210" spans="1:8" ht="28.8">
@@ -32063,13 +32007,13 @@
         <v>8</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="C210" s="2">
         <v>1</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="E210" s="2" t="s">
         <v>11</v>
@@ -32078,10 +32022,10 @@
         <v>12</v>
       </c>
       <c r="G210" s="3" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="H210" s="4" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
     </row>
     <row r="211" spans="1:8" ht="28.8">
@@ -32089,13 +32033,13 @@
         <v>8</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="C211" s="2">
         <v>0</v>
       </c>
       <c r="D211" s="2" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E211" s="2" t="s">
         <v>11</v>
@@ -32104,10 +32048,10 @@
         <v>12</v>
       </c>
       <c r="G211" s="3" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="H211" s="4" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
     </row>
     <row r="212" spans="1:8" ht="409.6">
@@ -32115,13 +32059,13 @@
         <v>8</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="C212" s="2">
         <v>1</v>
       </c>
       <c r="D212" s="2" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="E212" s="2" t="s">
         <v>11</v>
@@ -32130,10 +32074,10 @@
         <v>12</v>
       </c>
       <c r="G212" s="3" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="H212" s="3" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
     </row>
     <row r="213" spans="1:8" ht="86.4">
@@ -32141,13 +32085,13 @@
         <v>8</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="C213" s="2">
         <v>0</v>
       </c>
       <c r="D213" s="2" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="E213" s="2" t="s">
         <v>11</v>
@@ -32156,10 +32100,10 @@
         <v>12</v>
       </c>
       <c r="G213" s="3" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="H213" s="4" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="214" spans="1:8" ht="86.4">
@@ -32167,13 +32111,13 @@
         <v>8</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="C214" s="2">
         <v>1</v>
       </c>
       <c r="D214" s="2" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="E214" s="2" t="s">
         <v>11</v>
@@ -32182,10 +32126,10 @@
         <v>12</v>
       </c>
       <c r="G214" s="3" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="H214" s="3" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
     </row>
     <row r="215" spans="1:8" ht="28.8">
@@ -32193,13 +32137,13 @@
         <v>8</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="C215" s="2">
         <v>0</v>
       </c>
       <c r="D215" s="2" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="E215" s="2" t="s">
         <v>11</v>
@@ -32208,10 +32152,10 @@
         <v>12</v>
       </c>
       <c r="G215" s="3" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="H215" s="4" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="216" spans="1:8" ht="403.2">
@@ -32219,13 +32163,13 @@
         <v>8</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="C216" s="2">
         <v>1</v>
       </c>
       <c r="D216" s="2" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="E216" s="2" t="s">
         <v>11</v>
@@ -32234,10 +32178,10 @@
         <v>12</v>
       </c>
       <c r="G216" s="3" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="H216" s="3" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="217" spans="1:8" ht="187.2">
@@ -32245,13 +32189,13 @@
         <v>8</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="C217" s="2">
         <v>2</v>
       </c>
       <c r="D217" s="2" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="E217" s="2" t="s">
         <v>11</v>
@@ -32260,10 +32204,10 @@
         <v>12</v>
       </c>
       <c r="G217" s="3" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="H217" s="3" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
     </row>
     <row r="218" spans="1:8" ht="86.4">
@@ -32271,13 +32215,13 @@
         <v>8</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="C218" s="2">
         <v>0</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="E218" s="2" t="s">
         <v>11</v>
@@ -32286,10 +32230,10 @@
         <v>12</v>
       </c>
       <c r="G218" s="3" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="H218" s="3" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
     </row>
     <row r="219" spans="1:8">
@@ -32297,13 +32241,13 @@
         <v>8</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="C219" s="2">
         <v>1</v>
       </c>
       <c r="D219" s="2" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="E219" s="2" t="s">
         <v>11</v>
@@ -32315,7 +32259,7 @@
         <v>22</v>
       </c>
       <c r="H219" s="4" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
     </row>
     <row r="220" spans="1:8">
@@ -32323,13 +32267,13 @@
         <v>8</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="C220" s="2">
         <v>0</v>
       </c>
       <c r="D220" s="2" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="E220" s="2" t="s">
         <v>11</v>
@@ -32338,10 +32282,10 @@
         <v>12</v>
       </c>
       <c r="G220" s="3" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="H220" s="4" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
     </row>
     <row r="221" spans="1:8">
@@ -32349,13 +32293,13 @@
         <v>8</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="C221" s="2">
         <v>0</v>
       </c>
       <c r="D221" s="2" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="E221" s="2" t="s">
         <v>11</v>
@@ -32364,10 +32308,10 @@
         <v>12</v>
       </c>
       <c r="G221" s="3" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="H221" s="4" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
     </row>
     <row r="222" spans="1:8">
@@ -32375,13 +32319,13 @@
         <v>8</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="C222" s="2">
         <v>0</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="E222" s="2" t="s">
         <v>11</v>
@@ -32390,10 +32334,10 @@
         <v>12</v>
       </c>
       <c r="G222" s="3" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="H222" s="4" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
     </row>
     <row r="223" spans="1:8">
@@ -32401,13 +32345,13 @@
         <v>8</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="C223" s="2">
         <v>0</v>
       </c>
       <c r="D223" s="2" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="E223" s="2" t="s">
         <v>11</v>
@@ -32416,10 +32360,10 @@
         <v>12</v>
       </c>
       <c r="G223" s="3" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="H223" s="4" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
     </row>
     <row r="224" spans="1:8">
@@ -32427,13 +32371,13 @@
         <v>8</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="C224" s="2">
         <v>0</v>
       </c>
       <c r="D224" s="2" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="E224" s="2" t="s">
         <v>11</v>
@@ -32442,10 +32386,10 @@
         <v>12</v>
       </c>
       <c r="G224" s="3" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="H224" s="4" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
     </row>
     <row r="225" spans="1:8" ht="28.8">
@@ -32453,13 +32397,13 @@
         <v>8</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="C225" s="2">
         <v>0</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="E225" s="2" t="s">
         <v>11</v>
@@ -32468,10 +32412,10 @@
         <v>12</v>
       </c>
       <c r="G225" s="3" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="H225" s="4" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
     </row>
     <row r="226" spans="1:8" ht="28.8">
@@ -32479,13 +32423,13 @@
         <v>8</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="C226" s="2">
         <v>1</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="E226" s="2" t="s">
         <v>11</v>
@@ -32494,10 +32438,10 @@
         <v>12</v>
       </c>
       <c r="G226" s="3" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="H226" s="4" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
     </row>
     <row r="227" spans="1:8">
@@ -32505,13 +32449,13 @@
         <v>8</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="C227" s="2">
         <v>2</v>
       </c>
       <c r="D227" s="2" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="E227" s="2" t="s">
         <v>11</v>
@@ -32520,10 +32464,10 @@
         <v>12</v>
       </c>
       <c r="G227" s="3" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="H227" s="4" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
     </row>
     <row r="228" spans="1:8" ht="100.8">
@@ -32531,13 +32475,13 @@
         <v>8</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="C228" s="2">
         <v>3</v>
       </c>
       <c r="D228" s="2" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="E228" s="2" t="s">
         <v>11</v>
@@ -32546,10 +32490,10 @@
         <v>12</v>
       </c>
       <c r="G228" s="3" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="H228" s="3" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="229" spans="1:8" ht="187.2">
@@ -32557,13 +32501,13 @@
         <v>8</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="C229" s="2">
         <v>4</v>
       </c>
       <c r="D229" s="2" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="E229" s="2" t="s">
         <v>11</v>
@@ -32572,10 +32516,10 @@
         <v>12</v>
       </c>
       <c r="G229" s="3" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="H229" s="3" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
     </row>
     <row r="230" spans="1:8" ht="100.8">
@@ -32583,13 +32527,13 @@
         <v>8</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="C230" s="2">
         <v>5</v>
       </c>
       <c r="D230" s="2" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="E230" s="2" t="s">
         <v>11</v>
@@ -32598,10 +32542,10 @@
         <v>12</v>
       </c>
       <c r="G230" s="3" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="H230" s="3" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
     </row>
     <row r="231" spans="1:8" ht="100.8">
@@ -32609,13 +32553,13 @@
         <v>8</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="C231" s="2">
         <v>6</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="E231" s="2" t="s">
         <v>11</v>
@@ -32624,10 +32568,10 @@
         <v>12</v>
       </c>
       <c r="G231" s="3" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="H231" s="3" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
     </row>
     <row r="232" spans="1:8" ht="43.2">
@@ -32635,13 +32579,13 @@
         <v>8</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="C232" s="2">
         <v>7</v>
       </c>
       <c r="D232" s="2" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="E232" s="2" t="s">
         <v>11</v>
@@ -32650,10 +32594,10 @@
         <v>12</v>
       </c>
       <c r="G232" s="3" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="H232" s="3" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
     </row>
     <row r="233" spans="1:8" ht="100.8">
@@ -32661,13 +32605,13 @@
         <v>8</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="C233" s="2">
         <v>8</v>
       </c>
       <c r="D233" s="2" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="E233" s="2" t="s">
         <v>11</v>
@@ -32676,10 +32620,10 @@
         <v>12</v>
       </c>
       <c r="G233" s="3" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="H233" s="3" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
     </row>
     <row r="234" spans="1:8" ht="43.2">
@@ -32687,13 +32631,13 @@
         <v>8</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="C234" s="2">
         <v>9</v>
       </c>
       <c r="D234" s="2" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="E234" s="2" t="s">
         <v>11</v>
@@ -32702,10 +32646,10 @@
         <v>12</v>
       </c>
       <c r="G234" s="3" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="H234" s="3" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
     </row>
     <row r="235" spans="1:8" ht="409.6">
@@ -32713,13 +32657,13 @@
         <v>8</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="C235" s="2">
         <v>10</v>
       </c>
       <c r="D235" s="2" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="E235" s="2" t="s">
         <v>11</v>
@@ -32728,10 +32672,10 @@
         <v>12</v>
       </c>
       <c r="G235" s="3" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="H235" s="3" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
     </row>
     <row r="236" spans="1:8" ht="43.2">
@@ -32739,13 +32683,13 @@
         <v>8</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="C236" s="2">
         <v>11</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="E236" s="2" t="s">
         <v>11</v>
@@ -32754,10 +32698,10 @@
         <v>12</v>
       </c>
       <c r="G236" s="3" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="H236" s="3" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
     </row>
     <row r="237" spans="1:8" ht="43.2">
@@ -32765,13 +32709,13 @@
         <v>8</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="C237" s="2">
         <v>12</v>
       </c>
       <c r="D237" s="2" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="E237" s="2" t="s">
         <v>11</v>
@@ -32780,10 +32724,10 @@
         <v>12</v>
       </c>
       <c r="G237" s="3" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="H237" s="3" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
     </row>
     <row r="238" spans="1:8" ht="115.2">
@@ -32791,13 +32735,13 @@
         <v>8</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="C238" s="2">
         <v>13</v>
       </c>
       <c r="D238" s="2" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="E238" s="2" t="s">
         <v>11</v>
@@ -32806,10 +32750,10 @@
         <v>12</v>
       </c>
       <c r="G238" s="3" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="H238" s="3" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
     </row>
     <row r="239" spans="1:8" ht="43.2">
@@ -32817,13 +32761,13 @@
         <v>8</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="C239" s="2">
         <v>14</v>
       </c>
       <c r="D239" s="2" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="E239" s="2" t="s">
         <v>11</v>
@@ -32832,10 +32776,10 @@
         <v>12</v>
       </c>
       <c r="G239" s="3" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="H239" s="3" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
     </row>
     <row r="240" spans="1:8" ht="43.2">
@@ -32843,13 +32787,13 @@
         <v>8</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="C240" s="2">
         <v>15</v>
       </c>
       <c r="D240" s="2" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="E240" s="2" t="s">
         <v>11</v>
@@ -32858,10 +32802,10 @@
         <v>12</v>
       </c>
       <c r="G240" s="3" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="H240" s="3" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
     </row>
     <row r="241" spans="1:8" ht="115.2">
@@ -32869,13 +32813,13 @@
         <v>8</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="C241" s="2">
         <v>16</v>
       </c>
       <c r="D241" s="2" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="E241" s="2" t="s">
         <v>11</v>
@@ -32884,10 +32828,10 @@
         <v>12</v>
       </c>
       <c r="G241" s="3" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="H241" s="3" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
     </row>
     <row r="242" spans="1:8" ht="129.6">
@@ -32895,13 +32839,13 @@
         <v>8</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="C242" s="2">
         <v>17</v>
       </c>
       <c r="D242" s="2" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="E242" s="2" t="s">
         <v>11</v>
@@ -32910,10 +32854,10 @@
         <v>12</v>
       </c>
       <c r="G242" s="3" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="H242" s="3" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
     </row>
     <row r="243" spans="1:8" ht="129.6">
@@ -32921,13 +32865,13 @@
         <v>8</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="C243" s="2">
         <v>18</v>
       </c>
       <c r="D243" s="2" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="E243" s="2" t="s">
         <v>11</v>
@@ -32936,10 +32880,10 @@
         <v>12</v>
       </c>
       <c r="G243" s="3" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="H243" s="3" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
     </row>
     <row r="244" spans="1:8" ht="100.8">
@@ -32947,13 +32891,13 @@
         <v>8</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="C244" s="2">
         <v>19</v>
       </c>
       <c r="D244" s="2" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="E244" s="2" t="s">
         <v>11</v>
@@ -32962,10 +32906,10 @@
         <v>12</v>
       </c>
       <c r="G244" s="3" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="H244" s="3" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
     </row>
     <row r="245" spans="1:8" ht="86.4">
@@ -32973,13 +32917,13 @@
         <v>8</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="C245" s="2">
         <v>20</v>
       </c>
       <c r="D245" s="2" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="E245" s="2" t="s">
         <v>11</v>
@@ -32988,10 +32932,10 @@
         <v>12</v>
       </c>
       <c r="G245" s="3" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="H245" s="3" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
     </row>
     <row r="246" spans="1:8" ht="216">
@@ -32999,13 +32943,13 @@
         <v>8</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="C246" s="2">
         <v>21</v>
       </c>
       <c r="D246" s="2" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="E246" s="2" t="s">
         <v>11</v>
@@ -33014,10 +32958,10 @@
         <v>12</v>
       </c>
       <c r="G246" s="3" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="H246" s="3" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
     </row>
     <row r="247" spans="1:8" ht="100.8">
@@ -33025,13 +32969,13 @@
         <v>8</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="C247" s="2">
         <v>22</v>
       </c>
       <c r="D247" s="2" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="E247" s="2" t="s">
         <v>11</v>
@@ -33040,10 +32984,10 @@
         <v>12</v>
       </c>
       <c r="G247" s="3" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="H247" s="3" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
     </row>
     <row r="248" spans="1:8" ht="187.2">
@@ -33051,13 +32995,13 @@
         <v>8</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="C248" s="2">
         <v>23</v>
       </c>
       <c r="D248" s="2" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="E248" s="2" t="s">
         <v>11</v>
@@ -33066,10 +33010,10 @@
         <v>12</v>
       </c>
       <c r="G248" s="3" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="H248" s="3" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
     </row>
     <row r="249" spans="1:8" ht="28.8">
@@ -33077,13 +33021,13 @@
         <v>8</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="C249" s="2">
         <v>24</v>
       </c>
       <c r="D249" s="2" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="E249" s="2" t="s">
         <v>11</v>
@@ -33092,10 +33036,10 @@
         <v>12</v>
       </c>
       <c r="G249" s="3" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="H249" s="4" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
     </row>
     <row r="250" spans="1:8" ht="43.2">
@@ -33103,13 +33047,13 @@
         <v>8</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="C250" s="2">
         <v>25</v>
       </c>
       <c r="D250" s="2" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="E250" s="2" t="s">
         <v>11</v>
@@ -33118,10 +33062,10 @@
         <v>12</v>
       </c>
       <c r="G250" s="3" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="H250" s="3" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
     </row>
     <row r="251" spans="1:8" ht="43.2">
@@ -33129,13 +33073,13 @@
         <v>8</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="C251" s="2">
         <v>26</v>
       </c>
       <c r="D251" s="2" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="E251" s="2" t="s">
         <v>11</v>
@@ -33144,10 +33088,10 @@
         <v>12</v>
       </c>
       <c r="G251" s="3" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="H251" s="3" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
     </row>
     <row r="252" spans="1:8" ht="43.2">
@@ -33155,13 +33099,13 @@
         <v>8</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="C252" s="2">
         <v>27</v>
       </c>
       <c r="D252" s="2" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="E252" s="2" t="s">
         <v>11</v>
@@ -33170,10 +33114,10 @@
         <v>12</v>
       </c>
       <c r="G252" s="3" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="H252" s="3" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
     </row>
     <row r="253" spans="1:8">
@@ -33181,13 +33125,13 @@
         <v>8</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="C253" s="2">
         <v>0</v>
       </c>
       <c r="D253" s="2" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="E253" s="2" t="s">
         <v>11</v>
@@ -33196,10 +33140,10 @@
         <v>12</v>
       </c>
       <c r="G253" s="3" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="H253" s="4" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
     </row>
     <row r="254" spans="1:8" ht="100.8">
@@ -33207,13 +33151,13 @@
         <v>8</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="C254" s="2">
         <v>2</v>
       </c>
       <c r="D254" s="2" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="E254" s="2" t="s">
         <v>11</v>
@@ -33222,10 +33166,10 @@
         <v>12</v>
       </c>
       <c r="G254" s="3" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="H254" s="3" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
     </row>
     <row r="255" spans="1:8">
@@ -33233,13 +33177,13 @@
         <v>8</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="C255" s="2">
         <v>0</v>
       </c>
       <c r="D255" s="2" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="E255" s="2" t="s">
         <v>11</v>
@@ -33248,10 +33192,10 @@
         <v>12</v>
       </c>
       <c r="G255" s="3" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="H255" s="4" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
     </row>
     <row r="256" spans="1:8">
@@ -33259,13 +33203,13 @@
         <v>8</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="C256" s="2">
         <v>0</v>
       </c>
       <c r="D256" s="2" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="E256" s="2" t="s">
         <v>11</v>
@@ -33274,10 +33218,10 @@
         <v>12</v>
       </c>
       <c r="G256" s="3" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="H256" s="4" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
     </row>
     <row r="257" spans="1:8" ht="28.8">
@@ -33285,13 +33229,13 @@
         <v>8</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="C257" s="2">
         <v>0</v>
       </c>
       <c r="D257" s="2" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="E257" s="2" t="s">
         <v>11</v>
@@ -33300,10 +33244,10 @@
         <v>12</v>
       </c>
       <c r="G257" s="3" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="H257" s="3" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
     </row>
     <row r="258" spans="1:8" ht="43.2">
@@ -33311,13 +33255,13 @@
         <v>8</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="C258" s="2">
         <v>1</v>
       </c>
       <c r="D258" s="2" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="E258" s="2" t="s">
         <v>11</v>
@@ -33326,10 +33270,10 @@
         <v>12</v>
       </c>
       <c r="G258" s="3" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="H258" s="3" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
     </row>
     <row r="259" spans="1:8" ht="100.8">
@@ -33337,13 +33281,13 @@
         <v>8</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="C259" s="2">
         <v>2</v>
       </c>
       <c r="D259" s="2" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="E259" s="2" t="s">
         <v>11</v>
@@ -33352,10 +33296,10 @@
         <v>12</v>
       </c>
       <c r="G259" s="3" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="H259" s="3" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
     </row>
     <row r="260" spans="1:8" ht="43.2">
@@ -33363,13 +33307,13 @@
         <v>8</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="C260" s="2">
         <v>3</v>
       </c>
       <c r="D260" s="2" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="E260" s="2" t="s">
         <v>11</v>
@@ -33378,10 +33322,10 @@
         <v>12</v>
       </c>
       <c r="G260" s="3" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="H260" s="3" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
     </row>
     <row r="261" spans="1:8">
@@ -33389,13 +33333,13 @@
         <v>8</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="C261" s="2">
         <v>0</v>
       </c>
       <c r="D261" s="2" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="E261" s="2" t="s">
         <v>11</v>
@@ -33404,10 +33348,10 @@
         <v>12</v>
       </c>
       <c r="G261" s="3" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="H261" s="4" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
     </row>
     <row r="262" spans="1:8">
@@ -33415,13 +33359,13 @@
         <v>8</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="C262" s="2">
         <v>0</v>
       </c>
       <c r="D262" s="2" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="E262" s="2" t="s">
         <v>11</v>
@@ -33430,10 +33374,10 @@
         <v>12</v>
       </c>
       <c r="G262" s="3" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="H262" s="4" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
     </row>
     <row r="263" spans="1:8">
@@ -33441,13 +33385,13 @@
         <v>8</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="C263" s="2">
         <v>0</v>
       </c>
       <c r="D263" s="2" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="E263" s="2" t="s">
         <v>11</v>
@@ -33456,10 +33400,10 @@
         <v>12</v>
       </c>
       <c r="G263" s="3" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="H263" s="4" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
     </row>
     <row r="264" spans="1:8">
@@ -33467,13 +33411,13 @@
         <v>8</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="C264" s="2">
         <v>1</v>
       </c>
       <c r="D264" s="2" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="E264" s="2" t="s">
         <v>11</v>
@@ -33482,10 +33426,10 @@
         <v>12</v>
       </c>
       <c r="G264" s="3" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="H264" s="4" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
     </row>
     <row r="265" spans="1:8" ht="28.8">
@@ -33493,13 +33437,13 @@
         <v>8</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="C265" s="2">
         <v>0</v>
       </c>
       <c r="D265" s="2" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="E265" s="2" t="s">
         <v>11</v>
@@ -33508,10 +33452,10 @@
         <v>12</v>
       </c>
       <c r="G265" s="3" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="H265" s="4" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
     </row>
   </sheetData>

--- a/docassemble/PowerOfAttorneyProperty/data/sources/poa_property_es.xlsx
+++ b/docassemble/PowerOfAttorneyProperty/data/sources/poa_property_es.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mnewsted\local-DA-easyforms-dev\sources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9495667D-5045-4CC4-97C3-7A3E412DCFAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FADC3D69-E4A2-4306-ABAE-0B8DFC2924BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38625" yWindow="-3330" windowWidth="35685" windowHeight="16530" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -15393,9 +15393,6 @@
     <t>Edit</t>
   </si>
   <si>
-    <t>Por favor proporciona el texto en inglés que quieres que traduzca al español.</t>
-  </si>
-  <si>
     <t>7fc9488b8e13f6831ab32878d3386ddb</t>
   </si>
   <si>
@@ -18581,15 +18578,30 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">**Límites al poder de </t>
+    <t>09bb445a8d9cd08b8e49b48bb1bddd8a</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% if not additional_powers_check:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>**</t>
     </r>
     <r>
       <rPr>
@@ -18605,40 +18617,24 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">:**
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${agent_limits}</t>
-    </r>
-  </si>
-  <si>
-    <t>09bb445a8d9cd08b8e49b48bb1bddd8a</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% if not additional_powers_check:
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> is not granted any additional powers.**
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% else:
 </t>
     </r>
     <r>
@@ -18670,7 +18666,440 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> is not granted any additional powers.**
+      <t xml:space="preserve"> is granted these additional powers:**
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${additional_powers_text}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% endif
+</t>
+    </r>
+  </si>
+  <si>
+    <t>b250f3d34ca3869c0dc7662f4fa5567f</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">**Can </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${agent.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> delegate decision making powers?**
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% if delegate_decisions == "agent_only":
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">No
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% elif delegate_decisions == "anyone":
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Yes, to anyone they choose.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% elif delegate_decisions == "authorized":
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Yes, to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${delegate.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% endif
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">**¿Puede </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${agent.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> delegar el poder de tomar decisiones?**
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% if delegate_decisions == "agent_only":
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">No
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% elif delegate_decisions == "anyone":
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Sí, a cualquiera que elijan.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% elif delegate_decisions == "authorized":
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Sí, a </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${delegate.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>% endif</t>
+    </r>
+  </si>
+  <si>
+    <t>d4fc1f8627d6b060484713a48e79723a</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">**Will </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${agent.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> be paid?**
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% if agent_compensation == "expenses_only":
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Only for reasonable expenses.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% elif agent_compensation == "with_limits":
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Yes, no more than </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${currency(compensate_amount)}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${compensate_time.lower()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.
 </t>
     </r>
     <r>
@@ -18693,7 +19122,874 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>**</t>
+      <t xml:space="preserve">Yes, at their discretion.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% endif
+</t>
+    </r>
+  </si>
+  <si>
+    <t>f5ad0e38a023f8bb51614932835a55ad</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% if for_yourself == True:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">**Do you want to name successor agents?**
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% else:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">**Does </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${principal.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> want to name successor agents?**
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% endif
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${word(yesno(any_successors))}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% if for_yourself == True:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">**¿Quieres nombrar agentes sucesores?**
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% else:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">**¿Quiere </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${principal.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> nombrar agentes sucesores?**
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% endif
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${word(yesno(any_successors))}</t>
+    </r>
+  </si>
+  <si>
+    <t>3034428c38d756d04379888f9a892489</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">**Successors: (Edit to change names, addresses, and phone numbers)**
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% for person in successors:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  * </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${ person.name_full() }</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% endfor
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">**Sucesores: (Edite para cambiar nombres, direcciones y números de teléfono)**
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% for person in successors:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  * </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${ person.name_full() }</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>% endfor</t>
+    </r>
+  </si>
+  <si>
+    <t>649629ca79bcf47fe751a17a214f9d0c</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">**This Power of Attorney will take effect:**
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% if effective_date_choice == "immediately":
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Immediately
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% elif effective_date_choice == "doctor":
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Only when a doctor has made a written statement that </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${i_subject}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> cannot make financial decisions for </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${myself_their_self}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% elif effective_date_choice == "detained":
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Only if </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${i_subject}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${am_is}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> arrested, detained, or deported.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% elif effective_date_choice == "immigration":
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">When an Adverse Immigration Action stops </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${me_them}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> from managing </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${my_their}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> property.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% elif effective_date_choice == "other":
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${effective_date_text}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% endif
+</t>
+    </r>
+  </si>
+  <si>
+    <t>5dbfdc0e775f5aed9b8559b25a45d1c6</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% if for_yourself == True:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">**Will this Power of Attorney last until your death?**
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% else:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">**Will this Power of Attorney last until </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${principal.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">'s death?**
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% endif
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${word(yesno(end_at_death))}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% if for_yourself == True:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">**¿Este poder notarial durará hasta tu muerte?**
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% else:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">**¿Este poder notarial durará hasta la muerte de </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${principal.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">?**
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% endif
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${word(yesno(end_at_death))}</t>
+    </r>
+  </si>
+  <si>
+    <t>05570d8e33acc6d6a7968bae41cc824b</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">**This Power of Attorney shall terminate:**
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% if end_date_choice == "doctor":
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">When </t>
     </r>
     <r>
       <rPr>
@@ -18714,29 +20010,265 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> is granted these additional powers:**
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${additional_powers_text}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
+      <t xml:space="preserve"> gets a note from </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${my_subject}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> doctor that </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${i_they}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> can manage </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${my_their}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> financial affairs.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% elif end_date_choice == "custody":
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">When </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${i_subject}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${have_has}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> been released from custody.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% elif end_date_choice == "immigration":
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">When the Adverse Immigration Action ends, and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${i_they}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> state in writing </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${i_they}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> will manage </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${my_their}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> property again.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% elif end_date_choice == "other":
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">On </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${end_date_text}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.
 </t>
     </r>
     <r>
@@ -18750,2467 +20282,6 @@
       </rPr>
       <t xml:space="preserve">% endif
 </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% if not additional_powers_check:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>**</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${agent.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> no se le otorgan poderes adicionales.**
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% else:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>**</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${agent.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> recibe estos poderes adicionales:**
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${additional_powers_text}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>% endif</t>
-    </r>
-  </si>
-  <si>
-    <t>b250f3d34ca3869c0dc7662f4fa5567f</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">**Can </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${agent.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> delegate decision making powers?**
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% if delegate_decisions == "agent_only":
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">No
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% elif delegate_decisions == "anyone":
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Yes, to anyone they choose.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% elif delegate_decisions == "authorized":
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Yes, to </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${delegate.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% endif
-</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">**¿Puede </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${agent.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> delegar el poder de tomar decisiones?**
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% if delegate_decisions == "agent_only":
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">No
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% elif delegate_decisions == "anyone":
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Sí, a cualquiera que elijan.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% elif delegate_decisions == "authorized":
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Sí, a </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${delegate.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>% endif</t>
-    </r>
-  </si>
-  <si>
-    <t>d4fc1f8627d6b060484713a48e79723a</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">**Will </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${agent.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> be paid?**
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% if agent_compensation == "expenses_only":
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Only for reasonable expenses.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% elif agent_compensation == "with_limits":
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Yes, no more than </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${currency(compensate_amount)}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${compensate_time.lower()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% else:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Yes, at their discretion.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% endif
-</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">**¿Se le pagará a </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${agent.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">?**
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% if agent_compensation == "expenses_only":
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Solo para gastos razonables.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% elif agent_compensation == "with_limits":
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Sí, no más de </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${currency(compensate_amount)}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${compensate_time.lower()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% else:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Sí, a su discreción.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>% endif</t>
-    </r>
-  </si>
-  <si>
-    <t>f5ad0e38a023f8bb51614932835a55ad</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% if for_yourself == True:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">**Do you want to name successor agents?**
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% else:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">**Does </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${principal.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> want to name successor agents?**
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% endif
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${word(yesno(any_successors))}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% if for_yourself == True:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">**¿Quieres nombrar agentes sucesores?**
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% else:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">**¿Quiere </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${principal.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> nombrar agentes sucesores?**
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% endif
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${word(yesno(any_successors))}</t>
-    </r>
-  </si>
-  <si>
-    <t>3034428c38d756d04379888f9a892489</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">**Successors: (Edit to change names, addresses, and phone numbers)**
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% for person in successors:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  * </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${ person.name_full() }</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% endfor
-</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">**Sucesores: (Edite para cambiar nombres, direcciones y números de teléfono)**
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% for person in successors:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  * </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${ person.name_full() }</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>% endfor</t>
-    </r>
-  </si>
-  <si>
-    <t>649629ca79bcf47fe751a17a214f9d0c</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">**This Power of Attorney will take effect:**
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% if effective_date_choice == "immediately":
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Immediately
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% elif effective_date_choice == "doctor":
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Only when a doctor has made a written statement that </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${i_subject}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> cannot make financial decisions for </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${myself_their_self}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% elif effective_date_choice == "detained":
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Only if </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${i_subject}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${am_is}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> arrested, detained, or deported.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% elif effective_date_choice == "immigration":
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">When an Adverse Immigration Action stops </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${me_them}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> from managing </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${my_their}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> property.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% elif effective_date_choice == "other":
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${effective_date_text}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% endif
-</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">**Este poder notarial entrará en vigor:**
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% if effective_date_choice == "immediately":
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Inmediatamente
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% elif effective_date_choice == "doctor":
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Solo cuando un médico haya emitido una declaración por escrito de que </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${i_subject}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> no puede tomar decisiones financieras para </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${myself_their_self}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% elif effective_date_choice == "detained":
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Solo si </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${i_subject}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${am_is}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> arrestado, detenido o deportado.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% elif effective_date_choice == "immigration":
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Cuando una Acción Migratoria Adversa impide que </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${me_them}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> gestione la propiedad de </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${my_their}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% elif effective_date_choice == "other":
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${effective_date_text}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>% endif</t>
-    </r>
-  </si>
-  <si>
-    <t>5dbfdc0e775f5aed9b8559b25a45d1c6</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% if for_yourself == True:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">**Will this Power of Attorney last until your death?**
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% else:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">**Will this Power of Attorney last until </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${principal.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">'s death?**
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% endif
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${word(yesno(end_at_death))}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% if for_yourself == True:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">**¿Este poder notarial durará hasta tu muerte?**
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% else:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">**¿Este poder notarial durará hasta la muerte de </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${principal.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">?**
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% endif
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${word(yesno(end_at_death))}</t>
-    </r>
-  </si>
-  <si>
-    <t>05570d8e33acc6d6a7968bae41cc824b</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">**This Power of Attorney shall terminate:**
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% if end_date_choice == "doctor":
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">When </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${agent.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> gets a note from </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${my_subject}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> doctor that </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${i_they}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> can manage </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${my_their}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> financial affairs.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% elif end_date_choice == "custody":
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">When </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${i_subject}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${have_has}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> been released from custody.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% elif end_date_choice == "immigration":
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">When the Adverse Immigration Action ends, and </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${i_they}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> state in writing </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${i_they}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> will manage </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${my_their}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> property again.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% elif end_date_choice == "other":
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">On </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${end_date_text}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% endif
-</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">**Este Poder Notarial terminará:**
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% if end_date_choice == "doctor":
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Cuando </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${agent.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> reciba una nota del médico de </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${my_subject}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> que </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${i_they}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> pueda manejar </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${my_their}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> asuntos financieros.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% elif end_date_choice == "custody":
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Cuando </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${i_subject}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${have_has}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> sido liberado de la custodia.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% elif end_date_choice == "immigration":
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Cuando termine la Acción Migratoria Adversa, y </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${i_they}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> declare por escrito que </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${i_they}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> volverá a administrar </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${my_their}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> propiedad.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% elif end_date_choice == "other":
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">En </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${end_date_text}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>% endif</t>
     </r>
   </si>
   <si>
@@ -22251,67 +21322,6 @@
     <t>Un **agente sucesor** es un agente de respaldo que actuará como tu agente si tu primer agente no está disponible, fallece o deja de ser tu agente.</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Para usar este programa necesitarás saber:
-* El nombre, la ciudad, el estado y el número de teléfono de la persona que quieres nombrar como **{agente}** con poder notarial,
-* El nombre, la ciudad, el estado y el número de teléfono de cualquier **{agente sucesor}**,
-* Qué propiedad y finanzas tienes, y
-* Cuánto control quieres que tenga el agente sobre tu propiedad y tus finanzas.
-Reserva entre 15 y 30 minutos para completar este programa, y más tiempo si ves los videos. Puedes iniciar sesión y guardar tu trabajo para regresar más tarde. 
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${ collapse_template(help_example) }</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  
-Haz clic en **{palabras verdes}** para saber qué significan. Algunas preguntas tienen un signo de interrogación en un círculo </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${ fa_icon("question-circle", color_css="#0DCAF0" ) }</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> que también brinda ayuda.</t>
-    </r>
-  </si>
-  <si>
     <t>Este es un ejemplo de ayuda. Haz clic de nuevo para ocultarlo.</t>
   </si>
   <si>
@@ -22322,41 +21332,6 @@
   </si>
   <si>
     <t>Cómo completar este formulario</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Al final del programa, podrás descargar tu Poder Notarial para la Propiedad y Finanzas. No será oficial hasta que lo firmes frente a un testigo y un notario público. No necesitas saber quién será el testigo para usar este programa.
-Si quieres saber más sobre la planificación en caso de discapacidad o el cuidado al final de la vida, puedes revisar la guía de ILAO y CDEL [**Empodérate de tu Futuro**](</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${ preview.url_for() }</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>).
-Asegúrate de descargar y leer las instrucciones al final del programa.</t>
-    </r>
   </si>
   <si>
     <t>Otorgante</t>
@@ -25373,6 +24348,1368 @@
   <si>
     <r>
       <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>No. Puede listar a alguien fuera de los Estados Unidos como el agente sucesor. El agente sucesor no necesita ser ciudadano de los Estados Unidos. Sin embargo, puede haber problemas si un banco o una organización financiera no puede contactarlo. Quizá quiera consultar a un abogado para obtener asesoría. Usa [**Obtener ayuda legal**](</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>https://es.illinoislegalaid.org/get-legal-help</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>) para encontrar servicios legales gratuitos o de bajo costo en su zona.
+Para direcciones internacionales, habrá espacio para dos líneas para ingresar la dirección. Debe ingresar la dirección internacional usando el alfabeto inglés.</t>
+    </r>
+  </si>
+  <si>
+    <t>**Video: ¿Cuándo entra en vigor un poder notarial para la propiedad?**</t>
+  </si>
+  <si>
+    <t>[YOUTUBE Dg7Lc7efTJI]</t>
+  </si>
+  <si>
+    <t>**Demostrando la capacidad legal**</t>
+  </si>
+  <si>
+    <t>[YOUTUBE Xx99zYlIwgE]</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${collapse_template(video_when_end)}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% if for_yourself == True:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>This Power of Attorney for Property will last until your death. However, you may choose to end it earlier. If you only want the Power of Attorney to last for a specific time, click **No**.
+You can end a Power of Attorney by making a formal Revocation. To make a Power of Attorney Revocation, use ILAO's [**Power of Attorney Revocation Easy Form**](</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>https://www.illinoislegalaid.org/legal-information/power-attorney-revocation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">).
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% else:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">This Power of Attorney for Property will last until </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${principal.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">'s death. However, they may choose to end it earlier. If they only want the Power of Attorney to last for a specific time, click **No**.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${principal.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> can end a Power of Attorney by making a formal Revocation. To make a Power of Attorney Revocation, use ILAO's [**Power of Attorney Revocation Easy Form**](</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>https://www.illinoislegalaid.org/legal-information/power-attorney-revocation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">).
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% endif
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${collapse_template(video_when_end)}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% if for_yourself == True:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Este poder notarial para bienes durará hasta su muerte. Sin embargo, puede elegir terminarlo antes. Si solo desea que el poder notarial dure por un tiempo específico, haga clic en **No**.
+Puede terminar un poder notarial realizando una Revocación formal. Para realizar una Revocación de Poder Notarial, use el [**Formulario Fácil de Revocación de Poder Notarial**](https://es.illinoislegalaid.org/legal-information/power-attorney-revocation) de ILAO.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% else:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Este poder notarial para bienes durará hasta la muerte de </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${principal.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Sin embargo, la persona puede elegir terminarlo antes. Si la persona solo quiere que el poder notarial dure por un tiempo específico, haga clic en **No**.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${principal.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> puede terminar un poder notarial realizando una Revocación formal. Para realizar una Revocación de Poder Notarial, use el [**Formulario Fácil de Revocación de Poder Notarial**](https://es.illinoislegalaid.org/legal-information/power-attorney-revocation) de ILAO.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>% endif</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>They can create a Power of Attorney Revocation to end a Power of Attorney.
+To make a Power of Attorney Revocation, use ILAO's [**Power of Attorney Revocation Easy Form**](</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>https://www.illinoislegalaid.org/legal-information/power-attorney-revocation</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">).
+</t>
+    </r>
+  </si>
+  <si>
+    <t>Pueden crear una Revocación de Poder para terminar un poder.
+Para hacer una Revocación de Poder, use el [**Formulario Fácil de Revocación de Poder Notarial**](https://es.illinoislegalaid.org/legal-information/power-attorney-revocation) de ILAO].</t>
+  </si>
+  <si>
+    <t>Editar</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">**Límites al poder de </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${agent.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: (En inglés)**
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${agent_limits}</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% if not additional_powers_check:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>**</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${agent.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> no se le otorgan poderes adicionales.**
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% else:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>**</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${agent.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> recibe estos poderes adicionales: (En inglés)**
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${additional_powers_text}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>% endif</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">**¿Se le pagará a </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${agent.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">?**
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% if agent_compensation == "expenses_only":
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Solo para gastos razonables.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% elif agent_compensation == "with_limits":
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% if compensate_time == "per hour":
+Sí, no más de ${currency(compensate_amount)} por hora.
+% elif compensate_time == "per day":
+Sí, no más de ${currency(compensate_amount)} al día.
+% elif compensate_time == "per week":
+Sí, no más de ${currency(compensate_amount)} por semana.
+% else:
+Sí, no más de ${currency(compensate_amount)} al mes.
+% endif
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% else:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Sí, a su discreción.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>% endif</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">**Este poder notarial entrará en vigor: (En inglés)**
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% if effective_date_choice == "immediately":
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Inmediatamente
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% elif effective_date_choice == "doctor":
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Solo cuando un médico haya emitido una declaración por escrito de que </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${i_subject}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> no puede tomar decisiones financieras para </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${myself_their_self}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% elif effective_date_choice == "detained":
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Solo si </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${i_subject}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${am_is}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> arrestado, detenido o deportado.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% elif effective_date_choice == "immigration":
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Cuando una Acción Migratoria Adversa impide que </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${me_them}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> gestione la propiedad de </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${my_their}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% elif effective_date_choice == "other":
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${effective_date_text}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>% endif</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">**Este Poder Notarial terminará: (En inglés)**
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% if end_date_choice == "doctor":
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Cuando </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${agent.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> reciba una nota del médico de </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${my_subject}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> que </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${i_they}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> pueda manejar </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${my_their}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> asuntos financieros.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% elif end_date_choice == "custody":
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Cuando </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${i_subject}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${have_has}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> sido liberado de la custodia.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% elif end_date_choice == "immigration":
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Cuando termine la Acción Migratoria Adversa, y </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${i_they}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> declare por escrito que </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${i_they}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> volverá a administrar </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${my_their}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> propiedad.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% elif end_date_choice == "other":
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">En </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${end_date_text}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>% endif</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Para usar este programa necesitarás saber:
+* El nombre, la ciudad, el estado y el número de teléfono de la persona que quieres nombrar como **{agente}** con poder notarial,
+* El nombre, la ciudad, el estado y el número de teléfono de cualquier **{agentes sucesores}**,
+* Qué propiedad y finanzas tienes, y
+* Cuánto control quieres que tenga el agente sobre tu propiedad y tus finanzas.
+Reserva entre 15 y 30 minutos para completar este programa, y más tiempo si ves los videos. Puedes iniciar sesión y guardar tu trabajo para regresar más tarde. 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${ collapse_template(help_example) }</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  
+Haz clic en **{palabras verdes}** para saber qué significan. Algunas preguntas tienen un signo de interrogación en un círculo </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${ fa_icon("question-circle", color_css="#0DCAF0" ) }</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> que también brinda ayuda.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Al final del programa, podrás descargar tu Poder Notarial para la Propiedad y Finanzas. No será oficial hasta que lo firmes frente a un testigo y un notario público. No necesitas saber quién será el testigo para usar este programa.
+Si quieres saber más sobre la planificación en caso de discapacidad o el cuidado al final de la vida, puedes revisar la guía de ILAO y CDEL [**Empodérate de tu Futuro**](</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${ preview_es.url_for() }</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>).
+Asegúrate de descargar y leer las instrucciones al final del programa.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
         <b/>
         <sz val="11"/>
         <color rgb="FF008000"/>
@@ -25478,7 +25815,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> muere, se vuelve **{incompetent}**, renuncia o se niega a aceptar el cargo de agente.
+      <t xml:space="preserve"> muere, se vuelve **{incompetente}**, renuncia o se niega a aceptar el cargo de agente.
 If </t>
     </r>
     <r>
@@ -25513,40 +25850,6 @@
         <scheme val="minor"/>
       </rPr>
       <t>% endif</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>No. Puede listar a alguien fuera de los Estados Unidos como el agente sucesor. El agente sucesor no necesita ser ciudadano de los Estados Unidos. Sin embargo, puede haber problemas si un banco o una organización financiera no puede contactarlo. Quizá quiera consultar a un abogado para obtener asesoría. Usa [**Obtener ayuda legal**](</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>https://es.illinoislegalaid.org/get-legal-help</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>) para encontrar servicios legales gratuitos o de bajo costo en su zona.
-Para direcciones internacionales, habrá espacio para dos líneas para ingresar la dirección. Debe ingresar la dirección internacional usando el alfabeto inglés.</t>
     </r>
   </si>
   <si>
@@ -25768,7 +26071,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> aún puede cambiar de opinión y **{revoke}** el Poder Notarial después de firmarlo, siempre que tenga la **{legal capacity}** requerida.
+      <t xml:space="preserve"> aún puede cambiar de opinión y **{revocar}** el Poder Notarial después de firmarlo, siempre que tenga la **{capacidad legal}** requerida.
 </t>
     </r>
     <r>
@@ -25805,343 +26108,6 @@
       </rPr>
       <t>${collapse_template(prove_capacity)}</t>
     </r>
-  </si>
-  <si>
-    <t>**Video: ¿Cuándo entra en vigor un poder notarial para la propiedad?**</t>
-  </si>
-  <si>
-    <t>[YOUTUBE Dg7Lc7efTJI]</t>
-  </si>
-  <si>
-    <t>**Demostrando la capacidad legal**</t>
-  </si>
-  <si>
-    <t>[YOUTUBE Xx99zYlIwgE]</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${collapse_template(video_when_end)}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% if for_yourself == True:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>This Power of Attorney for Property will last until your death. However, you may choose to end it earlier. If you only want the Power of Attorney to last for a specific time, click **No**.
-You can end a Power of Attorney by making a formal Revocation. To make a Power of Attorney Revocation, use ILAO's [**Power of Attorney Revocation Easy Form**](</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>https://www.illinoislegalaid.org/legal-information/power-attorney-revocation</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">).
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% else:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">This Power of Attorney for Property will last until </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${principal.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">'s death. However, they may choose to end it earlier. If they only want the Power of Attorney to last for a specific time, click **No**.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${principal.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> can end a Power of Attorney by making a formal Revocation. To make a Power of Attorney Revocation, use ILAO's [**Power of Attorney Revocation Easy Form**](</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>https://www.illinoislegalaid.org/legal-information/power-attorney-revocation</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">).
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% endif
-</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${collapse_template(video_when_end)}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% if for_yourself == True:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Este poder notarial para bienes durará hasta su muerte. Sin embargo, puede elegir terminarlo antes. Si solo desea que el poder notarial dure por un tiempo específico, haga clic en **No**.
-Puede terminar un poder notarial realizando una Revocación formal. Para realizar una Revocación de Poder Notarial, use el [**Formulario Fácil de Revocación de Poder Notarial**](https://es.illinoislegalaid.org/legal-information/power-attorney-revocation) de ILAO.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% else:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Este poder notarial para bienes durará hasta la muerte de </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${principal.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">. Sin embargo, la persona puede elegir terminarlo antes. Si la persona solo quiere que el poder notarial dure por un tiempo específico, haga clic en **No**.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${principal.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> puede terminar un poder notarial realizando una Revocación formal. Para realizar una Revocación de Poder Notarial, use el [**Formulario Fácil de Revocación de Poder Notarial**](https://es.illinoislegalaid.org/legal-information/power-attorney-revocation) de ILAO.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>% endif</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>They can create a Power of Attorney Revocation to end a Power of Attorney.
-To make a Power of Attorney Revocation, use ILAO's [**Power of Attorney Revocation Easy Form**](</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>https://www.illinoislegalaid.org/legal-information/power-attorney-revocation</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">).
-</t>
-    </r>
-  </si>
-  <si>
-    <t>Pueden crear una Revocación de Poder para terminar un poder.
-Para hacer una Revocación de Poder, use el [**Formulario Fácil de Revocación de Poder Notarial**](https://es.illinoislegalaid.org/legal-information/power-attorney-revocation) de ILAO].</t>
   </si>
 </sst>
 </file>
@@ -26617,7 +26583,7 @@
         <v>13</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>780</v>
+        <v>774</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="403.2">
@@ -26631,7 +26597,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>843</v>
+        <v>835</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>11</v>
@@ -26640,10 +26606,10 @@
         <v>12</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>844</v>
+        <v>836</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>845</v>
+        <v>837</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="187.2">
@@ -26669,7 +26635,7 @@
         <v>16</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>781</v>
+        <v>775</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="28.8">
@@ -26695,7 +26661,7 @@
         <v>19</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>782</v>
+        <v>776</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="302.39999999999998">
@@ -26721,7 +26687,7 @@
         <v>21</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>846</v>
+        <v>838</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -26747,7 +26713,7 @@
         <v>24</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>743</v>
+        <v>737</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="72">
@@ -26773,7 +26739,7 @@
         <v>26</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>783</v>
+        <v>777</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -26799,7 +26765,7 @@
         <v>28</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>764</v>
+        <v>758</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="43.2">
@@ -26825,7 +26791,7 @@
         <v>30</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>784</v>
+        <v>778</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="28.8">
@@ -26877,7 +26843,7 @@
         <v>35</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>785</v>
+        <v>870</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="43.2">
@@ -26903,7 +26869,7 @@
         <v>38</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>786</v>
+        <v>779</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="43.2">
@@ -26929,7 +26895,7 @@
         <v>40</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>787</v>
+        <v>780</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="86.4">
@@ -26955,7 +26921,7 @@
         <v>43</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>849</v>
+        <v>841</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="115.2">
@@ -26981,7 +26947,7 @@
         <v>46</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>847</v>
+        <v>839</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="28.8">
@@ -27033,7 +26999,7 @@
         <v>52</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="273.60000000000002">
@@ -27059,7 +27025,7 @@
         <v>54</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>848</v>
+        <v>840</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="28.8">
@@ -27085,7 +27051,7 @@
         <v>57</v>
       </c>
       <c r="H20" t="s">
-        <v>789</v>
+        <v>782</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="129.6">
@@ -27111,7 +27077,7 @@
         <v>59</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>790</v>
+        <v>871</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -27137,7 +27103,7 @@
         <v>62</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>791</v>
+        <v>783</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="43.2">
@@ -27163,7 +27129,7 @@
         <v>64</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>792</v>
+        <v>784</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="72">
@@ -27189,7 +27155,7 @@
         <v>66</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>793</v>
+        <v>785</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="28.8">
@@ -27215,7 +27181,7 @@
         <v>68</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>794</v>
+        <v>786</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="57.6">
@@ -27241,7 +27207,7 @@
         <v>70</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>854</v>
+        <v>846</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -27267,7 +27233,7 @@
         <v>72</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>795</v>
+        <v>787</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -27293,7 +27259,7 @@
         <v>74</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>796</v>
+        <v>788</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="28.8">
@@ -27319,7 +27285,7 @@
         <v>77</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>797</v>
+        <v>789</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="259.2">
@@ -27345,7 +27311,7 @@
         <v>79</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>798</v>
+        <v>790</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="86.4">
@@ -27371,7 +27337,7 @@
         <v>82</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>799</v>
+        <v>791</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="403.2">
@@ -27397,7 +27363,7 @@
         <v>84</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -27423,7 +27389,7 @@
         <v>86</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>801</v>
+        <v>793</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -27449,7 +27415,7 @@
         <v>88</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>802</v>
+        <v>794</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -27475,7 +27441,7 @@
         <v>90</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>803</v>
+        <v>795</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -27501,7 +27467,7 @@
         <v>92</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>804</v>
+        <v>796</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -27553,7 +27519,7 @@
         <v>97</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>805</v>
+        <v>797</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="115.2">
@@ -27579,7 +27545,7 @@
         <v>100</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>806</v>
+        <v>798</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="28.8">
@@ -27605,7 +27571,7 @@
         <v>102</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>807</v>
+        <v>799</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="28.8">
@@ -27631,7 +27597,7 @@
         <v>105</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>808</v>
+        <v>800</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="86.4">
@@ -27657,7 +27623,7 @@
         <v>108</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>855</v>
+        <v>847</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="28.8">
@@ -27683,7 +27649,7 @@
         <v>111</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>856</v>
+        <v>848</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="144">
@@ -27735,7 +27701,7 @@
         <v>117</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>809</v>
+        <v>801</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="86.4">
@@ -27761,7 +27727,7 @@
         <v>120</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>810</v>
+        <v>802</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="86.4">
@@ -27787,7 +27753,7 @@
         <v>123</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>811</v>
+        <v>803</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="345.6">
@@ -27813,7 +27779,7 @@
         <v>125</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>812</v>
+        <v>804</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="28.8">
@@ -27839,7 +27805,7 @@
         <v>128</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>813</v>
+        <v>805</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="28.8">
@@ -27891,7 +27857,7 @@
         <v>133</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>814</v>
+        <v>806</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="43.2">
@@ -27917,7 +27883,7 @@
         <v>135</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>815</v>
+        <v>807</v>
       </c>
     </row>
     <row r="53" spans="1:8">
@@ -27943,7 +27909,7 @@
         <v>137</v>
       </c>
       <c r="H53" t="s">
-        <v>858</v>
+        <v>850</v>
       </c>
     </row>
     <row r="54" spans="1:8">
@@ -27969,7 +27935,7 @@
         <v>139</v>
       </c>
       <c r="H54" t="s">
-        <v>859</v>
+        <v>851</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="129.6">
@@ -27995,7 +27961,7 @@
         <v>142</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>850</v>
+        <v>842</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="28.8">
@@ -28021,7 +27987,7 @@
         <v>144</v>
       </c>
       <c r="H56" s="4" t="s">
-        <v>857</v>
+        <v>849</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="28.8">
@@ -28073,7 +28039,7 @@
         <v>150</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>816</v>
+        <v>808</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="115.2">
@@ -28099,7 +28065,7 @@
         <v>153</v>
       </c>
       <c r="H59" s="5" t="s">
-        <v>860</v>
+        <v>852</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="28.8">
@@ -28151,7 +28117,7 @@
         <v>159</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>817</v>
+        <v>809</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="244.8">
@@ -28177,7 +28143,7 @@
         <v>161</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>818</v>
+        <v>810</v>
       </c>
     </row>
     <row r="63" spans="1:8">
@@ -28203,7 +28169,7 @@
         <v>163</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>819</v>
+        <v>811</v>
       </c>
     </row>
     <row r="64" spans="1:8">
@@ -28229,7 +28195,7 @@
         <v>165</v>
       </c>
       <c r="H64" s="4" t="s">
-        <v>820</v>
+        <v>812</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="43.2">
@@ -28281,7 +28247,7 @@
         <v>170</v>
       </c>
       <c r="H66" s="4" t="s">
-        <v>821</v>
+        <v>813</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="43.2">
@@ -28307,7 +28273,7 @@
         <v>172</v>
       </c>
       <c r="H67" s="4" t="s">
-        <v>861</v>
+        <v>853</v>
       </c>
     </row>
     <row r="68" spans="1:8">
@@ -28359,7 +28325,7 @@
         <v>177</v>
       </c>
       <c r="H69" s="4" t="s">
-        <v>822</v>
+        <v>814</v>
       </c>
     </row>
     <row r="70" spans="1:8">
@@ -28385,7 +28351,7 @@
         <v>179</v>
       </c>
       <c r="H70" s="4" t="s">
-        <v>823</v>
+        <v>815</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="72">
@@ -28411,7 +28377,7 @@
         <v>181</v>
       </c>
       <c r="H71" s="4" t="s">
-        <v>824</v>
+        <v>816</v>
       </c>
     </row>
     <row r="72" spans="1:8">
@@ -28437,7 +28403,7 @@
         <v>183</v>
       </c>
       <c r="H72" s="4" t="s">
-        <v>825</v>
+        <v>817</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="43.2">
@@ -28463,7 +28429,7 @@
         <v>185</v>
       </c>
       <c r="H73" s="4" t="s">
-        <v>826</v>
+        <v>818</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -28515,7 +28481,7 @@
         <v>190</v>
       </c>
       <c r="H75" s="4" t="s">
-        <v>828</v>
+        <v>820</v>
       </c>
     </row>
     <row r="76" spans="1:8">
@@ -28541,7 +28507,7 @@
         <v>192</v>
       </c>
       <c r="H76" s="4" t="s">
-        <v>827</v>
+        <v>819</v>
       </c>
     </row>
     <row r="77" spans="1:8" ht="43.2">
@@ -28567,7 +28533,7 @@
         <v>194</v>
       </c>
       <c r="H77" s="4" t="s">
-        <v>829</v>
+        <v>821</v>
       </c>
     </row>
     <row r="78" spans="1:8">
@@ -28593,7 +28559,7 @@
         <v>196</v>
       </c>
       <c r="H78" s="4" t="s">
-        <v>830</v>
+        <v>822</v>
       </c>
     </row>
     <row r="79" spans="1:8" ht="57.6">
@@ -28619,7 +28585,7 @@
         <v>198</v>
       </c>
       <c r="H79" s="4" t="s">
-        <v>831</v>
+        <v>823</v>
       </c>
     </row>
     <row r="80" spans="1:8">
@@ -28671,7 +28637,7 @@
         <v>203</v>
       </c>
       <c r="H81" s="4" t="s">
-        <v>832</v>
+        <v>824</v>
       </c>
     </row>
     <row r="82" spans="1:8">
@@ -28723,7 +28689,7 @@
         <v>208</v>
       </c>
       <c r="H83" s="4" t="s">
-        <v>833</v>
+        <v>825</v>
       </c>
     </row>
     <row r="84" spans="1:8">
@@ -28775,7 +28741,7 @@
         <v>213</v>
       </c>
       <c r="H85" s="4" t="s">
-        <v>834</v>
+        <v>826</v>
       </c>
     </row>
     <row r="86" spans="1:8">
@@ -28827,7 +28793,7 @@
         <v>218</v>
       </c>
       <c r="H87" s="4" t="s">
-        <v>835</v>
+        <v>827</v>
       </c>
     </row>
     <row r="88" spans="1:8">
@@ -28879,7 +28845,7 @@
         <v>223</v>
       </c>
       <c r="H89" s="4" t="s">
-        <v>837</v>
+        <v>829</v>
       </c>
     </row>
     <row r="90" spans="1:8">
@@ -28905,7 +28871,7 @@
         <v>225</v>
       </c>
       <c r="H90" s="4" t="s">
-        <v>836</v>
+        <v>828</v>
       </c>
     </row>
     <row r="91" spans="1:8" ht="43.2">
@@ -28931,7 +28897,7 @@
         <v>227</v>
       </c>
       <c r="H91" s="4" t="s">
-        <v>838</v>
+        <v>830</v>
       </c>
     </row>
     <row r="92" spans="1:8">
@@ -28983,7 +28949,7 @@
         <v>232</v>
       </c>
       <c r="H93" s="4" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
     </row>
     <row r="94" spans="1:8">
@@ -29035,7 +29001,7 @@
         <v>238</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>840</v>
+        <v>832</v>
       </c>
     </row>
     <row r="96" spans="1:8" ht="100.8">
@@ -29061,7 +29027,7 @@
         <v>241</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>841</v>
+        <v>833</v>
       </c>
     </row>
     <row r="97" spans="1:8" ht="115.2">
@@ -29087,7 +29053,7 @@
         <v>244</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>842</v>
+        <v>834</v>
       </c>
     </row>
     <row r="98" spans="1:8" ht="259.2">
@@ -29113,7 +29079,7 @@
         <v>246</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>851</v>
+        <v>843</v>
       </c>
     </row>
     <row r="99" spans="1:8" ht="28.8">
@@ -29165,7 +29131,7 @@
         <v>252</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>852</v>
+        <v>844</v>
       </c>
     </row>
     <row r="101" spans="1:8" ht="86.4">
@@ -30647,7 +30613,7 @@
         <v>433</v>
       </c>
       <c r="H157" s="4" t="s">
-        <v>862</v>
+        <v>854</v>
       </c>
     </row>
     <row r="158" spans="1:8">
@@ -30751,7 +30717,7 @@
         <v>444</v>
       </c>
       <c r="H161" s="3" t="s">
-        <v>863</v>
+        <v>872</v>
       </c>
     </row>
     <row r="162" spans="1:8" ht="86.4">
@@ -30959,7 +30925,7 @@
         <v>471</v>
       </c>
       <c r="H169" s="3" t="s">
-        <v>864</v>
+        <v>855</v>
       </c>
     </row>
     <row r="170" spans="1:8" ht="28.8">
@@ -31063,7 +31029,7 @@
         <v>484</v>
       </c>
       <c r="H173" s="5" t="s">
-        <v>867</v>
+        <v>857</v>
       </c>
     </row>
     <row r="174" spans="1:8" ht="28.8">
@@ -31089,7 +31055,7 @@
         <v>486</v>
       </c>
       <c r="H174" s="4" t="s">
-        <v>866</v>
+        <v>856</v>
       </c>
     </row>
     <row r="175" spans="1:8">
@@ -31245,7 +31211,7 @@
         <v>504</v>
       </c>
       <c r="H180" s="3" t="s">
-        <v>865</v>
+        <v>873</v>
       </c>
     </row>
     <row r="181" spans="1:8">
@@ -31479,7 +31445,7 @@
         <v>531</v>
       </c>
       <c r="H189" s="4" t="s">
-        <v>868</v>
+        <v>858</v>
       </c>
     </row>
     <row r="190" spans="1:8" ht="115.2">
@@ -31505,7 +31471,7 @@
         <v>534</v>
       </c>
       <c r="H190" s="3" t="s">
-        <v>869</v>
+        <v>859</v>
       </c>
     </row>
     <row r="191" spans="1:8" ht="28.8">
@@ -31580,10 +31546,10 @@
         <v>12</v>
       </c>
       <c r="G193" s="3" t="s">
-        <v>870</v>
+        <v>860</v>
       </c>
       <c r="H193" s="3" t="s">
-        <v>871</v>
+        <v>861</v>
       </c>
     </row>
     <row r="194" spans="1:8" ht="86.4">
@@ -31606,10 +31572,10 @@
         <v>12</v>
       </c>
       <c r="G194" s="3" t="s">
-        <v>872</v>
+        <v>862</v>
       </c>
       <c r="H194" s="4" t="s">
-        <v>873</v>
+        <v>863</v>
       </c>
     </row>
     <row r="195" spans="1:8" ht="28.8">
@@ -32233,7 +32199,7 @@
         <v>624</v>
       </c>
       <c r="H218" s="3" t="s">
-        <v>853</v>
+        <v>845</v>
       </c>
     </row>
     <row r="219" spans="1:8">
@@ -32467,7 +32433,7 @@
         <v>656</v>
       </c>
       <c r="H227" s="4" t="s">
-        <v>657</v>
+        <v>864</v>
       </c>
     </row>
     <row r="228" spans="1:8" ht="100.8">
@@ -32481,7 +32447,7 @@
         <v>3</v>
       </c>
       <c r="D228" s="2" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="E228" s="2" t="s">
         <v>11</v>
@@ -32490,10 +32456,10 @@
         <v>12</v>
       </c>
       <c r="G228" s="3" t="s">
+        <v>658</v>
+      </c>
+      <c r="H228" s="3" t="s">
         <v>659</v>
-      </c>
-      <c r="H228" s="3" t="s">
-        <v>660</v>
       </c>
     </row>
     <row r="229" spans="1:8" ht="187.2">
@@ -32507,7 +32473,7 @@
         <v>4</v>
       </c>
       <c r="D229" s="2" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="E229" s="2" t="s">
         <v>11</v>
@@ -32516,10 +32482,10 @@
         <v>12</v>
       </c>
       <c r="G229" s="3" t="s">
+        <v>661</v>
+      </c>
+      <c r="H229" s="3" t="s">
         <v>662</v>
-      </c>
-      <c r="H229" s="3" t="s">
-        <v>663</v>
       </c>
     </row>
     <row r="230" spans="1:8" ht="100.8">
@@ -32533,7 +32499,7 @@
         <v>5</v>
       </c>
       <c r="D230" s="2" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="E230" s="2" t="s">
         <v>11</v>
@@ -32542,10 +32508,10 @@
         <v>12</v>
       </c>
       <c r="G230" s="3" t="s">
+        <v>664</v>
+      </c>
+      <c r="H230" s="3" t="s">
         <v>665</v>
-      </c>
-      <c r="H230" s="3" t="s">
-        <v>666</v>
       </c>
     </row>
     <row r="231" spans="1:8" ht="100.8">
@@ -32559,7 +32525,7 @@
         <v>6</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="E231" s="2" t="s">
         <v>11</v>
@@ -32568,10 +32534,10 @@
         <v>12</v>
       </c>
       <c r="G231" s="3" t="s">
+        <v>667</v>
+      </c>
+      <c r="H231" s="3" t="s">
         <v>668</v>
-      </c>
-      <c r="H231" s="3" t="s">
-        <v>669</v>
       </c>
     </row>
     <row r="232" spans="1:8" ht="43.2">
@@ -32585,7 +32551,7 @@
         <v>7</v>
       </c>
       <c r="D232" s="2" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="E232" s="2" t="s">
         <v>11</v>
@@ -32594,10 +32560,10 @@
         <v>12</v>
       </c>
       <c r="G232" s="3" t="s">
+        <v>670</v>
+      </c>
+      <c r="H232" s="3" t="s">
         <v>671</v>
-      </c>
-      <c r="H232" s="3" t="s">
-        <v>672</v>
       </c>
     </row>
     <row r="233" spans="1:8" ht="100.8">
@@ -32611,7 +32577,7 @@
         <v>8</v>
       </c>
       <c r="D233" s="2" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="E233" s="2" t="s">
         <v>11</v>
@@ -32620,10 +32586,10 @@
         <v>12</v>
       </c>
       <c r="G233" s="3" t="s">
+        <v>673</v>
+      </c>
+      <c r="H233" s="3" t="s">
         <v>674</v>
-      </c>
-      <c r="H233" s="3" t="s">
-        <v>675</v>
       </c>
     </row>
     <row r="234" spans="1:8" ht="43.2">
@@ -32637,7 +32603,7 @@
         <v>9</v>
       </c>
       <c r="D234" s="2" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="E234" s="2" t="s">
         <v>11</v>
@@ -32646,10 +32612,10 @@
         <v>12</v>
       </c>
       <c r="G234" s="3" t="s">
+        <v>676</v>
+      </c>
+      <c r="H234" s="3" t="s">
         <v>677</v>
-      </c>
-      <c r="H234" s="3" t="s">
-        <v>678</v>
       </c>
     </row>
     <row r="235" spans="1:8" ht="409.6">
@@ -32663,7 +32629,7 @@
         <v>10</v>
       </c>
       <c r="D235" s="2" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="E235" s="2" t="s">
         <v>11</v>
@@ -32672,10 +32638,10 @@
         <v>12</v>
       </c>
       <c r="G235" s="3" t="s">
+        <v>679</v>
+      </c>
+      <c r="H235" s="3" t="s">
         <v>680</v>
-      </c>
-      <c r="H235" s="3" t="s">
-        <v>681</v>
       </c>
     </row>
     <row r="236" spans="1:8" ht="43.2">
@@ -32689,7 +32655,7 @@
         <v>11</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="E236" s="2" t="s">
         <v>11</v>
@@ -32698,10 +32664,10 @@
         <v>12</v>
       </c>
       <c r="G236" s="3" t="s">
+        <v>682</v>
+      </c>
+      <c r="H236" s="3" t="s">
         <v>683</v>
-      </c>
-      <c r="H236" s="3" t="s">
-        <v>684</v>
       </c>
     </row>
     <row r="237" spans="1:8" ht="43.2">
@@ -32715,7 +32681,7 @@
         <v>12</v>
       </c>
       <c r="D237" s="2" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="E237" s="2" t="s">
         <v>11</v>
@@ -32724,10 +32690,10 @@
         <v>12</v>
       </c>
       <c r="G237" s="3" t="s">
+        <v>685</v>
+      </c>
+      <c r="H237" s="3" t="s">
         <v>686</v>
-      </c>
-      <c r="H237" s="3" t="s">
-        <v>687</v>
       </c>
     </row>
     <row r="238" spans="1:8" ht="115.2">
@@ -32741,7 +32707,7 @@
         <v>13</v>
       </c>
       <c r="D238" s="2" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="E238" s="2" t="s">
         <v>11</v>
@@ -32750,10 +32716,10 @@
         <v>12</v>
       </c>
       <c r="G238" s="3" t="s">
+        <v>688</v>
+      </c>
+      <c r="H238" s="3" t="s">
         <v>689</v>
-      </c>
-      <c r="H238" s="3" t="s">
-        <v>690</v>
       </c>
     </row>
     <row r="239" spans="1:8" ht="43.2">
@@ -32767,7 +32733,7 @@
         <v>14</v>
       </c>
       <c r="D239" s="2" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="E239" s="2" t="s">
         <v>11</v>
@@ -32776,10 +32742,10 @@
         <v>12</v>
       </c>
       <c r="G239" s="3" t="s">
+        <v>691</v>
+      </c>
+      <c r="H239" s="3" t="s">
         <v>692</v>
-      </c>
-      <c r="H239" s="3" t="s">
-        <v>693</v>
       </c>
     </row>
     <row r="240" spans="1:8" ht="43.2">
@@ -32793,7 +32759,7 @@
         <v>15</v>
       </c>
       <c r="D240" s="2" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="E240" s="2" t="s">
         <v>11</v>
@@ -32802,10 +32768,10 @@
         <v>12</v>
       </c>
       <c r="G240" s="3" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="H240" s="3" t="s">
-        <v>696</v>
+        <v>865</v>
       </c>
     </row>
     <row r="241" spans="1:8" ht="115.2">
@@ -32819,7 +32785,7 @@
         <v>16</v>
       </c>
       <c r="D241" s="2" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="E241" s="2" t="s">
         <v>11</v>
@@ -32828,10 +32794,10 @@
         <v>12</v>
       </c>
       <c r="G241" s="3" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="H241" s="3" t="s">
-        <v>699</v>
+        <v>866</v>
       </c>
     </row>
     <row r="242" spans="1:8" ht="129.6">
@@ -32845,7 +32811,7 @@
         <v>17</v>
       </c>
       <c r="D242" s="2" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="E242" s="2" t="s">
         <v>11</v>
@@ -32854,13 +32820,13 @@
         <v>12</v>
       </c>
       <c r="G242" s="3" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="H242" s="3" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
     </row>
-    <row r="243" spans="1:8" ht="129.6">
+    <row r="243" spans="1:8" ht="230.4">
       <c r="A243" s="2" t="s">
         <v>8</v>
       </c>
@@ -32871,7 +32837,7 @@
         <v>18</v>
       </c>
       <c r="D243" s="2" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="E243" s="2" t="s">
         <v>11</v>
@@ -32880,10 +32846,10 @@
         <v>12</v>
       </c>
       <c r="G243" s="3" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="H243" s="3" t="s">
-        <v>705</v>
+        <v>867</v>
       </c>
     </row>
     <row r="244" spans="1:8" ht="100.8">
@@ -32897,7 +32863,7 @@
         <v>19</v>
       </c>
       <c r="D244" s="2" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="E244" s="2" t="s">
         <v>11</v>
@@ -32906,10 +32872,10 @@
         <v>12</v>
       </c>
       <c r="G244" s="3" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="H244" s="3" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
     </row>
     <row r="245" spans="1:8" ht="86.4">
@@ -32923,7 +32889,7 @@
         <v>20</v>
       </c>
       <c r="D245" s="2" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="E245" s="2" t="s">
         <v>11</v>
@@ -32932,10 +32898,10 @@
         <v>12</v>
       </c>
       <c r="G245" s="3" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="H245" s="3" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
     </row>
     <row r="246" spans="1:8" ht="216">
@@ -32949,7 +32915,7 @@
         <v>21</v>
       </c>
       <c r="D246" s="2" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="E246" s="2" t="s">
         <v>11</v>
@@ -32958,10 +32924,10 @@
         <v>12</v>
       </c>
       <c r="G246" s="3" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="H246" s="3" t="s">
-        <v>714</v>
+        <v>868</v>
       </c>
     </row>
     <row r="247" spans="1:8" ht="100.8">
@@ -32975,7 +32941,7 @@
         <v>22</v>
       </c>
       <c r="D247" s="2" t="s">
-        <v>715</v>
+        <v>710</v>
       </c>
       <c r="E247" s="2" t="s">
         <v>11</v>
@@ -32984,10 +32950,10 @@
         <v>12</v>
       </c>
       <c r="G247" s="3" t="s">
-        <v>716</v>
+        <v>711</v>
       </c>
       <c r="H247" s="3" t="s">
-        <v>717</v>
+        <v>712</v>
       </c>
     </row>
     <row r="248" spans="1:8" ht="187.2">
@@ -33001,7 +32967,7 @@
         <v>23</v>
       </c>
       <c r="D248" s="2" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="E248" s="2" t="s">
         <v>11</v>
@@ -33010,10 +32976,10 @@
         <v>12</v>
       </c>
       <c r="G248" s="3" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="H248" s="3" t="s">
-        <v>720</v>
+        <v>869</v>
       </c>
     </row>
     <row r="249" spans="1:8" ht="28.8">
@@ -33027,7 +32993,7 @@
         <v>24</v>
       </c>
       <c r="D249" s="2" t="s">
-        <v>721</v>
+        <v>715</v>
       </c>
       <c r="E249" s="2" t="s">
         <v>11</v>
@@ -33036,10 +33002,10 @@
         <v>12</v>
       </c>
       <c r="G249" s="3" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="H249" s="4" t="s">
-        <v>723</v>
+        <v>717</v>
       </c>
     </row>
     <row r="250" spans="1:8" ht="43.2">
@@ -33053,7 +33019,7 @@
         <v>25</v>
       </c>
       <c r="D250" s="2" t="s">
-        <v>724</v>
+        <v>718</v>
       </c>
       <c r="E250" s="2" t="s">
         <v>11</v>
@@ -33062,10 +33028,10 @@
         <v>12</v>
       </c>
       <c r="G250" s="3" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="H250" s="3" t="s">
-        <v>726</v>
+        <v>720</v>
       </c>
     </row>
     <row r="251" spans="1:8" ht="43.2">
@@ -33079,7 +33045,7 @@
         <v>26</v>
       </c>
       <c r="D251" s="2" t="s">
-        <v>727</v>
+        <v>721</v>
       </c>
       <c r="E251" s="2" t="s">
         <v>11</v>
@@ -33088,10 +33054,10 @@
         <v>12</v>
       </c>
       <c r="G251" s="3" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="H251" s="3" t="s">
-        <v>729</v>
+        <v>723</v>
       </c>
     </row>
     <row r="252" spans="1:8" ht="43.2">
@@ -33105,7 +33071,7 @@
         <v>27</v>
       </c>
       <c r="D252" s="2" t="s">
-        <v>730</v>
+        <v>724</v>
       </c>
       <c r="E252" s="2" t="s">
         <v>11</v>
@@ -33114,10 +33080,10 @@
         <v>12</v>
       </c>
       <c r="G252" s="3" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="H252" s="3" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
     </row>
     <row r="253" spans="1:8">
@@ -33125,13 +33091,13 @@
         <v>8</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>733</v>
+        <v>727</v>
       </c>
       <c r="C253" s="2">
         <v>0</v>
       </c>
       <c r="D253" s="2" t="s">
-        <v>734</v>
+        <v>728</v>
       </c>
       <c r="E253" s="2" t="s">
         <v>11</v>
@@ -33140,10 +33106,10 @@
         <v>12</v>
       </c>
       <c r="G253" s="3" t="s">
-        <v>735</v>
+        <v>729</v>
       </c>
       <c r="H253" s="4" t="s">
-        <v>736</v>
+        <v>730</v>
       </c>
     </row>
     <row r="254" spans="1:8" ht="100.8">
@@ -33151,13 +33117,13 @@
         <v>8</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>733</v>
+        <v>727</v>
       </c>
       <c r="C254" s="2">
         <v>2</v>
       </c>
       <c r="D254" s="2" t="s">
-        <v>737</v>
+        <v>731</v>
       </c>
       <c r="E254" s="2" t="s">
         <v>11</v>
@@ -33166,10 +33132,10 @@
         <v>12</v>
       </c>
       <c r="G254" s="3" t="s">
-        <v>738</v>
+        <v>732</v>
       </c>
       <c r="H254" s="3" t="s">
-        <v>739</v>
+        <v>733</v>
       </c>
     </row>
     <row r="255" spans="1:8">
@@ -33177,13 +33143,13 @@
         <v>8</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>740</v>
+        <v>734</v>
       </c>
       <c r="C255" s="2">
         <v>0</v>
       </c>
       <c r="D255" s="2" t="s">
-        <v>741</v>
+        <v>735</v>
       </c>
       <c r="E255" s="2" t="s">
         <v>11</v>
@@ -33192,10 +33158,10 @@
         <v>12</v>
       </c>
       <c r="G255" s="3" t="s">
-        <v>742</v>
+        <v>736</v>
       </c>
       <c r="H255" s="4" t="s">
-        <v>743</v>
+        <v>737</v>
       </c>
     </row>
     <row r="256" spans="1:8">
@@ -33203,13 +33169,13 @@
         <v>8</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>744</v>
+        <v>738</v>
       </c>
       <c r="C256" s="2">
         <v>0</v>
       </c>
       <c r="D256" s="2" t="s">
-        <v>745</v>
+        <v>739</v>
       </c>
       <c r="E256" s="2" t="s">
         <v>11</v>
@@ -33218,10 +33184,10 @@
         <v>12</v>
       </c>
       <c r="G256" s="3" t="s">
-        <v>746</v>
+        <v>740</v>
       </c>
       <c r="H256" s="4" t="s">
-        <v>747</v>
+        <v>741</v>
       </c>
     </row>
     <row r="257" spans="1:8" ht="28.8">
@@ -33229,13 +33195,13 @@
         <v>8</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>748</v>
+        <v>742</v>
       </c>
       <c r="C257" s="2">
         <v>0</v>
       </c>
       <c r="D257" s="2" t="s">
-        <v>749</v>
+        <v>743</v>
       </c>
       <c r="E257" s="2" t="s">
         <v>11</v>
@@ -33244,10 +33210,10 @@
         <v>12</v>
       </c>
       <c r="G257" s="3" t="s">
-        <v>750</v>
+        <v>744</v>
       </c>
       <c r="H257" s="3" t="s">
-        <v>751</v>
+        <v>745</v>
       </c>
     </row>
     <row r="258" spans="1:8" ht="43.2">
@@ -33255,13 +33221,13 @@
         <v>8</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>748</v>
+        <v>742</v>
       </c>
       <c r="C258" s="2">
         <v>1</v>
       </c>
       <c r="D258" s="2" t="s">
-        <v>752</v>
+        <v>746</v>
       </c>
       <c r="E258" s="2" t="s">
         <v>11</v>
@@ -33270,10 +33236,10 @@
         <v>12</v>
       </c>
       <c r="G258" s="3" t="s">
-        <v>753</v>
+        <v>747</v>
       </c>
       <c r="H258" s="3" t="s">
-        <v>754</v>
+        <v>748</v>
       </c>
     </row>
     <row r="259" spans="1:8" ht="100.8">
@@ -33281,13 +33247,13 @@
         <v>8</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>748</v>
+        <v>742</v>
       </c>
       <c r="C259" s="2">
         <v>2</v>
       </c>
       <c r="D259" s="2" t="s">
-        <v>755</v>
+        <v>749</v>
       </c>
       <c r="E259" s="2" t="s">
         <v>11</v>
@@ -33296,10 +33262,10 @@
         <v>12</v>
       </c>
       <c r="G259" s="3" t="s">
-        <v>756</v>
+        <v>750</v>
       </c>
       <c r="H259" s="3" t="s">
-        <v>757</v>
+        <v>751</v>
       </c>
     </row>
     <row r="260" spans="1:8" ht="43.2">
@@ -33307,13 +33273,13 @@
         <v>8</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>748</v>
+        <v>742</v>
       </c>
       <c r="C260" s="2">
         <v>3</v>
       </c>
       <c r="D260" s="2" t="s">
-        <v>758</v>
+        <v>752</v>
       </c>
       <c r="E260" s="2" t="s">
         <v>11</v>
@@ -33322,10 +33288,10 @@
         <v>12</v>
       </c>
       <c r="G260" s="3" t="s">
-        <v>759</v>
+        <v>753</v>
       </c>
       <c r="H260" s="3" t="s">
-        <v>760</v>
+        <v>754</v>
       </c>
     </row>
     <row r="261" spans="1:8">
@@ -33333,13 +33299,13 @@
         <v>8</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>761</v>
+        <v>755</v>
       </c>
       <c r="C261" s="2">
         <v>0</v>
       </c>
       <c r="D261" s="2" t="s">
-        <v>762</v>
+        <v>756</v>
       </c>
       <c r="E261" s="2" t="s">
         <v>11</v>
@@ -33348,10 +33314,10 @@
         <v>12</v>
       </c>
       <c r="G261" s="3" t="s">
-        <v>763</v>
+        <v>757</v>
       </c>
       <c r="H261" s="4" t="s">
-        <v>764</v>
+        <v>758</v>
       </c>
     </row>
     <row r="262" spans="1:8">
@@ -33359,13 +33325,13 @@
         <v>8</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>765</v>
+        <v>759</v>
       </c>
       <c r="C262" s="2">
         <v>0</v>
       </c>
       <c r="D262" s="2" t="s">
-        <v>766</v>
+        <v>760</v>
       </c>
       <c r="E262" s="2" t="s">
         <v>11</v>
@@ -33374,10 +33340,10 @@
         <v>12</v>
       </c>
       <c r="G262" s="3" t="s">
-        <v>767</v>
+        <v>761</v>
       </c>
       <c r="H262" s="4" t="s">
-        <v>768</v>
+        <v>762</v>
       </c>
     </row>
     <row r="263" spans="1:8">
@@ -33385,13 +33351,13 @@
         <v>8</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>769</v>
+        <v>763</v>
       </c>
       <c r="C263" s="2">
         <v>0</v>
       </c>
       <c r="D263" s="2" t="s">
-        <v>770</v>
+        <v>764</v>
       </c>
       <c r="E263" s="2" t="s">
         <v>11</v>
@@ -33400,10 +33366,10 @@
         <v>12</v>
       </c>
       <c r="G263" s="3" t="s">
-        <v>771</v>
+        <v>765</v>
       </c>
       <c r="H263" s="4" t="s">
-        <v>772</v>
+        <v>766</v>
       </c>
     </row>
     <row r="264" spans="1:8">
@@ -33411,13 +33377,13 @@
         <v>8</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>769</v>
+        <v>763</v>
       </c>
       <c r="C264" s="2">
         <v>1</v>
       </c>
       <c r="D264" s="2" t="s">
-        <v>773</v>
+        <v>767</v>
       </c>
       <c r="E264" s="2" t="s">
         <v>11</v>
@@ -33426,10 +33392,10 @@
         <v>12</v>
       </c>
       <c r="G264" s="3" t="s">
-        <v>774</v>
+        <v>768</v>
       </c>
       <c r="H264" s="4" t="s">
-        <v>775</v>
+        <v>769</v>
       </c>
     </row>
     <row r="265" spans="1:8" ht="28.8">
@@ -33437,13 +33403,13 @@
         <v>8</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>776</v>
+        <v>770</v>
       </c>
       <c r="C265" s="2">
         <v>0</v>
       </c>
       <c r="D265" s="2" t="s">
-        <v>777</v>
+        <v>771</v>
       </c>
       <c r="E265" s="2" t="s">
         <v>11</v>
@@ -33452,10 +33418,10 @@
         <v>12</v>
       </c>
       <c r="G265" s="3" t="s">
-        <v>778</v>
+        <v>772</v>
       </c>
       <c r="H265" s="4" t="s">
-        <v>779</v>
+        <v>773</v>
       </c>
     </row>
   </sheetData>

--- a/docassemble/PowerOfAttorneyProperty/data/sources/poa_property_es.xlsx
+++ b/docassemble/PowerOfAttorneyProperty/data/sources/poa_property_es.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mnewsted\local-DA-easyforms-dev\sources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FADC3D69-E4A2-4306-ABAE-0B8DFC2924BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD53EF1A-201E-4428-8367-63AE692310AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38625" yWindow="-3330" windowWidth="35685" windowHeight="16530" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-34920" yWindow="-525" windowWidth="25725" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/docassemble/PowerOfAttorneyProperty/data/sources/poa_property_es.xlsx
+++ b/docassemble/PowerOfAttorneyProperty/data/sources/poa_property_es.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mnewsted\local-DA-easyforms-dev\sources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD53EF1A-201E-4428-8367-63AE692310AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65BA16E6-7E83-4ADE-80E9-31D37C50F427}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-34920" yWindow="-525" windowWidth="25725" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-35940" yWindow="-2955" windowWidth="25725" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -7032,56 +7032,6 @@
     </r>
   </si>
   <si>
-    <t>c2a97d85c8990c8d0a0b1ad00ee6aff9</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${your_subject}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> acting agent can amend or revoke that delegation at any time. 
-</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${your_subject}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> agente actuante puede enmendar o revocar esa delegación en cualquier momento.</t>
-    </r>
-  </si>
-  <si>
     <t>082c7d0ac8e63192470ce3f5a17e6eef</t>
   </si>
   <si>
@@ -26107,6 +26057,56 @@
         <scheme val="minor"/>
       </rPr>
       <t>${collapse_template(prove_capacity)}</t>
+    </r>
+  </si>
+  <si>
+    <t>8c0ad13a48d4426f27eaa339ea07d0b9</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${capitalize(your_subject)}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> acting agent can amend or revoke that delegation at any time. 
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${capitalize(your_subject)}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> agente actuante puede enmendar o revocar esa delegación en cualquier momento.</t>
     </r>
   </si>
 </sst>
@@ -26583,7 +26583,7 @@
         <v>13</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="403.2">
@@ -26597,7 +26597,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>11</v>
@@ -26606,10 +26606,10 @@
         <v>12</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="187.2">
@@ -26635,7 +26635,7 @@
         <v>16</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="28.8">
@@ -26661,7 +26661,7 @@
         <v>19</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="302.39999999999998">
@@ -26687,7 +26687,7 @@
         <v>21</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>838</v>
+        <v>835</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -26713,7 +26713,7 @@
         <v>24</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="72">
@@ -26739,7 +26739,7 @@
         <v>26</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -26765,7 +26765,7 @@
         <v>28</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="43.2">
@@ -26791,7 +26791,7 @@
         <v>30</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="28.8">
@@ -26843,7 +26843,7 @@
         <v>35</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>870</v>
+        <v>867</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="43.2">
@@ -26869,7 +26869,7 @@
         <v>38</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="43.2">
@@ -26895,7 +26895,7 @@
         <v>40</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="86.4">
@@ -26921,7 +26921,7 @@
         <v>43</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="115.2">
@@ -26947,7 +26947,7 @@
         <v>46</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="28.8">
@@ -26999,7 +26999,7 @@
         <v>52</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="273.60000000000002">
@@ -27025,7 +27025,7 @@
         <v>54</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="28.8">
@@ -27051,7 +27051,7 @@
         <v>57</v>
       </c>
       <c r="H20" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="129.6">
@@ -27077,7 +27077,7 @@
         <v>59</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>871</v>
+        <v>868</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -27103,7 +27103,7 @@
         <v>62</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="43.2">
@@ -27129,7 +27129,7 @@
         <v>64</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="72">
@@ -27155,7 +27155,7 @@
         <v>66</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="28.8">
@@ -27181,7 +27181,7 @@
         <v>68</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="57.6">
@@ -27207,7 +27207,7 @@
         <v>70</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -27233,7 +27233,7 @@
         <v>72</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -27259,7 +27259,7 @@
         <v>74</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="28.8">
@@ -27285,7 +27285,7 @@
         <v>77</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="259.2">
@@ -27311,7 +27311,7 @@
         <v>79</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="86.4">
@@ -27337,7 +27337,7 @@
         <v>82</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="403.2">
@@ -27363,7 +27363,7 @@
         <v>84</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -27389,7 +27389,7 @@
         <v>86</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -27415,7 +27415,7 @@
         <v>88</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -27441,7 +27441,7 @@
         <v>90</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -27467,7 +27467,7 @@
         <v>92</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -27519,7 +27519,7 @@
         <v>97</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="115.2">
@@ -27545,7 +27545,7 @@
         <v>100</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="28.8">
@@ -27571,7 +27571,7 @@
         <v>102</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="28.8">
@@ -27597,7 +27597,7 @@
         <v>105</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="86.4">
@@ -27623,7 +27623,7 @@
         <v>108</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="28.8">
@@ -27649,7 +27649,7 @@
         <v>111</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>848</v>
+        <v>845</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="144">
@@ -27701,7 +27701,7 @@
         <v>117</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>801</v>
+        <v>798</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="86.4">
@@ -27727,7 +27727,7 @@
         <v>120</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="86.4">
@@ -27753,7 +27753,7 @@
         <v>123</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="345.6">
@@ -27779,7 +27779,7 @@
         <v>125</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="28.8">
@@ -27805,7 +27805,7 @@
         <v>128</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="28.8">
@@ -27857,7 +27857,7 @@
         <v>133</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="43.2">
@@ -27883,7 +27883,7 @@
         <v>135</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
     </row>
     <row r="53" spans="1:8">
@@ -27909,7 +27909,7 @@
         <v>137</v>
       </c>
       <c r="H53" t="s">
-        <v>850</v>
+        <v>847</v>
       </c>
     </row>
     <row r="54" spans="1:8">
@@ -27935,7 +27935,7 @@
         <v>139</v>
       </c>
       <c r="H54" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="129.6">
@@ -27961,7 +27961,7 @@
         <v>142</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="28.8">
@@ -27987,7 +27987,7 @@
         <v>144</v>
       </c>
       <c r="H56" s="4" t="s">
-        <v>849</v>
+        <v>846</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="28.8">
@@ -28039,7 +28039,7 @@
         <v>150</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="115.2">
@@ -28065,7 +28065,7 @@
         <v>153</v>
       </c>
       <c r="H59" s="5" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="28.8">
@@ -28117,7 +28117,7 @@
         <v>159</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="244.8">
@@ -28143,7 +28143,7 @@
         <v>161</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>810</v>
+        <v>807</v>
       </c>
     </row>
     <row r="63" spans="1:8">
@@ -28169,7 +28169,7 @@
         <v>163</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
     </row>
     <row r="64" spans="1:8">
@@ -28195,7 +28195,7 @@
         <v>165</v>
       </c>
       <c r="H64" s="4" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="43.2">
@@ -28247,7 +28247,7 @@
         <v>170</v>
       </c>
       <c r="H66" s="4" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="43.2">
@@ -28273,7 +28273,7 @@
         <v>172</v>
       </c>
       <c r="H67" s="4" t="s">
-        <v>853</v>
+        <v>850</v>
       </c>
     </row>
     <row r="68" spans="1:8">
@@ -28325,7 +28325,7 @@
         <v>177</v>
       </c>
       <c r="H69" s="4" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
     </row>
     <row r="70" spans="1:8">
@@ -28351,7 +28351,7 @@
         <v>179</v>
       </c>
       <c r="H70" s="4" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="72">
@@ -28377,7 +28377,7 @@
         <v>181</v>
       </c>
       <c r="H71" s="4" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
     </row>
     <row r="72" spans="1:8">
@@ -28403,7 +28403,7 @@
         <v>183</v>
       </c>
       <c r="H72" s="4" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="43.2">
@@ -28429,7 +28429,7 @@
         <v>185</v>
       </c>
       <c r="H73" s="4" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -28481,7 +28481,7 @@
         <v>190</v>
       </c>
       <c r="H75" s="4" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
     </row>
     <row r="76" spans="1:8">
@@ -28507,7 +28507,7 @@
         <v>192</v>
       </c>
       <c r="H76" s="4" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
     </row>
     <row r="77" spans="1:8" ht="43.2">
@@ -28533,7 +28533,7 @@
         <v>194</v>
       </c>
       <c r="H77" s="4" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
     </row>
     <row r="78" spans="1:8">
@@ -28559,7 +28559,7 @@
         <v>196</v>
       </c>
       <c r="H78" s="4" t="s">
-        <v>822</v>
+        <v>819</v>
       </c>
     </row>
     <row r="79" spans="1:8" ht="57.6">
@@ -28585,7 +28585,7 @@
         <v>198</v>
       </c>
       <c r="H79" s="4" t="s">
-        <v>823</v>
+        <v>820</v>
       </c>
     </row>
     <row r="80" spans="1:8">
@@ -28637,7 +28637,7 @@
         <v>203</v>
       </c>
       <c r="H81" s="4" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
     </row>
     <row r="82" spans="1:8">
@@ -28689,7 +28689,7 @@
         <v>208</v>
       </c>
       <c r="H83" s="4" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
     </row>
     <row r="84" spans="1:8">
@@ -28741,7 +28741,7 @@
         <v>213</v>
       </c>
       <c r="H85" s="4" t="s">
-        <v>826</v>
+        <v>823</v>
       </c>
     </row>
     <row r="86" spans="1:8">
@@ -28793,7 +28793,7 @@
         <v>218</v>
       </c>
       <c r="H87" s="4" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
     </row>
     <row r="88" spans="1:8">
@@ -28845,7 +28845,7 @@
         <v>223</v>
       </c>
       <c r="H89" s="4" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
     </row>
     <row r="90" spans="1:8">
@@ -28871,7 +28871,7 @@
         <v>225</v>
       </c>
       <c r="H90" s="4" t="s">
-        <v>828</v>
+        <v>825</v>
       </c>
     </row>
     <row r="91" spans="1:8" ht="43.2">
@@ -28897,7 +28897,7 @@
         <v>227</v>
       </c>
       <c r="H91" s="4" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
     </row>
     <row r="92" spans="1:8">
@@ -28949,7 +28949,7 @@
         <v>232</v>
       </c>
       <c r="H93" s="4" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
     </row>
     <row r="94" spans="1:8">
@@ -29001,7 +29001,7 @@
         <v>238</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>832</v>
+        <v>829</v>
       </c>
     </row>
     <row r="96" spans="1:8" ht="100.8">
@@ -29027,7 +29027,7 @@
         <v>241</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>833</v>
+        <v>830</v>
       </c>
     </row>
     <row r="97" spans="1:8" ht="115.2">
@@ -29053,7 +29053,7 @@
         <v>244</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
     </row>
     <row r="98" spans="1:8" ht="259.2">
@@ -29079,7 +29079,7 @@
         <v>246</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
     </row>
     <row r="99" spans="1:8" ht="28.8">
@@ -29131,7 +29131,7 @@
         <v>252</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
     </row>
     <row r="101" spans="1:8" ht="86.4">
@@ -30122,7 +30122,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="139" spans="1:8" ht="28.8">
+    <row r="139" spans="1:8" ht="43.2">
       <c r="A139" s="2" t="s">
         <v>8</v>
       </c>
@@ -30133,7 +30133,7 @@
         <v>3</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>375</v>
+        <v>871</v>
       </c>
       <c r="E139" s="2" t="s">
         <v>11</v>
@@ -30142,10 +30142,10 @@
         <v>12</v>
       </c>
       <c r="G139" s="3" t="s">
-        <v>376</v>
+        <v>872</v>
       </c>
       <c r="H139" s="3" t="s">
-        <v>377</v>
+        <v>873</v>
       </c>
     </row>
     <row r="140" spans="1:8">
@@ -30159,7 +30159,7 @@
         <v>4</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="E140" s="2" t="s">
         <v>11</v>
@@ -30168,10 +30168,10 @@
         <v>12</v>
       </c>
       <c r="G140" s="3" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="H140" s="3" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
     </row>
     <row r="141" spans="1:8">
@@ -30185,7 +30185,7 @@
         <v>5</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="E141" s="2" t="s">
         <v>11</v>
@@ -30194,10 +30194,10 @@
         <v>12</v>
       </c>
       <c r="G141" s="3" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="H141" s="3" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
     </row>
     <row r="142" spans="1:8">
@@ -30211,7 +30211,7 @@
         <v>6</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="E142" s="2" t="s">
         <v>11</v>
@@ -30220,10 +30220,10 @@
         <v>12</v>
       </c>
       <c r="G142" s="3" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="H142" s="3" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
     </row>
     <row r="143" spans="1:8" ht="187.2">
@@ -30231,13 +30231,13 @@
         <v>8</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="C143" s="2">
         <v>0</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="E143" s="2" t="s">
         <v>11</v>
@@ -30246,10 +30246,10 @@
         <v>12</v>
       </c>
       <c r="G143" s="3" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="H143" s="3" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
     </row>
     <row r="144" spans="1:8" ht="28.8">
@@ -30257,13 +30257,13 @@
         <v>8</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="C144" s="2">
         <v>1</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="E144" s="2" t="s">
         <v>11</v>
@@ -30272,10 +30272,10 @@
         <v>12</v>
       </c>
       <c r="G144" s="3" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="H144" s="4" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
     </row>
     <row r="145" spans="1:8" ht="115.2">
@@ -30283,13 +30283,13 @@
         <v>8</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="C145" s="2">
         <v>0</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="E145" s="2" t="s">
         <v>11</v>
@@ -30298,10 +30298,10 @@
         <v>12</v>
       </c>
       <c r="G145" s="3" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="H145" s="3" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
     </row>
     <row r="146" spans="1:8" ht="316.8">
@@ -30309,13 +30309,13 @@
         <v>8</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="C146" s="2">
         <v>1</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="E146" s="2" t="s">
         <v>11</v>
@@ -30324,10 +30324,10 @@
         <v>12</v>
       </c>
       <c r="G146" s="3" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="H146" s="3" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="147" spans="1:8" ht="28.8">
@@ -30335,13 +30335,13 @@
         <v>8</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="C147" s="2">
         <v>2</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="E147" s="2" t="s">
         <v>11</v>
@@ -30350,10 +30350,10 @@
         <v>12</v>
       </c>
       <c r="G147" s="3" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="H147" s="3" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
     </row>
     <row r="148" spans="1:8">
@@ -30361,13 +30361,13 @@
         <v>8</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="C148" s="2">
         <v>3</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="E148" s="2" t="s">
         <v>11</v>
@@ -30376,10 +30376,10 @@
         <v>12</v>
       </c>
       <c r="G148" s="3" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="H148" s="3" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="149" spans="1:8" ht="28.8">
@@ -30387,13 +30387,13 @@
         <v>8</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="C149" s="2">
         <v>4</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="E149" s="2" t="s">
         <v>11</v>
@@ -30402,10 +30402,10 @@
         <v>12</v>
       </c>
       <c r="G149" s="3" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="H149" s="3" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
     </row>
     <row r="150" spans="1:8">
@@ -30413,13 +30413,13 @@
         <v>8</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="C150" s="2">
         <v>5</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="E150" s="2" t="s">
         <v>11</v>
@@ -30428,10 +30428,10 @@
         <v>12</v>
       </c>
       <c r="G150" s="3" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="H150" s="4" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="151" spans="1:8">
@@ -30439,13 +30439,13 @@
         <v>8</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="C151" s="2">
         <v>7</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="E151" s="2" t="s">
         <v>11</v>
@@ -30454,10 +30454,10 @@
         <v>12</v>
       </c>
       <c r="G151" s="3" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="H151" s="4" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
     </row>
     <row r="152" spans="1:8">
@@ -30465,13 +30465,13 @@
         <v>8</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="C152" s="2">
         <v>8</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="E152" s="2" t="s">
         <v>11</v>
@@ -30480,10 +30480,10 @@
         <v>12</v>
       </c>
       <c r="G152" s="3" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="H152" s="4" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
     </row>
     <row r="153" spans="1:8">
@@ -30491,13 +30491,13 @@
         <v>8</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="C153" s="2">
         <v>9</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="E153" s="2" t="s">
         <v>11</v>
@@ -30506,10 +30506,10 @@
         <v>12</v>
       </c>
       <c r="G153" s="3" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="H153" s="4" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
     </row>
     <row r="154" spans="1:8">
@@ -30517,13 +30517,13 @@
         <v>8</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="C154" s="2">
         <v>10</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="E154" s="2" t="s">
         <v>11</v>
@@ -30532,10 +30532,10 @@
         <v>12</v>
       </c>
       <c r="G154" s="3" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="H154" s="4" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
     </row>
     <row r="155" spans="1:8">
@@ -30543,13 +30543,13 @@
         <v>8</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="C155" s="2">
         <v>11</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="E155" s="2" t="s">
         <v>11</v>
@@ -30558,10 +30558,10 @@
         <v>12</v>
       </c>
       <c r="G155" s="3" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="H155" s="4" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
     </row>
     <row r="156" spans="1:8">
@@ -30569,13 +30569,13 @@
         <v>8</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="C156" s="2">
         <v>0</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="E156" s="2" t="s">
         <v>11</v>
@@ -30584,10 +30584,10 @@
         <v>12</v>
       </c>
       <c r="G156" s="3" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="H156" s="4" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
     </row>
     <row r="157" spans="1:8" ht="115.2">
@@ -30595,13 +30595,13 @@
         <v>8</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="C157" s="2">
         <v>1</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="E157" s="2" t="s">
         <v>11</v>
@@ -30610,10 +30610,10 @@
         <v>12</v>
       </c>
       <c r="G157" s="3" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="H157" s="4" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
     </row>
     <row r="158" spans="1:8">
@@ -30621,13 +30621,13 @@
         <v>8</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="C158" s="2">
         <v>2</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="E158" s="2" t="s">
         <v>11</v>
@@ -30636,10 +30636,10 @@
         <v>12</v>
       </c>
       <c r="G158" s="3" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="H158" s="4" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
     </row>
     <row r="159" spans="1:8" ht="43.2">
@@ -30647,13 +30647,13 @@
         <v>8</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="C159" s="2">
         <v>3</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="E159" s="2" t="s">
         <v>11</v>
@@ -30662,10 +30662,10 @@
         <v>12</v>
       </c>
       <c r="G159" s="3" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="H159" s="4" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
     </row>
     <row r="160" spans="1:8" ht="86.4">
@@ -30673,13 +30673,13 @@
         <v>8</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="C160" s="2">
         <v>4</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="E160" s="2" t="s">
         <v>11</v>
@@ -30688,10 +30688,10 @@
         <v>12</v>
       </c>
       <c r="G160" s="3" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="H160" s="3" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
     </row>
     <row r="161" spans="1:8" ht="216">
@@ -30699,13 +30699,13 @@
         <v>8</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="C161" s="2">
         <v>5</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="E161" s="2" t="s">
         <v>11</v>
@@ -30714,10 +30714,10 @@
         <v>12</v>
       </c>
       <c r="G161" s="3" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="H161" s="3" t="s">
-        <v>872</v>
+        <v>869</v>
       </c>
     </row>
     <row r="162" spans="1:8" ht="86.4">
@@ -30725,13 +30725,13 @@
         <v>8</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="C162" s="2">
         <v>0</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="E162" s="2" t="s">
         <v>11</v>
@@ -30740,10 +30740,10 @@
         <v>12</v>
       </c>
       <c r="G162" s="3" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="H162" s="3" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
     </row>
     <row r="163" spans="1:8" ht="72">
@@ -30751,13 +30751,13 @@
         <v>8</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="C163" s="2">
         <v>1</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="E163" s="2" t="s">
         <v>11</v>
@@ -30766,10 +30766,10 @@
         <v>12</v>
       </c>
       <c r="G163" s="3" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="H163" s="3" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
     </row>
     <row r="164" spans="1:8">
@@ -30777,13 +30777,13 @@
         <v>8</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="C164" s="2">
         <v>2</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="E164" s="2" t="s">
         <v>11</v>
@@ -30792,10 +30792,10 @@
         <v>12</v>
       </c>
       <c r="G164" s="3" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="H164" s="4" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
     </row>
     <row r="165" spans="1:8" ht="86.4">
@@ -30803,13 +30803,13 @@
         <v>8</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="C165" s="2">
         <v>0</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="E165" s="2" t="s">
         <v>11</v>
@@ -30818,10 +30818,10 @@
         <v>12</v>
       </c>
       <c r="G165" s="3" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="H165" s="3" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
     </row>
     <row r="166" spans="1:8" ht="28.8">
@@ -30829,13 +30829,13 @@
         <v>8</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="C166" s="2">
         <v>0</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="E166" s="2" t="s">
         <v>11</v>
@@ -30844,10 +30844,10 @@
         <v>12</v>
       </c>
       <c r="G166" s="3" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="H166" s="3" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
     </row>
     <row r="167" spans="1:8" ht="28.8">
@@ -30855,13 +30855,13 @@
         <v>8</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="C167" s="2">
         <v>1</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="E167" s="2" t="s">
         <v>11</v>
@@ -30870,10 +30870,10 @@
         <v>12</v>
       </c>
       <c r="G167" s="3" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="H167" s="5" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
     </row>
     <row r="168" spans="1:8">
@@ -30881,13 +30881,13 @@
         <v>8</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="C168" s="2">
         <v>2</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="E168" s="2" t="s">
         <v>11</v>
@@ -30896,10 +30896,10 @@
         <v>12</v>
       </c>
       <c r="G168" s="3" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H168" s="3" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
     </row>
     <row r="169" spans="1:8" ht="129.6">
@@ -30907,13 +30907,13 @@
         <v>8</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="C169" s="2">
         <v>0</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="E169" s="2" t="s">
         <v>11</v>
@@ -30922,10 +30922,10 @@
         <v>12</v>
       </c>
       <c r="G169" s="3" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="H169" s="3" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
     </row>
     <row r="170" spans="1:8" ht="28.8">
@@ -30933,13 +30933,13 @@
         <v>8</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="C170" s="2">
         <v>1</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="E170" s="2" t="s">
         <v>11</v>
@@ -30948,10 +30948,10 @@
         <v>12</v>
       </c>
       <c r="G170" s="3" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="H170" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
     </row>
     <row r="171" spans="1:8" ht="28.8">
@@ -30959,13 +30959,13 @@
         <v>8</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="C171" s="2">
         <v>0</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="E171" s="2" t="s">
         <v>11</v>
@@ -30974,10 +30974,10 @@
         <v>12</v>
       </c>
       <c r="G171" s="3" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="H171" s="3" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
     </row>
     <row r="172" spans="1:8" ht="100.8">
@@ -30985,13 +30985,13 @@
         <v>8</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="C172" s="2">
         <v>1</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="E172" s="2" t="s">
         <v>11</v>
@@ -31000,10 +31000,10 @@
         <v>12</v>
       </c>
       <c r="G172" s="3" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="H172" s="3" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
     </row>
     <row r="173" spans="1:8" ht="115.2">
@@ -31011,13 +31011,13 @@
         <v>8</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="C173" s="2">
         <v>0</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="E173" s="2" t="s">
         <v>11</v>
@@ -31026,10 +31026,10 @@
         <v>12</v>
       </c>
       <c r="G173" s="3" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="H173" s="5" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
     </row>
     <row r="174" spans="1:8" ht="28.8">
@@ -31037,13 +31037,13 @@
         <v>8</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="C174" s="2">
         <v>1</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="E174" s="2" t="s">
         <v>11</v>
@@ -31052,10 +31052,10 @@
         <v>12</v>
       </c>
       <c r="G174" s="3" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="H174" s="4" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
     </row>
     <row r="175" spans="1:8">
@@ -31063,13 +31063,13 @@
         <v>8</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="C175" s="2">
         <v>0</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="E175" s="2" t="s">
         <v>11</v>
@@ -31078,10 +31078,10 @@
         <v>12</v>
       </c>
       <c r="G175" s="3" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="H175" s="4" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
     </row>
     <row r="176" spans="1:8" ht="28.8">
@@ -31089,13 +31089,13 @@
         <v>8</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="C176" s="2">
         <v>1</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="E176" s="2" t="s">
         <v>11</v>
@@ -31104,10 +31104,10 @@
         <v>12</v>
       </c>
       <c r="G176" s="3" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="H176" s="4" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
     </row>
     <row r="177" spans="1:8">
@@ -31115,13 +31115,13 @@
         <v>8</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="C177" s="2">
         <v>2</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="E177" s="2" t="s">
         <v>11</v>
@@ -31130,10 +31130,10 @@
         <v>12</v>
       </c>
       <c r="G177" s="3" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="H177" s="4" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
     </row>
     <row r="178" spans="1:8" ht="86.4">
@@ -31141,13 +31141,13 @@
         <v>8</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="C178" s="2">
         <v>3</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="E178" s="2" t="s">
         <v>11</v>
@@ -31156,10 +31156,10 @@
         <v>12</v>
       </c>
       <c r="G178" s="3" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="H178" s="3" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
     </row>
     <row r="179" spans="1:8" ht="86.4">
@@ -31167,13 +31167,13 @@
         <v>8</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="C179" s="2">
         <v>4</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="E179" s="2" t="s">
         <v>11</v>
@@ -31182,10 +31182,10 @@
         <v>12</v>
       </c>
       <c r="G179" s="3" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="H179" s="3" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
     </row>
     <row r="180" spans="1:8" ht="409.6">
@@ -31193,13 +31193,13 @@
         <v>8</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="C180" s="2">
         <v>5</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="E180" s="2" t="s">
         <v>11</v>
@@ -31208,10 +31208,10 @@
         <v>12</v>
       </c>
       <c r="G180" s="3" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="H180" s="3" t="s">
-        <v>873</v>
+        <v>870</v>
       </c>
     </row>
     <row r="181" spans="1:8">
@@ -31219,13 +31219,13 @@
         <v>8</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="C181" s="2">
         <v>6</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="E181" s="2" t="s">
         <v>11</v>
@@ -31234,10 +31234,10 @@
         <v>12</v>
       </c>
       <c r="G181" s="3" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="H181" s="4" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
     </row>
     <row r="182" spans="1:8" ht="144">
@@ -31245,13 +31245,13 @@
         <v>8</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="C182" s="2">
         <v>7</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="E182" s="2" t="s">
         <v>11</v>
@@ -31260,10 +31260,10 @@
         <v>12</v>
       </c>
       <c r="G182" s="3" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="H182" s="3" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
     </row>
     <row r="183" spans="1:8" ht="28.8">
@@ -31271,13 +31271,13 @@
         <v>8</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="C183" s="2">
         <v>8</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="E183" s="2" t="s">
         <v>11</v>
@@ -31286,10 +31286,10 @@
         <v>12</v>
       </c>
       <c r="G183" s="3" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="H183" s="3" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
     </row>
     <row r="184" spans="1:8" ht="57.6">
@@ -31297,13 +31297,13 @@
         <v>8</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="C184" s="2">
         <v>9</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="E184" s="2" t="s">
         <v>11</v>
@@ -31312,10 +31312,10 @@
         <v>12</v>
       </c>
       <c r="G184" s="3" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="H184" s="3" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
     </row>
     <row r="185" spans="1:8" ht="28.8">
@@ -31323,13 +31323,13 @@
         <v>8</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="C185" s="2">
         <v>10</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="E185" s="2" t="s">
         <v>11</v>
@@ -31338,10 +31338,10 @@
         <v>12</v>
       </c>
       <c r="G185" s="3" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="H185" s="3" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
     </row>
     <row r="186" spans="1:8">
@@ -31349,13 +31349,13 @@
         <v>8</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="C186" s="2">
         <v>11</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="E186" s="2" t="s">
         <v>11</v>
@@ -31364,10 +31364,10 @@
         <v>12</v>
       </c>
       <c r="G186" s="3" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="H186" s="4" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
     </row>
     <row r="187" spans="1:8">
@@ -31375,13 +31375,13 @@
         <v>8</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="C187" s="2">
         <v>12</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="E187" s="2" t="s">
         <v>11</v>
@@ -31390,10 +31390,10 @@
         <v>12</v>
       </c>
       <c r="G187" s="3" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="H187" s="4" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
     </row>
     <row r="188" spans="1:8" ht="115.2">
@@ -31401,13 +31401,13 @@
         <v>8</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="C188" s="2">
         <v>0</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="E188" s="2" t="s">
         <v>11</v>
@@ -31416,10 +31416,10 @@
         <v>12</v>
       </c>
       <c r="G188" s="3" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="H188" s="3" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
     </row>
     <row r="189" spans="1:8" ht="28.8">
@@ -31427,13 +31427,13 @@
         <v>8</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="C189" s="2">
         <v>1</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="E189" s="2" t="s">
         <v>11</v>
@@ -31442,10 +31442,10 @@
         <v>12</v>
       </c>
       <c r="G189" s="3" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="H189" s="4" t="s">
-        <v>858</v>
+        <v>855</v>
       </c>
     </row>
     <row r="190" spans="1:8" ht="115.2">
@@ -31453,13 +31453,13 @@
         <v>8</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="C190" s="2">
         <v>0</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="E190" s="2" t="s">
         <v>11</v>
@@ -31468,10 +31468,10 @@
         <v>12</v>
       </c>
       <c r="G190" s="3" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="H190" s="3" t="s">
-        <v>859</v>
+        <v>856</v>
       </c>
     </row>
     <row r="191" spans="1:8" ht="28.8">
@@ -31479,13 +31479,13 @@
         <v>8</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="C191" s="2">
         <v>1</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="E191" s="2" t="s">
         <v>11</v>
@@ -31494,10 +31494,10 @@
         <v>12</v>
       </c>
       <c r="G191" s="3" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="H191" s="4" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
     </row>
     <row r="192" spans="1:8" ht="86.4">
@@ -31505,13 +31505,13 @@
         <v>8</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="C192" s="2">
         <v>0</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="E192" s="2" t="s">
         <v>11</v>
@@ -31520,10 +31520,10 @@
         <v>12</v>
       </c>
       <c r="G192" s="3" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="H192" s="3" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
     </row>
     <row r="193" spans="1:8" ht="316.8">
@@ -31531,13 +31531,13 @@
         <v>8</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="C193" s="2">
         <v>1</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="E193" s="2" t="s">
         <v>11</v>
@@ -31546,10 +31546,10 @@
         <v>12</v>
       </c>
       <c r="G193" s="3" t="s">
-        <v>860</v>
+        <v>857</v>
       </c>
       <c r="H193" s="3" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
     </row>
     <row r="194" spans="1:8" ht="86.4">
@@ -31557,13 +31557,13 @@
         <v>8</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="C194" s="2">
         <v>0</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="E194" s="2" t="s">
         <v>11</v>
@@ -31572,10 +31572,10 @@
         <v>12</v>
       </c>
       <c r="G194" s="3" t="s">
-        <v>862</v>
+        <v>859</v>
       </c>
       <c r="H194" s="4" t="s">
-        <v>863</v>
+        <v>860</v>
       </c>
     </row>
     <row r="195" spans="1:8" ht="28.8">
@@ -31583,13 +31583,13 @@
         <v>8</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="C195" s="2">
         <v>1</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="E195" s="2" t="s">
         <v>11</v>
@@ -31598,10 +31598,10 @@
         <v>12</v>
       </c>
       <c r="G195" s="3" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="H195" s="4" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
     </row>
     <row r="196" spans="1:8" ht="86.4">
@@ -31609,13 +31609,13 @@
         <v>8</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="C196" s="2">
         <v>0</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="E196" s="2" t="s">
         <v>11</v>
@@ -31624,10 +31624,10 @@
         <v>12</v>
       </c>
       <c r="G196" s="3" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="H196" s="3" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
     </row>
     <row r="197" spans="1:8" ht="201.6">
@@ -31635,13 +31635,13 @@
         <v>8</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="C197" s="2">
         <v>1</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="E197" s="2" t="s">
         <v>11</v>
@@ -31650,10 +31650,10 @@
         <v>12</v>
       </c>
       <c r="G197" s="3" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="H197" s="3" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
     </row>
     <row r="198" spans="1:8" ht="28.8">
@@ -31661,13 +31661,13 @@
         <v>8</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="C198" s="2">
         <v>2</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="E198" s="2" t="s">
         <v>11</v>
@@ -31676,10 +31676,10 @@
         <v>12</v>
       </c>
       <c r="G198" s="3" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="H198" s="3" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
     </row>
     <row r="199" spans="1:8">
@@ -31687,13 +31687,13 @@
         <v>8</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="C199" s="2">
         <v>3</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="E199" s="2" t="s">
         <v>11</v>
@@ -31702,10 +31702,10 @@
         <v>12</v>
       </c>
       <c r="G199" s="3" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="H199" s="3" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
     </row>
     <row r="200" spans="1:8" ht="100.8">
@@ -31713,13 +31713,13 @@
         <v>8</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="C200" s="2">
         <v>4</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="E200" s="2" t="s">
         <v>11</v>
@@ -31728,10 +31728,10 @@
         <v>12</v>
       </c>
       <c r="G200" s="3" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="H200" s="4" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
     </row>
     <row r="201" spans="1:8" ht="28.8">
@@ -31739,13 +31739,13 @@
         <v>8</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="C201" s="2">
         <v>5</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="E201" s="2" t="s">
         <v>11</v>
@@ -31754,10 +31754,10 @@
         <v>12</v>
       </c>
       <c r="G201" s="3" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="H201" s="3" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
     </row>
     <row r="202" spans="1:8">
@@ -31765,13 +31765,13 @@
         <v>8</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="C202" s="2">
         <v>6</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="E202" s="2" t="s">
         <v>11</v>
@@ -31780,10 +31780,10 @@
         <v>12</v>
       </c>
       <c r="G202" s="3" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="H202" s="4" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
     </row>
     <row r="203" spans="1:8">
@@ -31791,13 +31791,13 @@
         <v>8</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="C203" s="2">
         <v>7</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="E203" s="2" t="s">
         <v>11</v>
@@ -31806,10 +31806,10 @@
         <v>12</v>
       </c>
       <c r="G203" s="3" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="H203" s="4" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
     </row>
     <row r="204" spans="1:8" ht="100.8">
@@ -31817,13 +31817,13 @@
         <v>8</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="C204" s="2">
         <v>0</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="E204" s="2" t="s">
         <v>11</v>
@@ -31832,10 +31832,10 @@
         <v>12</v>
       </c>
       <c r="G204" s="3" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="H204" s="3" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
     </row>
     <row r="205" spans="1:8" ht="244.8">
@@ -31843,13 +31843,13 @@
         <v>8</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="C205" s="2">
         <v>1</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="E205" s="2" t="s">
         <v>11</v>
@@ -31858,10 +31858,10 @@
         <v>12</v>
       </c>
       <c r="G205" s="3" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="H205" s="3" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
     </row>
     <row r="206" spans="1:8" ht="28.8">
@@ -31869,13 +31869,13 @@
         <v>8</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="C206" s="2">
         <v>0</v>
       </c>
       <c r="D206" s="2" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="E206" s="2" t="s">
         <v>11</v>
@@ -31884,10 +31884,10 @@
         <v>12</v>
       </c>
       <c r="G206" s="3" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="H206" s="4" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
     </row>
     <row r="207" spans="1:8" ht="43.2">
@@ -31895,13 +31895,13 @@
         <v>8</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="C207" s="2">
         <v>1</v>
       </c>
       <c r="D207" s="2" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="E207" s="2" t="s">
         <v>11</v>
@@ -31910,10 +31910,10 @@
         <v>12</v>
       </c>
       <c r="G207" s="3" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="H207" s="3" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
     </row>
     <row r="208" spans="1:8" ht="28.8">
@@ -31921,13 +31921,13 @@
         <v>8</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="C208" s="2">
         <v>0</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="E208" s="2" t="s">
         <v>11</v>
@@ -31936,10 +31936,10 @@
         <v>12</v>
       </c>
       <c r="G208" s="3" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="H208" s="4" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
     </row>
     <row r="209" spans="1:8" ht="28.8">
@@ -31947,13 +31947,13 @@
         <v>8</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="C209" s="2">
         <v>0</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="E209" s="2" t="s">
         <v>11</v>
@@ -31962,10 +31962,10 @@
         <v>12</v>
       </c>
       <c r="G209" s="3" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="H209" s="4" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
     </row>
     <row r="210" spans="1:8" ht="28.8">
@@ -31973,13 +31973,13 @@
         <v>8</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="C210" s="2">
         <v>1</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="E210" s="2" t="s">
         <v>11</v>
@@ -31988,10 +31988,10 @@
         <v>12</v>
       </c>
       <c r="G210" s="3" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="H210" s="4" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
     </row>
     <row r="211" spans="1:8" ht="28.8">
@@ -31999,13 +31999,13 @@
         <v>8</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="C211" s="2">
         <v>0</v>
       </c>
       <c r="D211" s="2" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="E211" s="2" t="s">
         <v>11</v>
@@ -32014,10 +32014,10 @@
         <v>12</v>
       </c>
       <c r="G211" s="3" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="H211" s="4" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
     </row>
     <row r="212" spans="1:8" ht="409.6">
@@ -32025,13 +32025,13 @@
         <v>8</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="C212" s="2">
         <v>1</v>
       </c>
       <c r="D212" s="2" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="E212" s="2" t="s">
         <v>11</v>
@@ -32040,10 +32040,10 @@
         <v>12</v>
       </c>
       <c r="G212" s="3" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="H212" s="3" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="213" spans="1:8" ht="86.4">
@@ -32051,13 +32051,13 @@
         <v>8</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="C213" s="2">
         <v>0</v>
       </c>
       <c r="D213" s="2" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="E213" s="2" t="s">
         <v>11</v>
@@ -32066,10 +32066,10 @@
         <v>12</v>
       </c>
       <c r="G213" s="3" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="H213" s="4" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
     </row>
     <row r="214" spans="1:8" ht="86.4">
@@ -32077,13 +32077,13 @@
         <v>8</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="C214" s="2">
         <v>1</v>
       </c>
       <c r="D214" s="2" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="E214" s="2" t="s">
         <v>11</v>
@@ -32092,10 +32092,10 @@
         <v>12</v>
       </c>
       <c r="G214" s="3" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="H214" s="3" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
     </row>
     <row r="215" spans="1:8" ht="28.8">
@@ -32103,13 +32103,13 @@
         <v>8</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="C215" s="2">
         <v>0</v>
       </c>
       <c r="D215" s="2" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="E215" s="2" t="s">
         <v>11</v>
@@ -32118,10 +32118,10 @@
         <v>12</v>
       </c>
       <c r="G215" s="3" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="H215" s="4" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
     </row>
     <row r="216" spans="1:8" ht="403.2">
@@ -32129,13 +32129,13 @@
         <v>8</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="C216" s="2">
         <v>1</v>
       </c>
       <c r="D216" s="2" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="E216" s="2" t="s">
         <v>11</v>
@@ -32144,10 +32144,10 @@
         <v>12</v>
       </c>
       <c r="G216" s="3" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="H216" s="3" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
     </row>
     <row r="217" spans="1:8" ht="187.2">
@@ -32155,13 +32155,13 @@
         <v>8</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="C217" s="2">
         <v>2</v>
       </c>
       <c r="D217" s="2" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="E217" s="2" t="s">
         <v>11</v>
@@ -32170,10 +32170,10 @@
         <v>12</v>
       </c>
       <c r="G217" s="3" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="H217" s="3" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
     </row>
     <row r="218" spans="1:8" ht="86.4">
@@ -32181,13 +32181,13 @@
         <v>8</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="C218" s="2">
         <v>0</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="E218" s="2" t="s">
         <v>11</v>
@@ -32196,10 +32196,10 @@
         <v>12</v>
       </c>
       <c r="G218" s="3" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="H218" s="3" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
     </row>
     <row r="219" spans="1:8">
@@ -32207,13 +32207,13 @@
         <v>8</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="C219" s="2">
         <v>1</v>
       </c>
       <c r="D219" s="2" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="E219" s="2" t="s">
         <v>11</v>
@@ -32225,7 +32225,7 @@
         <v>22</v>
       </c>
       <c r="H219" s="4" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
     </row>
     <row r="220" spans="1:8">
@@ -32233,13 +32233,13 @@
         <v>8</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="C220" s="2">
         <v>0</v>
       </c>
       <c r="D220" s="2" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="E220" s="2" t="s">
         <v>11</v>
@@ -32248,10 +32248,10 @@
         <v>12</v>
       </c>
       <c r="G220" s="3" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="H220" s="4" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
     </row>
     <row r="221" spans="1:8">
@@ -32259,13 +32259,13 @@
         <v>8</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="C221" s="2">
         <v>0</v>
       </c>
       <c r="D221" s="2" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="E221" s="2" t="s">
         <v>11</v>
@@ -32274,10 +32274,10 @@
         <v>12</v>
       </c>
       <c r="G221" s="3" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="H221" s="4" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
     </row>
     <row r="222" spans="1:8">
@@ -32285,13 +32285,13 @@
         <v>8</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="C222" s="2">
         <v>0</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="E222" s="2" t="s">
         <v>11</v>
@@ -32300,10 +32300,10 @@
         <v>12</v>
       </c>
       <c r="G222" s="3" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="H222" s="4" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
     </row>
     <row r="223" spans="1:8">
@@ -32311,13 +32311,13 @@
         <v>8</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="C223" s="2">
         <v>0</v>
       </c>
       <c r="D223" s="2" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="E223" s="2" t="s">
         <v>11</v>
@@ -32326,10 +32326,10 @@
         <v>12</v>
       </c>
       <c r="G223" s="3" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="H223" s="4" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
     </row>
     <row r="224" spans="1:8">
@@ -32337,13 +32337,13 @@
         <v>8</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="C224" s="2">
         <v>0</v>
       </c>
       <c r="D224" s="2" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="E224" s="2" t="s">
         <v>11</v>
@@ -32352,10 +32352,10 @@
         <v>12</v>
       </c>
       <c r="G224" s="3" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="H224" s="4" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
     </row>
     <row r="225" spans="1:8" ht="28.8">
@@ -32363,13 +32363,13 @@
         <v>8</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C225" s="2">
         <v>0</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="E225" s="2" t="s">
         <v>11</v>
@@ -32378,10 +32378,10 @@
         <v>12</v>
       </c>
       <c r="G225" s="3" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="H225" s="4" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
     </row>
     <row r="226" spans="1:8" ht="28.8">
@@ -32389,13 +32389,13 @@
         <v>8</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C226" s="2">
         <v>1</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="E226" s="2" t="s">
         <v>11</v>
@@ -32404,10 +32404,10 @@
         <v>12</v>
       </c>
       <c r="G226" s="3" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="H226" s="4" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
     </row>
     <row r="227" spans="1:8">
@@ -32415,13 +32415,13 @@
         <v>8</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C227" s="2">
         <v>2</v>
       </c>
       <c r="D227" s="2" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="E227" s="2" t="s">
         <v>11</v>
@@ -32430,10 +32430,10 @@
         <v>12</v>
       </c>
       <c r="G227" s="3" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="H227" s="4" t="s">
-        <v>864</v>
+        <v>861</v>
       </c>
     </row>
     <row r="228" spans="1:8" ht="100.8">
@@ -32441,13 +32441,13 @@
         <v>8</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C228" s="2">
         <v>3</v>
       </c>
       <c r="D228" s="2" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="E228" s="2" t="s">
         <v>11</v>
@@ -32456,10 +32456,10 @@
         <v>12</v>
       </c>
       <c r="G228" s="3" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="H228" s="3" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
     </row>
     <row r="229" spans="1:8" ht="187.2">
@@ -32467,13 +32467,13 @@
         <v>8</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C229" s="2">
         <v>4</v>
       </c>
       <c r="D229" s="2" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="E229" s="2" t="s">
         <v>11</v>
@@ -32482,10 +32482,10 @@
         <v>12</v>
       </c>
       <c r="G229" s="3" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="H229" s="3" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
     </row>
     <row r="230" spans="1:8" ht="100.8">
@@ -32493,13 +32493,13 @@
         <v>8</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C230" s="2">
         <v>5</v>
       </c>
       <c r="D230" s="2" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="E230" s="2" t="s">
         <v>11</v>
@@ -32508,10 +32508,10 @@
         <v>12</v>
       </c>
       <c r="G230" s="3" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="H230" s="3" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
     </row>
     <row r="231" spans="1:8" ht="100.8">
@@ -32519,13 +32519,13 @@
         <v>8</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C231" s="2">
         <v>6</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="E231" s="2" t="s">
         <v>11</v>
@@ -32534,10 +32534,10 @@
         <v>12</v>
       </c>
       <c r="G231" s="3" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="H231" s="3" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
     </row>
     <row r="232" spans="1:8" ht="43.2">
@@ -32545,13 +32545,13 @@
         <v>8</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C232" s="2">
         <v>7</v>
       </c>
       <c r="D232" s="2" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="E232" s="2" t="s">
         <v>11</v>
@@ -32560,10 +32560,10 @@
         <v>12</v>
       </c>
       <c r="G232" s="3" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="H232" s="3" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
     </row>
     <row r="233" spans="1:8" ht="100.8">
@@ -32571,13 +32571,13 @@
         <v>8</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C233" s="2">
         <v>8</v>
       </c>
       <c r="D233" s="2" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="E233" s="2" t="s">
         <v>11</v>
@@ -32586,10 +32586,10 @@
         <v>12</v>
       </c>
       <c r="G233" s="3" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="H233" s="3" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
     </row>
     <row r="234" spans="1:8" ht="43.2">
@@ -32597,13 +32597,13 @@
         <v>8</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C234" s="2">
         <v>9</v>
       </c>
       <c r="D234" s="2" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="E234" s="2" t="s">
         <v>11</v>
@@ -32612,10 +32612,10 @@
         <v>12</v>
       </c>
       <c r="G234" s="3" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="H234" s="3" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
     </row>
     <row r="235" spans="1:8" ht="409.6">
@@ -32623,13 +32623,13 @@
         <v>8</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C235" s="2">
         <v>10</v>
       </c>
       <c r="D235" s="2" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="E235" s="2" t="s">
         <v>11</v>
@@ -32638,10 +32638,10 @@
         <v>12</v>
       </c>
       <c r="G235" s="3" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="H235" s="3" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
     </row>
     <row r="236" spans="1:8" ht="43.2">
@@ -32649,13 +32649,13 @@
         <v>8</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C236" s="2">
         <v>11</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="E236" s="2" t="s">
         <v>11</v>
@@ -32664,10 +32664,10 @@
         <v>12</v>
       </c>
       <c r="G236" s="3" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="H236" s="3" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
     </row>
     <row r="237" spans="1:8" ht="43.2">
@@ -32675,13 +32675,13 @@
         <v>8</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C237" s="2">
         <v>12</v>
       </c>
       <c r="D237" s="2" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="E237" s="2" t="s">
         <v>11</v>
@@ -32690,10 +32690,10 @@
         <v>12</v>
       </c>
       <c r="G237" s="3" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="H237" s="3" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
     </row>
     <row r="238" spans="1:8" ht="115.2">
@@ -32701,13 +32701,13 @@
         <v>8</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C238" s="2">
         <v>13</v>
       </c>
       <c r="D238" s="2" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="E238" s="2" t="s">
         <v>11</v>
@@ -32716,10 +32716,10 @@
         <v>12</v>
       </c>
       <c r="G238" s="3" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="H238" s="3" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
     </row>
     <row r="239" spans="1:8" ht="43.2">
@@ -32727,13 +32727,13 @@
         <v>8</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C239" s="2">
         <v>14</v>
       </c>
       <c r="D239" s="2" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="E239" s="2" t="s">
         <v>11</v>
@@ -32742,10 +32742,10 @@
         <v>12</v>
       </c>
       <c r="G239" s="3" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="H239" s="3" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
     </row>
     <row r="240" spans="1:8" ht="43.2">
@@ -32753,13 +32753,13 @@
         <v>8</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C240" s="2">
         <v>15</v>
       </c>
       <c r="D240" s="2" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="E240" s="2" t="s">
         <v>11</v>
@@ -32768,10 +32768,10 @@
         <v>12</v>
       </c>
       <c r="G240" s="3" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="H240" s="3" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
     </row>
     <row r="241" spans="1:8" ht="115.2">
@@ -32779,13 +32779,13 @@
         <v>8</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C241" s="2">
         <v>16</v>
       </c>
       <c r="D241" s="2" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="E241" s="2" t="s">
         <v>11</v>
@@ -32794,10 +32794,10 @@
         <v>12</v>
       </c>
       <c r="G241" s="3" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="H241" s="3" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
     </row>
     <row r="242" spans="1:8" ht="129.6">
@@ -32805,13 +32805,13 @@
         <v>8</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C242" s="2">
         <v>17</v>
       </c>
       <c r="D242" s="2" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="E242" s="2" t="s">
         <v>11</v>
@@ -32820,10 +32820,10 @@
         <v>12</v>
       </c>
       <c r="G242" s="3" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="H242" s="3" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
     </row>
     <row r="243" spans="1:8" ht="230.4">
@@ -32831,13 +32831,13 @@
         <v>8</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C243" s="2">
         <v>18</v>
       </c>
       <c r="D243" s="2" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="E243" s="2" t="s">
         <v>11</v>
@@ -32846,10 +32846,10 @@
         <v>12</v>
       </c>
       <c r="G243" s="3" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="H243" s="3" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
     </row>
     <row r="244" spans="1:8" ht="100.8">
@@ -32857,13 +32857,13 @@
         <v>8</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C244" s="2">
         <v>19</v>
       </c>
       <c r="D244" s="2" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="E244" s="2" t="s">
         <v>11</v>
@@ -32872,10 +32872,10 @@
         <v>12</v>
       </c>
       <c r="G244" s="3" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="H244" s="3" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
     </row>
     <row r="245" spans="1:8" ht="86.4">
@@ -32883,13 +32883,13 @@
         <v>8</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C245" s="2">
         <v>20</v>
       </c>
       <c r="D245" s="2" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="E245" s="2" t="s">
         <v>11</v>
@@ -32898,10 +32898,10 @@
         <v>12</v>
       </c>
       <c r="G245" s="3" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="H245" s="3" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
     </row>
     <row r="246" spans="1:8" ht="216">
@@ -32909,13 +32909,13 @@
         <v>8</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C246" s="2">
         <v>21</v>
       </c>
       <c r="D246" s="2" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="E246" s="2" t="s">
         <v>11</v>
@@ -32924,10 +32924,10 @@
         <v>12</v>
       </c>
       <c r="G246" s="3" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="H246" s="3" t="s">
-        <v>868</v>
+        <v>865</v>
       </c>
     </row>
     <row r="247" spans="1:8" ht="100.8">
@@ -32935,13 +32935,13 @@
         <v>8</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C247" s="2">
         <v>22</v>
       </c>
       <c r="D247" s="2" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="E247" s="2" t="s">
         <v>11</v>
@@ -32950,10 +32950,10 @@
         <v>12</v>
       </c>
       <c r="G247" s="3" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="H247" s="3" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
     </row>
     <row r="248" spans="1:8" ht="187.2">
@@ -32961,13 +32961,13 @@
         <v>8</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C248" s="2">
         <v>23</v>
       </c>
       <c r="D248" s="2" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="E248" s="2" t="s">
         <v>11</v>
@@ -32976,10 +32976,10 @@
         <v>12</v>
       </c>
       <c r="G248" s="3" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="H248" s="3" t="s">
-        <v>869</v>
+        <v>866</v>
       </c>
     </row>
     <row r="249" spans="1:8" ht="28.8">
@@ -32987,13 +32987,13 @@
         <v>8</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C249" s="2">
         <v>24</v>
       </c>
       <c r="D249" s="2" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="E249" s="2" t="s">
         <v>11</v>
@@ -33002,10 +33002,10 @@
         <v>12</v>
       </c>
       <c r="G249" s="3" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="H249" s="4" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
     </row>
     <row r="250" spans="1:8" ht="43.2">
@@ -33013,13 +33013,13 @@
         <v>8</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C250" s="2">
         <v>25</v>
       </c>
       <c r="D250" s="2" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="E250" s="2" t="s">
         <v>11</v>
@@ -33028,10 +33028,10 @@
         <v>12</v>
       </c>
       <c r="G250" s="3" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="H250" s="3" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
     </row>
     <row r="251" spans="1:8" ht="43.2">
@@ -33039,13 +33039,13 @@
         <v>8</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C251" s="2">
         <v>26</v>
       </c>
       <c r="D251" s="2" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="E251" s="2" t="s">
         <v>11</v>
@@ -33054,10 +33054,10 @@
         <v>12</v>
       </c>
       <c r="G251" s="3" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="H251" s="3" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
     </row>
     <row r="252" spans="1:8" ht="43.2">
@@ -33065,13 +33065,13 @@
         <v>8</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C252" s="2">
         <v>27</v>
       </c>
       <c r="D252" s="2" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="E252" s="2" t="s">
         <v>11</v>
@@ -33080,10 +33080,10 @@
         <v>12</v>
       </c>
       <c r="G252" s="3" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="H252" s="3" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
     </row>
     <row r="253" spans="1:8">
@@ -33091,13 +33091,13 @@
         <v>8</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="C253" s="2">
         <v>0</v>
       </c>
       <c r="D253" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E253" s="2" t="s">
         <v>11</v>
@@ -33106,10 +33106,10 @@
         <v>12</v>
       </c>
       <c r="G253" s="3" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="H253" s="4" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
     </row>
     <row r="254" spans="1:8" ht="100.8">
@@ -33117,13 +33117,13 @@
         <v>8</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="C254" s="2">
         <v>2</v>
       </c>
       <c r="D254" s="2" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="E254" s="2" t="s">
         <v>11</v>
@@ -33132,10 +33132,10 @@
         <v>12</v>
       </c>
       <c r="G254" s="3" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="H254" s="3" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
     </row>
     <row r="255" spans="1:8">
@@ -33143,13 +33143,13 @@
         <v>8</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="C255" s="2">
         <v>0</v>
       </c>
       <c r="D255" s="2" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="E255" s="2" t="s">
         <v>11</v>
@@ -33158,10 +33158,10 @@
         <v>12</v>
       </c>
       <c r="G255" s="3" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="H255" s="4" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
     </row>
     <row r="256" spans="1:8">
@@ -33169,13 +33169,13 @@
         <v>8</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="C256" s="2">
         <v>0</v>
       </c>
       <c r="D256" s="2" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="E256" s="2" t="s">
         <v>11</v>
@@ -33184,10 +33184,10 @@
         <v>12</v>
       </c>
       <c r="G256" s="3" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="H256" s="4" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
     </row>
     <row r="257" spans="1:8" ht="28.8">
@@ -33195,13 +33195,13 @@
         <v>8</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="C257" s="2">
         <v>0</v>
       </c>
       <c r="D257" s="2" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="E257" s="2" t="s">
         <v>11</v>
@@ -33210,10 +33210,10 @@
         <v>12</v>
       </c>
       <c r="G257" s="3" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="H257" s="3" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
     </row>
     <row r="258" spans="1:8" ht="43.2">
@@ -33221,13 +33221,13 @@
         <v>8</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="C258" s="2">
         <v>1</v>
       </c>
       <c r="D258" s="2" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="E258" s="2" t="s">
         <v>11</v>
@@ -33236,10 +33236,10 @@
         <v>12</v>
       </c>
       <c r="G258" s="3" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="H258" s="3" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
     </row>
     <row r="259" spans="1:8" ht="100.8">
@@ -33247,13 +33247,13 @@
         <v>8</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="C259" s="2">
         <v>2</v>
       </c>
       <c r="D259" s="2" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="E259" s="2" t="s">
         <v>11</v>
@@ -33262,10 +33262,10 @@
         <v>12</v>
       </c>
       <c r="G259" s="3" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="H259" s="3" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
     </row>
     <row r="260" spans="1:8" ht="43.2">
@@ -33273,13 +33273,13 @@
         <v>8</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="C260" s="2">
         <v>3</v>
       </c>
       <c r="D260" s="2" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="E260" s="2" t="s">
         <v>11</v>
@@ -33288,10 +33288,10 @@
         <v>12</v>
       </c>
       <c r="G260" s="3" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="H260" s="3" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
     </row>
     <row r="261" spans="1:8">
@@ -33299,13 +33299,13 @@
         <v>8</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="C261" s="2">
         <v>0</v>
       </c>
       <c r="D261" s="2" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="E261" s="2" t="s">
         <v>11</v>
@@ -33314,10 +33314,10 @@
         <v>12</v>
       </c>
       <c r="G261" s="3" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="H261" s="4" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
     </row>
     <row r="262" spans="1:8">
@@ -33325,13 +33325,13 @@
         <v>8</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="C262" s="2">
         <v>0</v>
       </c>
       <c r="D262" s="2" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="E262" s="2" t="s">
         <v>11</v>
@@ -33340,10 +33340,10 @@
         <v>12</v>
       </c>
       <c r="G262" s="3" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="H262" s="4" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
     </row>
     <row r="263" spans="1:8">
@@ -33351,13 +33351,13 @@
         <v>8</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="C263" s="2">
         <v>0</v>
       </c>
       <c r="D263" s="2" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="E263" s="2" t="s">
         <v>11</v>
@@ -33366,10 +33366,10 @@
         <v>12</v>
       </c>
       <c r="G263" s="3" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="H263" s="4" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
     </row>
     <row r="264" spans="1:8">
@@ -33377,13 +33377,13 @@
         <v>8</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="C264" s="2">
         <v>1</v>
       </c>
       <c r="D264" s="2" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="E264" s="2" t="s">
         <v>11</v>
@@ -33392,10 +33392,10 @@
         <v>12</v>
       </c>
       <c r="G264" s="3" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="H264" s="4" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
     </row>
     <row r="265" spans="1:8" ht="28.8">
@@ -33403,13 +33403,13 @@
         <v>8</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="C265" s="2">
         <v>0</v>
       </c>
       <c r="D265" s="2" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="E265" s="2" t="s">
         <v>11</v>
@@ -33418,10 +33418,10 @@
         <v>12</v>
       </c>
       <c r="G265" s="3" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="H265" s="4" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
     </row>
   </sheetData>

--- a/docassemble/PowerOfAttorneyProperty/data/sources/poa_property_es.xlsx
+++ b/docassemble/PowerOfAttorneyProperty/data/sources/poa_property_es.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mnewsted\local-DA-easyforms-dev\sources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65BA16E6-7E83-4ADE-80E9-31D37C50F427}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{667B85E0-3196-4831-B614-DC39CCF34DB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-35940" yWindow="-2955" windowWidth="25725" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38160" yWindow="-4650" windowWidth="19830" windowHeight="19665" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -3287,9 +3287,6 @@
     <t>All other property transactions</t>
   </si>
   <si>
-    <t>Todas las demás transacciones de propiedad</t>
-  </si>
-  <si>
     <t>ee7764928395d10b4a7eefe7ba8a05b1</t>
   </si>
   <si>
@@ -13132,151 +13129,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">“Nombrar” significa sugerir o proponer a una persona que un tribunal puede elegir para actuar como tutor.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% if for_yourself == True:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Un tribunal puede considerar necesario designar a un tutor legal para tomar decisiones sobre sus asuntos financieros. Un tutor de su patrimonio tendría derechos, poderes y deberes sobre su propiedad y finanzas.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% else:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Un tribunal puede considerar necesario designar a un tutor legal para tomar decisiones sobre </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${principal.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">'s financial affairs. Un tutor de su patrimonio tendría derechos, poderes y deberes sobre su propiedad y finanzas.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% endif
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Si hace clic en **No**, entonces un tribunal puede designar a alguien distinto de </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${agent.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> para que sea tutor si es necesario. Incluso si hace clic en **Sí**, un tribunal aún puede designar a otra persona como tutor si estima que </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${agent.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> está incumpliendo su deber.</t>
-    </r>
-  </si>
-  <si>
     <t>include preparer</t>
   </si>
   <si>
@@ -21281,9 +21133,6 @@
     <t>Acerca de los agentes</t>
   </si>
   <si>
-    <t>Cómo completar este formulario</t>
-  </si>
-  <si>
     <t>Otorgante</t>
   </si>
   <si>
@@ -21294,12 +21143,6 @@
   </si>
   <si>
     <t>¿Estás haciendo estos formularios para ti mismo(a)?</t>
-  </si>
-  <si>
-    <t>Sí, estoy haciendo un Poder Notarial para la Propiedad y Finanzas para mí.</t>
-  </si>
-  <si>
-    <t>No, estoy haciendo un Poder Notarial para la Propiedad y Finanzas para otra persona.</t>
   </si>
   <si>
     <t>Hacer un Poder Notarial para otra persona</t>
@@ -22056,172 +21899,6 @@
   <si>
     <r>
       <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${collapse_template(video_agent)}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% if for_yourself == False:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">El agente es la persona que tomará decisiones sobre la propiedad y finanzas de </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${principal.name_full()}.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 
-El agente es la persona en quien </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${principal.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> confía para tomar decisiones sobre su propiedad y sus finanzas. Es muy importante que </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>${principal.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> hable con su agente sobre sus deseos con respeto a sus finanzas y todo lo que posee. Estas conversaciones ayudarán a guiar las decisiones del agente y a asegurar que estén de acuerdo.
-Un agente tiene mucho poder, y es posible que abuse de ese poder.  </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${principal.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> debe elegir a alguien en quien confíe para manejar sus finanzas y todo lo que posee.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% else:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Tu agente es la persona en quien confías para tomar decisiones sobre tu propiedad y tus finanzas. Es muy importante que hables con tu agente sobre tus deseos sobre tus finanzas y todo lo que posees. Estas conversaciones ayudarán a guiar sus decisiones y a asegurar que estén de acuerdo.
-Un agente tiene mucho poder, y es posible que abuse de ese poder. Debes elegir a alguien en quien confíes para manejar tus finanzas y todo lo que posees.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>% endif</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
@@ -22484,285 +22161,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>${collapse_template(video_agent_powers)}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% if for_yourself:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Un Poder Notarial para la Propiedad y Finanzas generalmente le da al agente el poder de manejar toda la propiedad y las finanzas del otorgante. Si quieres que </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${agent.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> pueda tomar decisiones sobre toda tu propiedad y tus finanzas, puedes hacer clic en **</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${i_subject}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri (Body)"/>
-      </rPr>
-      <t>quiero que/ quiere que</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${agent.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> tenga todos estos poderes**.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">%  else:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Un Poder Notarial para la Propiedad y Finanzas generalmente le da al agente el poder de manejar toda la propiedad y las finanzas del otorgante. Si </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${principal.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> quiere que </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${agent.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> pueda tomar decisiones sobre todas su propiedad y sus finanzas, puedes hacer clic en **</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${i_subject}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> quiere que </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${agent.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> tenga todos estos poderes.**
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% endif
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Si no seleccionas una opción, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${agent.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> no podrá ayudarte con eso.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>${i_subject}</t>
     </r>
     <r>
@@ -22875,274 +22273,6 @@
   </si>
   <si>
     <t>Algunos ejemplos de **transacciones patrimoniales** son aceptar dinero o un regalo en nombre del otorgante.</t>
-  </si>
-  <si>
-    <t>Al seleccionar **todas las demás transacciones de propiedad**, el agente podrá realizar cualquier transacción con la propiedad del otorgante, incluso si no está listada arriba.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% if for_yourself == True:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">¿Quieres que </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${agent.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> tenga poder para cambiar los beneficiarios de tu seguro de vida?
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% else:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">¿Quiere </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${principal.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> que </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${agent.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> tenga poder para cambiar los beneficiarios de su seguro de vida?
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>% endif</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% if for_yourself == True:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">¿Quieres que </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${agent.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> tenga poder para declararse bancarrota en tu nombre?
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% else:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>¿</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${principal.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> quiere que </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${agent.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> tenga poder para declararse en bancarrota en nombre de </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${principal.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">?
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>% endif</t>
-    </r>
   </si>
   <si>
     <r>
@@ -24262,10 +23392,6 @@
     </r>
   </si>
   <si>
-    <t>En otras palabras, ¿eres tú el **{otorgante}** que quiere nombrar a un **{agente}**?
-Si estás haciendo estos formularios para alguien más, esa persona será el principal.</t>
-  </si>
-  <si>
     <t>% if for_yourself == True:
 ¿Vives en Illinois?
 % else:
@@ -25570,9 +24696,794 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
+      <t>Al final del programa, podrás descargar tu Poder Notarial para la Propiedad y Finanzas. No será oficial hasta que lo firmes frente a un testigo y un notario público. No necesitas saber quién será el testigo para usar este programa.
+Si quieres saber más sobre la planificación en caso de discapacidad o el cuidado al final de la vida, puedes revisar la guía de ILAO y CDEL [**Empodérate de tu Futuro**](</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${ preview_es.url_for() }</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>).
+Asegúrate de descargar y leer las instrucciones al final del programa.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% if for_yourself == True:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">La persona nombrada como un **{agente sucesor}** tendrá poder notarial para la propiedad por usted si </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${agent.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> muere, se vuelve **{incompetente}**, renuncia o se niega a actuar como su apoderado.
+If you list more than one successor agent, you should list them in order of preference
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% else:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">La persona nombrada como un sucesor agente tendrá poder notarial para la propiedad de </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${principal.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> si </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${agent.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> muere, se vuelve **{incompetente}**, renuncia o se niega a aceptar el cargo de agente.
+If </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${principal.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> lists more than one successor agent, they should list them in order of preference.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>% endif</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${collapse_template(video_when_effect)}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% if for_yourself == True:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Este Poder Notarial entrará en vigor cuando usted firme el formulario a menos que indique que debe entrar en vigencia en un momento posterior.
+Aún tendrá la autoridad para tomar decisiones. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${agent.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> podrá tomar decisiones por usted cuando no pueda hacerlo.
+Aún puede cambiar de opinión y **{revocar}** el Poder Notarial después de firmarlo, siempre que tenga la **{capacidad legal}** requerida.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% else:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Este Poder Notarial entrará en vigor cuando </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${principal.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> firme el formulario a menos que indique que debe entrar en vigencia en un momento posterior.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${principal.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> seguirá teniendo la autoridad para tomar decisiones. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${agent.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> podrá tomar decisiones por ellos cuando no puedan hacerlo.
+Este Poder Notarial entrará en vigor cuando </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${principal.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> firme el formulario a menos que indique que debe entrar en vigencia en un momento posterior.
+Ellos seguirán teniendo la autoridad para tomar decisiones. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${agent.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> podrá tomar decisiones por ellos cuando no puedan hacerlo.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${principal.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> aún puede cambiar de opinión y **{revocar}** el Poder Notarial después de firmarlo, siempre que tenga la **{capacidad legal}** requerida.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% endif
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${collapse_template(prove_capacity)}</t>
+    </r>
+  </si>
+  <si>
+    <t>8c0ad13a48d4426f27eaa339ea07d0b9</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${capitalize(your_subject)}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> acting agent can amend or revoke that delegation at any time. 
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${capitalize(your_subject)}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> agente actuante puede enmendar o revocar esa delegación en cualquier momento.</t>
+    </r>
+  </si>
+  <si>
+    <t>Después de descargar tu formulario</t>
+  </si>
+  <si>
+    <t>En otras palabras, ¿eres tú el **{otorgante}** que quiere nombrar a un **{agente}**?
+Si estás haciendo estos formularios para otra persona, esa persona será el otorgante.</t>
+  </si>
+  <si>
+    <t>Sí, estoy haciendo este poder notarial para mí.</t>
+  </si>
+  <si>
+    <t>No, estoy ayudando a otra persona a hacer un poder notarial.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${collapse_template(video_agent_powers)}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% if for_yourself:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Un Poder Notarial para la Propiedad y Finanzas generalmente le da al agente el poder de manejar toda la propiedad y las finanzas del otorgante. Si quieres que </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${agent.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> pueda tomar decisiones sobre toda tu propiedad y tus finanzas, puedes hacer clic en **</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${i_subject}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri (Body)"/>
+      </rPr>
+      <t>quiero que</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${agent.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> tenga todos estos poderes**.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">%  else:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Un Poder Notarial para la Propiedad y Finanzas generalmente le da al agente el poder de manejar toda la propiedad y las finanzas del otorgante. Si </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${principal.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> quiere que </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${agent.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> pueda tomar decisiones sobre todas su propiedad y sus finanzas, puedes hacer clic en **</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${i_subject}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> quiere que </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${agent.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> tenga todos estos poderes.**
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% endif
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Si no seleccionas una opción, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${agent.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> no podrá ayudarte con eso.</t>
+    </r>
+  </si>
+  <si>
+    <t>Cualquier otra transacción relacionada con la propiedad</t>
+  </si>
+  <si>
+    <t>Al seleccionar **cualquier otra transacción relacionada con la propiedad**, el agente podrá realizar cualquier transacción relacionada con los bienes del otorgante, incluso si no está incluida en las opciones anteriores.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">Para usar este programa necesitarás saber:
-* El nombre, la ciudad, el estado y el número de teléfono de la persona que quieres nombrar como **{agente}** con poder notarial,
-* El nombre, la ciudad, el estado y el número de teléfono de cualquier **{agentes sucesores}**,
+* El nombre, la ciudad, el estado y el número de teléfono de la persona que quieres nombrar como **{agente}** mediante un poder notarial,
+* El nombre, la ciudad, el estado y el número de teléfono de cualquiera de los **{agentes sucesores}**,
 * Qué propiedad y finanzas tienes, y
 * Cuánto control quieres que tenga el agente sobre tu propiedad y tus finanzas.
 Reserva entre 15 y 30 minutos para completar este programa, y más tiempo si ves los videos. Puedes iniciar sesión y guardar tu trabajo para regresar más tarde. 
@@ -25625,36 +25536,127 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Al final del programa, podrás descargar tu Poder Notarial para la Propiedad y Finanzas. No será oficial hasta que lo firmes frente a un testigo y un notario público. No necesitas saber quién será el testigo para usar este programa.
-Si quieres saber más sobre la planificación en caso de discapacidad o el cuidado al final de la vida, puedes revisar la guía de ILAO y CDEL [**Empodérate de tu Futuro**](</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${ preview_es.url_for() }</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>).
-Asegúrate de descargar y leer las instrucciones al final del programa.</t>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${collapse_template(video_agent)}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% if for_yourself == False:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">El agente es la persona que tomará decisiones sobre la propiedad y finanzas de </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${principal.name_full()}.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 
+El agente es la persona en quien ${principal.name_full()} confía para tomar decisiones sobre su propiedad y sus finanzas. Es muy importante que ${principal.name_full()} hable con su agente sobre cómo quiere que se manejen sus finanzas y todo lo que posee. Estas conversaciones ayudarán a guiar sus decisiones y a asegurarse de que ambos estén de acuerdo.
+Un agente tiene mucho poder, y es posible que abuse de ese poder.  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${principal.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> debe elegir a alguien en quien confíe para manejar sus finanzas y todo lo que posee.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% else:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Tu agente es la persona en quien confías para tomar decisiones sobre tu propiedad y tus finanzas. Es muy importante que hables con tu agente sobre cómo quieres que se manejen tus finanzas y todo lo que posees. Estas conversaciones ayudarán a guiar sus decisiones y a asegurarse de que ambos estén de acuerdo.
+Un agente tiene mucho poder, y es posible que abuse de ese poder. Debes elegir a alguien en quien confíes para manejar tus finanzas y todo lo que posees.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>% endif</t>
     </r>
   </si>
   <si>
@@ -25678,7 +25680,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">La persona nombrada como un **{agente sucesor}** tendrá poder notarial para la propiedad por usted si </t>
+      <t xml:space="preserve">¿Quieres que </t>
     </r>
     <r>
       <rPr>
@@ -25699,8 +25701,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> muere, se vuelve **{incompetente}**, renuncia o se niega a actuar como su apoderado.
-If you list more than one successor agent, you should list them in order of preference
+      <t xml:space="preserve"> tenga la autoridad para cambiar los beneficiarios de tu seguro de vida?
 </t>
     </r>
     <r>
@@ -25723,7 +25724,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">La persona nombrada como un sucesor agente tendrá poder notarial para la propiedad de </t>
+      <t xml:space="preserve">¿Quiere </t>
     </r>
     <r>
       <rPr>
@@ -25744,7 +25745,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> si </t>
+      <t xml:space="preserve"> que </t>
     </r>
     <r>
       <rPr>
@@ -25765,8 +25766,77 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> muere, se vuelve **{incompetente}**, renuncia o se niega a aceptar el cargo de agente.
-If </t>
+      <t xml:space="preserve"> tenga la autoridad para cambiar los beneficiarios de su seguro de vida?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>% endif</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">“Nominar” significa sugerir o proponer a una persona que un tribunal puede elegir para actuar como tutor.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% if for_yourself == True:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Un tribunal puede considerar necesario designar a un tutor legal que tome decisiones sobre tus asuntos financieros. Un tutor de tu patrimonio tendría derechos, poderes y deberes sobre su propiedad y finanzas.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% else:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Un tribunal puede considerar necesario designar a un tutor legal para tomar decisiones sobre </t>
     </r>
     <r>
       <rPr>
@@ -25787,7 +25857,141 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> lists more than one successor agent, they should list them in order of preference.
+      <t xml:space="preserve">'s financial affairs. Un tutor de su patrimonio tendría derechos, poderes y deberes sobre su propiedad y finanzas.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% endif
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Si hace clic en **No**, entonces un tribunal puede designar a alguien que no sea </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${agent.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> como tutor si fuera necesario. Incluso si hace clic en **Sí**, un tribunal podría designar a otra persona como tutor si determina que </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${agent.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> está incumpliendo sus obligaciones.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% if for_yourself == True:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">¿Quieres que </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${agent.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> tenga la autoridad para presentar una solicitud de bancarrota en tu nombre?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% else:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">¿Quiere ${principal.name_full()} que ${agent.name_full()} tenga la autoridad para presentar una solicitud de bancarrota en su nombre?
 </t>
     </r>
     <r>
@@ -25800,313 +26004,6 @@
         <scheme val="minor"/>
       </rPr>
       <t>% endif</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${collapse_template(video_when_effect)}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% if for_yourself == True:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Este Poder Notarial entrará en vigor cuando usted firme el formulario a menos que indique que debe entrar en vigencia en un momento posterior.
-Aún tendrá la autoridad para tomar decisiones. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${agent.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> podrá tomar decisiones por usted cuando no pueda hacerlo.
-Aún puede cambiar de opinión y **{revocar}** el Poder Notarial después de firmarlo, siempre que tenga la **{capacidad legal}** requerida.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% else:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Este Poder Notarial entrará en vigor cuando </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${principal.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> firme el formulario a menos que indique que debe entrar en vigencia en un momento posterior.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${principal.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> seguirá teniendo la autoridad para tomar decisiones. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${agent.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> podrá tomar decisiones por ellos cuando no puedan hacerlo.
-Este Poder Notarial entrará en vigor cuando </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${principal.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> firme el formulario a menos que indique que debe entrar en vigencia en un momento posterior.
-Ellos seguirán teniendo la autoridad para tomar decisiones. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${agent.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> podrá tomar decisiones por ellos cuando no puedan hacerlo.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${principal.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> aún puede cambiar de opinión y **{revocar}** el Poder Notarial después de firmarlo, siempre que tenga la **{capacidad legal}** requerida.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% endif
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${collapse_template(prove_capacity)}</t>
-    </r>
-  </si>
-  <si>
-    <t>8c0ad13a48d4426f27eaa339ea07d0b9</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${capitalize(your_subject)}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> acting agent can amend or revoke that delegation at any time. 
-</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${capitalize(your_subject)}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> agente actuante puede enmendar o revocar esa delegación en cualquier momento.</t>
     </r>
   </si>
 </sst>
@@ -26583,7 +26480,7 @@
         <v>13</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="403.2">
@@ -26597,7 +26494,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>832</v>
+        <v>822</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>11</v>
@@ -26606,10 +26503,10 @@
         <v>12</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>833</v>
+        <v>823</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>834</v>
+        <v>824</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="187.2">
@@ -26635,7 +26532,7 @@
         <v>16</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="28.8">
@@ -26661,7 +26558,7 @@
         <v>19</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="302.39999999999998">
@@ -26687,7 +26584,7 @@
         <v>21</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>835</v>
+        <v>825</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -26713,7 +26610,7 @@
         <v>24</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="72">
@@ -26739,7 +26636,7 @@
         <v>26</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -26765,7 +26662,7 @@
         <v>28</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="43.2">
@@ -26791,7 +26688,7 @@
         <v>30</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="28.8">
@@ -26843,7 +26740,7 @@
         <v>35</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="43.2">
@@ -26869,7 +26766,7 @@
         <v>38</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="43.2">
@@ -26895,7 +26792,7 @@
         <v>40</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="86.4">
@@ -26921,7 +26818,7 @@
         <v>43</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>838</v>
+        <v>828</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="115.2">
@@ -26947,7 +26844,7 @@
         <v>46</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>836</v>
+        <v>826</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="28.8">
@@ -26999,7 +26896,7 @@
         <v>52</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="273.60000000000002">
@@ -27025,7 +26922,7 @@
         <v>54</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>837</v>
+        <v>827</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="28.8">
@@ -27051,7 +26948,7 @@
         <v>57</v>
       </c>
       <c r="H20" t="s">
-        <v>779</v>
+        <v>862</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="129.6">
@@ -27077,7 +26974,7 @@
         <v>59</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>868</v>
+        <v>856</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -27103,7 +27000,7 @@
         <v>62</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="43.2">
@@ -27129,7 +27026,7 @@
         <v>64</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="72">
@@ -27155,7 +27052,7 @@
         <v>66</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="28.8">
@@ -27181,7 +27078,7 @@
         <v>68</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="57.6">
@@ -27207,7 +27104,7 @@
         <v>70</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>843</v>
+        <v>863</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -27233,7 +27130,7 @@
         <v>72</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>784</v>
+        <v>864</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -27259,7 +27156,7 @@
         <v>74</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>785</v>
+        <v>865</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="28.8">
@@ -27285,7 +27182,7 @@
         <v>77</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>786</v>
+        <v>781</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="259.2">
@@ -27311,7 +27208,7 @@
         <v>79</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>787</v>
+        <v>782</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="86.4">
@@ -27337,7 +27234,7 @@
         <v>82</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="403.2">
@@ -27363,7 +27260,7 @@
         <v>84</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>789</v>
+        <v>784</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -27389,7 +27286,7 @@
         <v>86</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>790</v>
+        <v>785</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -27415,7 +27312,7 @@
         <v>88</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>791</v>
+        <v>786</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -27441,7 +27338,7 @@
         <v>90</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>792</v>
+        <v>787</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -27467,7 +27364,7 @@
         <v>92</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>793</v>
+        <v>788</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -27519,7 +27416,7 @@
         <v>97</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>794</v>
+        <v>789</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="115.2">
@@ -27545,7 +27442,7 @@
         <v>100</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>795</v>
+        <v>790</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="28.8">
@@ -27571,7 +27468,7 @@
         <v>102</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>796</v>
+        <v>791</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="28.8">
@@ -27597,7 +27494,7 @@
         <v>105</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>797</v>
+        <v>792</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="86.4">
@@ -27623,7 +27520,7 @@
         <v>108</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>844</v>
+        <v>833</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="28.8">
@@ -27649,7 +27546,7 @@
         <v>111</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>845</v>
+        <v>834</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="144">
@@ -27701,7 +27598,7 @@
         <v>117</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>798</v>
+        <v>793</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="86.4">
@@ -27727,7 +27624,7 @@
         <v>120</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>799</v>
+        <v>794</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="86.4">
@@ -27753,7 +27650,7 @@
         <v>123</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>800</v>
+        <v>795</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="345.6">
@@ -27779,7 +27676,7 @@
         <v>125</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>801</v>
+        <v>870</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="28.8">
@@ -27805,7 +27702,7 @@
         <v>128</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>802</v>
+        <v>796</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="28.8">
@@ -27857,7 +27754,7 @@
         <v>133</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>803</v>
+        <v>797</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="43.2">
@@ -27883,7 +27780,7 @@
         <v>135</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>804</v>
+        <v>798</v>
       </c>
     </row>
     <row r="53" spans="1:8">
@@ -27909,7 +27806,7 @@
         <v>137</v>
       </c>
       <c r="H53" t="s">
-        <v>847</v>
+        <v>836</v>
       </c>
     </row>
     <row r="54" spans="1:8">
@@ -27935,7 +27832,7 @@
         <v>139</v>
       </c>
       <c r="H54" t="s">
-        <v>848</v>
+        <v>837</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="129.6">
@@ -27961,7 +27858,7 @@
         <v>142</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>839</v>
+        <v>829</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="28.8">
@@ -27987,7 +27884,7 @@
         <v>144</v>
       </c>
       <c r="H56" s="4" t="s">
-        <v>846</v>
+        <v>835</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="28.8">
@@ -28039,7 +27936,7 @@
         <v>150</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>805</v>
+        <v>799</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="115.2">
@@ -28065,7 +27962,7 @@
         <v>153</v>
       </c>
       <c r="H59" s="5" t="s">
-        <v>849</v>
+        <v>838</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="28.8">
@@ -28117,7 +28014,7 @@
         <v>159</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>806</v>
+        <v>800</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="244.8">
@@ -28143,7 +28040,7 @@
         <v>161</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>807</v>
+        <v>866</v>
       </c>
     </row>
     <row r="63" spans="1:8">
@@ -28169,7 +28066,7 @@
         <v>163</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>808</v>
+        <v>801</v>
       </c>
     </row>
     <row r="64" spans="1:8">
@@ -28195,7 +28092,7 @@
         <v>165</v>
       </c>
       <c r="H64" s="4" t="s">
-        <v>809</v>
+        <v>802</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="43.2">
@@ -28247,7 +28144,7 @@
         <v>170</v>
       </c>
       <c r="H66" s="4" t="s">
-        <v>810</v>
+        <v>803</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="43.2">
@@ -28273,7 +28170,7 @@
         <v>172</v>
       </c>
       <c r="H67" s="4" t="s">
-        <v>850</v>
+        <v>839</v>
       </c>
     </row>
     <row r="68" spans="1:8">
@@ -28325,7 +28222,7 @@
         <v>177</v>
       </c>
       <c r="H69" s="4" t="s">
-        <v>811</v>
+        <v>804</v>
       </c>
     </row>
     <row r="70" spans="1:8">
@@ -28351,7 +28248,7 @@
         <v>179</v>
       </c>
       <c r="H70" s="4" t="s">
-        <v>812</v>
+        <v>805</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="72">
@@ -28377,7 +28274,7 @@
         <v>181</v>
       </c>
       <c r="H71" s="4" t="s">
-        <v>813</v>
+        <v>806</v>
       </c>
     </row>
     <row r="72" spans="1:8">
@@ -28403,7 +28300,7 @@
         <v>183</v>
       </c>
       <c r="H72" s="4" t="s">
-        <v>814</v>
+        <v>807</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="43.2">
@@ -28429,7 +28326,7 @@
         <v>185</v>
       </c>
       <c r="H73" s="4" t="s">
-        <v>815</v>
+        <v>808</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -28481,7 +28378,7 @@
         <v>190</v>
       </c>
       <c r="H75" s="4" t="s">
-        <v>817</v>
+        <v>810</v>
       </c>
     </row>
     <row r="76" spans="1:8">
@@ -28507,7 +28404,7 @@
         <v>192</v>
       </c>
       <c r="H76" s="4" t="s">
-        <v>816</v>
+        <v>809</v>
       </c>
     </row>
     <row r="77" spans="1:8" ht="43.2">
@@ -28533,7 +28430,7 @@
         <v>194</v>
       </c>
       <c r="H77" s="4" t="s">
-        <v>818</v>
+        <v>811</v>
       </c>
     </row>
     <row r="78" spans="1:8">
@@ -28559,7 +28456,7 @@
         <v>196</v>
       </c>
       <c r="H78" s="4" t="s">
-        <v>819</v>
+        <v>812</v>
       </c>
     </row>
     <row r="79" spans="1:8" ht="57.6">
@@ -28585,7 +28482,7 @@
         <v>198</v>
       </c>
       <c r="H79" s="4" t="s">
-        <v>820</v>
+        <v>813</v>
       </c>
     </row>
     <row r="80" spans="1:8">
@@ -28637,7 +28534,7 @@
         <v>203</v>
       </c>
       <c r="H81" s="4" t="s">
-        <v>821</v>
+        <v>814</v>
       </c>
     </row>
     <row r="82" spans="1:8">
@@ -28689,7 +28586,7 @@
         <v>208</v>
       </c>
       <c r="H83" s="4" t="s">
-        <v>822</v>
+        <v>815</v>
       </c>
     </row>
     <row r="84" spans="1:8">
@@ -28741,7 +28638,7 @@
         <v>213</v>
       </c>
       <c r="H85" s="4" t="s">
-        <v>823</v>
+        <v>816</v>
       </c>
     </row>
     <row r="86" spans="1:8">
@@ -28793,7 +28690,7 @@
         <v>218</v>
       </c>
       <c r="H87" s="4" t="s">
-        <v>824</v>
+        <v>817</v>
       </c>
     </row>
     <row r="88" spans="1:8">
@@ -28845,7 +28742,7 @@
         <v>223</v>
       </c>
       <c r="H89" s="4" t="s">
-        <v>826</v>
+        <v>819</v>
       </c>
     </row>
     <row r="90" spans="1:8">
@@ -28871,7 +28768,7 @@
         <v>225</v>
       </c>
       <c r="H90" s="4" t="s">
-        <v>825</v>
+        <v>818</v>
       </c>
     </row>
     <row r="91" spans="1:8" ht="43.2">
@@ -28897,7 +28794,7 @@
         <v>227</v>
       </c>
       <c r="H91" s="4" t="s">
-        <v>827</v>
+        <v>820</v>
       </c>
     </row>
     <row r="92" spans="1:8">
@@ -28923,7 +28820,7 @@
         <v>229</v>
       </c>
       <c r="H92" s="4" t="s">
-        <v>230</v>
+        <v>867</v>
       </c>
     </row>
     <row r="93" spans="1:8" ht="43.2">
@@ -28937,7 +28834,7 @@
         <v>32</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>11</v>
@@ -28946,10 +28843,10 @@
         <v>12</v>
       </c>
       <c r="G93" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H93" s="4" t="s">
-        <v>828</v>
+        <v>868</v>
       </c>
     </row>
     <row r="94" spans="1:8">
@@ -28963,7 +28860,7 @@
         <v>33</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>11</v>
@@ -28972,10 +28869,10 @@
         <v>12</v>
       </c>
       <c r="G94" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="H94" s="4" t="s">
         <v>234</v>
-      </c>
-      <c r="H94" s="4" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="95" spans="1:8" ht="115.2">
@@ -28983,13 +28880,13 @@
         <v>8</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C95" s="2">
         <v>0</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>11</v>
@@ -28998,10 +28895,10 @@
         <v>12</v>
       </c>
       <c r="G95" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>829</v>
+        <v>871</v>
       </c>
     </row>
     <row r="96" spans="1:8" ht="100.8">
@@ -29009,13 +28906,13 @@
         <v>8</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C96" s="2">
         <v>0</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>11</v>
@@ -29024,10 +28921,10 @@
         <v>12</v>
       </c>
       <c r="G96" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>830</v>
+        <v>873</v>
       </c>
     </row>
     <row r="97" spans="1:8" ht="115.2">
@@ -29035,13 +28932,13 @@
         <v>8</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C97" s="2">
         <v>0</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>11</v>
@@ -29050,10 +28947,10 @@
         <v>12</v>
       </c>
       <c r="G97" s="3" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>831</v>
+        <v>821</v>
       </c>
     </row>
     <row r="98" spans="1:8" ht="259.2">
@@ -29061,13 +28958,13 @@
         <v>8</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C98" s="2">
         <v>1</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>11</v>
@@ -29076,10 +28973,10 @@
         <v>12</v>
       </c>
       <c r="G98" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>840</v>
+        <v>830</v>
       </c>
     </row>
     <row r="99" spans="1:8" ht="28.8">
@@ -29087,13 +28984,13 @@
         <v>8</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C99" s="2">
         <v>0</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>11</v>
@@ -29102,10 +28999,10 @@
         <v>12</v>
       </c>
       <c r="G99" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="H99" s="4" t="s">
         <v>249</v>
-      </c>
-      <c r="H99" s="4" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="100" spans="1:8" ht="388.8">
@@ -29113,13 +29010,13 @@
         <v>8</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C100" s="2">
         <v>1</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>11</v>
@@ -29128,10 +29025,10 @@
         <v>12</v>
       </c>
       <c r="G100" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>841</v>
+        <v>831</v>
       </c>
     </row>
     <row r="101" spans="1:8" ht="86.4">
@@ -29139,13 +29036,13 @@
         <v>8</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C101" s="2">
         <v>0</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>11</v>
@@ -29154,10 +29051,10 @@
         <v>12</v>
       </c>
       <c r="G101" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="H101" s="3" t="s">
         <v>255</v>
-      </c>
-      <c r="H101" s="3" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="102" spans="1:8" ht="115.2">
@@ -29165,13 +29062,13 @@
         <v>8</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C102" s="2">
         <v>1</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>11</v>
@@ -29180,10 +29077,10 @@
         <v>12</v>
       </c>
       <c r="G102" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="H102" s="3" t="s">
         <v>258</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="103" spans="1:8" ht="115.2">
@@ -29191,13 +29088,13 @@
         <v>8</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C103" s="2">
         <v>0</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>11</v>
@@ -29206,10 +29103,10 @@
         <v>12</v>
       </c>
       <c r="G103" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="H103" s="3" t="s">
         <v>262</v>
-      </c>
-      <c r="H103" s="3" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="104" spans="1:8">
@@ -29217,13 +29114,13 @@
         <v>8</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C104" s="2">
         <v>1</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>11</v>
@@ -29232,10 +29129,10 @@
         <v>12</v>
       </c>
       <c r="G104" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="H104" s="4" t="s">
         <v>265</v>
-      </c>
-      <c r="H104" s="4" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="105" spans="1:8">
@@ -29243,13 +29140,13 @@
         <v>8</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C105" s="2">
         <v>2</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>11</v>
@@ -29258,10 +29155,10 @@
         <v>12</v>
       </c>
       <c r="G105" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="H105" s="4" t="s">
         <v>268</v>
-      </c>
-      <c r="H105" s="4" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="106" spans="1:8">
@@ -29269,13 +29166,13 @@
         <v>8</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C106" s="2">
         <v>3</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>11</v>
@@ -29284,10 +29181,10 @@
         <v>12</v>
       </c>
       <c r="G106" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="H106" s="4" t="s">
         <v>271</v>
-      </c>
-      <c r="H106" s="4" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="107" spans="1:8">
@@ -29295,13 +29192,13 @@
         <v>8</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C107" s="2">
         <v>4</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>11</v>
@@ -29310,10 +29207,10 @@
         <v>12</v>
       </c>
       <c r="G107" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="H107" s="4" t="s">
         <v>274</v>
-      </c>
-      <c r="H107" s="4" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="108" spans="1:8">
@@ -29321,13 +29218,13 @@
         <v>8</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C108" s="2">
         <v>5</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>11</v>
@@ -29336,10 +29233,10 @@
         <v>12</v>
       </c>
       <c r="G108" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="H108" s="4" t="s">
         <v>277</v>
-      </c>
-      <c r="H108" s="4" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="109" spans="1:8">
@@ -29347,13 +29244,13 @@
         <v>8</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C109" s="2">
         <v>6</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>11</v>
@@ -29362,10 +29259,10 @@
         <v>12</v>
       </c>
       <c r="G109" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="H109" s="4" t="s">
         <v>280</v>
-      </c>
-      <c r="H109" s="4" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="110" spans="1:8">
@@ -29373,13 +29270,13 @@
         <v>8</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C110" s="2">
         <v>7</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>11</v>
@@ -29388,10 +29285,10 @@
         <v>12</v>
       </c>
       <c r="G110" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="H110" s="4" t="s">
         <v>283</v>
-      </c>
-      <c r="H110" s="4" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="111" spans="1:8">
@@ -29399,13 +29296,13 @@
         <v>8</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C111" s="2">
         <v>8</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>11</v>
@@ -29414,10 +29311,10 @@
         <v>12</v>
       </c>
       <c r="G111" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="H111" s="4" t="s">
         <v>286</v>
-      </c>
-      <c r="H111" s="4" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="112" spans="1:8" ht="28.8">
@@ -29425,13 +29322,13 @@
         <v>8</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C112" s="2">
         <v>9</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>11</v>
@@ -29440,10 +29337,10 @@
         <v>12</v>
       </c>
       <c r="G112" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="H112" s="4" t="s">
         <v>289</v>
-      </c>
-      <c r="H112" s="4" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="113" spans="1:8">
@@ -29451,13 +29348,13 @@
         <v>8</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C113" s="2">
         <v>10</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>11</v>
@@ -29466,10 +29363,10 @@
         <v>12</v>
       </c>
       <c r="G113" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="H113" s="4" t="s">
         <v>292</v>
-      </c>
-      <c r="H113" s="4" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="114" spans="1:8">
@@ -29477,13 +29374,13 @@
         <v>8</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C114" s="2">
         <v>13</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>11</v>
@@ -29492,10 +29389,10 @@
         <v>12</v>
       </c>
       <c r="G114" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="H114" s="4" t="s">
         <v>295</v>
-      </c>
-      <c r="H114" s="4" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="115" spans="1:8" ht="28.8">
@@ -29503,13 +29400,13 @@
         <v>8</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C115" s="2">
         <v>14</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>11</v>
@@ -29518,10 +29415,10 @@
         <v>12</v>
       </c>
       <c r="G115" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="H115" s="4" t="s">
         <v>298</v>
-      </c>
-      <c r="H115" s="4" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="116" spans="1:8">
@@ -29529,13 +29426,13 @@
         <v>8</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C116" s="2">
         <v>15</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>11</v>
@@ -29544,10 +29441,10 @@
         <v>12</v>
       </c>
       <c r="G116" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="H116" s="4" t="s">
         <v>301</v>
-      </c>
-      <c r="H116" s="4" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="117" spans="1:8">
@@ -29555,13 +29452,13 @@
         <v>8</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C117" s="2">
         <v>16</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>11</v>
@@ -29570,10 +29467,10 @@
         <v>12</v>
       </c>
       <c r="G117" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="H117" s="4" t="s">
         <v>304</v>
-      </c>
-      <c r="H117" s="4" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="118" spans="1:8">
@@ -29581,13 +29478,13 @@
         <v>8</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C118" s="2">
         <v>17</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>11</v>
@@ -29596,10 +29493,10 @@
         <v>12</v>
       </c>
       <c r="G118" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="H118" s="4" t="s">
         <v>307</v>
-      </c>
-      <c r="H118" s="4" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="119" spans="1:8">
@@ -29607,13 +29504,13 @@
         <v>8</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C119" s="2">
         <v>18</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>11</v>
@@ -29622,10 +29519,10 @@
         <v>12</v>
       </c>
       <c r="G119" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="H119" s="4" t="s">
         <v>310</v>
-      </c>
-      <c r="H119" s="4" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="120" spans="1:8">
@@ -29633,13 +29530,13 @@
         <v>8</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C120" s="2">
         <v>19</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>11</v>
@@ -29648,10 +29545,10 @@
         <v>12</v>
       </c>
       <c r="G120" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="H120" s="4" t="s">
         <v>313</v>
-      </c>
-      <c r="H120" s="4" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="121" spans="1:8">
@@ -29659,13 +29556,13 @@
         <v>8</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C121" s="2">
         <v>20</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>11</v>
@@ -29674,10 +29571,10 @@
         <v>12</v>
       </c>
       <c r="G121" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="H121" s="4" t="s">
         <v>316</v>
-      </c>
-      <c r="H121" s="4" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="122" spans="1:8" ht="43.2">
@@ -29685,13 +29582,13 @@
         <v>8</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C122" s="2">
         <v>21</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>11</v>
@@ -29700,10 +29597,10 @@
         <v>12</v>
       </c>
       <c r="G122" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="H122" s="4" t="s">
         <v>319</v>
-      </c>
-      <c r="H122" s="4" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="123" spans="1:8" ht="86.4">
@@ -29711,13 +29608,13 @@
         <v>8</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C123" s="2">
         <v>0</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>11</v>
@@ -29726,10 +29623,10 @@
         <v>12</v>
       </c>
       <c r="G123" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="H123" s="3" t="s">
         <v>323</v>
-      </c>
-      <c r="H123" s="3" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="124" spans="1:8" ht="43.2">
@@ -29737,13 +29634,13 @@
         <v>8</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C124" s="2">
         <v>1</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>11</v>
@@ -29752,10 +29649,10 @@
         <v>12</v>
       </c>
       <c r="G124" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="H124" s="4" t="s">
         <v>326</v>
-      </c>
-      <c r="H124" s="4" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="125" spans="1:8">
@@ -29763,13 +29660,13 @@
         <v>8</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C125" s="2">
         <v>2</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>11</v>
@@ -29778,10 +29675,10 @@
         <v>12</v>
       </c>
       <c r="G125" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="H125" s="4" t="s">
         <v>329</v>
-      </c>
-      <c r="H125" s="4" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="126" spans="1:8" ht="100.8">
@@ -29789,13 +29686,13 @@
         <v>8</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C126" s="2">
         <v>0</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>11</v>
@@ -29804,10 +29701,10 @@
         <v>12</v>
       </c>
       <c r="G126" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="H126" s="3" t="s">
         <v>333</v>
-      </c>
-      <c r="H126" s="3" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="127" spans="1:8" ht="115.2">
@@ -29815,13 +29712,13 @@
         <v>8</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C127" s="2">
         <v>1</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>11</v>
@@ -29830,10 +29727,10 @@
         <v>12</v>
       </c>
       <c r="G127" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="H127" s="3" t="s">
         <v>336</v>
-      </c>
-      <c r="H127" s="3" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="128" spans="1:8" ht="86.4">
@@ -29841,13 +29738,13 @@
         <v>8</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C128" s="2">
         <v>0</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>11</v>
@@ -29856,10 +29753,10 @@
         <v>12</v>
       </c>
       <c r="G128" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="H128" s="3" t="s">
         <v>340</v>
-      </c>
-      <c r="H128" s="3" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="129" spans="1:8" ht="115.2">
@@ -29867,13 +29764,13 @@
         <v>8</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C129" s="2">
         <v>1</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>11</v>
@@ -29882,10 +29779,10 @@
         <v>12</v>
       </c>
       <c r="G129" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="H129" s="3" t="s">
         <v>343</v>
-      </c>
-      <c r="H129" s="3" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="130" spans="1:8">
@@ -29893,13 +29790,13 @@
         <v>8</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C130" s="2">
         <v>2</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>11</v>
@@ -29908,10 +29805,10 @@
         <v>12</v>
       </c>
       <c r="G130" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="H130" s="4" t="s">
         <v>346</v>
-      </c>
-      <c r="H130" s="4" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="131" spans="1:8" ht="100.8">
@@ -29919,13 +29816,13 @@
         <v>8</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C131" s="2">
         <v>0</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>11</v>
@@ -29934,10 +29831,10 @@
         <v>12</v>
       </c>
       <c r="G131" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="H131" s="3" t="s">
         <v>350</v>
-      </c>
-      <c r="H131" s="3" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="132" spans="1:8" ht="144">
@@ -29945,13 +29842,13 @@
         <v>8</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C132" s="2">
         <v>1</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>11</v>
@@ -29960,10 +29857,10 @@
         <v>12</v>
       </c>
       <c r="G132" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="H132" s="3" t="s">
         <v>353</v>
-      </c>
-      <c r="H132" s="3" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="133" spans="1:8">
@@ -29971,13 +29868,13 @@
         <v>8</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C133" s="2">
         <v>2</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>11</v>
@@ -29986,10 +29883,10 @@
         <v>12</v>
       </c>
       <c r="G133" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="H133" s="3" t="s">
         <v>356</v>
-      </c>
-      <c r="H133" s="3" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="134" spans="1:8" ht="115.2">
@@ -29997,13 +29894,13 @@
         <v>8</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C134" s="2">
         <v>0</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E134" s="2" t="s">
         <v>11</v>
@@ -30012,10 +29909,10 @@
         <v>12</v>
       </c>
       <c r="G134" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="H134" s="4" t="s">
         <v>360</v>
-      </c>
-      <c r="H134" s="4" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="135" spans="1:8" ht="28.8">
@@ -30023,13 +29920,13 @@
         <v>8</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C135" s="2">
         <v>1</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>11</v>
@@ -30038,10 +29935,10 @@
         <v>12</v>
       </c>
       <c r="G135" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="H135" s="4" t="s">
         <v>363</v>
-      </c>
-      <c r="H135" s="4" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="136" spans="1:8" ht="115.2">
@@ -30049,13 +29946,13 @@
         <v>8</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C136" s="2">
         <v>0</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E136" s="2" t="s">
         <v>11</v>
@@ -30064,10 +29961,10 @@
         <v>12</v>
       </c>
       <c r="G136" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="H136" s="3" t="s">
         <v>367</v>
-      </c>
-      <c r="H136" s="3" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="137" spans="1:8" ht="129.6">
@@ -30075,13 +29972,13 @@
         <v>8</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C137" s="2">
         <v>1</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E137" s="2" t="s">
         <v>11</v>
@@ -30090,10 +29987,10 @@
         <v>12</v>
       </c>
       <c r="G137" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="H137" s="3" t="s">
         <v>370</v>
-      </c>
-      <c r="H137" s="3" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="138" spans="1:8">
@@ -30101,13 +29998,13 @@
         <v>8</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C138" s="2">
         <v>2</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="E138" s="2" t="s">
         <v>11</v>
@@ -30116,10 +30013,10 @@
         <v>12</v>
       </c>
       <c r="G138" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="H138" s="3" t="s">
         <v>373</v>
-      </c>
-      <c r="H138" s="3" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="139" spans="1:8" ht="43.2">
@@ -30127,13 +30024,13 @@
         <v>8</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C139" s="2">
         <v>3</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>871</v>
+        <v>859</v>
       </c>
       <c r="E139" s="2" t="s">
         <v>11</v>
@@ -30142,10 +30039,10 @@
         <v>12</v>
       </c>
       <c r="G139" s="3" t="s">
-        <v>872</v>
+        <v>860</v>
       </c>
       <c r="H139" s="3" t="s">
-        <v>873</v>
+        <v>861</v>
       </c>
     </row>
     <row r="140" spans="1:8">
@@ -30153,13 +30050,13 @@
         <v>8</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C140" s="2">
         <v>4</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="E140" s="2" t="s">
         <v>11</v>
@@ -30168,10 +30065,10 @@
         <v>12</v>
       </c>
       <c r="G140" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="H140" s="3" t="s">
         <v>376</v>
-      </c>
-      <c r="H140" s="3" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="141" spans="1:8">
@@ -30179,13 +30076,13 @@
         <v>8</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C141" s="2">
         <v>5</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E141" s="2" t="s">
         <v>11</v>
@@ -30194,10 +30091,10 @@
         <v>12</v>
       </c>
       <c r="G141" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="H141" s="3" t="s">
         <v>379</v>
-      </c>
-      <c r="H141" s="3" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="142" spans="1:8">
@@ -30205,13 +30102,13 @@
         <v>8</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C142" s="2">
         <v>6</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E142" s="2" t="s">
         <v>11</v>
@@ -30220,10 +30117,10 @@
         <v>12</v>
       </c>
       <c r="G142" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="H142" s="3" t="s">
         <v>382</v>
-      </c>
-      <c r="H142" s="3" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="143" spans="1:8" ht="187.2">
@@ -30231,13 +30128,13 @@
         <v>8</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C143" s="2">
         <v>0</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E143" s="2" t="s">
         <v>11</v>
@@ -30246,10 +30143,10 @@
         <v>12</v>
       </c>
       <c r="G143" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="H143" s="3" t="s">
         <v>386</v>
-      </c>
-      <c r="H143" s="3" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="144" spans="1:8" ht="28.8">
@@ -30257,13 +30154,13 @@
         <v>8</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C144" s="2">
         <v>1</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="E144" s="2" t="s">
         <v>11</v>
@@ -30272,10 +30169,10 @@
         <v>12</v>
       </c>
       <c r="G144" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="H144" s="4" t="s">
         <v>389</v>
-      </c>
-      <c r="H144" s="4" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="145" spans="1:8" ht="115.2">
@@ -30283,13 +30180,13 @@
         <v>8</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C145" s="2">
         <v>0</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E145" s="2" t="s">
         <v>11</v>
@@ -30298,10 +30195,10 @@
         <v>12</v>
       </c>
       <c r="G145" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="H145" s="3" t="s">
         <v>393</v>
-      </c>
-      <c r="H145" s="3" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="146" spans="1:8" ht="316.8">
@@ -30309,13 +30206,13 @@
         <v>8</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C146" s="2">
         <v>1</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E146" s="2" t="s">
         <v>11</v>
@@ -30324,10 +30221,10 @@
         <v>12</v>
       </c>
       <c r="G146" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="H146" s="3" t="s">
         <v>396</v>
-      </c>
-      <c r="H146" s="3" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="147" spans="1:8" ht="28.8">
@@ -30335,13 +30232,13 @@
         <v>8</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C147" s="2">
         <v>2</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="E147" s="2" t="s">
         <v>11</v>
@@ -30350,10 +30247,10 @@
         <v>12</v>
       </c>
       <c r="G147" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="H147" s="3" t="s">
         <v>399</v>
-      </c>
-      <c r="H147" s="3" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="148" spans="1:8">
@@ -30361,13 +30258,13 @@
         <v>8</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C148" s="2">
         <v>3</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="E148" s="2" t="s">
         <v>11</v>
@@ -30376,10 +30273,10 @@
         <v>12</v>
       </c>
       <c r="G148" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="H148" s="3" t="s">
         <v>402</v>
-      </c>
-      <c r="H148" s="3" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="149" spans="1:8" ht="28.8">
@@ -30387,13 +30284,13 @@
         <v>8</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C149" s="2">
         <v>4</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E149" s="2" t="s">
         <v>11</v>
@@ -30402,10 +30299,10 @@
         <v>12</v>
       </c>
       <c r="G149" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="H149" s="3" t="s">
         <v>405</v>
-      </c>
-      <c r="H149" s="3" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="150" spans="1:8">
@@ -30413,13 +30310,13 @@
         <v>8</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C150" s="2">
         <v>5</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E150" s="2" t="s">
         <v>11</v>
@@ -30428,10 +30325,10 @@
         <v>12</v>
       </c>
       <c r="G150" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="H150" s="4" t="s">
         <v>408</v>
-      </c>
-      <c r="H150" s="4" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="151" spans="1:8">
@@ -30439,13 +30336,13 @@
         <v>8</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C151" s="2">
         <v>7</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E151" s="2" t="s">
         <v>11</v>
@@ -30454,10 +30351,10 @@
         <v>12</v>
       </c>
       <c r="G151" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="H151" s="4" t="s">
         <v>411</v>
-      </c>
-      <c r="H151" s="4" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="152" spans="1:8">
@@ -30465,13 +30362,13 @@
         <v>8</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C152" s="2">
         <v>8</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E152" s="2" t="s">
         <v>11</v>
@@ -30480,10 +30377,10 @@
         <v>12</v>
       </c>
       <c r="G152" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="H152" s="4" t="s">
         <v>414</v>
-      </c>
-      <c r="H152" s="4" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="153" spans="1:8">
@@ -30491,13 +30388,13 @@
         <v>8</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C153" s="2">
         <v>9</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E153" s="2" t="s">
         <v>11</v>
@@ -30506,10 +30403,10 @@
         <v>12</v>
       </c>
       <c r="G153" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="H153" s="4" t="s">
         <v>417</v>
-      </c>
-      <c r="H153" s="4" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="154" spans="1:8">
@@ -30517,13 +30414,13 @@
         <v>8</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C154" s="2">
         <v>10</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E154" s="2" t="s">
         <v>11</v>
@@ -30532,10 +30429,10 @@
         <v>12</v>
       </c>
       <c r="G154" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="H154" s="4" t="s">
         <v>420</v>
-      </c>
-      <c r="H154" s="4" t="s">
-        <v>421</v>
       </c>
     </row>
     <row r="155" spans="1:8">
@@ -30543,13 +30440,13 @@
         <v>8</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C155" s="2">
         <v>11</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E155" s="2" t="s">
         <v>11</v>
@@ -30558,10 +30455,10 @@
         <v>12</v>
       </c>
       <c r="G155" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="H155" s="4" t="s">
         <v>423</v>
-      </c>
-      <c r="H155" s="4" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="156" spans="1:8">
@@ -30569,13 +30466,13 @@
         <v>8</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C156" s="2">
         <v>0</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E156" s="2" t="s">
         <v>11</v>
@@ -30584,10 +30481,10 @@
         <v>12</v>
       </c>
       <c r="G156" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="H156" s="4" t="s">
         <v>427</v>
-      </c>
-      <c r="H156" s="4" t="s">
-        <v>428</v>
       </c>
     </row>
     <row r="157" spans="1:8" ht="115.2">
@@ -30595,13 +30492,13 @@
         <v>8</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C157" s="2">
         <v>1</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E157" s="2" t="s">
         <v>11</v>
@@ -30610,10 +30507,10 @@
         <v>12</v>
       </c>
       <c r="G157" s="3" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H157" s="4" t="s">
-        <v>851</v>
+        <v>840</v>
       </c>
     </row>
     <row r="158" spans="1:8">
@@ -30621,13 +30518,13 @@
         <v>8</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C158" s="2">
         <v>2</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E158" s="2" t="s">
         <v>11</v>
@@ -30636,10 +30533,10 @@
         <v>12</v>
       </c>
       <c r="G158" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="H158" s="4" t="s">
         <v>432</v>
-      </c>
-      <c r="H158" s="4" t="s">
-        <v>433</v>
       </c>
     </row>
     <row r="159" spans="1:8" ht="43.2">
@@ -30647,13 +30544,13 @@
         <v>8</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C159" s="2">
         <v>3</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E159" s="2" t="s">
         <v>11</v>
@@ -30662,10 +30559,10 @@
         <v>12</v>
       </c>
       <c r="G159" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="H159" s="4" t="s">
         <v>435</v>
-      </c>
-      <c r="H159" s="4" t="s">
-        <v>436</v>
       </c>
     </row>
     <row r="160" spans="1:8" ht="86.4">
@@ -30673,13 +30570,13 @@
         <v>8</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C160" s="2">
         <v>4</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E160" s="2" t="s">
         <v>11</v>
@@ -30688,10 +30585,10 @@
         <v>12</v>
       </c>
       <c r="G160" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="H160" s="3" t="s">
         <v>438</v>
-      </c>
-      <c r="H160" s="3" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="161" spans="1:8" ht="216">
@@ -30699,13 +30596,13 @@
         <v>8</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C161" s="2">
         <v>5</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E161" s="2" t="s">
         <v>11</v>
@@ -30714,10 +30611,10 @@
         <v>12</v>
       </c>
       <c r="G161" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H161" s="3" t="s">
-        <v>869</v>
+        <v>857</v>
       </c>
     </row>
     <row r="162" spans="1:8" ht="86.4">
@@ -30725,13 +30622,13 @@
         <v>8</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C162" s="2">
         <v>0</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E162" s="2" t="s">
         <v>11</v>
@@ -30740,10 +30637,10 @@
         <v>12</v>
       </c>
       <c r="G162" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="H162" s="3" t="s">
         <v>444</v>
-      </c>
-      <c r="H162" s="3" t="s">
-        <v>445</v>
       </c>
     </row>
     <row r="163" spans="1:8" ht="72">
@@ -30751,13 +30648,13 @@
         <v>8</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C163" s="2">
         <v>1</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="E163" s="2" t="s">
         <v>11</v>
@@ -30766,10 +30663,10 @@
         <v>12</v>
       </c>
       <c r="G163" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="H163" s="3" t="s">
         <v>447</v>
-      </c>
-      <c r="H163" s="3" t="s">
-        <v>448</v>
       </c>
     </row>
     <row r="164" spans="1:8">
@@ -30777,13 +30674,13 @@
         <v>8</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C164" s="2">
         <v>2</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E164" s="2" t="s">
         <v>11</v>
@@ -30792,10 +30689,10 @@
         <v>12</v>
       </c>
       <c r="G164" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="H164" s="4" t="s">
         <v>450</v>
-      </c>
-      <c r="H164" s="4" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="165" spans="1:8" ht="86.4">
@@ -30803,13 +30700,13 @@
         <v>8</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C165" s="2">
         <v>0</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E165" s="2" t="s">
         <v>11</v>
@@ -30818,10 +30715,10 @@
         <v>12</v>
       </c>
       <c r="G165" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="H165" s="3" t="s">
         <v>454</v>
-      </c>
-      <c r="H165" s="3" t="s">
-        <v>455</v>
       </c>
     </row>
     <row r="166" spans="1:8" ht="28.8">
@@ -30829,13 +30726,13 @@
         <v>8</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C166" s="2">
         <v>0</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="E166" s="2" t="s">
         <v>11</v>
@@ -30844,10 +30741,10 @@
         <v>12</v>
       </c>
       <c r="G166" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="H166" s="3" t="s">
         <v>458</v>
-      </c>
-      <c r="H166" s="3" t="s">
-        <v>459</v>
       </c>
     </row>
     <row r="167" spans="1:8" ht="28.8">
@@ -30855,13 +30752,13 @@
         <v>8</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C167" s="2">
         <v>1</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E167" s="2" t="s">
         <v>11</v>
@@ -30870,10 +30767,10 @@
         <v>12</v>
       </c>
       <c r="G167" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="H167" s="5" t="s">
         <v>461</v>
-      </c>
-      <c r="H167" s="5" t="s">
-        <v>462</v>
       </c>
     </row>
     <row r="168" spans="1:8">
@@ -30881,13 +30778,13 @@
         <v>8</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C168" s="2">
         <v>2</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="E168" s="2" t="s">
         <v>11</v>
@@ -30896,10 +30793,10 @@
         <v>12</v>
       </c>
       <c r="G168" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="H168" s="3" t="s">
         <v>464</v>
-      </c>
-      <c r="H168" s="3" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="169" spans="1:8" ht="129.6">
@@ -30907,13 +30804,13 @@
         <v>8</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C169" s="2">
         <v>0</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="E169" s="2" t="s">
         <v>11</v>
@@ -30922,10 +30819,10 @@
         <v>12</v>
       </c>
       <c r="G169" s="3" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H169" s="3" t="s">
-        <v>852</v>
+        <v>841</v>
       </c>
     </row>
     <row r="170" spans="1:8" ht="28.8">
@@ -30933,13 +30830,13 @@
         <v>8</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C170" s="2">
         <v>1</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="E170" s="2" t="s">
         <v>11</v>
@@ -30948,10 +30845,10 @@
         <v>12</v>
       </c>
       <c r="G170" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="H170" s="4" t="s">
         <v>470</v>
-      </c>
-      <c r="H170" s="4" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="171" spans="1:8" ht="28.8">
@@ -30959,13 +30856,13 @@
         <v>8</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C171" s="2">
         <v>0</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="E171" s="2" t="s">
         <v>11</v>
@@ -30974,10 +30871,10 @@
         <v>12</v>
       </c>
       <c r="G171" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="H171" s="3" t="s">
         <v>474</v>
-      </c>
-      <c r="H171" s="3" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="172" spans="1:8" ht="100.8">
@@ -30985,13 +30882,13 @@
         <v>8</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C172" s="2">
         <v>1</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E172" s="2" t="s">
         <v>11</v>
@@ -31000,10 +30897,10 @@
         <v>12</v>
       </c>
       <c r="G172" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="H172" s="3" t="s">
         <v>477</v>
-      </c>
-      <c r="H172" s="3" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="173" spans="1:8" ht="115.2">
@@ -31011,13 +30908,13 @@
         <v>8</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C173" s="2">
         <v>0</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="E173" s="2" t="s">
         <v>11</v>
@@ -31026,10 +30923,10 @@
         <v>12</v>
       </c>
       <c r="G173" s="3" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H173" s="5" t="s">
-        <v>854</v>
+        <v>843</v>
       </c>
     </row>
     <row r="174" spans="1:8" ht="28.8">
@@ -31037,13 +30934,13 @@
         <v>8</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C174" s="2">
         <v>1</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="E174" s="2" t="s">
         <v>11</v>
@@ -31052,10 +30949,10 @@
         <v>12</v>
       </c>
       <c r="G174" s="3" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H174" s="4" t="s">
-        <v>853</v>
+        <v>842</v>
       </c>
     </row>
     <row r="175" spans="1:8">
@@ -31063,13 +30960,13 @@
         <v>8</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C175" s="2">
         <v>0</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="E175" s="2" t="s">
         <v>11</v>
@@ -31078,10 +30975,10 @@
         <v>12</v>
       </c>
       <c r="G175" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="H175" s="4" t="s">
         <v>486</v>
-      </c>
-      <c r="H175" s="4" t="s">
-        <v>487</v>
       </c>
     </row>
     <row r="176" spans="1:8" ht="28.8">
@@ -31089,13 +30986,13 @@
         <v>8</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C176" s="2">
         <v>1</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E176" s="2" t="s">
         <v>11</v>
@@ -31104,10 +31001,10 @@
         <v>12</v>
       </c>
       <c r="G176" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="H176" s="4" t="s">
         <v>489</v>
-      </c>
-      <c r="H176" s="4" t="s">
-        <v>490</v>
       </c>
     </row>
     <row r="177" spans="1:8">
@@ -31115,13 +31012,13 @@
         <v>8</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C177" s="2">
         <v>2</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="E177" s="2" t="s">
         <v>11</v>
@@ -31130,10 +31027,10 @@
         <v>12</v>
       </c>
       <c r="G177" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="H177" s="4" t="s">
         <v>492</v>
-      </c>
-      <c r="H177" s="4" t="s">
-        <v>493</v>
       </c>
     </row>
     <row r="178" spans="1:8" ht="86.4">
@@ -31141,13 +31038,13 @@
         <v>8</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C178" s="2">
         <v>3</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="E178" s="2" t="s">
         <v>11</v>
@@ -31156,10 +31053,10 @@
         <v>12</v>
       </c>
       <c r="G178" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="H178" s="3" t="s">
         <v>495</v>
-      </c>
-      <c r="H178" s="3" t="s">
-        <v>496</v>
       </c>
     </row>
     <row r="179" spans="1:8" ht="86.4">
@@ -31167,13 +31064,13 @@
         <v>8</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C179" s="2">
         <v>4</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="E179" s="2" t="s">
         <v>11</v>
@@ -31182,10 +31079,10 @@
         <v>12</v>
       </c>
       <c r="G179" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="H179" s="3" t="s">
         <v>498</v>
-      </c>
-      <c r="H179" s="3" t="s">
-        <v>499</v>
       </c>
     </row>
     <row r="180" spans="1:8" ht="409.6">
@@ -31193,13 +31090,13 @@
         <v>8</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C180" s="2">
         <v>5</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E180" s="2" t="s">
         <v>11</v>
@@ -31208,10 +31105,10 @@
         <v>12</v>
       </c>
       <c r="G180" s="3" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H180" s="3" t="s">
-        <v>870</v>
+        <v>858</v>
       </c>
     </row>
     <row r="181" spans="1:8">
@@ -31219,13 +31116,13 @@
         <v>8</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C181" s="2">
         <v>6</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E181" s="2" t="s">
         <v>11</v>
@@ -31234,10 +31131,10 @@
         <v>12</v>
       </c>
       <c r="G181" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="H181" s="4" t="s">
         <v>503</v>
-      </c>
-      <c r="H181" s="4" t="s">
-        <v>504</v>
       </c>
     </row>
     <row r="182" spans="1:8" ht="144">
@@ -31245,13 +31142,13 @@
         <v>8</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C182" s="2">
         <v>7</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="E182" s="2" t="s">
         <v>11</v>
@@ -31260,10 +31157,10 @@
         <v>12</v>
       </c>
       <c r="G182" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="H182" s="3" t="s">
         <v>506</v>
-      </c>
-      <c r="H182" s="3" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="183" spans="1:8" ht="28.8">
@@ -31271,13 +31168,13 @@
         <v>8</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C183" s="2">
         <v>8</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="E183" s="2" t="s">
         <v>11</v>
@@ -31286,10 +31183,10 @@
         <v>12</v>
       </c>
       <c r="G183" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="H183" s="3" t="s">
         <v>509</v>
-      </c>
-      <c r="H183" s="3" t="s">
-        <v>510</v>
       </c>
     </row>
     <row r="184" spans="1:8" ht="57.6">
@@ -31297,13 +31194,13 @@
         <v>8</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C184" s="2">
         <v>9</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="E184" s="2" t="s">
         <v>11</v>
@@ -31312,10 +31209,10 @@
         <v>12</v>
       </c>
       <c r="G184" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="H184" s="3" t="s">
         <v>512</v>
-      </c>
-      <c r="H184" s="3" t="s">
-        <v>513</v>
       </c>
     </row>
     <row r="185" spans="1:8" ht="28.8">
@@ -31323,13 +31220,13 @@
         <v>8</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C185" s="2">
         <v>10</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E185" s="2" t="s">
         <v>11</v>
@@ -31338,10 +31235,10 @@
         <v>12</v>
       </c>
       <c r="G185" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="H185" s="3" t="s">
         <v>515</v>
-      </c>
-      <c r="H185" s="3" t="s">
-        <v>516</v>
       </c>
     </row>
     <row r="186" spans="1:8">
@@ -31349,13 +31246,13 @@
         <v>8</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C186" s="2">
         <v>11</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="E186" s="2" t="s">
         <v>11</v>
@@ -31364,10 +31261,10 @@
         <v>12</v>
       </c>
       <c r="G186" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="H186" s="4" t="s">
         <v>518</v>
-      </c>
-      <c r="H186" s="4" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="187" spans="1:8">
@@ -31375,13 +31272,13 @@
         <v>8</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C187" s="2">
         <v>12</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E187" s="2" t="s">
         <v>11</v>
@@ -31390,10 +31287,10 @@
         <v>12</v>
       </c>
       <c r="G187" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="H187" s="4" t="s">
         <v>521</v>
-      </c>
-      <c r="H187" s="4" t="s">
-        <v>522</v>
       </c>
     </row>
     <row r="188" spans="1:8" ht="115.2">
@@ -31401,13 +31298,13 @@
         <v>8</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C188" s="2">
         <v>0</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="E188" s="2" t="s">
         <v>11</v>
@@ -31416,10 +31313,10 @@
         <v>12</v>
       </c>
       <c r="G188" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="H188" s="3" t="s">
         <v>525</v>
-      </c>
-      <c r="H188" s="3" t="s">
-        <v>526</v>
       </c>
     </row>
     <row r="189" spans="1:8" ht="28.8">
@@ -31427,13 +31324,13 @@
         <v>8</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C189" s="2">
         <v>1</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="E189" s="2" t="s">
         <v>11</v>
@@ -31442,10 +31339,10 @@
         <v>12</v>
       </c>
       <c r="G189" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H189" s="4" t="s">
-        <v>855</v>
+        <v>844</v>
       </c>
     </row>
     <row r="190" spans="1:8" ht="115.2">
@@ -31453,13 +31350,13 @@
         <v>8</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C190" s="2">
         <v>0</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="E190" s="2" t="s">
         <v>11</v>
@@ -31468,10 +31365,10 @@
         <v>12</v>
       </c>
       <c r="G190" s="3" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H190" s="3" t="s">
-        <v>856</v>
+        <v>845</v>
       </c>
     </row>
     <row r="191" spans="1:8" ht="28.8">
@@ -31479,13 +31376,13 @@
         <v>8</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C191" s="2">
         <v>1</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="E191" s="2" t="s">
         <v>11</v>
@@ -31494,10 +31391,10 @@
         <v>12</v>
       </c>
       <c r="G191" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="H191" s="4" t="s">
         <v>533</v>
-      </c>
-      <c r="H191" s="4" t="s">
-        <v>534</v>
       </c>
     </row>
     <row r="192" spans="1:8" ht="86.4">
@@ -31505,13 +31402,13 @@
         <v>8</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C192" s="2">
         <v>0</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="E192" s="2" t="s">
         <v>11</v>
@@ -31520,10 +31417,10 @@
         <v>12</v>
       </c>
       <c r="G192" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="H192" s="3" t="s">
         <v>537</v>
-      </c>
-      <c r="H192" s="3" t="s">
-        <v>538</v>
       </c>
     </row>
     <row r="193" spans="1:8" ht="316.8">
@@ -31531,13 +31428,13 @@
         <v>8</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C193" s="2">
         <v>1</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="E193" s="2" t="s">
         <v>11</v>
@@ -31546,10 +31443,10 @@
         <v>12</v>
       </c>
       <c r="G193" s="3" t="s">
-        <v>857</v>
+        <v>846</v>
       </c>
       <c r="H193" s="3" t="s">
-        <v>858</v>
+        <v>847</v>
       </c>
     </row>
     <row r="194" spans="1:8" ht="86.4">
@@ -31557,13 +31454,13 @@
         <v>8</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C194" s="2">
         <v>0</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="E194" s="2" t="s">
         <v>11</v>
@@ -31572,10 +31469,10 @@
         <v>12</v>
       </c>
       <c r="G194" s="3" t="s">
-        <v>859</v>
+        <v>848</v>
       </c>
       <c r="H194" s="4" t="s">
-        <v>860</v>
+        <v>849</v>
       </c>
     </row>
     <row r="195" spans="1:8" ht="28.8">
@@ -31583,13 +31480,13 @@
         <v>8</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C195" s="2">
         <v>1</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="E195" s="2" t="s">
         <v>11</v>
@@ -31598,10 +31495,10 @@
         <v>12</v>
       </c>
       <c r="G195" s="3" t="s">
+        <v>542</v>
+      </c>
+      <c r="H195" s="4" t="s">
         <v>543</v>
-      </c>
-      <c r="H195" s="4" t="s">
-        <v>544</v>
       </c>
     </row>
     <row r="196" spans="1:8" ht="86.4">
@@ -31609,13 +31506,13 @@
         <v>8</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C196" s="2">
         <v>0</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="E196" s="2" t="s">
         <v>11</v>
@@ -31624,10 +31521,10 @@
         <v>12</v>
       </c>
       <c r="G196" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="H196" s="3" t="s">
         <v>547</v>
-      </c>
-      <c r="H196" s="3" t="s">
-        <v>548</v>
       </c>
     </row>
     <row r="197" spans="1:8" ht="201.6">
@@ -31635,13 +31532,13 @@
         <v>8</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C197" s="2">
         <v>1</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="E197" s="2" t="s">
         <v>11</v>
@@ -31650,10 +31547,10 @@
         <v>12</v>
       </c>
       <c r="G197" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="H197" s="3" t="s">
         <v>550</v>
-      </c>
-      <c r="H197" s="3" t="s">
-        <v>551</v>
       </c>
     </row>
     <row r="198" spans="1:8" ht="28.8">
@@ -31661,13 +31558,13 @@
         <v>8</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C198" s="2">
         <v>2</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="E198" s="2" t="s">
         <v>11</v>
@@ -31676,10 +31573,10 @@
         <v>12</v>
       </c>
       <c r="G198" s="3" t="s">
+        <v>552</v>
+      </c>
+      <c r="H198" s="3" t="s">
         <v>553</v>
-      </c>
-      <c r="H198" s="3" t="s">
-        <v>554</v>
       </c>
     </row>
     <row r="199" spans="1:8">
@@ -31687,13 +31584,13 @@
         <v>8</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C199" s="2">
         <v>3</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="E199" s="2" t="s">
         <v>11</v>
@@ -31702,10 +31599,10 @@
         <v>12</v>
       </c>
       <c r="G199" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="H199" s="3" t="s">
         <v>556</v>
-      </c>
-      <c r="H199" s="3" t="s">
-        <v>557</v>
       </c>
     </row>
     <row r="200" spans="1:8" ht="100.8">
@@ -31713,13 +31610,13 @@
         <v>8</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C200" s="2">
         <v>4</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="E200" s="2" t="s">
         <v>11</v>
@@ -31728,10 +31625,10 @@
         <v>12</v>
       </c>
       <c r="G200" s="3" t="s">
+        <v>558</v>
+      </c>
+      <c r="H200" s="4" t="s">
         <v>559</v>
-      </c>
-      <c r="H200" s="4" t="s">
-        <v>560</v>
       </c>
     </row>
     <row r="201" spans="1:8" ht="28.8">
@@ -31739,13 +31636,13 @@
         <v>8</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C201" s="2">
         <v>5</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="E201" s="2" t="s">
         <v>11</v>
@@ -31754,10 +31651,10 @@
         <v>12</v>
       </c>
       <c r="G201" s="3" t="s">
+        <v>561</v>
+      </c>
+      <c r="H201" s="3" t="s">
         <v>562</v>
-      </c>
-      <c r="H201" s="3" t="s">
-        <v>563</v>
       </c>
     </row>
     <row r="202" spans="1:8">
@@ -31765,13 +31662,13 @@
         <v>8</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C202" s="2">
         <v>6</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="E202" s="2" t="s">
         <v>11</v>
@@ -31780,10 +31677,10 @@
         <v>12</v>
       </c>
       <c r="G202" s="3" t="s">
+        <v>564</v>
+      </c>
+      <c r="H202" s="4" t="s">
         <v>565</v>
-      </c>
-      <c r="H202" s="4" t="s">
-        <v>566</v>
       </c>
     </row>
     <row r="203" spans="1:8">
@@ -31791,13 +31688,13 @@
         <v>8</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C203" s="2">
         <v>7</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="E203" s="2" t="s">
         <v>11</v>
@@ -31806,10 +31703,10 @@
         <v>12</v>
       </c>
       <c r="G203" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="H203" s="4" t="s">
         <v>568</v>
-      </c>
-      <c r="H203" s="4" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="204" spans="1:8" ht="100.8">
@@ -31817,13 +31714,13 @@
         <v>8</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C204" s="2">
         <v>0</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E204" s="2" t="s">
         <v>11</v>
@@ -31832,10 +31729,10 @@
         <v>12</v>
       </c>
       <c r="G204" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="H204" s="3" t="s">
         <v>572</v>
-      </c>
-      <c r="H204" s="3" t="s">
-        <v>573</v>
       </c>
     </row>
     <row r="205" spans="1:8" ht="244.8">
@@ -31843,13 +31740,13 @@
         <v>8</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C205" s="2">
         <v>1</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="E205" s="2" t="s">
         <v>11</v>
@@ -31858,10 +31755,10 @@
         <v>12</v>
       </c>
       <c r="G205" s="3" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H205" s="3" t="s">
-        <v>576</v>
+        <v>872</v>
       </c>
     </row>
     <row r="206" spans="1:8" ht="28.8">
@@ -31869,13 +31766,13 @@
         <v>8</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="C206" s="2">
         <v>0</v>
       </c>
       <c r="D206" s="2" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="E206" s="2" t="s">
         <v>11</v>
@@ -31884,10 +31781,10 @@
         <v>12</v>
       </c>
       <c r="G206" s="3" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="H206" s="4" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
     </row>
     <row r="207" spans="1:8" ht="43.2">
@@ -31895,13 +31792,13 @@
         <v>8</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="C207" s="2">
         <v>1</v>
       </c>
       <c r="D207" s="2" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="E207" s="2" t="s">
         <v>11</v>
@@ -31910,10 +31807,10 @@
         <v>12</v>
       </c>
       <c r="G207" s="3" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="H207" s="3" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
     </row>
     <row r="208" spans="1:8" ht="28.8">
@@ -31921,13 +31818,13 @@
         <v>8</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="C208" s="2">
         <v>0</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="E208" s="2" t="s">
         <v>11</v>
@@ -31936,10 +31833,10 @@
         <v>12</v>
       </c>
       <c r="G208" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="H208" s="4" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
     </row>
     <row r="209" spans="1:8" ht="28.8">
@@ -31947,13 +31844,13 @@
         <v>8</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="C209" s="2">
         <v>0</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="E209" s="2" t="s">
         <v>11</v>
@@ -31962,10 +31859,10 @@
         <v>12</v>
       </c>
       <c r="G209" s="3" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="H209" s="4" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
     </row>
     <row r="210" spans="1:8" ht="28.8">
@@ -31973,13 +31870,13 @@
         <v>8</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="C210" s="2">
         <v>1</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="E210" s="2" t="s">
         <v>11</v>
@@ -31988,10 +31885,10 @@
         <v>12</v>
       </c>
       <c r="G210" s="3" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="H210" s="4" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
     </row>
     <row r="211" spans="1:8" ht="28.8">
@@ -31999,13 +31896,13 @@
         <v>8</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="C211" s="2">
         <v>0</v>
       </c>
       <c r="D211" s="2" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="E211" s="2" t="s">
         <v>11</v>
@@ -32014,10 +31911,10 @@
         <v>12</v>
       </c>
       <c r="G211" s="3" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="H211" s="4" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
     </row>
     <row r="212" spans="1:8" ht="409.6">
@@ -32025,13 +31922,13 @@
         <v>8</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="C212" s="2">
         <v>1</v>
       </c>
       <c r="D212" s="2" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="E212" s="2" t="s">
         <v>11</v>
@@ -32040,10 +31937,10 @@
         <v>12</v>
       </c>
       <c r="G212" s="3" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="H212" s="3" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="213" spans="1:8" ht="86.4">
@@ -32051,13 +31948,13 @@
         <v>8</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="C213" s="2">
         <v>0</v>
       </c>
       <c r="D213" s="2" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="E213" s="2" t="s">
         <v>11</v>
@@ -32066,10 +31963,10 @@
         <v>12</v>
       </c>
       <c r="G213" s="3" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="H213" s="4" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
     </row>
     <row r="214" spans="1:8" ht="86.4">
@@ -32077,13 +31974,13 @@
         <v>8</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="C214" s="2">
         <v>1</v>
       </c>
       <c r="D214" s="2" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="E214" s="2" t="s">
         <v>11</v>
@@ -32092,10 +31989,10 @@
         <v>12</v>
       </c>
       <c r="G214" s="3" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="H214" s="3" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
     </row>
     <row r="215" spans="1:8" ht="28.8">
@@ -32103,13 +32000,13 @@
         <v>8</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="C215" s="2">
         <v>0</v>
       </c>
       <c r="D215" s="2" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="E215" s="2" t="s">
         <v>11</v>
@@ -32118,10 +32015,10 @@
         <v>12</v>
       </c>
       <c r="G215" s="3" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="H215" s="4" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
     </row>
     <row r="216" spans="1:8" ht="403.2">
@@ -32129,13 +32026,13 @@
         <v>8</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="C216" s="2">
         <v>1</v>
       </c>
       <c r="D216" s="2" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="E216" s="2" t="s">
         <v>11</v>
@@ -32144,10 +32041,10 @@
         <v>12</v>
       </c>
       <c r="G216" s="3" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="H216" s="3" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
     </row>
     <row r="217" spans="1:8" ht="187.2">
@@ -32155,13 +32052,13 @@
         <v>8</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="C217" s="2">
         <v>2</v>
       </c>
       <c r="D217" s="2" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="E217" s="2" t="s">
         <v>11</v>
@@ -32170,10 +32067,10 @@
         <v>12</v>
       </c>
       <c r="G217" s="3" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="H217" s="3" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
     </row>
     <row r="218" spans="1:8" ht="86.4">
@@ -32181,13 +32078,13 @@
         <v>8</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="C218" s="2">
         <v>0</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="E218" s="2" t="s">
         <v>11</v>
@@ -32196,10 +32093,10 @@
         <v>12</v>
       </c>
       <c r="G218" s="3" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="H218" s="3" t="s">
-        <v>842</v>
+        <v>832</v>
       </c>
     </row>
     <row r="219" spans="1:8">
@@ -32207,13 +32104,13 @@
         <v>8</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="C219" s="2">
         <v>1</v>
       </c>
       <c r="D219" s="2" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="E219" s="2" t="s">
         <v>11</v>
@@ -32225,7 +32122,7 @@
         <v>22</v>
       </c>
       <c r="H219" s="4" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
     </row>
     <row r="220" spans="1:8">
@@ -32233,13 +32130,13 @@
         <v>8</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="C220" s="2">
         <v>0</v>
       </c>
       <c r="D220" s="2" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="E220" s="2" t="s">
         <v>11</v>
@@ -32248,10 +32145,10 @@
         <v>12</v>
       </c>
       <c r="G220" s="3" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="H220" s="4" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
     </row>
     <row r="221" spans="1:8">
@@ -32259,13 +32156,13 @@
         <v>8</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="C221" s="2">
         <v>0</v>
       </c>
       <c r="D221" s="2" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="E221" s="2" t="s">
         <v>11</v>
@@ -32274,10 +32171,10 @@
         <v>12</v>
       </c>
       <c r="G221" s="3" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="H221" s="4" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
     </row>
     <row r="222" spans="1:8">
@@ -32285,13 +32182,13 @@
         <v>8</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="C222" s="2">
         <v>0</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="E222" s="2" t="s">
         <v>11</v>
@@ -32300,10 +32197,10 @@
         <v>12</v>
       </c>
       <c r="G222" s="3" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="H222" s="4" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
     </row>
     <row r="223" spans="1:8">
@@ -32311,13 +32208,13 @@
         <v>8</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="C223" s="2">
         <v>0</v>
       </c>
       <c r="D223" s="2" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="E223" s="2" t="s">
         <v>11</v>
@@ -32326,10 +32223,10 @@
         <v>12</v>
       </c>
       <c r="G223" s="3" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="H223" s="4" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
     </row>
     <row r="224" spans="1:8">
@@ -32337,13 +32234,13 @@
         <v>8</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="C224" s="2">
         <v>0</v>
       </c>
       <c r="D224" s="2" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="E224" s="2" t="s">
         <v>11</v>
@@ -32352,10 +32249,10 @@
         <v>12</v>
       </c>
       <c r="G224" s="3" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="H224" s="4" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
     </row>
     <row r="225" spans="1:8" ht="28.8">
@@ -32363,13 +32260,13 @@
         <v>8</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="C225" s="2">
         <v>0</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="E225" s="2" t="s">
         <v>11</v>
@@ -32378,10 +32275,10 @@
         <v>12</v>
       </c>
       <c r="G225" s="3" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="H225" s="4" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
     </row>
     <row r="226" spans="1:8" ht="28.8">
@@ -32389,13 +32286,13 @@
         <v>8</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="C226" s="2">
         <v>1</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="E226" s="2" t="s">
         <v>11</v>
@@ -32404,10 +32301,10 @@
         <v>12</v>
       </c>
       <c r="G226" s="3" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="H226" s="4" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
     </row>
     <row r="227" spans="1:8">
@@ -32415,13 +32312,13 @@
         <v>8</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="C227" s="2">
         <v>2</v>
       </c>
       <c r="D227" s="2" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="E227" s="2" t="s">
         <v>11</v>
@@ -32430,10 +32327,10 @@
         <v>12</v>
       </c>
       <c r="G227" s="3" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="H227" s="4" t="s">
-        <v>861</v>
+        <v>850</v>
       </c>
     </row>
     <row r="228" spans="1:8" ht="100.8">
@@ -32441,13 +32338,13 @@
         <v>8</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="C228" s="2">
         <v>3</v>
       </c>
       <c r="D228" s="2" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="E228" s="2" t="s">
         <v>11</v>
@@ -32456,10 +32353,10 @@
         <v>12</v>
       </c>
       <c r="G228" s="3" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="H228" s="3" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
     </row>
     <row r="229" spans="1:8" ht="187.2">
@@ -32467,13 +32364,13 @@
         <v>8</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="C229" s="2">
         <v>4</v>
       </c>
       <c r="D229" s="2" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="E229" s="2" t="s">
         <v>11</v>
@@ -32482,10 +32379,10 @@
         <v>12</v>
       </c>
       <c r="G229" s="3" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="H229" s="3" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
     </row>
     <row r="230" spans="1:8" ht="100.8">
@@ -32493,13 +32390,13 @@
         <v>8</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="C230" s="2">
         <v>5</v>
       </c>
       <c r="D230" s="2" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="E230" s="2" t="s">
         <v>11</v>
@@ -32508,10 +32405,10 @@
         <v>12</v>
       </c>
       <c r="G230" s="3" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="H230" s="3" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="231" spans="1:8" ht="100.8">
@@ -32519,13 +32416,13 @@
         <v>8</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="C231" s="2">
         <v>6</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="E231" s="2" t="s">
         <v>11</v>
@@ -32534,10 +32431,10 @@
         <v>12</v>
       </c>
       <c r="G231" s="3" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="H231" s="3" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
     </row>
     <row r="232" spans="1:8" ht="43.2">
@@ -32545,13 +32442,13 @@
         <v>8</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="C232" s="2">
         <v>7</v>
       </c>
       <c r="D232" s="2" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="E232" s="2" t="s">
         <v>11</v>
@@ -32560,10 +32457,10 @@
         <v>12</v>
       </c>
       <c r="G232" s="3" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="H232" s="3" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
     </row>
     <row r="233" spans="1:8" ht="100.8">
@@ -32571,13 +32468,13 @@
         <v>8</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="C233" s="2">
         <v>8</v>
       </c>
       <c r="D233" s="2" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="E233" s="2" t="s">
         <v>11</v>
@@ -32586,10 +32483,10 @@
         <v>12</v>
       </c>
       <c r="G233" s="3" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="H233" s="3" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
     </row>
     <row r="234" spans="1:8" ht="43.2">
@@ -32597,13 +32494,13 @@
         <v>8</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="C234" s="2">
         <v>9</v>
       </c>
       <c r="D234" s="2" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="E234" s="2" t="s">
         <v>11</v>
@@ -32612,10 +32509,10 @@
         <v>12</v>
       </c>
       <c r="G234" s="3" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="H234" s="3" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
     </row>
     <row r="235" spans="1:8" ht="409.6">
@@ -32623,13 +32520,13 @@
         <v>8</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="C235" s="2">
         <v>10</v>
       </c>
       <c r="D235" s="2" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="E235" s="2" t="s">
         <v>11</v>
@@ -32638,10 +32535,10 @@
         <v>12</v>
       </c>
       <c r="G235" s="3" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="H235" s="3" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
     </row>
     <row r="236" spans="1:8" ht="43.2">
@@ -32649,13 +32546,13 @@
         <v>8</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="C236" s="2">
         <v>11</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="E236" s="2" t="s">
         <v>11</v>
@@ -32664,10 +32561,10 @@
         <v>12</v>
       </c>
       <c r="G236" s="3" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="H236" s="3" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
     </row>
     <row r="237" spans="1:8" ht="43.2">
@@ -32675,13 +32572,13 @@
         <v>8</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="C237" s="2">
         <v>12</v>
       </c>
       <c r="D237" s="2" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="E237" s="2" t="s">
         <v>11</v>
@@ -32690,10 +32587,10 @@
         <v>12</v>
       </c>
       <c r="G237" s="3" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="H237" s="3" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
     </row>
     <row r="238" spans="1:8" ht="115.2">
@@ -32701,13 +32598,13 @@
         <v>8</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="C238" s="2">
         <v>13</v>
       </c>
       <c r="D238" s="2" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="E238" s="2" t="s">
         <v>11</v>
@@ -32716,10 +32613,10 @@
         <v>12</v>
       </c>
       <c r="G238" s="3" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="H238" s="3" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
     </row>
     <row r="239" spans="1:8" ht="43.2">
@@ -32727,13 +32624,13 @@
         <v>8</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="C239" s="2">
         <v>14</v>
       </c>
       <c r="D239" s="2" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="E239" s="2" t="s">
         <v>11</v>
@@ -32742,10 +32639,10 @@
         <v>12</v>
       </c>
       <c r="G239" s="3" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="H239" s="3" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
     </row>
     <row r="240" spans="1:8" ht="43.2">
@@ -32753,13 +32650,13 @@
         <v>8</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="C240" s="2">
         <v>15</v>
       </c>
       <c r="D240" s="2" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="E240" s="2" t="s">
         <v>11</v>
@@ -32768,10 +32665,10 @@
         <v>12</v>
       </c>
       <c r="G240" s="3" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="H240" s="3" t="s">
-        <v>862</v>
+        <v>851</v>
       </c>
     </row>
     <row r="241" spans="1:8" ht="115.2">
@@ -32779,13 +32676,13 @@
         <v>8</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="C241" s="2">
         <v>16</v>
       </c>
       <c r="D241" s="2" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="E241" s="2" t="s">
         <v>11</v>
@@ -32794,10 +32691,10 @@
         <v>12</v>
       </c>
       <c r="G241" s="3" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="H241" s="3" t="s">
-        <v>863</v>
+        <v>852</v>
       </c>
     </row>
     <row r="242" spans="1:8" ht="129.6">
@@ -32805,13 +32702,13 @@
         <v>8</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="C242" s="2">
         <v>17</v>
       </c>
       <c r="D242" s="2" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="E242" s="2" t="s">
         <v>11</v>
@@ -32820,10 +32717,10 @@
         <v>12</v>
       </c>
       <c r="G242" s="3" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="H242" s="3" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
     </row>
     <row r="243" spans="1:8" ht="230.4">
@@ -32831,13 +32728,13 @@
         <v>8</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="C243" s="2">
         <v>18</v>
       </c>
       <c r="D243" s="2" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="E243" s="2" t="s">
         <v>11</v>
@@ -32846,10 +32743,10 @@
         <v>12</v>
       </c>
       <c r="G243" s="3" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="H243" s="3" t="s">
-        <v>864</v>
+        <v>853</v>
       </c>
     </row>
     <row r="244" spans="1:8" ht="100.8">
@@ -32857,13 +32754,13 @@
         <v>8</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="C244" s="2">
         <v>19</v>
       </c>
       <c r="D244" s="2" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="E244" s="2" t="s">
         <v>11</v>
@@ -32872,10 +32769,10 @@
         <v>12</v>
       </c>
       <c r="G244" s="3" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="H244" s="3" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
     </row>
     <row r="245" spans="1:8" ht="86.4">
@@ -32883,13 +32780,13 @@
         <v>8</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="C245" s="2">
         <v>20</v>
       </c>
       <c r="D245" s="2" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="E245" s="2" t="s">
         <v>11</v>
@@ -32898,10 +32795,10 @@
         <v>12</v>
       </c>
       <c r="G245" s="3" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="H245" s="3" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
     </row>
     <row r="246" spans="1:8" ht="216">
@@ -32909,13 +32806,13 @@
         <v>8</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="C246" s="2">
         <v>21</v>
       </c>
       <c r="D246" s="2" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="E246" s="2" t="s">
         <v>11</v>
@@ -32924,10 +32821,10 @@
         <v>12</v>
       </c>
       <c r="G246" s="3" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="H246" s="3" t="s">
-        <v>865</v>
+        <v>854</v>
       </c>
     </row>
     <row r="247" spans="1:8" ht="100.8">
@@ -32935,13 +32832,13 @@
         <v>8</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="C247" s="2">
         <v>22</v>
       </c>
       <c r="D247" s="2" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="E247" s="2" t="s">
         <v>11</v>
@@ -32950,10 +32847,10 @@
         <v>12</v>
       </c>
       <c r="G247" s="3" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="H247" s="3" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
     </row>
     <row r="248" spans="1:8" ht="187.2">
@@ -32961,13 +32858,13 @@
         <v>8</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="C248" s="2">
         <v>23</v>
       </c>
       <c r="D248" s="2" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="E248" s="2" t="s">
         <v>11</v>
@@ -32976,10 +32873,10 @@
         <v>12</v>
       </c>
       <c r="G248" s="3" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="H248" s="3" t="s">
-        <v>866</v>
+        <v>855</v>
       </c>
     </row>
     <row r="249" spans="1:8" ht="28.8">
@@ -32987,13 +32884,13 @@
         <v>8</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="C249" s="2">
         <v>24</v>
       </c>
       <c r="D249" s="2" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="E249" s="2" t="s">
         <v>11</v>
@@ -33002,10 +32899,10 @@
         <v>12</v>
       </c>
       <c r="G249" s="3" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="H249" s="4" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
     </row>
     <row r="250" spans="1:8" ht="43.2">
@@ -33013,13 +32910,13 @@
         <v>8</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="C250" s="2">
         <v>25</v>
       </c>
       <c r="D250" s="2" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="E250" s="2" t="s">
         <v>11</v>
@@ -33028,10 +32925,10 @@
         <v>12</v>
       </c>
       <c r="G250" s="3" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="H250" s="3" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
     </row>
     <row r="251" spans="1:8" ht="43.2">
@@ -33039,13 +32936,13 @@
         <v>8</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="C251" s="2">
         <v>26</v>
       </c>
       <c r="D251" s="2" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="E251" s="2" t="s">
         <v>11</v>
@@ -33054,10 +32951,10 @@
         <v>12</v>
       </c>
       <c r="G251" s="3" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="H251" s="3" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
     </row>
     <row r="252" spans="1:8" ht="43.2">
@@ -33065,13 +32962,13 @@
         <v>8</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="C252" s="2">
         <v>27</v>
       </c>
       <c r="D252" s="2" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="E252" s="2" t="s">
         <v>11</v>
@@ -33080,10 +32977,10 @@
         <v>12</v>
       </c>
       <c r="G252" s="3" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="H252" s="3" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
     </row>
     <row r="253" spans="1:8">
@@ -33091,13 +32988,13 @@
         <v>8</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="C253" s="2">
         <v>0</v>
       </c>
       <c r="D253" s="2" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="E253" s="2" t="s">
         <v>11</v>
@@ -33106,10 +33003,10 @@
         <v>12</v>
       </c>
       <c r="G253" s="3" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="H253" s="4" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
     </row>
     <row r="254" spans="1:8" ht="100.8">
@@ -33117,13 +33014,13 @@
         <v>8</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="C254" s="2">
         <v>2</v>
       </c>
       <c r="D254" s="2" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="E254" s="2" t="s">
         <v>11</v>
@@ -33132,10 +33029,10 @@
         <v>12</v>
       </c>
       <c r="G254" s="3" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="H254" s="3" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
     </row>
     <row r="255" spans="1:8">
@@ -33143,13 +33040,13 @@
         <v>8</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="C255" s="2">
         <v>0</v>
       </c>
       <c r="D255" s="2" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="E255" s="2" t="s">
         <v>11</v>
@@ -33158,10 +33055,10 @@
         <v>12</v>
       </c>
       <c r="G255" s="3" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="H255" s="4" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
     </row>
     <row r="256" spans="1:8">
@@ -33169,13 +33066,13 @@
         <v>8</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="C256" s="2">
         <v>0</v>
       </c>
       <c r="D256" s="2" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="E256" s="2" t="s">
         <v>11</v>
@@ -33184,10 +33081,10 @@
         <v>12</v>
       </c>
       <c r="G256" s="3" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="H256" s="4" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
     </row>
     <row r="257" spans="1:8" ht="28.8">
@@ -33195,13 +33092,13 @@
         <v>8</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="C257" s="2">
         <v>0</v>
       </c>
       <c r="D257" s="2" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="E257" s="2" t="s">
         <v>11</v>
@@ -33210,10 +33107,10 @@
         <v>12</v>
       </c>
       <c r="G257" s="3" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="H257" s="3" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
     </row>
     <row r="258" spans="1:8" ht="43.2">
@@ -33221,13 +33118,13 @@
         <v>8</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="C258" s="2">
         <v>1</v>
       </c>
       <c r="D258" s="2" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="E258" s="2" t="s">
         <v>11</v>
@@ -33236,10 +33133,10 @@
         <v>12</v>
       </c>
       <c r="G258" s="3" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="H258" s="3" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
     </row>
     <row r="259" spans="1:8" ht="100.8">
@@ -33247,13 +33144,13 @@
         <v>8</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="C259" s="2">
         <v>2</v>
       </c>
       <c r="D259" s="2" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="E259" s="2" t="s">
         <v>11</v>
@@ -33262,10 +33159,10 @@
         <v>12</v>
       </c>
       <c r="G259" s="3" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="H259" s="3" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
     </row>
     <row r="260" spans="1:8" ht="43.2">
@@ -33273,13 +33170,13 @@
         <v>8</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="C260" s="2">
         <v>3</v>
       </c>
       <c r="D260" s="2" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="E260" s="2" t="s">
         <v>11</v>
@@ -33288,10 +33185,10 @@
         <v>12</v>
       </c>
       <c r="G260" s="3" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="H260" s="3" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
     </row>
     <row r="261" spans="1:8">
@@ -33299,13 +33196,13 @@
         <v>8</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="C261" s="2">
         <v>0</v>
       </c>
       <c r="D261" s="2" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="E261" s="2" t="s">
         <v>11</v>
@@ -33314,10 +33211,10 @@
         <v>12</v>
       </c>
       <c r="G261" s="3" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="H261" s="4" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
     </row>
     <row r="262" spans="1:8">
@@ -33325,13 +33222,13 @@
         <v>8</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="C262" s="2">
         <v>0</v>
       </c>
       <c r="D262" s="2" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="E262" s="2" t="s">
         <v>11</v>
@@ -33340,10 +33237,10 @@
         <v>12</v>
       </c>
       <c r="G262" s="3" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="H262" s="4" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
     </row>
     <row r="263" spans="1:8">
@@ -33351,13 +33248,13 @@
         <v>8</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="C263" s="2">
         <v>0</v>
       </c>
       <c r="D263" s="2" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="E263" s="2" t="s">
         <v>11</v>
@@ -33366,10 +33263,10 @@
         <v>12</v>
       </c>
       <c r="G263" s="3" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="H263" s="4" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
     </row>
     <row r="264" spans="1:8">
@@ -33377,13 +33274,13 @@
         <v>8</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="C264" s="2">
         <v>1</v>
       </c>
       <c r="D264" s="2" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="E264" s="2" t="s">
         <v>11</v>
@@ -33392,10 +33289,10 @@
         <v>12</v>
       </c>
       <c r="G264" s="3" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="H264" s="4" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
     </row>
     <row r="265" spans="1:8" ht="28.8">
@@ -33403,13 +33300,13 @@
         <v>8</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="C265" s="2">
         <v>0</v>
       </c>
       <c r="D265" s="2" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="E265" s="2" t="s">
         <v>11</v>
@@ -33418,10 +33315,10 @@
         <v>12</v>
       </c>
       <c r="G265" s="3" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="H265" s="4" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
     </row>
   </sheetData>

--- a/docassemble/PowerOfAttorneyProperty/data/sources/poa_property_es.xlsx
+++ b/docassemble/PowerOfAttorneyProperty/data/sources/poa_property_es.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mnewsted\local-DA-easyforms-dev\sources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{667B85E0-3196-4831-B614-DC39CCF34DB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25D019AD-8D8E-43CA-B7E7-FFE38A3E22AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38160" yWindow="-4650" windowWidth="19830" windowHeight="19665" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38160" yWindow="-4650" windowWidth="24360" windowHeight="19665" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -5464,6 +5464,12 @@
     </r>
   </si>
   <si>
+    <t>agent limits</t>
+  </si>
+  <si>
+    <t>37150abefb3be9f6e255fbda816e0c6e</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -5479,12 +5485,12 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Puede limitar cualquiera de los poderes otorgados a un agente. También puede enumerar cualquier poder específico que no desee que el agente tenga.
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">What limits or special rules do you want to include?
 </t>
     </r>
     <r>
@@ -5501,6 +5507,16 @@
     </r>
     <r>
       <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">What limits or special rules does </t>
+    </r>
+    <r>
+      <rPr>
         <b/>
         <sz val="11"/>
         <color rgb="FF0000FF"/>
@@ -5513,12 +5529,93 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> puede limitar cualquiera de los poderes otorgados a un agente. También puede enumerar cualquier poder específico que no desee que el agente tenga.
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> want to include?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% endif
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% if for_yourself == True:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">¿Qué límites o reglas especiales quieres incluir?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% else:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">¿Qué límites o reglas especiales quiere incluir </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${principal.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">?
 </t>
     </r>
     <r>
@@ -5534,10 +5631,7 @@
     </r>
   </si>
   <si>
-    <t>agent limits</t>
-  </si>
-  <si>
-    <t>37150abefb3be9f6e255fbda816e0c6e</t>
+    <t>783fd288b9ef3041644668e13c6ad667</t>
   </si>
   <si>
     <r>
@@ -5560,7 +5654,28 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">What limits or special rules do you want to include?
+      <t xml:space="preserve">  For example, you can place conditions on the sale of real estate or make special rules on borrowing by </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${agent.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.
 </t>
     </r>
     <r>
@@ -5583,7 +5698,372 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">What limits or special rules does </t>
+      <t xml:space="preserve">For example, they can place conditions on the sale of real estate or make special rules on borrowing by </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${agent.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% endif
+</t>
+    </r>
+  </si>
+  <si>
+    <t>b7a95c6586d57b909e3a9973bf21cccf</t>
+  </si>
+  <si>
+    <t>Limits</t>
+  </si>
+  <si>
+    <t>Límites</t>
+  </si>
+  <si>
+    <t>any additional powers</t>
+  </si>
+  <si>
+    <t>ab561acc5fd96bb157258a42cee1b135</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% if for_yourself == True:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Do you want to give any additional powers to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${agent.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% else:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Does </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${ principal.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> want to give any additional powers to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${agent.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% endif
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% if for_yourself == True:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">¿Quieres otorgar poderes adicionales a </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${agent.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% else:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">¿Quiere </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${ principal.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> otorgar poderes adicionales a </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${agent.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>% endif</t>
+    </r>
+  </si>
+  <si>
+    <t>ac917267914505b128fc8bd6c9b77b2c</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% if for_yourself == True:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">If you want, you may give other powers to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${agent.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. These powers will be in addition to the ones already provided.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% else:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">If </t>
     </r>
     <r>
       <rPr>
@@ -5604,127 +6084,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> want to include?
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% endif
-</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% if for_yourself == True:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">¿Qué límites o reglas especiales quieres incluir?
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% else:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">¿Qué límites o reglas especiales quiere incluir </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${principal.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">?
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>% endif</t>
-    </r>
-  </si>
-  <si>
-    <t>783fd288b9ef3041644668e13c6ad667</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% if for_yourself == True:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  For example, you can place conditions on the sale of real estate or make special rules on borrowing by </t>
+      <t xml:space="preserve"> wants, they may give other powers to </t>
     </r>
     <r>
       <rPr>
@@ -5745,31 +6105,59 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% else:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">For example, they can place conditions on the sale of real estate or make special rules on borrowing by </t>
-    </r>
+      <t xml:space="preserve">. These powers will be in addition to the ones already provided.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% endif 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${collapse_template(powers_example)}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+  </si>
+  <si>
+    <t>b1a5d6b7f256f8486866e92697883254</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -5789,734 +6177,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% endif
-</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% if for_yourself == True:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  Por ejemplo, puedes imponer condiciones en la venta de bienes raíces o establecer reglas especiales sobre el endeudamiento por </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${agent.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% else:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Por ejemplo, ellos pueden imponer condiciones en la venta de bienes raíces o establecer reglas especiales sobre el endeudamiento por </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${agent.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>% endif</t>
-    </r>
-  </si>
-  <si>
-    <t>b7a95c6586d57b909e3a9973bf21cccf</t>
-  </si>
-  <si>
-    <t>Limits</t>
-  </si>
-  <si>
-    <t>Límites</t>
-  </si>
-  <si>
-    <t>any additional powers</t>
-  </si>
-  <si>
-    <t>ab561acc5fd96bb157258a42cee1b135</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% if for_yourself == True:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Do you want to give any additional powers to </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${agent.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">?
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% else:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Does </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${ principal.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> want to give any additional powers to </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${agent.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">?
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% endif
-</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% if for_yourself == True:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">¿Quieres otorgar poderes adicionales a </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${agent.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">?
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% else:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">¿Quiere </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${ principal.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> otorgar poderes adicionales a </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${agent.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">?
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>% endif</t>
-    </r>
-  </si>
-  <si>
-    <t>ac917267914505b128fc8bd6c9b77b2c</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% if for_yourself == True:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">If you want, you may give other powers to </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${agent.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">. These powers will be in addition to the ones already provided.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% else:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">If </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${principal.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> wants, they may give other powers to </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${agent.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">. These powers will be in addition to the ones already provided.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% endif 
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${collapse_template(powers_example)}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% if for_yourself == True:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Si quieres, puedes otorgar otros poderes a </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${agent.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">. Estos poderes se añadirán a los que ya se te han proporcionado.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% else:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Si </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${principal.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> quiere, ellos pueden otorgar otros poderes a </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${agent.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">. Estos poderes se añadirán a los que ya se te han proporcionado.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% endif 
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${collapse_template(powers_example)}</t>
-    </r>
-  </si>
-  <si>
-    <t>b1a5d6b7f256f8486866e92697883254</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${agent.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
       <t xml:space="preserve"> is granted the following additional powers:</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${agent.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> se le otorgan los siguientes poderes adicionales:</t>
     </r>
   </si>
   <si>
@@ -6535,14 +6196,6 @@
 </t>
   </si>
   <si>
-    <t>Otros poderes que un mandante podría otorgar a un apoderado incluyen:
-* El poder de entregar tu propiedad a otras personas como regalos,
-* El poder de ejercer poderes de designación,
-* El poder de nombrar o cambiar beneficiarios o copropietarios conjuntos,
-* El derecho a acceder a tus cuentas de redes sociales, y
-* El poder de revocar o enmendar un fideicomiso.</t>
-  </si>
-  <si>
     <t>c8516ec3b4d906e37405219d35b2903d</t>
   </si>
   <si>
@@ -6975,15 +6628,18 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">No, solo </t>
+    <t>082c7d0ac8e63192470ce3f5a17e6eef</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Yes, </t>
     </r>
     <r>
       <rPr>
@@ -6999,48 +6655,24 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> puede tomar decisiones para </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${me_subject}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <t>082c7d0ac8e63192470ce3f5a17e6eef</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Yes, </t>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> can choose any person as a delegate.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Sí, </t>
     </r>
     <r>
       <rPr>
@@ -7056,39 +6688,6 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> can choose any person as a delegate.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Sí, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${agent.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
@@ -7134,94 +6733,7 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Solo pueden delegar a alguien que </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${i_subject}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> autorice.</t>
-    </r>
-  </si>
-  <si>
     <t>7404bb876506871b1cfdd715498355b5</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Who </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${do_does}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${you_subject}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> authorize as delegate?</t>
-    </r>
   </si>
   <si>
     <r>
@@ -8512,9 +8024,6 @@
   <si>
     <t xml:space="preserve">A **successor agent** is a back-up agent. They would have power of attorney if the first dies, becomes incompetent, quits, or refuses to act as your power of attorney agent.
 </t>
-  </si>
-  <si>
-    <t>**Un agente sustituto** es un agente de respaldo. Tendría poder notarial si el primero muere, queda incapacitado, renuncia o se niega a actuar como tu agente de poder notarial.</t>
   </si>
   <si>
     <t>636a7aa4d17e633bd48ac8d7a7290e47</t>
@@ -12981,152 +12490,6 @@
   </si>
   <si>
     <t>9eed0ffa505ad02d1a0b04d29c1c44bc</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">To "nominate" means to suggest or propose a person a court can choose to act as guardian.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% if for_yourself == True:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">A court may find it necessary to appoint a legal guardian to make decisions about your financial affairs. A guardian of your estate would have rights, powers, and duties over your property and finances.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% else:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">A court may find it necessary to appoint a legal guardian to make decisions about </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${principal.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">'s financial affairs. A guardian of their estate would have rights, powers, and duties over their property and finances.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% endif
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-If you click **No**, then a court may appoint someone other than </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${agent.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> to be guardian if needed. Even if you click **Yes**, a court may still appoint someone else as guardian if they find that </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${agent.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> is breaching their duty.
-</t>
-    </r>
   </si>
   <si>
     <t>include preparer</t>
@@ -24727,151 +24090,6 @@
       <rPr>
         <b/>
         <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% if for_yourself == True:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">La persona nombrada como un **{agente sucesor}** tendrá poder notarial para la propiedad por usted si </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${agent.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> muere, se vuelve **{incompetente}**, renuncia o se niega a actuar como su apoderado.
-If you list more than one successor agent, you should list them in order of preference
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">% else:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">La persona nombrada como un sucesor agente tendrá poder notarial para la propiedad de </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${principal.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> si </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${agent.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> muere, se vuelve **{incompetente}**, renuncia o se niega a aceptar el cargo de agente.
-If </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>${principal.name_full()}</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> lists more than one successor agent, they should list them in order of preference.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF008000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>% endif</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
         <color rgb="FF0000FF"/>
         <rFont val="Calibri"/>
         <family val="2"/>
@@ -25784,6 +25002,225 @@
   <si>
     <r>
       <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% if for_yourself == True:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">¿Quieres que </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${agent.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> tenga la autoridad para presentar una solicitud de bancarrota en tu nombre?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% else:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">¿Quiere ${principal.name_full()} que ${agent.name_full()} tenga la autoridad para presentar una solicitud de bancarrota en su nombre?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>% endif</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">To "nominate" means to suggest or propose a person a court can choose to act as guardian.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% if for_yourself == True:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">A court may find it necessary to appoint a legal guardian to make decisions about your financial affairs. A guardian of your estate would have rights, powers, and duties over your property and finances.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% else:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">A court may find it necessary to appoint a legal guardian to make decisions about </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${principal.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">'s financial affairs. A guardian of their estate would have rights, powers, and duties over their property and finances.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% endif
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+If you click **No**, then a court may appoint someone other than </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${agent.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to be guardian if needed. Even if you click **Yes**, a court may still appoint someone else as guardian if they find that </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${agent.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> is breaching their duty.
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
@@ -25813,7 +25250,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">Un tribunal puede considerar necesario designar a un tutor legal que tome decisiones sobre tus asuntos financieros. Un tutor de tu patrimonio tendría derechos, poderes y deberes sobre su propiedad y finanzas.
+      <t xml:space="preserve">Un tribunal puede considerar necesario designar a un tutor legal para que tome decisiones sobre tus asuntos financieros. Un tutor de tu patrimonio tendría derechos, poderes y deberes sobre tu propiedad y finanzas.
 </t>
     </r>
     <r>
@@ -25947,7 +25384,77 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">¿Quieres que </t>
+      <t xml:space="preserve">Puedes limitar cualquiera de los poderes otorgados a un agente. También puedes enumerar cualquier poder específico que no desees que el agente tenga.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% else:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${principal.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> puede limitar cualquiera de los poderes otorgados a un agente. También puede enumerar cualquier poder específico que no desee que el agente tenga.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>% endif</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% if for_yourself == True:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  Por ejemplo, puedes imponer condiciones para la venta de bienes raíces o establecer reglas especiales sobre el endeudamiento por parte de </t>
     </r>
     <r>
       <rPr>
@@ -25968,7 +25475,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> tenga la autoridad para presentar una solicitud de bancarrota en tu nombre?
+      <t xml:space="preserve">.
 </t>
     </r>
     <r>
@@ -25991,7 +25498,28 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">¿Quiere ${principal.name_full()} que ${agent.name_full()} tenga la autoridad para presentar una solicitud de bancarrota en su nombre?
+      <t xml:space="preserve">Por ejemplo, ellos pueden imponer condiciones para la venta de bienes raíces o establecer reglas especiales sobre el endeudamiento por parte de </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${agent.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.
 </t>
     </r>
     <r>
@@ -26005,6 +25533,464 @@
       </rPr>
       <t>% endif</t>
     </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% if for_yourself == True:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Si quieres, puedes otorgar otros poderes a </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${agent.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Estos poderes se añadirán a los que ya le hayas otorgado.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% else:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Si </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${principal.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> quiere, ellos pueden otorgar otros poderes a </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${agent.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. Estos poderes se añadirán a los que ya le haya otorgado.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% endif 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${collapse_template(powers_example)}</t>
+    </r>
+  </si>
+  <si>
+    <t>Otros poderes que un mandante podría otorgar a un apoderado incluyen:
+* El poder de regalar tu propiedad a otras personas,
+* El poder de ejercer poderes de designación,
+* El poder de nombrar o cambiar beneficiarios o copropietarios conjuntos,
+* El derecho a acceder a tus cuentas de redes sociales, y
+* El poder de revocar o modificar un fideicomiso.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Se le otorgan los siguientes poderes adicionales a ${agent.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">No, solo </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${agent.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> puede tomar decisiones por </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${me_subject}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Solo puede delegar en alguien que </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${i_subject_lower}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> autorice.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Who </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${do_does}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${you_subject}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> authorize as delegate?</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% if for_yourself == True:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">La persona nombrada como **{agente sucesor}** tendrá poder notarial sobre tu propiedad si </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${agent.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> muere, se vuelve **{incompetente}**, renuncia o se niega a actuar como su apoderado.
+Si nombras a más de un agente sucesor, debes incluirlos en orden de preferencia.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">% else:
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">La persona nombrada como un sucesor agente tendrá poder notarial para la propiedad de </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${principal.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> si </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${agent.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> muere, se vuelve **{incompetente}**, renuncia o se niega a aceptar el cargo de agente.
+If </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>${principal.name_full()}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> lists more than one successor agent, they should list them in order of preference.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF008000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>% endif</t>
+    </r>
+  </si>
+  <si>
+    <t>**Un agente sucesor** es un agente de respaldo. Tendría poder notarial si el primero muere, queda incapacitado, renuncia o se niega a actuar como tu agente de poder notarial.</t>
   </si>
 </sst>
 </file>
@@ -26480,7 +26466,7 @@
         <v>13</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>769</v>
+        <v>759</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="403.2">
@@ -26494,7 +26480,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>822</v>
+        <v>812</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>11</v>
@@ -26503,10 +26489,10 @@
         <v>12</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>823</v>
+        <v>813</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>824</v>
+        <v>814</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="187.2">
@@ -26532,7 +26518,7 @@
         <v>16</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>770</v>
+        <v>760</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="28.8">
@@ -26558,7 +26544,7 @@
         <v>19</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>771</v>
+        <v>761</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="302.39999999999998">
@@ -26584,7 +26570,7 @@
         <v>21</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>825</v>
+        <v>815</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -26610,7 +26596,7 @@
         <v>24</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>732</v>
+        <v>722</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="72">
@@ -26636,7 +26622,7 @@
         <v>26</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>772</v>
+        <v>762</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -26662,7 +26648,7 @@
         <v>28</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>753</v>
+        <v>743</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="43.2">
@@ -26688,7 +26674,7 @@
         <v>30</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>773</v>
+        <v>763</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="28.8">
@@ -26740,7 +26726,7 @@
         <v>35</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>869</v>
+        <v>858</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="43.2">
@@ -26766,7 +26752,7 @@
         <v>38</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>774</v>
+        <v>764</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="43.2">
@@ -26792,7 +26778,7 @@
         <v>40</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>775</v>
+        <v>765</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="86.4">
@@ -26818,7 +26804,7 @@
         <v>43</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>828</v>
+        <v>818</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="115.2">
@@ -26844,7 +26830,7 @@
         <v>46</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>826</v>
+        <v>816</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="28.8">
@@ -26896,7 +26882,7 @@
         <v>52</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>776</v>
+        <v>766</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="273.60000000000002">
@@ -26922,7 +26908,7 @@
         <v>54</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>827</v>
+        <v>817</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="28.8">
@@ -26948,7 +26934,7 @@
         <v>57</v>
       </c>
       <c r="H20" t="s">
-        <v>862</v>
+        <v>851</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="129.6">
@@ -26974,7 +26960,7 @@
         <v>59</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>856</v>
+        <v>846</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -27000,7 +26986,7 @@
         <v>62</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>777</v>
+        <v>767</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="43.2">
@@ -27026,7 +27012,7 @@
         <v>64</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>778</v>
+        <v>768</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="72">
@@ -27052,7 +27038,7 @@
         <v>66</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>779</v>
+        <v>769</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="28.8">
@@ -27078,7 +27064,7 @@
         <v>68</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>780</v>
+        <v>770</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="57.6">
@@ -27104,7 +27090,7 @@
         <v>70</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>863</v>
+        <v>852</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -27130,7 +27116,7 @@
         <v>72</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>864</v>
+        <v>853</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -27156,7 +27142,7 @@
         <v>74</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>865</v>
+        <v>854</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="28.8">
@@ -27182,7 +27168,7 @@
         <v>77</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>781</v>
+        <v>771</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="259.2">
@@ -27208,7 +27194,7 @@
         <v>79</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>782</v>
+        <v>772</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="86.4">
@@ -27234,7 +27220,7 @@
         <v>82</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>783</v>
+        <v>773</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="403.2">
@@ -27260,7 +27246,7 @@
         <v>84</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>784</v>
+        <v>774</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -27286,7 +27272,7 @@
         <v>86</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>785</v>
+        <v>775</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -27312,7 +27298,7 @@
         <v>88</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>786</v>
+        <v>776</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -27338,7 +27324,7 @@
         <v>90</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>787</v>
+        <v>777</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -27364,7 +27350,7 @@
         <v>92</v>
       </c>
       <c r="H36" s="5" t="s">
-        <v>788</v>
+        <v>778</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -27416,7 +27402,7 @@
         <v>97</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>789</v>
+        <v>779</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="115.2">
@@ -27442,7 +27428,7 @@
         <v>100</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>790</v>
+        <v>780</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="28.8">
@@ -27468,7 +27454,7 @@
         <v>102</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>791</v>
+        <v>781</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="28.8">
@@ -27494,7 +27480,7 @@
         <v>105</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>792</v>
+        <v>782</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="86.4">
@@ -27520,7 +27506,7 @@
         <v>108</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>833</v>
+        <v>823</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="28.8">
@@ -27546,7 +27532,7 @@
         <v>111</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>834</v>
+        <v>824</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="144">
@@ -27598,7 +27584,7 @@
         <v>117</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>793</v>
+        <v>783</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="86.4">
@@ -27624,7 +27610,7 @@
         <v>120</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>794</v>
+        <v>784</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="86.4">
@@ -27650,7 +27636,7 @@
         <v>123</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>795</v>
+        <v>785</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="345.6">
@@ -27676,7 +27662,7 @@
         <v>125</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>870</v>
+        <v>859</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="28.8">
@@ -27702,7 +27688,7 @@
         <v>128</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>796</v>
+        <v>786</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="28.8">
@@ -27754,7 +27740,7 @@
         <v>133</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>797</v>
+        <v>787</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="43.2">
@@ -27780,7 +27766,7 @@
         <v>135</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>798</v>
+        <v>788</v>
       </c>
     </row>
     <row r="53" spans="1:8">
@@ -27806,7 +27792,7 @@
         <v>137</v>
       </c>
       <c r="H53" t="s">
-        <v>836</v>
+        <v>826</v>
       </c>
     </row>
     <row r="54" spans="1:8">
@@ -27832,7 +27818,7 @@
         <v>139</v>
       </c>
       <c r="H54" t="s">
-        <v>837</v>
+        <v>827</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="129.6">
@@ -27858,7 +27844,7 @@
         <v>142</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>829</v>
+        <v>819</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="28.8">
@@ -27884,7 +27870,7 @@
         <v>144</v>
       </c>
       <c r="H56" s="4" t="s">
-        <v>835</v>
+        <v>825</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="28.8">
@@ -27936,7 +27922,7 @@
         <v>150</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>799</v>
+        <v>789</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="115.2">
@@ -27962,7 +27948,7 @@
         <v>153</v>
       </c>
       <c r="H59" s="5" t="s">
-        <v>838</v>
+        <v>828</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="28.8">
@@ -28014,7 +28000,7 @@
         <v>159</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>800</v>
+        <v>790</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="244.8">
@@ -28040,7 +28026,7 @@
         <v>161</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>866</v>
+        <v>855</v>
       </c>
     </row>
     <row r="63" spans="1:8">
@@ -28066,7 +28052,7 @@
         <v>163</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>801</v>
+        <v>791</v>
       </c>
     </row>
     <row r="64" spans="1:8">
@@ -28092,7 +28078,7 @@
         <v>165</v>
       </c>
       <c r="H64" s="4" t="s">
-        <v>802</v>
+        <v>792</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="43.2">
@@ -28144,7 +28130,7 @@
         <v>170</v>
       </c>
       <c r="H66" s="4" t="s">
-        <v>803</v>
+        <v>793</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="43.2">
@@ -28170,7 +28156,7 @@
         <v>172</v>
       </c>
       <c r="H67" s="4" t="s">
-        <v>839</v>
+        <v>829</v>
       </c>
     </row>
     <row r="68" spans="1:8">
@@ -28222,7 +28208,7 @@
         <v>177</v>
       </c>
       <c r="H69" s="4" t="s">
-        <v>804</v>
+        <v>794</v>
       </c>
     </row>
     <row r="70" spans="1:8">
@@ -28248,7 +28234,7 @@
         <v>179</v>
       </c>
       <c r="H70" s="4" t="s">
-        <v>805</v>
+        <v>795</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="72">
@@ -28274,7 +28260,7 @@
         <v>181</v>
       </c>
       <c r="H71" s="4" t="s">
-        <v>806</v>
+        <v>796</v>
       </c>
     </row>
     <row r="72" spans="1:8">
@@ -28300,7 +28286,7 @@
         <v>183</v>
       </c>
       <c r="H72" s="4" t="s">
-        <v>807</v>
+        <v>797</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="43.2">
@@ -28326,7 +28312,7 @@
         <v>185</v>
       </c>
       <c r="H73" s="4" t="s">
-        <v>808</v>
+        <v>798</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -28378,7 +28364,7 @@
         <v>190</v>
       </c>
       <c r="H75" s="4" t="s">
-        <v>810</v>
+        <v>800</v>
       </c>
     </row>
     <row r="76" spans="1:8">
@@ -28404,7 +28390,7 @@
         <v>192</v>
       </c>
       <c r="H76" s="4" t="s">
-        <v>809</v>
+        <v>799</v>
       </c>
     </row>
     <row r="77" spans="1:8" ht="43.2">
@@ -28430,7 +28416,7 @@
         <v>194</v>
       </c>
       <c r="H77" s="4" t="s">
-        <v>811</v>
+        <v>801</v>
       </c>
     </row>
     <row r="78" spans="1:8">
@@ -28456,7 +28442,7 @@
         <v>196</v>
       </c>
       <c r="H78" s="4" t="s">
-        <v>812</v>
+        <v>802</v>
       </c>
     </row>
     <row r="79" spans="1:8" ht="57.6">
@@ -28482,7 +28468,7 @@
         <v>198</v>
       </c>
       <c r="H79" s="4" t="s">
-        <v>813</v>
+        <v>803</v>
       </c>
     </row>
     <row r="80" spans="1:8">
@@ -28534,7 +28520,7 @@
         <v>203</v>
       </c>
       <c r="H81" s="4" t="s">
-        <v>814</v>
+        <v>804</v>
       </c>
     </row>
     <row r="82" spans="1:8">
@@ -28586,7 +28572,7 @@
         <v>208</v>
       </c>
       <c r="H83" s="4" t="s">
-        <v>815</v>
+        <v>805</v>
       </c>
     </row>
     <row r="84" spans="1:8">
@@ -28638,7 +28624,7 @@
         <v>213</v>
       </c>
       <c r="H85" s="4" t="s">
-        <v>816</v>
+        <v>806</v>
       </c>
     </row>
     <row r="86" spans="1:8">
@@ -28690,7 +28676,7 @@
         <v>218</v>
       </c>
       <c r="H87" s="4" t="s">
-        <v>817</v>
+        <v>807</v>
       </c>
     </row>
     <row r="88" spans="1:8">
@@ -28742,7 +28728,7 @@
         <v>223</v>
       </c>
       <c r="H89" s="4" t="s">
-        <v>819</v>
+        <v>809</v>
       </c>
     </row>
     <row r="90" spans="1:8">
@@ -28768,7 +28754,7 @@
         <v>225</v>
       </c>
       <c r="H90" s="4" t="s">
-        <v>818</v>
+        <v>808</v>
       </c>
     </row>
     <row r="91" spans="1:8" ht="43.2">
@@ -28794,7 +28780,7 @@
         <v>227</v>
       </c>
       <c r="H91" s="4" t="s">
-        <v>820</v>
+        <v>810</v>
       </c>
     </row>
     <row r="92" spans="1:8">
@@ -28820,7 +28806,7 @@
         <v>229</v>
       </c>
       <c r="H92" s="4" t="s">
-        <v>867</v>
+        <v>856</v>
       </c>
     </row>
     <row r="93" spans="1:8" ht="43.2">
@@ -28846,7 +28832,7 @@
         <v>231</v>
       </c>
       <c r="H93" s="4" t="s">
-        <v>868</v>
+        <v>857</v>
       </c>
     </row>
     <row r="94" spans="1:8">
@@ -28898,7 +28884,7 @@
         <v>237</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>871</v>
+        <v>860</v>
       </c>
     </row>
     <row r="96" spans="1:8" ht="100.8">
@@ -28924,7 +28910,7 @@
         <v>240</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>873</v>
+        <v>861</v>
       </c>
     </row>
     <row r="97" spans="1:8" ht="115.2">
@@ -28950,7 +28936,7 @@
         <v>243</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>821</v>
+        <v>811</v>
       </c>
     </row>
     <row r="98" spans="1:8" ht="259.2">
@@ -28976,7 +28962,7 @@
         <v>245</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>830</v>
+        <v>820</v>
       </c>
     </row>
     <row r="99" spans="1:8" ht="28.8">
@@ -29028,7 +29014,7 @@
         <v>251</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>831</v>
+        <v>821</v>
       </c>
     </row>
     <row r="101" spans="1:8" ht="86.4">
@@ -29730,7 +29716,7 @@
         <v>335</v>
       </c>
       <c r="H127" s="3" t="s">
-        <v>336</v>
+        <v>864</v>
       </c>
     </row>
     <row r="128" spans="1:8" ht="86.4">
@@ -29738,13 +29724,13 @@
         <v>8</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C128" s="2">
         <v>0</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>11</v>
@@ -29753,10 +29739,10 @@
         <v>12</v>
       </c>
       <c r="G128" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="H128" s="3" t="s">
         <v>339</v>
-      </c>
-      <c r="H128" s="3" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="129" spans="1:8" ht="115.2">
@@ -29764,13 +29750,13 @@
         <v>8</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C129" s="2">
         <v>1</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>11</v>
@@ -29779,10 +29765,10 @@
         <v>12</v>
       </c>
       <c r="G129" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H129" s="3" t="s">
-        <v>343</v>
+        <v>865</v>
       </c>
     </row>
     <row r="130" spans="1:8">
@@ -29790,13 +29776,13 @@
         <v>8</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C130" s="2">
         <v>2</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>11</v>
@@ -29805,10 +29791,10 @@
         <v>12</v>
       </c>
       <c r="G130" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="H130" s="4" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="131" spans="1:8" ht="100.8">
@@ -29816,13 +29802,13 @@
         <v>8</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C131" s="2">
         <v>0</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>11</v>
@@ -29831,10 +29817,10 @@
         <v>12</v>
       </c>
       <c r="G131" s="3" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="H131" s="3" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="132" spans="1:8" ht="144">
@@ -29842,13 +29828,13 @@
         <v>8</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C132" s="2">
         <v>1</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>11</v>
@@ -29857,10 +29843,10 @@
         <v>12</v>
       </c>
       <c r="G132" s="3" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="H132" s="3" t="s">
-        <v>353</v>
+        <v>866</v>
       </c>
     </row>
     <row r="133" spans="1:8">
@@ -29868,13 +29854,13 @@
         <v>8</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C133" s="2">
         <v>2</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>11</v>
@@ -29883,10 +29869,10 @@
         <v>12</v>
       </c>
       <c r="G133" s="3" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="H133" s="3" t="s">
-        <v>356</v>
+        <v>868</v>
       </c>
     </row>
     <row r="134" spans="1:8" ht="115.2">
@@ -29894,13 +29880,13 @@
         <v>8</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="C134" s="2">
         <v>0</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="E134" s="2" t="s">
         <v>11</v>
@@ -29909,10 +29895,10 @@
         <v>12</v>
       </c>
       <c r="G134" s="3" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="H134" s="4" t="s">
-        <v>360</v>
+        <v>867</v>
       </c>
     </row>
     <row r="135" spans="1:8" ht="28.8">
@@ -29920,13 +29906,13 @@
         <v>8</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="C135" s="2">
         <v>1</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>11</v>
@@ -29935,10 +29921,10 @@
         <v>12</v>
       </c>
       <c r="G135" s="3" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="H135" s="4" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
     </row>
     <row r="136" spans="1:8" ht="115.2">
@@ -29946,13 +29932,13 @@
         <v>8</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C136" s="2">
         <v>0</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="E136" s="2" t="s">
         <v>11</v>
@@ -29961,10 +29947,10 @@
         <v>12</v>
       </c>
       <c r="G136" s="3" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="H136" s="3" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
     </row>
     <row r="137" spans="1:8" ht="129.6">
@@ -29972,13 +29958,13 @@
         <v>8</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C137" s="2">
         <v>1</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="E137" s="2" t="s">
         <v>11</v>
@@ -29987,10 +29973,10 @@
         <v>12</v>
       </c>
       <c r="G137" s="3" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="H137" s="3" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
     </row>
     <row r="138" spans="1:8">
@@ -29998,13 +29984,13 @@
         <v>8</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C138" s="2">
         <v>2</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="E138" s="2" t="s">
         <v>11</v>
@@ -30013,10 +29999,10 @@
         <v>12</v>
       </c>
       <c r="G138" s="3" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="H138" s="3" t="s">
-        <v>373</v>
+        <v>869</v>
       </c>
     </row>
     <row r="139" spans="1:8" ht="43.2">
@@ -30024,13 +30010,13 @@
         <v>8</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C139" s="2">
         <v>3</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>859</v>
+        <v>848</v>
       </c>
       <c r="E139" s="2" t="s">
         <v>11</v>
@@ -30039,10 +30025,10 @@
         <v>12</v>
       </c>
       <c r="G139" s="3" t="s">
-        <v>860</v>
+        <v>849</v>
       </c>
       <c r="H139" s="3" t="s">
-        <v>861</v>
+        <v>850</v>
       </c>
     </row>
     <row r="140" spans="1:8">
@@ -30050,13 +30036,13 @@
         <v>8</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C140" s="2">
         <v>4</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="E140" s="2" t="s">
         <v>11</v>
@@ -30065,10 +30051,10 @@
         <v>12</v>
       </c>
       <c r="G140" s="3" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="H140" s="3" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
     </row>
     <row r="141" spans="1:8">
@@ -30076,13 +30062,13 @@
         <v>8</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C141" s="2">
         <v>5</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="E141" s="2" t="s">
         <v>11</v>
@@ -30091,10 +30077,10 @@
         <v>12</v>
       </c>
       <c r="G141" s="3" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="H141" s="3" t="s">
-        <v>379</v>
+        <v>870</v>
       </c>
     </row>
     <row r="142" spans="1:8">
@@ -30102,13 +30088,13 @@
         <v>8</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C142" s="2">
         <v>6</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="E142" s="2" t="s">
         <v>11</v>
@@ -30117,10 +30103,10 @@
         <v>12</v>
       </c>
       <c r="G142" s="3" t="s">
-        <v>381</v>
+        <v>871</v>
       </c>
       <c r="H142" s="3" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
     </row>
     <row r="143" spans="1:8" ht="187.2">
@@ -30128,13 +30114,13 @@
         <v>8</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="C143" s="2">
         <v>0</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="E143" s="2" t="s">
         <v>11</v>
@@ -30143,10 +30129,10 @@
         <v>12</v>
       </c>
       <c r="G143" s="3" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="H143" s="3" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
     </row>
     <row r="144" spans="1:8" ht="28.8">
@@ -30154,13 +30140,13 @@
         <v>8</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="C144" s="2">
         <v>1</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="E144" s="2" t="s">
         <v>11</v>
@@ -30169,10 +30155,10 @@
         <v>12</v>
       </c>
       <c r="G144" s="3" t="s">
-        <v>388</v>
+        <v>380</v>
       </c>
       <c r="H144" s="4" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
     </row>
     <row r="145" spans="1:8" ht="115.2">
@@ -30180,13 +30166,13 @@
         <v>8</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="C145" s="2">
         <v>0</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>391</v>
+        <v>383</v>
       </c>
       <c r="E145" s="2" t="s">
         <v>11</v>
@@ -30195,10 +30181,10 @@
         <v>12</v>
       </c>
       <c r="G145" s="3" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="H145" s="3" t="s">
-        <v>393</v>
+        <v>385</v>
       </c>
     </row>
     <row r="146" spans="1:8" ht="316.8">
@@ -30206,13 +30192,13 @@
         <v>8</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="C146" s="2">
         <v>1</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="E146" s="2" t="s">
         <v>11</v>
@@ -30221,10 +30207,10 @@
         <v>12</v>
       </c>
       <c r="G146" s="3" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="H146" s="3" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
     </row>
     <row r="147" spans="1:8" ht="28.8">
@@ -30232,13 +30218,13 @@
         <v>8</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="C147" s="2">
         <v>2</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="E147" s="2" t="s">
         <v>11</v>
@@ -30247,10 +30233,10 @@
         <v>12</v>
       </c>
       <c r="G147" s="3" t="s">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="H147" s="3" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
     </row>
     <row r="148" spans="1:8">
@@ -30258,13 +30244,13 @@
         <v>8</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="C148" s="2">
         <v>3</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="E148" s="2" t="s">
         <v>11</v>
@@ -30273,10 +30259,10 @@
         <v>12</v>
       </c>
       <c r="G148" s="3" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="H148" s="3" t="s">
-        <v>402</v>
+        <v>394</v>
       </c>
     </row>
     <row r="149" spans="1:8" ht="28.8">
@@ -30284,13 +30270,13 @@
         <v>8</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="C149" s="2">
         <v>4</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="E149" s="2" t="s">
         <v>11</v>
@@ -30299,10 +30285,10 @@
         <v>12</v>
       </c>
       <c r="G149" s="3" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="H149" s="3" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
     </row>
     <row r="150" spans="1:8">
@@ -30310,13 +30296,13 @@
         <v>8</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="C150" s="2">
         <v>5</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="E150" s="2" t="s">
         <v>11</v>
@@ -30325,10 +30311,10 @@
         <v>12</v>
       </c>
       <c r="G150" s="3" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="H150" s="4" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
     </row>
     <row r="151" spans="1:8">
@@ -30336,13 +30322,13 @@
         <v>8</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="C151" s="2">
         <v>7</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="E151" s="2" t="s">
         <v>11</v>
@@ -30351,10 +30337,10 @@
         <v>12</v>
       </c>
       <c r="G151" s="3" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="H151" s="4" t="s">
-        <v>411</v>
+        <v>403</v>
       </c>
     </row>
     <row r="152" spans="1:8">
@@ -30362,13 +30348,13 @@
         <v>8</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="C152" s="2">
         <v>8</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="E152" s="2" t="s">
         <v>11</v>
@@ -30377,10 +30363,10 @@
         <v>12</v>
       </c>
       <c r="G152" s="3" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="H152" s="4" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
     </row>
     <row r="153" spans="1:8">
@@ -30388,13 +30374,13 @@
         <v>8</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="C153" s="2">
         <v>9</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="E153" s="2" t="s">
         <v>11</v>
@@ -30403,10 +30389,10 @@
         <v>12</v>
       </c>
       <c r="G153" s="3" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="H153" s="4" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
     </row>
     <row r="154" spans="1:8">
@@ -30414,13 +30400,13 @@
         <v>8</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="C154" s="2">
         <v>10</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="E154" s="2" t="s">
         <v>11</v>
@@ -30429,10 +30415,10 @@
         <v>12</v>
       </c>
       <c r="G154" s="3" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="H154" s="4" t="s">
-        <v>420</v>
+        <v>412</v>
       </c>
     </row>
     <row r="155" spans="1:8">
@@ -30440,13 +30426,13 @@
         <v>8</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="C155" s="2">
         <v>11</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="E155" s="2" t="s">
         <v>11</v>
@@ -30455,10 +30441,10 @@
         <v>12</v>
       </c>
       <c r="G155" s="3" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="H155" s="4" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
     </row>
     <row r="156" spans="1:8">
@@ -30466,13 +30452,13 @@
         <v>8</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="C156" s="2">
         <v>0</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="E156" s="2" t="s">
         <v>11</v>
@@ -30481,10 +30467,10 @@
         <v>12</v>
       </c>
       <c r="G156" s="3" t="s">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="H156" s="4" t="s">
-        <v>427</v>
+        <v>419</v>
       </c>
     </row>
     <row r="157" spans="1:8" ht="115.2">
@@ -30492,13 +30478,13 @@
         <v>8</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="C157" s="2">
         <v>1</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="E157" s="2" t="s">
         <v>11</v>
@@ -30507,10 +30493,10 @@
         <v>12</v>
       </c>
       <c r="G157" s="3" t="s">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="H157" s="4" t="s">
-        <v>840</v>
+        <v>830</v>
       </c>
     </row>
     <row r="158" spans="1:8">
@@ -30518,13 +30504,13 @@
         <v>8</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="C158" s="2">
         <v>2</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="E158" s="2" t="s">
         <v>11</v>
@@ -30533,10 +30519,10 @@
         <v>12</v>
       </c>
       <c r="G158" s="3" t="s">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="H158" s="4" t="s">
-        <v>432</v>
+        <v>424</v>
       </c>
     </row>
     <row r="159" spans="1:8" ht="43.2">
@@ -30544,13 +30530,13 @@
         <v>8</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="C159" s="2">
         <v>3</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>433</v>
+        <v>425</v>
       </c>
       <c r="E159" s="2" t="s">
         <v>11</v>
@@ -30559,10 +30545,10 @@
         <v>12</v>
       </c>
       <c r="G159" s="3" t="s">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="H159" s="4" t="s">
-        <v>435</v>
+        <v>873</v>
       </c>
     </row>
     <row r="160" spans="1:8" ht="86.4">
@@ -30570,13 +30556,13 @@
         <v>8</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="C160" s="2">
         <v>4</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>436</v>
+        <v>427</v>
       </c>
       <c r="E160" s="2" t="s">
         <v>11</v>
@@ -30585,10 +30571,10 @@
         <v>12</v>
       </c>
       <c r="G160" s="3" t="s">
-        <v>437</v>
+        <v>428</v>
       </c>
       <c r="H160" s="3" t="s">
-        <v>438</v>
+        <v>429</v>
       </c>
     </row>
     <row r="161" spans="1:8" ht="216">
@@ -30596,13 +30582,13 @@
         <v>8</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="C161" s="2">
         <v>5</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>439</v>
+        <v>430</v>
       </c>
       <c r="E161" s="2" t="s">
         <v>11</v>
@@ -30611,10 +30597,10 @@
         <v>12</v>
       </c>
       <c r="G161" s="3" t="s">
-        <v>440</v>
+        <v>431</v>
       </c>
       <c r="H161" s="3" t="s">
-        <v>857</v>
+        <v>872</v>
       </c>
     </row>
     <row r="162" spans="1:8" ht="86.4">
@@ -30622,13 +30608,13 @@
         <v>8</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>441</v>
+        <v>432</v>
       </c>
       <c r="C162" s="2">
         <v>0</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>442</v>
+        <v>433</v>
       </c>
       <c r="E162" s="2" t="s">
         <v>11</v>
@@ -30637,10 +30623,10 @@
         <v>12</v>
       </c>
       <c r="G162" s="3" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="H162" s="3" t="s">
-        <v>444</v>
+        <v>435</v>
       </c>
     </row>
     <row r="163" spans="1:8" ht="72">
@@ -30648,13 +30634,13 @@
         <v>8</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>441</v>
+        <v>432</v>
       </c>
       <c r="C163" s="2">
         <v>1</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>445</v>
+        <v>436</v>
       </c>
       <c r="E163" s="2" t="s">
         <v>11</v>
@@ -30663,10 +30649,10 @@
         <v>12</v>
       </c>
       <c r="G163" s="3" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="H163" s="3" t="s">
-        <v>447</v>
+        <v>438</v>
       </c>
     </row>
     <row r="164" spans="1:8">
@@ -30674,13 +30660,13 @@
         <v>8</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>441</v>
+        <v>432</v>
       </c>
       <c r="C164" s="2">
         <v>2</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>448</v>
+        <v>439</v>
       </c>
       <c r="E164" s="2" t="s">
         <v>11</v>
@@ -30689,10 +30675,10 @@
         <v>12</v>
       </c>
       <c r="G164" s="3" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="H164" s="4" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
     </row>
     <row r="165" spans="1:8" ht="86.4">
@@ -30700,13 +30686,13 @@
         <v>8</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>451</v>
+        <v>442</v>
       </c>
       <c r="C165" s="2">
         <v>0</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>452</v>
+        <v>443</v>
       </c>
       <c r="E165" s="2" t="s">
         <v>11</v>
@@ -30715,10 +30701,10 @@
         <v>12</v>
       </c>
       <c r="G165" s="3" t="s">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="H165" s="3" t="s">
-        <v>454</v>
+        <v>445</v>
       </c>
     </row>
     <row r="166" spans="1:8" ht="28.8">
@@ -30726,13 +30712,13 @@
         <v>8</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>455</v>
+        <v>446</v>
       </c>
       <c r="C166" s="2">
         <v>0</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>456</v>
+        <v>447</v>
       </c>
       <c r="E166" s="2" t="s">
         <v>11</v>
@@ -30741,10 +30727,10 @@
         <v>12</v>
       </c>
       <c r="G166" s="3" t="s">
-        <v>457</v>
+        <v>448</v>
       </c>
       <c r="H166" s="3" t="s">
-        <v>458</v>
+        <v>449</v>
       </c>
     </row>
     <row r="167" spans="1:8" ht="28.8">
@@ -30752,13 +30738,13 @@
         <v>8</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>455</v>
+        <v>446</v>
       </c>
       <c r="C167" s="2">
         <v>1</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>459</v>
+        <v>450</v>
       </c>
       <c r="E167" s="2" t="s">
         <v>11</v>
@@ -30767,10 +30753,10 @@
         <v>12</v>
       </c>
       <c r="G167" s="3" t="s">
-        <v>460</v>
+        <v>451</v>
       </c>
       <c r="H167" s="5" t="s">
-        <v>461</v>
+        <v>452</v>
       </c>
     </row>
     <row r="168" spans="1:8">
@@ -30778,13 +30764,13 @@
         <v>8</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>455</v>
+        <v>446</v>
       </c>
       <c r="C168" s="2">
         <v>2</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="E168" s="2" t="s">
         <v>11</v>
@@ -30793,10 +30779,10 @@
         <v>12</v>
       </c>
       <c r="G168" s="3" t="s">
-        <v>463</v>
+        <v>454</v>
       </c>
       <c r="H168" s="3" t="s">
-        <v>464</v>
+        <v>455</v>
       </c>
     </row>
     <row r="169" spans="1:8" ht="129.6">
@@ -30804,13 +30790,13 @@
         <v>8</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>465</v>
+        <v>456</v>
       </c>
       <c r="C169" s="2">
         <v>0</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>466</v>
+        <v>457</v>
       </c>
       <c r="E169" s="2" t="s">
         <v>11</v>
@@ -30819,10 +30805,10 @@
         <v>12</v>
       </c>
       <c r="G169" s="3" t="s">
-        <v>467</v>
+        <v>458</v>
       </c>
       <c r="H169" s="3" t="s">
-        <v>841</v>
+        <v>831</v>
       </c>
     </row>
     <row r="170" spans="1:8" ht="28.8">
@@ -30830,13 +30816,13 @@
         <v>8</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>465</v>
+        <v>456</v>
       </c>
       <c r="C170" s="2">
         <v>1</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="E170" s="2" t="s">
         <v>11</v>
@@ -30845,10 +30831,10 @@
         <v>12</v>
       </c>
       <c r="G170" s="3" t="s">
-        <v>469</v>
+        <v>460</v>
       </c>
       <c r="H170" s="4" t="s">
-        <v>470</v>
+        <v>461</v>
       </c>
     </row>
     <row r="171" spans="1:8" ht="28.8">
@@ -30856,13 +30842,13 @@
         <v>8</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>471</v>
+        <v>462</v>
       </c>
       <c r="C171" s="2">
         <v>0</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>472</v>
+        <v>463</v>
       </c>
       <c r="E171" s="2" t="s">
         <v>11</v>
@@ -30871,10 +30857,10 @@
         <v>12</v>
       </c>
       <c r="G171" s="3" t="s">
-        <v>473</v>
+        <v>464</v>
       </c>
       <c r="H171" s="3" t="s">
-        <v>474</v>
+        <v>465</v>
       </c>
     </row>
     <row r="172" spans="1:8" ht="100.8">
@@ -30882,13 +30868,13 @@
         <v>8</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>471</v>
+        <v>462</v>
       </c>
       <c r="C172" s="2">
         <v>1</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>475</v>
+        <v>466</v>
       </c>
       <c r="E172" s="2" t="s">
         <v>11</v>
@@ -30897,10 +30883,10 @@
         <v>12</v>
       </c>
       <c r="G172" s="3" t="s">
-        <v>476</v>
+        <v>467</v>
       </c>
       <c r="H172" s="3" t="s">
-        <v>477</v>
+        <v>468</v>
       </c>
     </row>
     <row r="173" spans="1:8" ht="115.2">
@@ -30908,13 +30894,13 @@
         <v>8</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>478</v>
+        <v>469</v>
       </c>
       <c r="C173" s="2">
         <v>0</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>479</v>
+        <v>470</v>
       </c>
       <c r="E173" s="2" t="s">
         <v>11</v>
@@ -30923,10 +30909,10 @@
         <v>12</v>
       </c>
       <c r="G173" s="3" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
       <c r="H173" s="5" t="s">
-        <v>843</v>
+        <v>833</v>
       </c>
     </row>
     <row r="174" spans="1:8" ht="28.8">
@@ -30934,13 +30920,13 @@
         <v>8</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>478</v>
+        <v>469</v>
       </c>
       <c r="C174" s="2">
         <v>1</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
       <c r="E174" s="2" t="s">
         <v>11</v>
@@ -30949,10 +30935,10 @@
         <v>12</v>
       </c>
       <c r="G174" s="3" t="s">
-        <v>482</v>
+        <v>473</v>
       </c>
       <c r="H174" s="4" t="s">
-        <v>842</v>
+        <v>832</v>
       </c>
     </row>
     <row r="175" spans="1:8">
@@ -30960,13 +30946,13 @@
         <v>8</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>483</v>
+        <v>474</v>
       </c>
       <c r="C175" s="2">
         <v>0</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>484</v>
+        <v>475</v>
       </c>
       <c r="E175" s="2" t="s">
         <v>11</v>
@@ -30975,10 +30961,10 @@
         <v>12</v>
       </c>
       <c r="G175" s="3" t="s">
-        <v>485</v>
+        <v>476</v>
       </c>
       <c r="H175" s="4" t="s">
-        <v>486</v>
+        <v>477</v>
       </c>
     </row>
     <row r="176" spans="1:8" ht="28.8">
@@ -30986,13 +30972,13 @@
         <v>8</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>483</v>
+        <v>474</v>
       </c>
       <c r="C176" s="2">
         <v>1</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>487</v>
+        <v>478</v>
       </c>
       <c r="E176" s="2" t="s">
         <v>11</v>
@@ -31001,10 +30987,10 @@
         <v>12</v>
       </c>
       <c r="G176" s="3" t="s">
-        <v>488</v>
+        <v>479</v>
       </c>
       <c r="H176" s="4" t="s">
-        <v>489</v>
+        <v>480</v>
       </c>
     </row>
     <row r="177" spans="1:8">
@@ -31012,13 +30998,13 @@
         <v>8</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>483</v>
+        <v>474</v>
       </c>
       <c r="C177" s="2">
         <v>2</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>490</v>
+        <v>481</v>
       </c>
       <c r="E177" s="2" t="s">
         <v>11</v>
@@ -31027,10 +31013,10 @@
         <v>12</v>
       </c>
       <c r="G177" s="3" t="s">
-        <v>491</v>
+        <v>482</v>
       </c>
       <c r="H177" s="4" t="s">
-        <v>492</v>
+        <v>483</v>
       </c>
     </row>
     <row r="178" spans="1:8" ht="86.4">
@@ -31038,13 +31024,13 @@
         <v>8</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>483</v>
+        <v>474</v>
       </c>
       <c r="C178" s="2">
         <v>3</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>493</v>
+        <v>484</v>
       </c>
       <c r="E178" s="2" t="s">
         <v>11</v>
@@ -31053,10 +31039,10 @@
         <v>12</v>
       </c>
       <c r="G178" s="3" t="s">
-        <v>494</v>
+        <v>485</v>
       </c>
       <c r="H178" s="3" t="s">
-        <v>495</v>
+        <v>486</v>
       </c>
     </row>
     <row r="179" spans="1:8" ht="86.4">
@@ -31064,13 +31050,13 @@
         <v>8</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>483</v>
+        <v>474</v>
       </c>
       <c r="C179" s="2">
         <v>4</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>496</v>
+        <v>487</v>
       </c>
       <c r="E179" s="2" t="s">
         <v>11</v>
@@ -31079,10 +31065,10 @@
         <v>12</v>
       </c>
       <c r="G179" s="3" t="s">
-        <v>497</v>
+        <v>488</v>
       </c>
       <c r="H179" s="3" t="s">
-        <v>498</v>
+        <v>489</v>
       </c>
     </row>
     <row r="180" spans="1:8" ht="409.6">
@@ -31090,13 +31076,13 @@
         <v>8</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>483</v>
+        <v>474</v>
       </c>
       <c r="C180" s="2">
         <v>5</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>499</v>
+        <v>490</v>
       </c>
       <c r="E180" s="2" t="s">
         <v>11</v>
@@ -31105,10 +31091,10 @@
         <v>12</v>
       </c>
       <c r="G180" s="3" t="s">
-        <v>500</v>
+        <v>491</v>
       </c>
       <c r="H180" s="3" t="s">
-        <v>858</v>
+        <v>847</v>
       </c>
     </row>
     <row r="181" spans="1:8">
@@ -31116,13 +31102,13 @@
         <v>8</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>483</v>
+        <v>474</v>
       </c>
       <c r="C181" s="2">
         <v>6</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>501</v>
+        <v>492</v>
       </c>
       <c r="E181" s="2" t="s">
         <v>11</v>
@@ -31131,10 +31117,10 @@
         <v>12</v>
       </c>
       <c r="G181" s="3" t="s">
-        <v>502</v>
+        <v>493</v>
       </c>
       <c r="H181" s="4" t="s">
-        <v>503</v>
+        <v>494</v>
       </c>
     </row>
     <row r="182" spans="1:8" ht="144">
@@ -31142,13 +31128,13 @@
         <v>8</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>483</v>
+        <v>474</v>
       </c>
       <c r="C182" s="2">
         <v>7</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>504</v>
+        <v>495</v>
       </c>
       <c r="E182" s="2" t="s">
         <v>11</v>
@@ -31157,10 +31143,10 @@
         <v>12</v>
       </c>
       <c r="G182" s="3" t="s">
-        <v>505</v>
+        <v>496</v>
       </c>
       <c r="H182" s="3" t="s">
-        <v>506</v>
+        <v>497</v>
       </c>
     </row>
     <row r="183" spans="1:8" ht="28.8">
@@ -31168,13 +31154,13 @@
         <v>8</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>483</v>
+        <v>474</v>
       </c>
       <c r="C183" s="2">
         <v>8</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>507</v>
+        <v>498</v>
       </c>
       <c r="E183" s="2" t="s">
         <v>11</v>
@@ -31183,10 +31169,10 @@
         <v>12</v>
       </c>
       <c r="G183" s="3" t="s">
-        <v>508</v>
+        <v>499</v>
       </c>
       <c r="H183" s="3" t="s">
-        <v>509</v>
+        <v>500</v>
       </c>
     </row>
     <row r="184" spans="1:8" ht="57.6">
@@ -31194,13 +31180,13 @@
         <v>8</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>483</v>
+        <v>474</v>
       </c>
       <c r="C184" s="2">
         <v>9</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>510</v>
+        <v>501</v>
       </c>
       <c r="E184" s="2" t="s">
         <v>11</v>
@@ -31209,10 +31195,10 @@
         <v>12</v>
       </c>
       <c r="G184" s="3" t="s">
-        <v>511</v>
+        <v>502</v>
       </c>
       <c r="H184" s="3" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
     </row>
     <row r="185" spans="1:8" ht="28.8">
@@ -31220,13 +31206,13 @@
         <v>8</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>483</v>
+        <v>474</v>
       </c>
       <c r="C185" s="2">
         <v>10</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="E185" s="2" t="s">
         <v>11</v>
@@ -31235,10 +31221,10 @@
         <v>12</v>
       </c>
       <c r="G185" s="3" t="s">
-        <v>514</v>
+        <v>505</v>
       </c>
       <c r="H185" s="3" t="s">
-        <v>515</v>
+        <v>506</v>
       </c>
     </row>
     <row r="186" spans="1:8">
@@ -31246,13 +31232,13 @@
         <v>8</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>483</v>
+        <v>474</v>
       </c>
       <c r="C186" s="2">
         <v>11</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>516</v>
+        <v>507</v>
       </c>
       <c r="E186" s="2" t="s">
         <v>11</v>
@@ -31261,10 +31247,10 @@
         <v>12</v>
       </c>
       <c r="G186" s="3" t="s">
-        <v>517</v>
+        <v>508</v>
       </c>
       <c r="H186" s="4" t="s">
-        <v>518</v>
+        <v>509</v>
       </c>
     </row>
     <row r="187" spans="1:8">
@@ -31272,13 +31258,13 @@
         <v>8</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>483</v>
+        <v>474</v>
       </c>
       <c r="C187" s="2">
         <v>12</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>519</v>
+        <v>510</v>
       </c>
       <c r="E187" s="2" t="s">
         <v>11</v>
@@ -31287,10 +31273,10 @@
         <v>12</v>
       </c>
       <c r="G187" s="3" t="s">
-        <v>520</v>
+        <v>511</v>
       </c>
       <c r="H187" s="4" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
     </row>
     <row r="188" spans="1:8" ht="115.2">
@@ -31298,13 +31284,13 @@
         <v>8</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>522</v>
+        <v>513</v>
       </c>
       <c r="C188" s="2">
         <v>0</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>523</v>
+        <v>514</v>
       </c>
       <c r="E188" s="2" t="s">
         <v>11</v>
@@ -31313,10 +31299,10 @@
         <v>12</v>
       </c>
       <c r="G188" s="3" t="s">
-        <v>524</v>
+        <v>515</v>
       </c>
       <c r="H188" s="3" t="s">
-        <v>525</v>
+        <v>516</v>
       </c>
     </row>
     <row r="189" spans="1:8" ht="28.8">
@@ -31324,13 +31310,13 @@
         <v>8</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>522</v>
+        <v>513</v>
       </c>
       <c r="C189" s="2">
         <v>1</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>526</v>
+        <v>517</v>
       </c>
       <c r="E189" s="2" t="s">
         <v>11</v>
@@ -31339,10 +31325,10 @@
         <v>12</v>
       </c>
       <c r="G189" s="3" t="s">
-        <v>527</v>
+        <v>518</v>
       </c>
       <c r="H189" s="4" t="s">
-        <v>844</v>
+        <v>834</v>
       </c>
     </row>
     <row r="190" spans="1:8" ht="115.2">
@@ -31350,13 +31336,13 @@
         <v>8</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>528</v>
+        <v>519</v>
       </c>
       <c r="C190" s="2">
         <v>0</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>529</v>
+        <v>520</v>
       </c>
       <c r="E190" s="2" t="s">
         <v>11</v>
@@ -31365,10 +31351,10 @@
         <v>12</v>
       </c>
       <c r="G190" s="3" t="s">
-        <v>530</v>
+        <v>521</v>
       </c>
       <c r="H190" s="3" t="s">
-        <v>845</v>
+        <v>835</v>
       </c>
     </row>
     <row r="191" spans="1:8" ht="28.8">
@@ -31376,13 +31362,13 @@
         <v>8</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>528</v>
+        <v>519</v>
       </c>
       <c r="C191" s="2">
         <v>1</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>531</v>
+        <v>522</v>
       </c>
       <c r="E191" s="2" t="s">
         <v>11</v>
@@ -31391,10 +31377,10 @@
         <v>12</v>
       </c>
       <c r="G191" s="3" t="s">
-        <v>532</v>
+        <v>523</v>
       </c>
       <c r="H191" s="4" t="s">
-        <v>533</v>
+        <v>524</v>
       </c>
     </row>
     <row r="192" spans="1:8" ht="86.4">
@@ -31402,13 +31388,13 @@
         <v>8</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>534</v>
+        <v>525</v>
       </c>
       <c r="C192" s="2">
         <v>0</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>535</v>
+        <v>526</v>
       </c>
       <c r="E192" s="2" t="s">
         <v>11</v>
@@ -31417,10 +31403,10 @@
         <v>12</v>
       </c>
       <c r="G192" s="3" t="s">
-        <v>536</v>
+        <v>527</v>
       </c>
       <c r="H192" s="3" t="s">
-        <v>537</v>
+        <v>528</v>
       </c>
     </row>
     <row r="193" spans="1:8" ht="316.8">
@@ -31428,13 +31414,13 @@
         <v>8</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>534</v>
+        <v>525</v>
       </c>
       <c r="C193" s="2">
         <v>1</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>538</v>
+        <v>529</v>
       </c>
       <c r="E193" s="2" t="s">
         <v>11</v>
@@ -31443,10 +31429,10 @@
         <v>12</v>
       </c>
       <c r="G193" s="3" t="s">
-        <v>846</v>
+        <v>836</v>
       </c>
       <c r="H193" s="3" t="s">
-        <v>847</v>
+        <v>837</v>
       </c>
     </row>
     <row r="194" spans="1:8" ht="86.4">
@@ -31454,13 +31440,13 @@
         <v>8</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>539</v>
+        <v>530</v>
       </c>
       <c r="C194" s="2">
         <v>0</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>540</v>
+        <v>531</v>
       </c>
       <c r="E194" s="2" t="s">
         <v>11</v>
@@ -31469,10 +31455,10 @@
         <v>12</v>
       </c>
       <c r="G194" s="3" t="s">
-        <v>848</v>
+        <v>838</v>
       </c>
       <c r="H194" s="4" t="s">
-        <v>849</v>
+        <v>839</v>
       </c>
     </row>
     <row r="195" spans="1:8" ht="28.8">
@@ -31480,13 +31466,13 @@
         <v>8</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>539</v>
+        <v>530</v>
       </c>
       <c r="C195" s="2">
         <v>1</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>541</v>
+        <v>532</v>
       </c>
       <c r="E195" s="2" t="s">
         <v>11</v>
@@ -31495,10 +31481,10 @@
         <v>12</v>
       </c>
       <c r="G195" s="3" t="s">
-        <v>542</v>
+        <v>533</v>
       </c>
       <c r="H195" s="4" t="s">
-        <v>543</v>
+        <v>534</v>
       </c>
     </row>
     <row r="196" spans="1:8" ht="86.4">
@@ -31506,13 +31492,13 @@
         <v>8</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>544</v>
+        <v>535</v>
       </c>
       <c r="C196" s="2">
         <v>0</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>545</v>
+        <v>536</v>
       </c>
       <c r="E196" s="2" t="s">
         <v>11</v>
@@ -31521,10 +31507,10 @@
         <v>12</v>
       </c>
       <c r="G196" s="3" t="s">
-        <v>546</v>
+        <v>537</v>
       </c>
       <c r="H196" s="3" t="s">
-        <v>547</v>
+        <v>538</v>
       </c>
     </row>
     <row r="197" spans="1:8" ht="201.6">
@@ -31532,13 +31518,13 @@
         <v>8</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>544</v>
+        <v>535</v>
       </c>
       <c r="C197" s="2">
         <v>1</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>548</v>
+        <v>539</v>
       </c>
       <c r="E197" s="2" t="s">
         <v>11</v>
@@ -31547,10 +31533,10 @@
         <v>12</v>
       </c>
       <c r="G197" s="3" t="s">
-        <v>549</v>
+        <v>540</v>
       </c>
       <c r="H197" s="3" t="s">
-        <v>550</v>
+        <v>541</v>
       </c>
     </row>
     <row r="198" spans="1:8" ht="28.8">
@@ -31558,13 +31544,13 @@
         <v>8</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>544</v>
+        <v>535</v>
       </c>
       <c r="C198" s="2">
         <v>2</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>551</v>
+        <v>542</v>
       </c>
       <c r="E198" s="2" t="s">
         <v>11</v>
@@ -31573,10 +31559,10 @@
         <v>12</v>
       </c>
       <c r="G198" s="3" t="s">
-        <v>552</v>
+        <v>543</v>
       </c>
       <c r="H198" s="3" t="s">
-        <v>553</v>
+        <v>544</v>
       </c>
     </row>
     <row r="199" spans="1:8">
@@ -31584,13 +31570,13 @@
         <v>8</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>544</v>
+        <v>535</v>
       </c>
       <c r="C199" s="2">
         <v>3</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>554</v>
+        <v>545</v>
       </c>
       <c r="E199" s="2" t="s">
         <v>11</v>
@@ -31599,10 +31585,10 @@
         <v>12</v>
       </c>
       <c r="G199" s="3" t="s">
-        <v>555</v>
+        <v>546</v>
       </c>
       <c r="H199" s="3" t="s">
-        <v>556</v>
+        <v>547</v>
       </c>
     </row>
     <row r="200" spans="1:8" ht="100.8">
@@ -31610,13 +31596,13 @@
         <v>8</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>544</v>
+        <v>535</v>
       </c>
       <c r="C200" s="2">
         <v>4</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>557</v>
+        <v>548</v>
       </c>
       <c r="E200" s="2" t="s">
         <v>11</v>
@@ -31625,10 +31611,10 @@
         <v>12</v>
       </c>
       <c r="G200" s="3" t="s">
-        <v>558</v>
+        <v>549</v>
       </c>
       <c r="H200" s="4" t="s">
-        <v>559</v>
+        <v>550</v>
       </c>
     </row>
     <row r="201" spans="1:8" ht="28.8">
@@ -31636,13 +31622,13 @@
         <v>8</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>544</v>
+        <v>535</v>
       </c>
       <c r="C201" s="2">
         <v>5</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>560</v>
+        <v>551</v>
       </c>
       <c r="E201" s="2" t="s">
         <v>11</v>
@@ -31651,10 +31637,10 @@
         <v>12</v>
       </c>
       <c r="G201" s="3" t="s">
-        <v>561</v>
+        <v>552</v>
       </c>
       <c r="H201" s="3" t="s">
-        <v>562</v>
+        <v>553</v>
       </c>
     </row>
     <row r="202" spans="1:8">
@@ -31662,13 +31648,13 @@
         <v>8</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>544</v>
+        <v>535</v>
       </c>
       <c r="C202" s="2">
         <v>6</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>563</v>
+        <v>554</v>
       </c>
       <c r="E202" s="2" t="s">
         <v>11</v>
@@ -31677,10 +31663,10 @@
         <v>12</v>
       </c>
       <c r="G202" s="3" t="s">
-        <v>564</v>
+        <v>555</v>
       </c>
       <c r="H202" s="4" t="s">
-        <v>565</v>
+        <v>556</v>
       </c>
     </row>
     <row r="203" spans="1:8">
@@ -31688,13 +31674,13 @@
         <v>8</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>544</v>
+        <v>535</v>
       </c>
       <c r="C203" s="2">
         <v>7</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>566</v>
+        <v>557</v>
       </c>
       <c r="E203" s="2" t="s">
         <v>11</v>
@@ -31703,10 +31689,10 @@
         <v>12</v>
       </c>
       <c r="G203" s="3" t="s">
-        <v>567</v>
+        <v>558</v>
       </c>
       <c r="H203" s="4" t="s">
-        <v>568</v>
+        <v>559</v>
       </c>
     </row>
     <row r="204" spans="1:8" ht="100.8">
@@ -31714,13 +31700,13 @@
         <v>8</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>569</v>
+        <v>560</v>
       </c>
       <c r="C204" s="2">
         <v>0</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>570</v>
+        <v>561</v>
       </c>
       <c r="E204" s="2" t="s">
         <v>11</v>
@@ -31729,10 +31715,10 @@
         <v>12</v>
       </c>
       <c r="G204" s="3" t="s">
-        <v>571</v>
+        <v>562</v>
       </c>
       <c r="H204" s="3" t="s">
-        <v>572</v>
+        <v>563</v>
       </c>
     </row>
     <row r="205" spans="1:8" ht="244.8">
@@ -31740,13 +31726,13 @@
         <v>8</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>569</v>
+        <v>560</v>
       </c>
       <c r="C205" s="2">
         <v>1</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>573</v>
+        <v>564</v>
       </c>
       <c r="E205" s="2" t="s">
         <v>11</v>
@@ -31755,10 +31741,10 @@
         <v>12</v>
       </c>
       <c r="G205" s="3" t="s">
-        <v>574</v>
+        <v>862</v>
       </c>
       <c r="H205" s="3" t="s">
-        <v>872</v>
+        <v>863</v>
       </c>
     </row>
     <row r="206" spans="1:8" ht="28.8">
@@ -31766,13 +31752,13 @@
         <v>8</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>575</v>
+        <v>565</v>
       </c>
       <c r="C206" s="2">
         <v>0</v>
       </c>
       <c r="D206" s="2" t="s">
-        <v>576</v>
+        <v>566</v>
       </c>
       <c r="E206" s="2" t="s">
         <v>11</v>
@@ -31781,10 +31767,10 @@
         <v>12</v>
       </c>
       <c r="G206" s="3" t="s">
-        <v>577</v>
+        <v>567</v>
       </c>
       <c r="H206" s="4" t="s">
-        <v>578</v>
+        <v>568</v>
       </c>
     </row>
     <row r="207" spans="1:8" ht="43.2">
@@ -31792,13 +31778,13 @@
         <v>8</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>575</v>
+        <v>565</v>
       </c>
       <c r="C207" s="2">
         <v>1</v>
       </c>
       <c r="D207" s="2" t="s">
-        <v>579</v>
+        <v>569</v>
       </c>
       <c r="E207" s="2" t="s">
         <v>11</v>
@@ -31807,10 +31793,10 @@
         <v>12</v>
       </c>
       <c r="G207" s="3" t="s">
-        <v>580</v>
+        <v>570</v>
       </c>
       <c r="H207" s="3" t="s">
-        <v>581</v>
+        <v>571</v>
       </c>
     </row>
     <row r="208" spans="1:8" ht="28.8">
@@ -31818,13 +31804,13 @@
         <v>8</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>582</v>
+        <v>572</v>
       </c>
       <c r="C208" s="2">
         <v>0</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>583</v>
+        <v>573</v>
       </c>
       <c r="E208" s="2" t="s">
         <v>11</v>
@@ -31833,10 +31819,10 @@
         <v>12</v>
       </c>
       <c r="G208" s="3" t="s">
-        <v>584</v>
+        <v>574</v>
       </c>
       <c r="H208" s="4" t="s">
-        <v>585</v>
+        <v>575</v>
       </c>
     </row>
     <row r="209" spans="1:8" ht="28.8">
@@ -31844,13 +31830,13 @@
         <v>8</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>586</v>
+        <v>576</v>
       </c>
       <c r="C209" s="2">
         <v>0</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>587</v>
+        <v>577</v>
       </c>
       <c r="E209" s="2" t="s">
         <v>11</v>
@@ -31859,10 +31845,10 @@
         <v>12</v>
       </c>
       <c r="G209" s="3" t="s">
-        <v>588</v>
+        <v>578</v>
       </c>
       <c r="H209" s="4" t="s">
-        <v>589</v>
+        <v>579</v>
       </c>
     </row>
     <row r="210" spans="1:8" ht="28.8">
@@ -31870,13 +31856,13 @@
         <v>8</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>586</v>
+        <v>576</v>
       </c>
       <c r="C210" s="2">
         <v>1</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>590</v>
+        <v>580</v>
       </c>
       <c r="E210" s="2" t="s">
         <v>11</v>
@@ -31885,10 +31871,10 @@
         <v>12</v>
       </c>
       <c r="G210" s="3" t="s">
-        <v>591</v>
+        <v>581</v>
       </c>
       <c r="H210" s="4" t="s">
-        <v>592</v>
+        <v>582</v>
       </c>
     </row>
     <row r="211" spans="1:8" ht="28.8">
@@ -31896,13 +31882,13 @@
         <v>8</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>593</v>
+        <v>583</v>
       </c>
       <c r="C211" s="2">
         <v>0</v>
       </c>
       <c r="D211" s="2" t="s">
-        <v>594</v>
+        <v>584</v>
       </c>
       <c r="E211" s="2" t="s">
         <v>11</v>
@@ -31911,10 +31897,10 @@
         <v>12</v>
       </c>
       <c r="G211" s="3" t="s">
-        <v>595</v>
+        <v>585</v>
       </c>
       <c r="H211" s="4" t="s">
-        <v>596</v>
+        <v>586</v>
       </c>
     </row>
     <row r="212" spans="1:8" ht="409.6">
@@ -31922,13 +31908,13 @@
         <v>8</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>593</v>
+        <v>583</v>
       </c>
       <c r="C212" s="2">
         <v>1</v>
       </c>
       <c r="D212" s="2" t="s">
-        <v>597</v>
+        <v>587</v>
       </c>
       <c r="E212" s="2" t="s">
         <v>11</v>
@@ -31937,10 +31923,10 @@
         <v>12</v>
       </c>
       <c r="G212" s="3" t="s">
-        <v>598</v>
+        <v>588</v>
       </c>
       <c r="H212" s="3" t="s">
-        <v>599</v>
+        <v>589</v>
       </c>
     </row>
     <row r="213" spans="1:8" ht="86.4">
@@ -31948,13 +31934,13 @@
         <v>8</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>600</v>
+        <v>590</v>
       </c>
       <c r="C213" s="2">
         <v>0</v>
       </c>
       <c r="D213" s="2" t="s">
-        <v>601</v>
+        <v>591</v>
       </c>
       <c r="E213" s="2" t="s">
         <v>11</v>
@@ -31963,10 +31949,10 @@
         <v>12</v>
       </c>
       <c r="G213" s="3" t="s">
-        <v>602</v>
+        <v>592</v>
       </c>
       <c r="H213" s="4" t="s">
-        <v>603</v>
+        <v>593</v>
       </c>
     </row>
     <row r="214" spans="1:8" ht="86.4">
@@ -31974,13 +31960,13 @@
         <v>8</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>600</v>
+        <v>590</v>
       </c>
       <c r="C214" s="2">
         <v>1</v>
       </c>
       <c r="D214" s="2" t="s">
-        <v>604</v>
+        <v>594</v>
       </c>
       <c r="E214" s="2" t="s">
         <v>11</v>
@@ -31989,10 +31975,10 @@
         <v>12</v>
       </c>
       <c r="G214" s="3" t="s">
-        <v>605</v>
+        <v>595</v>
       </c>
       <c r="H214" s="3" t="s">
-        <v>606</v>
+        <v>596</v>
       </c>
     </row>
     <row r="215" spans="1:8" ht="28.8">
@@ -32000,13 +31986,13 @@
         <v>8</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>607</v>
+        <v>597</v>
       </c>
       <c r="C215" s="2">
         <v>0</v>
       </c>
       <c r="D215" s="2" t="s">
-        <v>608</v>
+        <v>598</v>
       </c>
       <c r="E215" s="2" t="s">
         <v>11</v>
@@ -32015,10 +32001,10 @@
         <v>12</v>
       </c>
       <c r="G215" s="3" t="s">
-        <v>609</v>
+        <v>599</v>
       </c>
       <c r="H215" s="4" t="s">
-        <v>610</v>
+        <v>600</v>
       </c>
     </row>
     <row r="216" spans="1:8" ht="403.2">
@@ -32026,13 +32012,13 @@
         <v>8</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>607</v>
+        <v>597</v>
       </c>
       <c r="C216" s="2">
         <v>1</v>
       </c>
       <c r="D216" s="2" t="s">
-        <v>611</v>
+        <v>601</v>
       </c>
       <c r="E216" s="2" t="s">
         <v>11</v>
@@ -32041,10 +32027,10 @@
         <v>12</v>
       </c>
       <c r="G216" s="3" t="s">
-        <v>612</v>
+        <v>602</v>
       </c>
       <c r="H216" s="3" t="s">
-        <v>613</v>
+        <v>603</v>
       </c>
     </row>
     <row r="217" spans="1:8" ht="187.2">
@@ -32052,13 +32038,13 @@
         <v>8</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>607</v>
+        <v>597</v>
       </c>
       <c r="C217" s="2">
         <v>2</v>
       </c>
       <c r="D217" s="2" t="s">
-        <v>614</v>
+        <v>604</v>
       </c>
       <c r="E217" s="2" t="s">
         <v>11</v>
@@ -32067,10 +32053,10 @@
         <v>12</v>
       </c>
       <c r="G217" s="3" t="s">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="H217" s="3" t="s">
-        <v>616</v>
+        <v>606</v>
       </c>
     </row>
     <row r="218" spans="1:8" ht="86.4">
@@ -32078,13 +32064,13 @@
         <v>8</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>617</v>
+        <v>607</v>
       </c>
       <c r="C218" s="2">
         <v>0</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>618</v>
+        <v>608</v>
       </c>
       <c r="E218" s="2" t="s">
         <v>11</v>
@@ -32093,10 +32079,10 @@
         <v>12</v>
       </c>
       <c r="G218" s="3" t="s">
-        <v>619</v>
+        <v>609</v>
       </c>
       <c r="H218" s="3" t="s">
-        <v>832</v>
+        <v>822</v>
       </c>
     </row>
     <row r="219" spans="1:8">
@@ -32104,13 +32090,13 @@
         <v>8</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>620</v>
+        <v>610</v>
       </c>
       <c r="C219" s="2">
         <v>1</v>
       </c>
       <c r="D219" s="2" t="s">
-        <v>621</v>
+        <v>611</v>
       </c>
       <c r="E219" s="2" t="s">
         <v>11</v>
@@ -32122,7 +32108,7 @@
         <v>22</v>
       </c>
       <c r="H219" s="4" t="s">
-        <v>622</v>
+        <v>612</v>
       </c>
     </row>
     <row r="220" spans="1:8">
@@ -32130,13 +32116,13 @@
         <v>8</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>623</v>
+        <v>613</v>
       </c>
       <c r="C220" s="2">
         <v>0</v>
       </c>
       <c r="D220" s="2" t="s">
-        <v>624</v>
+        <v>614</v>
       </c>
       <c r="E220" s="2" t="s">
         <v>11</v>
@@ -32145,10 +32131,10 @@
         <v>12</v>
       </c>
       <c r="G220" s="3" t="s">
-        <v>625</v>
+        <v>615</v>
       </c>
       <c r="H220" s="4" t="s">
-        <v>626</v>
+        <v>616</v>
       </c>
     </row>
     <row r="221" spans="1:8">
@@ -32156,13 +32142,13 @@
         <v>8</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="C221" s="2">
         <v>0</v>
       </c>
       <c r="D221" s="2" t="s">
-        <v>628</v>
+        <v>618</v>
       </c>
       <c r="E221" s="2" t="s">
         <v>11</v>
@@ -32171,10 +32157,10 @@
         <v>12</v>
       </c>
       <c r="G221" s="3" t="s">
-        <v>629</v>
+        <v>619</v>
       </c>
       <c r="H221" s="4" t="s">
-        <v>630</v>
+        <v>620</v>
       </c>
     </row>
     <row r="222" spans="1:8">
@@ -32182,13 +32168,13 @@
         <v>8</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>631</v>
+        <v>621</v>
       </c>
       <c r="C222" s="2">
         <v>0</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>632</v>
+        <v>622</v>
       </c>
       <c r="E222" s="2" t="s">
         <v>11</v>
@@ -32197,10 +32183,10 @@
         <v>12</v>
       </c>
       <c r="G222" s="3" t="s">
-        <v>633</v>
+        <v>623</v>
       </c>
       <c r="H222" s="4" t="s">
-        <v>634</v>
+        <v>624</v>
       </c>
     </row>
     <row r="223" spans="1:8">
@@ -32208,13 +32194,13 @@
         <v>8</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>635</v>
+        <v>625</v>
       </c>
       <c r="C223" s="2">
         <v>0</v>
       </c>
       <c r="D223" s="2" t="s">
-        <v>636</v>
+        <v>626</v>
       </c>
       <c r="E223" s="2" t="s">
         <v>11</v>
@@ -32223,10 +32209,10 @@
         <v>12</v>
       </c>
       <c r="G223" s="3" t="s">
-        <v>637</v>
+        <v>627</v>
       </c>
       <c r="H223" s="4" t="s">
-        <v>638</v>
+        <v>628</v>
       </c>
     </row>
     <row r="224" spans="1:8">
@@ -32234,13 +32220,13 @@
         <v>8</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>639</v>
+        <v>629</v>
       </c>
       <c r="C224" s="2">
         <v>0</v>
       </c>
       <c r="D224" s="2" t="s">
-        <v>640</v>
+        <v>630</v>
       </c>
       <c r="E224" s="2" t="s">
         <v>11</v>
@@ -32249,10 +32235,10 @@
         <v>12</v>
       </c>
       <c r="G224" s="3" t="s">
-        <v>641</v>
+        <v>631</v>
       </c>
       <c r="H224" s="4" t="s">
-        <v>642</v>
+        <v>632</v>
       </c>
     </row>
     <row r="225" spans="1:8" ht="28.8">
@@ -32260,13 +32246,13 @@
         <v>8</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>643</v>
+        <v>633</v>
       </c>
       <c r="C225" s="2">
         <v>0</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>644</v>
+        <v>634</v>
       </c>
       <c r="E225" s="2" t="s">
         <v>11</v>
@@ -32275,10 +32261,10 @@
         <v>12</v>
       </c>
       <c r="G225" s="3" t="s">
-        <v>645</v>
+        <v>635</v>
       </c>
       <c r="H225" s="4" t="s">
-        <v>646</v>
+        <v>636</v>
       </c>
     </row>
     <row r="226" spans="1:8" ht="28.8">
@@ -32286,13 +32272,13 @@
         <v>8</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>643</v>
+        <v>633</v>
       </c>
       <c r="C226" s="2">
         <v>1</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>647</v>
+        <v>637</v>
       </c>
       <c r="E226" s="2" t="s">
         <v>11</v>
@@ -32301,10 +32287,10 @@
         <v>12</v>
       </c>
       <c r="G226" s="3" t="s">
-        <v>648</v>
+        <v>638</v>
       </c>
       <c r="H226" s="4" t="s">
-        <v>649</v>
+        <v>639</v>
       </c>
     </row>
     <row r="227" spans="1:8">
@@ -32312,13 +32298,13 @@
         <v>8</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>643</v>
+        <v>633</v>
       </c>
       <c r="C227" s="2">
         <v>2</v>
       </c>
       <c r="D227" s="2" t="s">
-        <v>650</v>
+        <v>640</v>
       </c>
       <c r="E227" s="2" t="s">
         <v>11</v>
@@ -32327,10 +32313,10 @@
         <v>12</v>
       </c>
       <c r="G227" s="3" t="s">
-        <v>651</v>
+        <v>641</v>
       </c>
       <c r="H227" s="4" t="s">
-        <v>850</v>
+        <v>840</v>
       </c>
     </row>
     <row r="228" spans="1:8" ht="100.8">
@@ -32338,13 +32324,13 @@
         <v>8</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>643</v>
+        <v>633</v>
       </c>
       <c r="C228" s="2">
         <v>3</v>
       </c>
       <c r="D228" s="2" t="s">
-        <v>652</v>
+        <v>642</v>
       </c>
       <c r="E228" s="2" t="s">
         <v>11</v>
@@ -32353,10 +32339,10 @@
         <v>12</v>
       </c>
       <c r="G228" s="3" t="s">
-        <v>653</v>
+        <v>643</v>
       </c>
       <c r="H228" s="3" t="s">
-        <v>654</v>
+        <v>644</v>
       </c>
     </row>
     <row r="229" spans="1:8" ht="187.2">
@@ -32364,13 +32350,13 @@
         <v>8</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>643</v>
+        <v>633</v>
       </c>
       <c r="C229" s="2">
         <v>4</v>
       </c>
       <c r="D229" s="2" t="s">
-        <v>655</v>
+        <v>645</v>
       </c>
       <c r="E229" s="2" t="s">
         <v>11</v>
@@ -32379,10 +32365,10 @@
         <v>12</v>
       </c>
       <c r="G229" s="3" t="s">
-        <v>656</v>
+        <v>646</v>
       </c>
       <c r="H229" s="3" t="s">
-        <v>657</v>
+        <v>647</v>
       </c>
     </row>
     <row r="230" spans="1:8" ht="100.8">
@@ -32390,13 +32376,13 @@
         <v>8</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>643</v>
+        <v>633</v>
       </c>
       <c r="C230" s="2">
         <v>5</v>
       </c>
       <c r="D230" s="2" t="s">
-        <v>658</v>
+        <v>648</v>
       </c>
       <c r="E230" s="2" t="s">
         <v>11</v>
@@ -32405,10 +32391,10 @@
         <v>12</v>
       </c>
       <c r="G230" s="3" t="s">
-        <v>659</v>
+        <v>649</v>
       </c>
       <c r="H230" s="3" t="s">
-        <v>660</v>
+        <v>650</v>
       </c>
     </row>
     <row r="231" spans="1:8" ht="100.8">
@@ -32416,13 +32402,13 @@
         <v>8</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>643</v>
+        <v>633</v>
       </c>
       <c r="C231" s="2">
         <v>6</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>661</v>
+        <v>651</v>
       </c>
       <c r="E231" s="2" t="s">
         <v>11</v>
@@ -32431,10 +32417,10 @@
         <v>12</v>
       </c>
       <c r="G231" s="3" t="s">
-        <v>662</v>
+        <v>652</v>
       </c>
       <c r="H231" s="3" t="s">
-        <v>663</v>
+        <v>653</v>
       </c>
     </row>
     <row r="232" spans="1:8" ht="43.2">
@@ -32442,13 +32428,13 @@
         <v>8</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>643</v>
+        <v>633</v>
       </c>
       <c r="C232" s="2">
         <v>7</v>
       </c>
       <c r="D232" s="2" t="s">
-        <v>664</v>
+        <v>654</v>
       </c>
       <c r="E232" s="2" t="s">
         <v>11</v>
@@ -32457,10 +32443,10 @@
         <v>12</v>
       </c>
       <c r="G232" s="3" t="s">
-        <v>665</v>
+        <v>655</v>
       </c>
       <c r="H232" s="3" t="s">
-        <v>666</v>
+        <v>656</v>
       </c>
     </row>
     <row r="233" spans="1:8" ht="100.8">
@@ -32468,13 +32454,13 @@
         <v>8</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>643</v>
+        <v>633</v>
       </c>
       <c r="C233" s="2">
         <v>8</v>
       </c>
       <c r="D233" s="2" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="E233" s="2" t="s">
         <v>11</v>
@@ -32483,10 +32469,10 @@
         <v>12</v>
       </c>
       <c r="G233" s="3" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
       <c r="H233" s="3" t="s">
-        <v>669</v>
+        <v>659</v>
       </c>
     </row>
     <row r="234" spans="1:8" ht="43.2">
@@ -32494,13 +32480,13 @@
         <v>8</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>643</v>
+        <v>633</v>
       </c>
       <c r="C234" s="2">
         <v>9</v>
       </c>
       <c r="D234" s="2" t="s">
-        <v>670</v>
+        <v>660</v>
       </c>
       <c r="E234" s="2" t="s">
         <v>11</v>
@@ -32509,10 +32495,10 @@
         <v>12</v>
       </c>
       <c r="G234" s="3" t="s">
-        <v>671</v>
+        <v>661</v>
       </c>
       <c r="H234" s="3" t="s">
-        <v>672</v>
+        <v>662</v>
       </c>
     </row>
     <row r="235" spans="1:8" ht="409.6">
@@ -32520,13 +32506,13 @@
         <v>8</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>643</v>
+        <v>633</v>
       </c>
       <c r="C235" s="2">
         <v>10</v>
       </c>
       <c r="D235" s="2" t="s">
-        <v>673</v>
+        <v>663</v>
       </c>
       <c r="E235" s="2" t="s">
         <v>11</v>
@@ -32535,10 +32521,10 @@
         <v>12</v>
       </c>
       <c r="G235" s="3" t="s">
-        <v>674</v>
+        <v>664</v>
       </c>
       <c r="H235" s="3" t="s">
-        <v>675</v>
+        <v>665</v>
       </c>
     </row>
     <row r="236" spans="1:8" ht="43.2">
@@ -32546,13 +32532,13 @@
         <v>8</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>643</v>
+        <v>633</v>
       </c>
       <c r="C236" s="2">
         <v>11</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>676</v>
+        <v>666</v>
       </c>
       <c r="E236" s="2" t="s">
         <v>11</v>
@@ -32561,10 +32547,10 @@
         <v>12</v>
       </c>
       <c r="G236" s="3" t="s">
-        <v>677</v>
+        <v>667</v>
       </c>
       <c r="H236" s="3" t="s">
-        <v>678</v>
+        <v>668</v>
       </c>
     </row>
     <row r="237" spans="1:8" ht="43.2">
@@ -32572,13 +32558,13 @@
         <v>8</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>643</v>
+        <v>633</v>
       </c>
       <c r="C237" s="2">
         <v>12</v>
       </c>
       <c r="D237" s="2" t="s">
-        <v>679</v>
+        <v>669</v>
       </c>
       <c r="E237" s="2" t="s">
         <v>11</v>
@@ -32587,10 +32573,10 @@
         <v>12</v>
       </c>
       <c r="G237" s="3" t="s">
-        <v>680</v>
+        <v>670</v>
       </c>
       <c r="H237" s="3" t="s">
-        <v>681</v>
+        <v>671</v>
       </c>
     </row>
     <row r="238" spans="1:8" ht="115.2">
@@ -32598,13 +32584,13 @@
         <v>8</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>643</v>
+        <v>633</v>
       </c>
       <c r="C238" s="2">
         <v>13</v>
       </c>
       <c r="D238" s="2" t="s">
-        <v>682</v>
+        <v>672</v>
       </c>
       <c r="E238" s="2" t="s">
         <v>11</v>
@@ -32613,10 +32599,10 @@
         <v>12</v>
       </c>
       <c r="G238" s="3" t="s">
-        <v>683</v>
+        <v>673</v>
       </c>
       <c r="H238" s="3" t="s">
-        <v>684</v>
+        <v>674</v>
       </c>
     </row>
     <row r="239" spans="1:8" ht="43.2">
@@ -32624,13 +32610,13 @@
         <v>8</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>643</v>
+        <v>633</v>
       </c>
       <c r="C239" s="2">
         <v>14</v>
       </c>
       <c r="D239" s="2" t="s">
-        <v>685</v>
+        <v>675</v>
       </c>
       <c r="E239" s="2" t="s">
         <v>11</v>
@@ -32639,10 +32625,10 @@
         <v>12</v>
       </c>
       <c r="G239" s="3" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="H239" s="3" t="s">
-        <v>687</v>
+        <v>677</v>
       </c>
     </row>
     <row r="240" spans="1:8" ht="43.2">
@@ -32650,13 +32636,13 @@
         <v>8</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>643</v>
+        <v>633</v>
       </c>
       <c r="C240" s="2">
         <v>15</v>
       </c>
       <c r="D240" s="2" t="s">
-        <v>688</v>
+        <v>678</v>
       </c>
       <c r="E240" s="2" t="s">
         <v>11</v>
@@ -32665,10 +32651,10 @@
         <v>12</v>
       </c>
       <c r="G240" s="3" t="s">
-        <v>689</v>
+        <v>679</v>
       </c>
       <c r="H240" s="3" t="s">
-        <v>851</v>
+        <v>841</v>
       </c>
     </row>
     <row r="241" spans="1:8" ht="115.2">
@@ -32676,13 +32662,13 @@
         <v>8</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>643</v>
+        <v>633</v>
       </c>
       <c r="C241" s="2">
         <v>16</v>
       </c>
       <c r="D241" s="2" t="s">
-        <v>690</v>
+        <v>680</v>
       </c>
       <c r="E241" s="2" t="s">
         <v>11</v>
@@ -32691,10 +32677,10 @@
         <v>12</v>
       </c>
       <c r="G241" s="3" t="s">
-        <v>691</v>
+        <v>681</v>
       </c>
       <c r="H241" s="3" t="s">
-        <v>852</v>
+        <v>842</v>
       </c>
     </row>
     <row r="242" spans="1:8" ht="129.6">
@@ -32702,13 +32688,13 @@
         <v>8</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>643</v>
+        <v>633</v>
       </c>
       <c r="C242" s="2">
         <v>17</v>
       </c>
       <c r="D242" s="2" t="s">
-        <v>692</v>
+        <v>682</v>
       </c>
       <c r="E242" s="2" t="s">
         <v>11</v>
@@ -32717,10 +32703,10 @@
         <v>12</v>
       </c>
       <c r="G242" s="3" t="s">
-        <v>693</v>
+        <v>683</v>
       </c>
       <c r="H242" s="3" t="s">
-        <v>694</v>
+        <v>684</v>
       </c>
     </row>
     <row r="243" spans="1:8" ht="230.4">
@@ -32728,13 +32714,13 @@
         <v>8</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>643</v>
+        <v>633</v>
       </c>
       <c r="C243" s="2">
         <v>18</v>
       </c>
       <c r="D243" s="2" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="E243" s="2" t="s">
         <v>11</v>
@@ -32743,10 +32729,10 @@
         <v>12</v>
       </c>
       <c r="G243" s="3" t="s">
-        <v>696</v>
+        <v>686</v>
       </c>
       <c r="H243" s="3" t="s">
-        <v>853</v>
+        <v>843</v>
       </c>
     </row>
     <row r="244" spans="1:8" ht="100.8">
@@ -32754,13 +32740,13 @@
         <v>8</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>643</v>
+        <v>633</v>
       </c>
       <c r="C244" s="2">
         <v>19</v>
       </c>
       <c r="D244" s="2" t="s">
-        <v>697</v>
+        <v>687</v>
       </c>
       <c r="E244" s="2" t="s">
         <v>11</v>
@@ -32769,10 +32755,10 @@
         <v>12</v>
       </c>
       <c r="G244" s="3" t="s">
-        <v>698</v>
+        <v>688</v>
       </c>
       <c r="H244" s="3" t="s">
-        <v>699</v>
+        <v>689</v>
       </c>
     </row>
     <row r="245" spans="1:8" ht="86.4">
@@ -32780,13 +32766,13 @@
         <v>8</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>643</v>
+        <v>633</v>
       </c>
       <c r="C245" s="2">
         <v>20</v>
       </c>
       <c r="D245" s="2" t="s">
-        <v>700</v>
+        <v>690</v>
       </c>
       <c r="E245" s="2" t="s">
         <v>11</v>
@@ -32795,10 +32781,10 @@
         <v>12</v>
       </c>
       <c r="G245" s="3" t="s">
-        <v>701</v>
+        <v>691</v>
       </c>
       <c r="H245" s="3" t="s">
-        <v>702</v>
+        <v>692</v>
       </c>
     </row>
     <row r="246" spans="1:8" ht="216">
@@ -32806,13 +32792,13 @@
         <v>8</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>643</v>
+        <v>633</v>
       </c>
       <c r="C246" s="2">
         <v>21</v>
       </c>
       <c r="D246" s="2" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="E246" s="2" t="s">
         <v>11</v>
@@ -32821,10 +32807,10 @@
         <v>12</v>
       </c>
       <c r="G246" s="3" t="s">
-        <v>704</v>
+        <v>694</v>
       </c>
       <c r="H246" s="3" t="s">
-        <v>854</v>
+        <v>844</v>
       </c>
     </row>
     <row r="247" spans="1:8" ht="100.8">
@@ -32832,13 +32818,13 @@
         <v>8</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>643</v>
+        <v>633</v>
       </c>
       <c r="C247" s="2">
         <v>22</v>
       </c>
       <c r="D247" s="2" t="s">
-        <v>705</v>
+        <v>695</v>
       </c>
       <c r="E247" s="2" t="s">
         <v>11</v>
@@ -32847,10 +32833,10 @@
         <v>12</v>
       </c>
       <c r="G247" s="3" t="s">
-        <v>706</v>
+        <v>696</v>
       </c>
       <c r="H247" s="3" t="s">
-        <v>707</v>
+        <v>697</v>
       </c>
     </row>
     <row r="248" spans="1:8" ht="187.2">
@@ -32858,13 +32844,13 @@
         <v>8</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>643</v>
+        <v>633</v>
       </c>
       <c r="C248" s="2">
         <v>23</v>
       </c>
       <c r="D248" s="2" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="E248" s="2" t="s">
         <v>11</v>
@@ -32873,10 +32859,10 @@
         <v>12</v>
       </c>
       <c r="G248" s="3" t="s">
-        <v>709</v>
+        <v>699</v>
       </c>
       <c r="H248" s="3" t="s">
-        <v>855</v>
+        <v>845</v>
       </c>
     </row>
     <row r="249" spans="1:8" ht="28.8">
@@ -32884,13 +32870,13 @@
         <v>8</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>643</v>
+        <v>633</v>
       </c>
       <c r="C249" s="2">
         <v>24</v>
       </c>
       <c r="D249" s="2" t="s">
-        <v>710</v>
+        <v>700</v>
       </c>
       <c r="E249" s="2" t="s">
         <v>11</v>
@@ -32899,10 +32885,10 @@
         <v>12</v>
       </c>
       <c r="G249" s="3" t="s">
-        <v>711</v>
+        <v>701</v>
       </c>
       <c r="H249" s="4" t="s">
-        <v>712</v>
+        <v>702</v>
       </c>
     </row>
     <row r="250" spans="1:8" ht="43.2">
@@ -32910,13 +32896,13 @@
         <v>8</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>643</v>
+        <v>633</v>
       </c>
       <c r="C250" s="2">
         <v>25</v>
       </c>
       <c r="D250" s="2" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="E250" s="2" t="s">
         <v>11</v>
@@ -32925,10 +32911,10 @@
         <v>12</v>
       </c>
       <c r="G250" s="3" t="s">
-        <v>714</v>
+        <v>704</v>
       </c>
       <c r="H250" s="3" t="s">
-        <v>715</v>
+        <v>705</v>
       </c>
     </row>
     <row r="251" spans="1:8" ht="43.2">
@@ -32936,13 +32922,13 @@
         <v>8</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>643</v>
+        <v>633</v>
       </c>
       <c r="C251" s="2">
         <v>26</v>
       </c>
       <c r="D251" s="2" t="s">
-        <v>716</v>
+        <v>706</v>
       </c>
       <c r="E251" s="2" t="s">
         <v>11</v>
@@ -32951,10 +32937,10 @@
         <v>12</v>
       </c>
       <c r="G251" s="3" t="s">
-        <v>717</v>
+        <v>707</v>
       </c>
       <c r="H251" s="3" t="s">
-        <v>718</v>
+        <v>708</v>
       </c>
     </row>
     <row r="252" spans="1:8" ht="43.2">
@@ -32962,13 +32948,13 @@
         <v>8</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>643</v>
+        <v>633</v>
       </c>
       <c r="C252" s="2">
         <v>27</v>
       </c>
       <c r="D252" s="2" t="s">
-        <v>719</v>
+        <v>709</v>
       </c>
       <c r="E252" s="2" t="s">
         <v>11</v>
@@ -32977,10 +32963,10 @@
         <v>12</v>
       </c>
       <c r="G252" s="3" t="s">
-        <v>720</v>
+        <v>710</v>
       </c>
       <c r="H252" s="3" t="s">
-        <v>721</v>
+        <v>711</v>
       </c>
     </row>
     <row r="253" spans="1:8">
@@ -32988,13 +32974,13 @@
         <v>8</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>722</v>
+        <v>712</v>
       </c>
       <c r="C253" s="2">
         <v>0</v>
       </c>
       <c r="D253" s="2" t="s">
-        <v>723</v>
+        <v>713</v>
       </c>
       <c r="E253" s="2" t="s">
         <v>11</v>
@@ -33003,10 +32989,10 @@
         <v>12</v>
       </c>
       <c r="G253" s="3" t="s">
-        <v>724</v>
+        <v>714</v>
       </c>
       <c r="H253" s="4" t="s">
-        <v>725</v>
+        <v>715</v>
       </c>
     </row>
     <row r="254" spans="1:8" ht="100.8">
@@ -33014,13 +33000,13 @@
         <v>8</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>722</v>
+        <v>712</v>
       </c>
       <c r="C254" s="2">
         <v>2</v>
       </c>
       <c r="D254" s="2" t="s">
-        <v>726</v>
+        <v>716</v>
       </c>
       <c r="E254" s="2" t="s">
         <v>11</v>
@@ -33029,10 +33015,10 @@
         <v>12</v>
       </c>
       <c r="G254" s="3" t="s">
-        <v>727</v>
+        <v>717</v>
       </c>
       <c r="H254" s="3" t="s">
-        <v>728</v>
+        <v>718</v>
       </c>
     </row>
     <row r="255" spans="1:8">
@@ -33040,13 +33026,13 @@
         <v>8</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>729</v>
+        <v>719</v>
       </c>
       <c r="C255" s="2">
         <v>0</v>
       </c>
       <c r="D255" s="2" t="s">
-        <v>730</v>
+        <v>720</v>
       </c>
       <c r="E255" s="2" t="s">
         <v>11</v>
@@ -33055,10 +33041,10 @@
         <v>12</v>
       </c>
       <c r="G255" s="3" t="s">
-        <v>731</v>
+        <v>721</v>
       </c>
       <c r="H255" s="4" t="s">
-        <v>732</v>
+        <v>722</v>
       </c>
     </row>
     <row r="256" spans="1:8">
@@ -33066,13 +33052,13 @@
         <v>8</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>733</v>
+        <v>723</v>
       </c>
       <c r="C256" s="2">
         <v>0</v>
       </c>
       <c r="D256" s="2" t="s">
-        <v>734</v>
+        <v>724</v>
       </c>
       <c r="E256" s="2" t="s">
         <v>11</v>
@@ -33081,10 +33067,10 @@
         <v>12</v>
       </c>
       <c r="G256" s="3" t="s">
-        <v>735</v>
+        <v>725</v>
       </c>
       <c r="H256" s="4" t="s">
-        <v>736</v>
+        <v>726</v>
       </c>
     </row>
     <row r="257" spans="1:8" ht="28.8">
@@ -33092,13 +33078,13 @@
         <v>8</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>737</v>
+        <v>727</v>
       </c>
       <c r="C257" s="2">
         <v>0</v>
       </c>
       <c r="D257" s="2" t="s">
-        <v>738</v>
+        <v>728</v>
       </c>
       <c r="E257" s="2" t="s">
         <v>11</v>
@@ -33107,10 +33093,10 @@
         <v>12</v>
       </c>
       <c r="G257" s="3" t="s">
-        <v>739</v>
+        <v>729</v>
       </c>
       <c r="H257" s="3" t="s">
-        <v>740</v>
+        <v>730</v>
       </c>
     </row>
     <row r="258" spans="1:8" ht="43.2">
@@ -33118,13 +33104,13 @@
         <v>8</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>737</v>
+        <v>727</v>
       </c>
       <c r="C258" s="2">
         <v>1</v>
       </c>
       <c r="D258" s="2" t="s">
-        <v>741</v>
+        <v>731</v>
       </c>
       <c r="E258" s="2" t="s">
         <v>11</v>
@@ -33133,10 +33119,10 @@
         <v>12</v>
       </c>
       <c r="G258" s="3" t="s">
-        <v>742</v>
+        <v>732</v>
       </c>
       <c r="H258" s="3" t="s">
-        <v>743</v>
+        <v>733</v>
       </c>
     </row>
     <row r="259" spans="1:8" ht="100.8">
@@ -33144,13 +33130,13 @@
         <v>8</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>737</v>
+        <v>727</v>
       </c>
       <c r="C259" s="2">
         <v>2</v>
       </c>
       <c r="D259" s="2" t="s">
-        <v>744</v>
+        <v>734</v>
       </c>
       <c r="E259" s="2" t="s">
         <v>11</v>
@@ -33159,10 +33145,10 @@
         <v>12</v>
       </c>
       <c r="G259" s="3" t="s">
-        <v>745</v>
+        <v>735</v>
       </c>
       <c r="H259" s="3" t="s">
-        <v>746</v>
+        <v>736</v>
       </c>
     </row>
     <row r="260" spans="1:8" ht="43.2">
@@ -33170,13 +33156,13 @@
         <v>8</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>737</v>
+        <v>727</v>
       </c>
       <c r="C260" s="2">
         <v>3</v>
       </c>
       <c r="D260" s="2" t="s">
-        <v>747</v>
+        <v>737</v>
       </c>
       <c r="E260" s="2" t="s">
         <v>11</v>
@@ -33185,10 +33171,10 @@
         <v>12</v>
       </c>
       <c r="G260" s="3" t="s">
-        <v>748</v>
+        <v>738</v>
       </c>
       <c r="H260" s="3" t="s">
-        <v>749</v>
+        <v>739</v>
       </c>
     </row>
     <row r="261" spans="1:8">
@@ -33196,13 +33182,13 @@
         <v>8</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>750</v>
+        <v>740</v>
       </c>
       <c r="C261" s="2">
         <v>0</v>
       </c>
       <c r="D261" s="2" t="s">
-        <v>751</v>
+        <v>741</v>
       </c>
       <c r="E261" s="2" t="s">
         <v>11</v>
@@ -33211,10 +33197,10 @@
         <v>12</v>
       </c>
       <c r="G261" s="3" t="s">
-        <v>752</v>
+        <v>742</v>
       </c>
       <c r="H261" s="4" t="s">
-        <v>753</v>
+        <v>743</v>
       </c>
     </row>
     <row r="262" spans="1:8">
@@ -33222,13 +33208,13 @@
         <v>8</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>754</v>
+        <v>744</v>
       </c>
       <c r="C262" s="2">
         <v>0</v>
       </c>
       <c r="D262" s="2" t="s">
-        <v>755</v>
+        <v>745</v>
       </c>
       <c r="E262" s="2" t="s">
         <v>11</v>
@@ -33237,10 +33223,10 @@
         <v>12</v>
       </c>
       <c r="G262" s="3" t="s">
-        <v>756</v>
+        <v>746</v>
       </c>
       <c r="H262" s="4" t="s">
-        <v>757</v>
+        <v>747</v>
       </c>
     </row>
     <row r="263" spans="1:8">
@@ -33248,13 +33234,13 @@
         <v>8</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>758</v>
+        <v>748</v>
       </c>
       <c r="C263" s="2">
         <v>0</v>
       </c>
       <c r="D263" s="2" t="s">
-        <v>759</v>
+        <v>749</v>
       </c>
       <c r="E263" s="2" t="s">
         <v>11</v>
@@ -33263,10 +33249,10 @@
         <v>12</v>
       </c>
       <c r="G263" s="3" t="s">
-        <v>760</v>
+        <v>750</v>
       </c>
       <c r="H263" s="4" t="s">
-        <v>761</v>
+        <v>751</v>
       </c>
     </row>
     <row r="264" spans="1:8">
@@ -33274,13 +33260,13 @@
         <v>8</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>758</v>
+        <v>748</v>
       </c>
       <c r="C264" s="2">
         <v>1</v>
       </c>
       <c r="D264" s="2" t="s">
-        <v>762</v>
+        <v>752</v>
       </c>
       <c r="E264" s="2" t="s">
         <v>11</v>
@@ -33289,10 +33275,10 @@
         <v>12</v>
       </c>
       <c r="G264" s="3" t="s">
-        <v>763</v>
+        <v>753</v>
       </c>
       <c r="H264" s="4" t="s">
-        <v>764</v>
+        <v>754</v>
       </c>
     </row>
     <row r="265" spans="1:8" ht="28.8">
@@ -33300,13 +33286,13 @@
         <v>8</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>765</v>
+        <v>755</v>
       </c>
       <c r="C265" s="2">
         <v>0</v>
       </c>
       <c r="D265" s="2" t="s">
-        <v>766</v>
+        <v>756</v>
       </c>
       <c r="E265" s="2" t="s">
         <v>11</v>
@@ -33315,10 +33301,10 @@
         <v>12</v>
       </c>
       <c r="G265" s="3" t="s">
-        <v>767</v>
+        <v>757</v>
       </c>
       <c r="H265" s="4" t="s">
-        <v>768</v>
+        <v>758</v>
       </c>
     </row>
   </sheetData>
